--- a/data/TIT.MI.xlsx
+++ b/data/TIT.MI.xlsx
@@ -62886,6 +62886,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>4634320</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>7.68300008773804</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>7.59299993515015</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>7.63000011444092</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>7.59299993515015</v>
+      </c>
+      <c r="G2719" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TIT.MI.xlsx
+++ b/data/TIT.MI.xlsx
@@ -62909,6 +62909,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>6159205</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>7.64499998092651</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>7.49399995803833</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>7.53999996185303</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>7.60300016403198</v>
+      </c>
+      <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TIT.MI.xlsx
+++ b/data/TIT.MI.xlsx
@@ -62932,6 +62932,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>7918716</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>7.6710000038147</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>7.60300016403198</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>7.65000009536743</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>7.64699983596802</v>
+      </c>
+      <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TIT.MI.xlsx
+++ b/data/TIT.MI.xlsx
@@ -62955,6 +62955,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>16223379</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>7.87799978256226</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>7.65000009536743</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>7.65000009536743</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>7.875</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TIT.MI.xlsx
+++ b/data/TIT.MI.xlsx
@@ -62796,22 +62796,22 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
-        <v>16290143</v>
+        <v>14073482</v>
       </c>
       <c r="C2715" t="n">
-        <v>7.76800012588501</v>
+        <v>7.75</v>
       </c>
       <c r="D2715" t="n">
-        <v>7.60799980163574</v>
+        <v>7.35799980163574</v>
       </c>
       <c r="E2715" t="n">
-        <v>7.61999988555908</v>
+        <v>7.69000005722046</v>
       </c>
       <c r="F2715" t="n">
-        <v>7.69000005722046</v>
+        <v>7.47399997711182</v>
       </c>
       <c r="G2715" t="s">
         <v>7</v>
@@ -62819,22 +62819,22 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>9373341</v>
+        <v>16290143</v>
       </c>
       <c r="C2716" t="n">
-        <v>7.68900012969971</v>
+        <v>7.76800012588501</v>
       </c>
       <c r="D2716" t="n">
-        <v>7.51399993896484</v>
+        <v>7.60799980163574</v>
       </c>
       <c r="E2716" t="n">
-        <v>7.64499998092651</v>
+        <v>7.61999988555908</v>
       </c>
       <c r="F2716" t="n">
-        <v>7.52299976348877</v>
+        <v>7.69000005722046</v>
       </c>
       <c r="G2716" t="s">
         <v>7</v>
@@ -62842,22 +62842,22 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
-        <v>13617438</v>
+        <v>9373341</v>
       </c>
       <c r="C2717" t="n">
+        <v>7.68900012969971</v>
+      </c>
+      <c r="D2717" t="n">
+        <v>7.51399993896484</v>
+      </c>
+      <c r="E2717" t="n">
+        <v>7.64499998092651</v>
+      </c>
+      <c r="F2717" t="n">
         <v>7.52299976348877</v>
-      </c>
-      <c r="D2717" t="n">
-        <v>7.44299983978271</v>
-      </c>
-      <c r="E2717" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="F2717" t="n">
-        <v>7.47900009155273</v>
       </c>
       <c r="G2717" t="s">
         <v>7</v>
@@ -62865,22 +62865,22 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>11571220</v>
+        <v>13617438</v>
       </c>
       <c r="C2718" t="n">
-        <v>7.61700010299683</v>
+        <v>7.52299976348877</v>
       </c>
       <c r="D2718" t="n">
-        <v>7.48000001907349</v>
+        <v>7.44299983978271</v>
       </c>
       <c r="E2718" t="n">
-        <v>7.49100017547607</v>
+        <v>7.5</v>
       </c>
       <c r="F2718" t="n">
-        <v>7.61499977111816</v>
+        <v>7.47900009155273</v>
       </c>
       <c r="G2718" t="s">
         <v>7</v>
@@ -62888,22 +62888,22 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>4634320</v>
+        <v>11571220</v>
       </c>
       <c r="C2719" t="n">
-        <v>7.68300008773804</v>
+        <v>7.61700010299683</v>
       </c>
       <c r="D2719" t="n">
-        <v>7.59299993515015</v>
+        <v>7.48000001907349</v>
       </c>
       <c r="E2719" t="n">
-        <v>7.63000011444092</v>
+        <v>7.49100017547607</v>
       </c>
       <c r="F2719" t="n">
-        <v>7.59299993515015</v>
+        <v>7.61499977111816</v>
       </c>
       <c r="G2719" t="s">
         <v>7</v>
@@ -62911,22 +62911,22 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>6159205</v>
+        <v>4634320</v>
       </c>
       <c r="C2720" t="n">
-        <v>7.64499998092651</v>
+        <v>7.68300008773804</v>
       </c>
       <c r="D2720" t="n">
-        <v>7.49399995803833</v>
+        <v>7.59299993515015</v>
       </c>
       <c r="E2720" t="n">
-        <v>7.53999996185303</v>
+        <v>7.63000011444092</v>
       </c>
       <c r="F2720" t="n">
-        <v>7.60300016403198</v>
+        <v>7.59299993515015</v>
       </c>
       <c r="G2720" t="s">
         <v>7</v>
@@ -62934,22 +62934,22 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>7918716</v>
+        <v>6159205</v>
       </c>
       <c r="C2721" t="n">
-        <v>7.6710000038147</v>
+        <v>7.64499998092651</v>
       </c>
       <c r="D2721" t="n">
+        <v>7.49399995803833</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>7.53999996185303</v>
+      </c>
+      <c r="F2721" t="n">
         <v>7.60300016403198</v>
-      </c>
-      <c r="E2721" t="n">
-        <v>7.65000009536743</v>
-      </c>
-      <c r="F2721" t="n">
-        <v>7.64699983596802</v>
       </c>
       <c r="G2721" t="s">
         <v>7</v>
@@ -62957,24 +62957,47 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>16223379</v>
+        <v>7918716</v>
       </c>
       <c r="C2722" t="n">
-        <v>7.87799978256226</v>
+        <v>7.6710000038147</v>
       </c>
       <c r="D2722" t="n">
-        <v>7.65000009536743</v>
+        <v>7.60300016403198</v>
       </c>
       <c r="E2722" t="n">
         <v>7.65000009536743</v>
       </c>
       <c r="F2722" t="n">
-        <v>7.875</v>
+        <v>7.64699983596802</v>
       </c>
       <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>85281833</v>
+      </c>
+      <c r="C2723" t="n">
+        <v>7.8899998664856</v>
+      </c>
+      <c r="D2723" t="n">
+        <v>7.74499988555908</v>
+      </c>
+      <c r="E2723" t="n">
+        <v>7.81899976730347</v>
+      </c>
+      <c r="F2723" t="n">
+        <v>7.74499988555908</v>
+      </c>
+      <c r="G2723" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/TIT.MI.xlsx
+++ b/data/TIT.MI.xlsx
@@ -733,7 +733,7 @@
         <v>9.76500034332275</v>
       </c>
       <c r="G14" t="n">
-        <v>9.29015159606934</v>
+        <v>9.29015254974365</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>9.77000045776367</v>
       </c>
       <c r="G20" t="n">
-        <v>9.29490852355957</v>
+        <v>9.29490947723389</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G27" t="n">
-        <v>7.99152803421021</v>
+        <v>7.99152851104736</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G28" t="n">
-        <v>8.27694034576416</v>
+        <v>8.27693939208984</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>8.25500011444092</v>
       </c>
       <c r="G30" t="n">
-        <v>7.85357904434204</v>
+        <v>7.8535795211792</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G31" t="n">
-        <v>8.17228889465332</v>
+        <v>8.17228984832764</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>8.76500034332275</v>
       </c>
       <c r="G32" t="n">
-        <v>8.33877944946289</v>
+        <v>8.33878040313721</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G33" t="n">
-        <v>7.80125379562378</v>
+        <v>7.80125331878662</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>8.98999977111816</v>
       </c>
       <c r="G42" t="n">
-        <v>8.55283832550049</v>
+        <v>8.55283737182617</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G44" t="n">
-        <v>8.98095512390137</v>
+        <v>8.98095607757568</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G46" t="n">
-        <v>9.70399856567383</v>
+        <v>9.70399951934814</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>9.82499980926514</v>
       </c>
       <c r="G47" t="n">
-        <v>9.34723472595215</v>
+        <v>9.34723377227783</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G49" t="n">
-        <v>9.64691734313965</v>
+        <v>9.64691638946533</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G51" t="n">
-        <v>9.91330051422119</v>
+        <v>9.91330146789551</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G52" t="n">
-        <v>9.81816387176514</v>
+        <v>9.81816291809082</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>10.3299999237061</v>
       </c>
       <c r="G54" t="n">
-        <v>9.82767772674561</v>
+        <v>9.82767677307129</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>10.4099998474121</v>
       </c>
       <c r="G57" t="n">
-        <v>9.90378665924072</v>
+        <v>9.90378761291504</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G64" t="n">
-        <v>8.70505809783936</v>
+        <v>8.70505714416504</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>8.58500003814697</v>
       </c>
       <c r="G66" t="n">
-        <v>8.16753196716309</v>
+        <v>8.1675329208374</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G67" t="n">
-        <v>8.18180370330811</v>
+        <v>8.18180274963379</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G68" t="n">
-        <v>7.95347309112549</v>
+        <v>7.95347356796265</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>8.98999977111816</v>
       </c>
       <c r="G70" t="n">
-        <v>8.55283832550049</v>
+        <v>8.55283737182617</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>8.65499973297119</v>
       </c>
       <c r="G81" t="n">
-        <v>8.23412799835205</v>
+        <v>8.23412895202637</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G83" t="n">
-        <v>8.25791358947754</v>
+        <v>8.25791263580322</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>8.46500015258789</v>
       </c>
       <c r="G85" t="n">
-        <v>8.05336856842041</v>
+        <v>8.05336761474609</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>8.36499977111816</v>
       </c>
       <c r="G86" t="n">
-        <v>7.95823001861572</v>
+        <v>7.95823049545288</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G87" t="n">
-        <v>8.04861164093018</v>
+        <v>8.04861068725586</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G92" t="n">
-        <v>8.05812549591064</v>
+        <v>8.05812454223633</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>8.48999977111816</v>
       </c>
       <c r="G96" t="n">
-        <v>8.07715225219727</v>
+        <v>8.07715129852295</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>8.30500030517578</v>
       </c>
       <c r="G98" t="n">
-        <v>7.90114879608154</v>
+        <v>7.90114784240723</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G99" t="n">
-        <v>7.87736368179321</v>
+        <v>7.87736320495605</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G102" t="n">
-        <v>7.91541862487793</v>
+        <v>7.91541814804077</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G104" t="n">
-        <v>8.27694034576416</v>
+        <v>8.27693939208984</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G114" t="n">
-        <v>7.82028150558472</v>
+        <v>7.82028198242188</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>7.91499996185303</v>
       </c>
       <c r="G115" t="n">
-        <v>7.53011274337769</v>
+        <v>7.53011322021484</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>7.59499979019165</v>
       </c>
       <c r="G117" t="n">
-        <v>7.22567319869995</v>
+        <v>7.22567367553711</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G118" t="n">
-        <v>7.04015636444092</v>
+        <v>7.04015588760376</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>8.27499961853027</v>
       </c>
       <c r="G123" t="n">
-        <v>7.87260675430298</v>
+        <v>7.87260627746582</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>6.67500019073486</v>
       </c>
       <c r="G125" t="n">
-        <v>6.35041093826294</v>
+        <v>6.3504114151001</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>7.44500017166138</v>
       </c>
       <c r="G127" t="n">
-        <v>7.08296775817871</v>
+        <v>7.08296823501587</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G129" t="n">
-        <v>7.04015636444092</v>
+        <v>7.04015588760376</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>6.33500003814697</v>
       </c>
       <c r="G133" t="n">
-        <v>6.02694416046143</v>
+        <v>6.02694463729858</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G135" t="n">
-        <v>6.30759954452515</v>
+        <v>6.30759906768799</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>6.92500019073486</v>
       </c>
       <c r="G136" t="n">
-        <v>6.58825397491455</v>
+        <v>6.58825445175171</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G140" t="n">
-        <v>6.60252523422241</v>
+        <v>6.60252475738525</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>6.86499977111816</v>
       </c>
       <c r="G142" t="n">
-        <v>6.53117179870605</v>
+        <v>6.5311713218689</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>7</v>
       </c>
       <c r="G145" t="n">
-        <v>6.65960693359375</v>
+        <v>6.65960741043091</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>7.46999979019165</v>
       </c>
       <c r="G147" t="n">
-        <v>7.10675191879272</v>
+        <v>7.10675239562988</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>7.63500022888184</v>
       </c>
       <c r="G149" t="n">
-        <v>7.26372909545898</v>
+        <v>7.26372861862183</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>7.44500017166138</v>
       </c>
       <c r="G151" t="n">
-        <v>7.08296775817871</v>
+        <v>7.08296823501587</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G156" t="n">
-        <v>7.24945831298828</v>
+        <v>7.24945783615112</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>7.92999982833862</v>
       </c>
       <c r="G164" t="n">
-        <v>7.54438304901123</v>
+        <v>7.54438352584839</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>8.0649995803833</v>
       </c>
       <c r="G167" t="n">
-        <v>7.67281866073608</v>
+        <v>7.67281818389893</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>8.24499988555908</v>
       </c>
       <c r="G170" t="n">
-        <v>7.84406518936157</v>
+        <v>7.84406566619873</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>8.13500022888184</v>
       </c>
       <c r="G171" t="n">
-        <v>7.73941516876221</v>
+        <v>7.73941469192505</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>8.16499996185303</v>
       </c>
       <c r="G172" t="n">
-        <v>7.7679557800293</v>
+        <v>7.76795625686646</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G173" t="n">
-        <v>7.80125379562378</v>
+        <v>7.80125331878662</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>8.04500007629395</v>
       </c>
       <c r="G176" t="n">
-        <v>7.6537914276123</v>
+        <v>7.65379095077515</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>8.16499996185303</v>
       </c>
       <c r="G177" t="n">
-        <v>7.7679557800293</v>
+        <v>7.76795625686646</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G178" t="n">
-        <v>7.64903402328491</v>
+        <v>7.64903450012207</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>7.88500022888184</v>
       </c>
       <c r="G179" t="n">
-        <v>7.5015721321106</v>
+        <v>7.50157165527344</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>7.53499984741211</v>
       </c>
       <c r="G182" t="n">
-        <v>7.16859149932861</v>
+        <v>7.16859102249146</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>7.28499984741211</v>
       </c>
       <c r="G185" t="n">
-        <v>6.930748462677</v>
+        <v>6.93074798583984</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>7.63500022888184</v>
       </c>
       <c r="G188" t="n">
-        <v>7.26372909545898</v>
+        <v>7.26372861862183</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>7.34499979019165</v>
       </c>
       <c r="G190" t="n">
-        <v>6.98783016204834</v>
+        <v>6.9878306388855</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>7.49499988555908</v>
       </c>
       <c r="G191" t="n">
-        <v>7.1305365562439</v>
+        <v>7.13053607940674</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G193" t="n">
-        <v>7.03064250946045</v>
+        <v>7.03064203262329</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>7.29500007629395</v>
       </c>
       <c r="G196" t="n">
-        <v>6.94026231765747</v>
+        <v>6.94026184082031</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G199" t="n">
-        <v>7.04015636444092</v>
+        <v>7.04015588760376</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G200" t="n">
-        <v>6.86890888214111</v>
+        <v>6.86890840530396</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>6.94500017166138</v>
       </c>
       <c r="G202" t="n">
-        <v>6.60728216171265</v>
+        <v>6.60728168487549</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>7.57499980926514</v>
       </c>
       <c r="G205" t="n">
-        <v>7.20664596557617</v>
+        <v>7.20664644241333</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>7.59499979019165</v>
       </c>
       <c r="G207" t="n">
-        <v>7.22567319869995</v>
+        <v>7.22567367553711</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G208" t="n">
-        <v>7.35410928726196</v>
+        <v>7.3541088104248</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>7.92999982833862</v>
       </c>
       <c r="G209" t="n">
-        <v>7.54438304901123</v>
+        <v>7.54438352584839</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G216" t="n">
-        <v>7.35410928726196</v>
+        <v>7.3541088104248</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>7.70499992370605</v>
       </c>
       <c r="G217" t="n">
-        <v>7.33032464981079</v>
+        <v>7.33032417297363</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>7.45499992370605</v>
       </c>
       <c r="G221" t="n">
-        <v>7.09248161315918</v>
+        <v>7.09248113632202</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G227" t="n">
-        <v>6.67863416671753</v>
+        <v>6.67863464355469</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>6.86499977111816</v>
       </c>
       <c r="G228" t="n">
-        <v>6.53117179870605</v>
+        <v>6.5311713218689</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G232" t="n">
-        <v>6.70717620849609</v>
+        <v>6.70717573165894</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>7.14499998092651</v>
       </c>
       <c r="G233" t="n">
-        <v>6.79755592346191</v>
+        <v>6.79755640029907</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>7</v>
       </c>
       <c r="G239" t="n">
-        <v>6.65960693359375</v>
+        <v>6.65960741043091</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>7.54500007629395</v>
       </c>
       <c r="G241" t="n">
-        <v>7.17810535430908</v>
+        <v>7.17810487747192</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>7.625</v>
       </c>
       <c r="G243" t="n">
-        <v>7.25421524047852</v>
+        <v>7.25421476364136</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>8.06999969482422</v>
       </c>
       <c r="G248" t="n">
-        <v>7.67757558822632</v>
+        <v>7.67757511138916</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G251" t="n">
-        <v>7.99152803421021</v>
+        <v>7.99152851104736</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G254" t="n">
-        <v>8.27694034576416</v>
+        <v>8.27693939208984</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>8.42500019073486</v>
       </c>
       <c r="G255" t="n">
-        <v>8.01531219482422</v>
+        <v>8.01531314849854</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G257" t="n">
-        <v>7.96298694610596</v>
+        <v>7.96298742294312</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G258" t="n">
-        <v>8.16277503967285</v>
+        <v>8.16277599334717</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>8.42500019073486</v>
       </c>
       <c r="G261" t="n">
-        <v>8.01531219482422</v>
+        <v>8.01531314849854</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G263" t="n">
-        <v>7.82028150558472</v>
+        <v>7.82028198242188</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G264" t="n">
-        <v>7.87736368179321</v>
+        <v>7.87736320495605</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G265" t="n">
-        <v>8.04861164093018</v>
+        <v>8.04861068725586</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G266" t="n">
-        <v>7.93444633483887</v>
+        <v>7.93444681167603</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G268" t="n">
-        <v>8.10569381713867</v>
+        <v>8.10569286346436</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>8.375</v>
       </c>
       <c r="G269" t="n">
-        <v>7.96774387359619</v>
+        <v>7.96774482727051</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>8.3100004196167</v>
       </c>
       <c r="G270" t="n">
-        <v>7.90590572357178</v>
+        <v>7.90590524673462</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G271" t="n">
-        <v>7.99152803421021</v>
+        <v>7.99152851104736</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G272" t="n">
-        <v>8.04861164093018</v>
+        <v>8.04861068725586</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G273" t="n">
-        <v>7.99152803421021</v>
+        <v>7.99152851104736</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>8.3100004196167</v>
       </c>
       <c r="G274" t="n">
-        <v>7.90590572357178</v>
+        <v>7.90590524673462</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G275" t="n">
-        <v>7.82979440689087</v>
+        <v>7.82979536056519</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G281" t="n">
-        <v>7.59195232391357</v>
+        <v>7.59195184707642</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G285" t="n">
-        <v>7.79173994064331</v>
+        <v>7.79174041748047</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>8.25</v>
       </c>
       <c r="G286" t="n">
-        <v>7.84882211685181</v>
+        <v>7.84882259368896</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G287" t="n">
-        <v>7.64903402328491</v>
+        <v>7.64903450012207</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>7.97499990463257</v>
       </c>
       <c r="G289" t="n">
-        <v>7.58719539642334</v>
+        <v>7.58719491958618</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>7.91499996185303</v>
       </c>
       <c r="G291" t="n">
-        <v>7.53011274337769</v>
+        <v>7.53011322021484</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G294" t="n">
-        <v>7.3255672454834</v>
+        <v>7.32556772232056</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>7.59499979019165</v>
       </c>
       <c r="G295" t="n">
-        <v>7.22567319869995</v>
+        <v>7.22567367553711</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>7.79500007629395</v>
       </c>
       <c r="G304" t="n">
-        <v>7.41594839096069</v>
+        <v>7.41594791412354</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G305" t="n">
-        <v>7.35410928726196</v>
+        <v>7.3541088104248</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>7.83500003814697</v>
       </c>
       <c r="G306" t="n">
-        <v>7.45400333404541</v>
+        <v>7.45400285720825</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>7.88500022888184</v>
       </c>
       <c r="G310" t="n">
-        <v>7.5015721321106</v>
+        <v>7.50157165527344</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>8.125</v>
       </c>
       <c r="G314" t="n">
-        <v>7.72990083694458</v>
+        <v>7.72990131378174</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G317" t="n">
-        <v>7.93444633483887</v>
+        <v>7.93444681167603</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G319" t="n">
-        <v>8.10569381713867</v>
+        <v>8.10569286346436</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G320" t="n">
-        <v>8.01055526733398</v>
+        <v>8.0105562210083</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>8.45499992370605</v>
       </c>
       <c r="G321" t="n">
-        <v>8.04385471343994</v>
+        <v>8.04385375976562</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>8.13500022888184</v>
       </c>
       <c r="G325" t="n">
-        <v>7.73941516876221</v>
+        <v>7.73941469192505</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G329" t="n">
-        <v>7.64903402328491</v>
+        <v>7.64903450012207</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>8.04500007629395</v>
       </c>
       <c r="G330" t="n">
-        <v>7.6537914276123</v>
+        <v>7.65379095077515</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>7.875</v>
       </c>
       <c r="G335" t="n">
-        <v>7.49205827713013</v>
+        <v>7.49205780029297</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G337" t="n">
-        <v>7.87736368179321</v>
+        <v>7.87736320495605</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G346" t="n">
-        <v>8.50527000427246</v>
+        <v>8.50526905059814</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>9.14500045776367</v>
       </c>
       <c r="G351" t="n">
-        <v>8.70030212402344</v>
+        <v>8.70030117034912</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G358" t="n">
-        <v>8.23888492584229</v>
+        <v>8.2388858795166</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G360" t="n">
-        <v>8.05812549591064</v>
+        <v>8.05812454223633</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>8.3100004196167</v>
       </c>
       <c r="G361" t="n">
-        <v>7.90590572357178</v>
+        <v>7.90590524673462</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G363" t="n">
-        <v>7.93444633483887</v>
+        <v>7.93444681167603</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G367" t="n">
-        <v>7.88687801361084</v>
+        <v>7.88687753677368</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>8.3100004196167</v>
       </c>
       <c r="G368" t="n">
-        <v>7.90590572357178</v>
+        <v>7.90590524673462</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>8.25</v>
       </c>
       <c r="G369" t="n">
-        <v>7.84882211685181</v>
+        <v>7.84882259368896</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>8.27499961853027</v>
       </c>
       <c r="G370" t="n">
-        <v>7.87260675430298</v>
+        <v>7.87260627746582</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G371" t="n">
-        <v>7.91541862487793</v>
+        <v>7.91541814804077</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>8.33500003814697</v>
       </c>
       <c r="G372" t="n">
-        <v>7.92968940734863</v>
+        <v>7.92968988418579</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>8.25</v>
       </c>
       <c r="G373" t="n">
-        <v>7.84882211685181</v>
+        <v>7.84882259368896</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G376" t="n">
-        <v>7.88687801361084</v>
+        <v>7.88687753677368</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G377" t="n">
-        <v>7.91541862487793</v>
+        <v>7.91541814804077</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G378" t="n">
-        <v>7.82979440689087</v>
+        <v>7.82979536056519</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>8.0649995803833</v>
       </c>
       <c r="G381" t="n">
-        <v>7.67281866073608</v>
+        <v>7.67281818389893</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G385" t="n">
-        <v>7.82979440689087</v>
+        <v>7.82979536056519</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G387" t="n">
-        <v>7.63000726699829</v>
+        <v>7.63000774383545</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>8.04500007629395</v>
       </c>
       <c r="G388" t="n">
-        <v>7.6537914276123</v>
+        <v>7.65379095077515</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>7.88500022888184</v>
       </c>
       <c r="G391" t="n">
-        <v>7.5015721321106</v>
+        <v>7.50157165527344</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G393" t="n">
-        <v>7.86785078048706</v>
+        <v>7.8678503036499</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>8.04500007629395</v>
       </c>
       <c r="G394" t="n">
-        <v>7.6537914276123</v>
+        <v>7.65379095077515</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>8.125</v>
       </c>
       <c r="G399" t="n">
-        <v>7.72990083694458</v>
+        <v>7.72990131378174</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G403" t="n">
-        <v>8.23888492584229</v>
+        <v>8.2388858795166</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>8.70499992370605</v>
       </c>
       <c r="G405" t="n">
-        <v>8.28169727325439</v>
+        <v>8.28169631958008</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>8.70499992370605</v>
       </c>
       <c r="G408" t="n">
-        <v>8.28169727325439</v>
+        <v>8.28169631958008</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G415" t="n">
-        <v>8.05812549591064</v>
+        <v>8.05812454223633</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>8.33500003814697</v>
       </c>
       <c r="G418" t="n">
-        <v>7.92968940734863</v>
+        <v>7.92968988418579</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>8.27499961853027</v>
       </c>
       <c r="G419" t="n">
-        <v>7.87260675430298</v>
+        <v>7.87260627746582</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>8.04500007629395</v>
       </c>
       <c r="G427" t="n">
-        <v>7.6537914276123</v>
+        <v>7.65379095077515</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>7.83500003814697</v>
       </c>
       <c r="G429" t="n">
-        <v>7.45400333404541</v>
+        <v>7.45400285720825</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>7.88500022888184</v>
       </c>
       <c r="G435" t="n">
-        <v>7.5015721321106</v>
+        <v>7.50157165527344</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>8.02499961853027</v>
       </c>
       <c r="G440" t="n">
-        <v>7.63476324081421</v>
+        <v>7.63476371765137</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G442" t="n">
-        <v>7.57292509078979</v>
+        <v>7.57292461395264</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>7.93499994277954</v>
       </c>
       <c r="G445" t="n">
-        <v>7.54913997650146</v>
+        <v>7.54914045333862</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G447" t="n">
-        <v>7.59195232391357</v>
+        <v>7.59195184707642</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>7.63500022888184</v>
       </c>
       <c r="G454" t="n">
-        <v>7.26372909545898</v>
+        <v>7.26372861862183</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>7.54500007629395</v>
       </c>
       <c r="G455" t="n">
-        <v>7.17810535430908</v>
+        <v>7.17810487747192</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>7.625</v>
       </c>
       <c r="G459" t="n">
-        <v>7.25421524047852</v>
+        <v>7.25421476364136</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>7.68499994277954</v>
       </c>
       <c r="G463" t="n">
-        <v>7.31129693984985</v>
+        <v>7.31129741668701</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>7.63500022888184</v>
       </c>
       <c r="G472" t="n">
-        <v>7.26372909545898</v>
+        <v>7.26372861862183</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>7.35500001907349</v>
       </c>
       <c r="G476" t="n">
-        <v>6.99734401702881</v>
+        <v>6.99734449386597</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>6.89499998092651</v>
       </c>
       <c r="G479" t="n">
-        <v>6.5597128868103</v>
+        <v>6.55971336364746</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>6.81500005722046</v>
       </c>
       <c r="G481" t="n">
-        <v>6.48360300064087</v>
+        <v>6.48360347747803</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>6.89499998092651</v>
       </c>
       <c r="G482" t="n">
-        <v>6.5597128868103</v>
+        <v>6.55971336364746</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>7.04500007629395</v>
       </c>
       <c r="G490" t="n">
-        <v>6.70241928100586</v>
+        <v>6.7024188041687</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G494" t="n">
-        <v>6.7166895866394</v>
+        <v>6.71668910980225</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>7.46999979019165</v>
       </c>
       <c r="G497" t="n">
-        <v>7.10675191879272</v>
+        <v>7.10675239562988</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>7.54500007629395</v>
       </c>
       <c r="G498" t="n">
-        <v>7.17810535430908</v>
+        <v>7.17810487747192</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>7.2649998664856</v>
       </c>
       <c r="G502" t="n">
-        <v>6.91172027587891</v>
+        <v>6.91172075271606</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>7.34499979019165</v>
       </c>
       <c r="G504" t="n">
-        <v>6.98783016204834</v>
+        <v>6.9878306388855</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G505" t="n">
-        <v>7.04015636444092</v>
+        <v>7.04015588760376</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>7.34499979019165</v>
       </c>
       <c r="G507" t="n">
-        <v>6.98783016204834</v>
+        <v>6.9878306388855</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G508" t="n">
-        <v>7.02112865447998</v>
+        <v>7.02112913131714</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>7.29500007629395</v>
       </c>
       <c r="G510" t="n">
-        <v>6.94026231765747</v>
+        <v>6.94026184082031</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>7.20499992370605</v>
       </c>
       <c r="G511" t="n">
-        <v>6.85463857650757</v>
+        <v>6.85463809967041</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>7.25500011444092</v>
       </c>
       <c r="G512" t="n">
-        <v>6.9022068977356</v>
+        <v>6.90220737457275</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>7.25</v>
       </c>
       <c r="G513" t="n">
-        <v>6.89744997024536</v>
+        <v>6.89745044708252</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G514" t="n">
-        <v>6.98307371139526</v>
+        <v>6.98307418823242</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>7.38500022888184</v>
       </c>
       <c r="G515" t="n">
-        <v>7.02588605880737</v>
+        <v>7.02588558197021</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>7.43499994277954</v>
       </c>
       <c r="G520" t="n">
-        <v>7.07345390319824</v>
+        <v>7.0734543800354</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>7.38500022888184</v>
       </c>
       <c r="G521" t="n">
-        <v>7.02588605880737</v>
+        <v>7.02588558197021</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>7.20499992370605</v>
       </c>
       <c r="G530" t="n">
-        <v>6.85463857650757</v>
+        <v>6.85463809967041</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>7.21199989318848</v>
       </c>
       <c r="G538" t="n">
-        <v>6.86129760742188</v>
+        <v>6.86129808425903</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>6.98799991607666</v>
       </c>
       <c r="G540" t="n">
-        <v>6.64819097518921</v>
+        <v>6.64819049835205</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G543" t="n">
-        <v>6.54544258117676</v>
+        <v>6.5454421043396</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>7.19600009918213</v>
       </c>
       <c r="G548" t="n">
-        <v>6.84607601165771</v>
+        <v>6.84607648849487</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G551" t="n">
-        <v>7.02112865447998</v>
+        <v>7.02112913131714</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G553" t="n">
-        <v>7.04015636444092</v>
+        <v>7.04015588760376</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>7.39799976348877</v>
       </c>
       <c r="G554" t="n">
-        <v>7.03825283050537</v>
+        <v>7.03825330734253</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>7.24599981307983</v>
       </c>
       <c r="G555" t="n">
-        <v>6.8936448097229</v>
+        <v>6.89364433288574</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>7.28800010681152</v>
       </c>
       <c r="G556" t="n">
-        <v>6.93360233306885</v>
+        <v>6.93360280990601</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G559" t="n">
-        <v>7.82979440689087</v>
+        <v>7.82979536056519</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G560" t="n">
-        <v>7.91541862487793</v>
+        <v>7.91541814804077</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>8.20199966430664</v>
       </c>
       <c r="G561" t="n">
-        <v>7.80315637588501</v>
+        <v>7.80315589904785</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>8.00800037384033</v>
       </c>
       <c r="G562" t="n">
-        <v>7.61859083175659</v>
+        <v>7.61859130859375</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>7.83199977874756</v>
       </c>
       <c r="G563" t="n">
-        <v>7.45114898681641</v>
+        <v>7.45114850997925</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>8.08800029754639</v>
       </c>
       <c r="G565" t="n">
-        <v>7.69470024108887</v>
+        <v>7.69470071792603</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>8.11600017547607</v>
       </c>
       <c r="G566" t="n">
-        <v>7.72133874893188</v>
+        <v>7.72133922576904</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>7.72599983215332</v>
       </c>
       <c r="G570" t="n">
-        <v>7.35030364990234</v>
+        <v>7.35030317306519</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>7.61399984359741</v>
       </c>
       <c r="G572" t="n">
-        <v>7.24374961853027</v>
+        <v>7.24375009536743</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>7.58199977874756</v>
       </c>
       <c r="G576" t="n">
-        <v>7.21330595016479</v>
+        <v>7.21330547332764</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>8.61200046539307</v>
       </c>
       <c r="G582" t="n">
-        <v>8.19321918487549</v>
+        <v>8.1932201385498</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>8.38199996948242</v>
       </c>
       <c r="G585" t="n">
-        <v>7.97440385818481</v>
+        <v>7.97440338134766</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>8.76200008392334</v>
       </c>
       <c r="G588" t="n">
-        <v>8.33592510223389</v>
+        <v>8.3359260559082</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G589" t="n">
-        <v>8.27694034576416</v>
+        <v>8.27693939208984</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>8.26200008392334</v>
       </c>
       <c r="G591" t="n">
-        <v>7.86023902893066</v>
+        <v>7.86023950576782</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G596" t="n">
-        <v>7.96298694610596</v>
+        <v>7.96298742294312</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G599" t="n">
-        <v>8.01055526733398</v>
+        <v>8.0105562210083</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G600" t="n">
-        <v>7.88687801361084</v>
+        <v>7.88687753677368</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G605" t="n">
-        <v>7.35410928726196</v>
+        <v>7.3541088104248</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G606" t="n">
-        <v>7.30654001235962</v>
+        <v>7.30654048919678</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G609" t="n">
-        <v>7.02112865447998</v>
+        <v>7.02112913131714</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>7.31199979782104</v>
       </c>
       <c r="G610" t="n">
-        <v>6.95643520355225</v>
+        <v>6.95643472671509</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>7.30999994277954</v>
       </c>
       <c r="G611" t="n">
-        <v>6.95453262329102</v>
+        <v>6.95453214645386</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>7.14400005340576</v>
       </c>
       <c r="G613" t="n">
-        <v>6.7966046333313</v>
+        <v>6.79660511016846</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>7.01599979400635</v>
       </c>
       <c r="G615" t="n">
-        <v>6.67482852935791</v>
+        <v>6.67482900619507</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>6.87200021743774</v>
       </c>
       <c r="G616" t="n">
-        <v>6.53783130645752</v>
+        <v>6.53783178329468</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>6.98600006103516</v>
       </c>
       <c r="G618" t="n">
-        <v>6.64628791809082</v>
+        <v>6.64628839492798</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>6.91599988937378</v>
       </c>
       <c r="G620" t="n">
-        <v>6.57969188690186</v>
+        <v>6.5796914100647</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>6.72200012207031</v>
       </c>
       <c r="G622" t="n">
-        <v>6.39512586593628</v>
+        <v>6.39512538909912</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>6.87200021743774</v>
       </c>
       <c r="G623" t="n">
-        <v>6.53783130645752</v>
+        <v>6.53783178329468</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>6.85799980163574</v>
       </c>
       <c r="G624" t="n">
-        <v>6.52451181411743</v>
+        <v>6.52451229095459</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>6.7519998550415</v>
       </c>
       <c r="G627" t="n">
-        <v>6.42366647720337</v>
+        <v>6.42366695404053</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>6.76599979400635</v>
       </c>
       <c r="G628" t="n">
-        <v>6.4369854927063</v>
+        <v>6.43698596954346</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G631" t="n">
-        <v>6.33614015579224</v>
+        <v>6.33614063262939</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>6.45599985122681</v>
       </c>
       <c r="G635" t="n">
-        <v>6.14206075668335</v>
+        <v>6.14206027984619</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>6.37400007247925</v>
       </c>
       <c r="G637" t="n">
-        <v>6.06404781341553</v>
+        <v>6.06404829025269</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>6.28200006484985</v>
       </c>
       <c r="G638" t="n">
-        <v>5.97652149200439</v>
+        <v>5.97652196884155</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>6.52400016784668</v>
       </c>
       <c r="G640" t="n">
-        <v>6.20675420761108</v>
+        <v>6.20675373077393</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>6.55200004577637</v>
       </c>
       <c r="G642" t="n">
-        <v>6.2333927154541</v>
+        <v>6.23339223861694</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>6.36600017547607</v>
       </c>
       <c r="G644" t="n">
-        <v>6.05643749237061</v>
+        <v>6.05643701553345</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G645" t="n">
-        <v>6.01267385482788</v>
+        <v>6.01267433166504</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>6.14599990844727</v>
       </c>
       <c r="G646" t="n">
-        <v>5.84713506698608</v>
+        <v>5.84713459014893</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>6.07399988174438</v>
       </c>
       <c r="G648" t="n">
-        <v>5.77863645553589</v>
+        <v>5.77863597869873</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G658" t="n">
-        <v>6.2790584564209</v>
+        <v>6.27905797958374</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>6.50400018692017</v>
       </c>
       <c r="G660" t="n">
-        <v>6.1877269744873</v>
+        <v>6.18772649765015</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>6.38199996948242</v>
       </c>
       <c r="G661" t="n">
-        <v>6.07165908813477</v>
+        <v>6.07165861129761</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>6</v>
       </c>
       <c r="G675" t="n">
-        <v>5.70823431015015</v>
+        <v>5.7082347869873</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>5.98799991607666</v>
       </c>
       <c r="G676" t="n">
-        <v>5.69681835174561</v>
+        <v>5.69681787490845</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>6.0019998550415</v>
       </c>
       <c r="G677" t="n">
-        <v>5.71013736724854</v>
+        <v>5.71013689041138</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>5.93800020217896</v>
       </c>
       <c r="G678" t="n">
-        <v>5.64924955368042</v>
+        <v>5.64925003051758</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G681" t="n">
-        <v>5.22303485870361</v>
+        <v>5.22303438186646</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G682" t="n">
-        <v>5.28011703491211</v>
+        <v>5.28011751174927</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>5.25</v>
       </c>
       <c r="G683" t="n">
-        <v>4.99470567703247</v>
+        <v>4.99470520019531</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>5.4060001373291</v>
       </c>
       <c r="G689" t="n">
-        <v>5.14311933517456</v>
+        <v>5.14311981201172</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>5.71400022506714</v>
       </c>
       <c r="G693" t="n">
-        <v>5.4361424446106</v>
+        <v>5.43614196777344</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>5.68599987030029</v>
       </c>
       <c r="G695" t="n">
-        <v>5.40950393676758</v>
+        <v>5.40950345993042</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>5.68599987030029</v>
       </c>
       <c r="G696" t="n">
-        <v>5.40950393676758</v>
+        <v>5.40950345993042</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>5.60599994659424</v>
       </c>
       <c r="G697" t="n">
-        <v>5.33339405059814</v>
+        <v>5.33339357376099</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G698" t="n">
-        <v>5.30865859985352</v>
+        <v>5.30865812301636</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>4.95300006866455</v>
       </c>
       <c r="G702" t="n">
-        <v>4.71214818954468</v>
+        <v>4.71214771270752</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>4.95699977874756</v>
       </c>
       <c r="G705" t="n">
-        <v>4.71595287322998</v>
+        <v>4.71595335006714</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>5.03200006484985</v>
       </c>
       <c r="G709" t="n">
-        <v>4.78730630874634</v>
+        <v>4.78730583190918</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G710" t="n">
-        <v>4.77588987350464</v>
+        <v>4.77588939666748</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>4.98600006103516</v>
       </c>
       <c r="G716" t="n">
-        <v>4.74354267120361</v>
+        <v>4.74354314804077</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>5.19199991226196</v>
       </c>
       <c r="G724" t="n">
-        <v>4.93952560424805</v>
+        <v>4.93952608108521</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>5.35400009155273</v>
       </c>
       <c r="G727" t="n">
-        <v>5.09364795684814</v>
+        <v>5.0936484336853</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G729" t="n">
-        <v>5.08984231948853</v>
+        <v>5.08984279632568</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G731" t="n">
-        <v>4.90908193588257</v>
+        <v>4.90908145904541</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>5.30399990081787</v>
       </c>
       <c r="G732" t="n">
-        <v>5.04607963562012</v>
+        <v>5.04607915878296</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G734" t="n">
-        <v>4.9566502571106</v>
+        <v>4.95665073394775</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>5.16400003433228</v>
       </c>
       <c r="G735" t="n">
-        <v>4.91288757324219</v>
+        <v>4.91288709640503</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>5.26200008392334</v>
       </c>
       <c r="G736" t="n">
-        <v>5.00612163543701</v>
+        <v>5.00612211227417</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>5.74599981307983</v>
       </c>
       <c r="G747" t="n">
-        <v>5.46658563613892</v>
+        <v>5.46658611297607</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>5.69199991226196</v>
       </c>
       <c r="G748" t="n">
-        <v>5.41521167755127</v>
+        <v>5.41521215438843</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G754" t="n">
-        <v>5.42282295227051</v>
+        <v>5.42282247543335</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>5.4520001411438</v>
       </c>
       <c r="G759" t="n">
-        <v>5.18688297271729</v>
+        <v>5.18688249588013</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>5.2020001411438</v>
       </c>
       <c r="G760" t="n">
-        <v>4.94903993606567</v>
+        <v>4.94903945922852</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G762" t="n">
-        <v>4.58561563491821</v>
+        <v>4.58561515808105</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>4.83300018310547</v>
       </c>
       <c r="G763" t="n">
-        <v>4.59798288345337</v>
+        <v>4.59798336029053</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>5.06199979782104</v>
       </c>
       <c r="G768" t="n">
-        <v>4.81584692001343</v>
+        <v>4.81584739685059</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>4.95900011062622</v>
       </c>
       <c r="G769" t="n">
-        <v>4.71785593032837</v>
+        <v>4.71785640716553</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>5.00600004196167</v>
       </c>
       <c r="G771" t="n">
-        <v>4.76257085800171</v>
+        <v>4.76257038116455</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>5.01599979400635</v>
       </c>
       <c r="G772" t="n">
-        <v>4.77208423614502</v>
+        <v>4.77208375930786</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>5.02400016784668</v>
       </c>
       <c r="G773" t="n">
-        <v>4.7796950340271</v>
+        <v>4.77969551086426</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>4.88500022888184</v>
       </c>
       <c r="G776" t="n">
-        <v>4.64745426177979</v>
+        <v>4.64745473861694</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>4.48400020599365</v>
       </c>
       <c r="G779" t="n">
-        <v>4.26595449447632</v>
+        <v>4.26595401763916</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>4.52899980545044</v>
       </c>
       <c r="G780" t="n">
-        <v>4.30876541137695</v>
+        <v>4.30876588821411</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>4.58199977874756</v>
       </c>
       <c r="G783" t="n">
-        <v>4.35918807983398</v>
+        <v>4.35918855667114</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G784" t="n">
-        <v>4.40485429763794</v>
+        <v>4.4048547744751</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>5.02400016784668</v>
       </c>
       <c r="G788" t="n">
-        <v>4.7796950340271</v>
+        <v>4.77969551086426</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G791" t="n">
-        <v>4.49047756195068</v>
+        <v>4.49047803878784</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>4.81599998474121</v>
       </c>
       <c r="G793" t="n">
-        <v>4.58180952072144</v>
+        <v>4.58180999755859</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>4.8270001411438</v>
       </c>
       <c r="G795" t="n">
-        <v>4.59227466583252</v>
+        <v>4.59227514266968</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G797" t="n">
-        <v>5.0422739982605</v>
+        <v>5.04227447509766</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G802" t="n">
-        <v>5.09935665130615</v>
+        <v>5.09935617446899</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>5.32200002670288</v>
       </c>
       <c r="G806" t="n">
-        <v>5.06320428848267</v>
+        <v>5.06320381164551</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>5.5</v>
       </c>
       <c r="G808" t="n">
-        <v>5.23254871368408</v>
+        <v>5.23254823684692</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>5.64799976348877</v>
       </c>
       <c r="G809" t="n">
-        <v>5.37335157394409</v>
+        <v>5.37335109710693</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G810" t="n">
-        <v>5.33719968795776</v>
+        <v>5.33719921112061</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>5.35599994659424</v>
       </c>
       <c r="G818" t="n">
-        <v>5.09555101394653</v>
+        <v>5.09555053710938</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G820" t="n">
-        <v>5.0422739982605</v>
+        <v>5.04227447509766</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>5.25799989700317</v>
       </c>
       <c r="G821" t="n">
-        <v>5.00231599807739</v>
+        <v>5.00231647491455</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>5.31599998474121</v>
       </c>
       <c r="G823" t="n">
-        <v>5.05749559402466</v>
+        <v>5.05749607086182</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>5.35599994659424</v>
       </c>
       <c r="G824" t="n">
-        <v>5.09555101394653</v>
+        <v>5.09555053710938</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G825" t="n">
-        <v>5.14692497253418</v>
+        <v>5.14692449569702</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G828" t="n">
-        <v>5.08984231948853</v>
+        <v>5.08984279632568</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>5.40199995040894</v>
       </c>
       <c r="G829" t="n">
-        <v>5.13931369781494</v>
+        <v>5.1393141746521</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>5.36800003051758</v>
       </c>
       <c r="G831" t="n">
-        <v>5.10696697235107</v>
+        <v>5.10696744918823</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>5.33599996566772</v>
       </c>
       <c r="G832" t="n">
-        <v>5.0765233039856</v>
+        <v>5.07652378082275</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>5.34899997711182</v>
       </c>
       <c r="G833" t="n">
-        <v>5.08889102935791</v>
+        <v>5.08889150619507</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>5.25500011444092</v>
       </c>
       <c r="G838" t="n">
-        <v>4.99946260452271</v>
+        <v>4.99946212768555</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>4.98600006103516</v>
       </c>
       <c r="G846" t="n">
-        <v>4.74354267120361</v>
+        <v>4.74354314804077</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>4.95900011062622</v>
       </c>
       <c r="G847" t="n">
-        <v>4.71785593032837</v>
+        <v>4.71785640716553</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>4.67199993133545</v>
       </c>
       <c r="G853" t="n">
-        <v>4.44481182098389</v>
+        <v>4.44481229782104</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>4.45800018310547</v>
       </c>
       <c r="G856" t="n">
-        <v>4.24121856689453</v>
+        <v>4.24121809005737</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>4.57800006866455</v>
       </c>
       <c r="G859" t="n">
-        <v>4.35538291931152</v>
+        <v>4.35538339614868</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>4.38100004196167</v>
       </c>
       <c r="G863" t="n">
-        <v>4.16796255111694</v>
+        <v>4.1679630279541</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G870" t="n">
-        <v>4.32398748397827</v>
+        <v>4.32398796081543</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>4.63100004196167</v>
       </c>
       <c r="G877" t="n">
-        <v>4.40580558776855</v>
+        <v>4.40580606460571</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>4.84200000762939</v>
       </c>
       <c r="G882" t="n">
-        <v>4.60654497146606</v>
+        <v>4.60654544830322</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>5.00899982452393</v>
       </c>
       <c r="G883" t="n">
-        <v>4.7654242515564</v>
+        <v>4.76542472839355</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>4.82800006866455</v>
       </c>
       <c r="G889" t="n">
-        <v>4.59322595596313</v>
+        <v>4.59322643280029</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>4.78299999237061</v>
       </c>
       <c r="G890" t="n">
-        <v>4.55041456222534</v>
+        <v>4.55041408538818</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>4.92199993133545</v>
       </c>
       <c r="G891" t="n">
-        <v>4.6826548576355</v>
+        <v>4.68265533447266</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>4.96299982070923</v>
       </c>
       <c r="G893" t="n">
-        <v>4.72166156768799</v>
+        <v>4.72166109085083</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>5.01300001144409</v>
       </c>
       <c r="G898" t="n">
-        <v>4.76922988891602</v>
+        <v>4.76923036575317</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>5.06099987030029</v>
       </c>
       <c r="G902" t="n">
-        <v>4.81489562988281</v>
+        <v>4.81489610671997</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>4.91099977493286</v>
       </c>
       <c r="G903" t="n">
-        <v>4.67219018936157</v>
+        <v>4.67218971252441</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>4.95699977874756</v>
       </c>
       <c r="G905" t="n">
-        <v>4.71595287322998</v>
+        <v>4.71595335006714</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G909" t="n">
-        <v>4.985191822052</v>
+        <v>4.98519134521484</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>5.10599994659424</v>
       </c>
       <c r="G911" t="n">
-        <v>4.85770797729492</v>
+        <v>4.85770750045776</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>4.99599981307983</v>
       </c>
       <c r="G913" t="n">
-        <v>4.75305700302124</v>
+        <v>4.75305652618408</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>4.83400011062622</v>
       </c>
       <c r="G915" t="n">
-        <v>4.59893465042114</v>
+        <v>4.59893417358398</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>4.81599998474121</v>
       </c>
       <c r="G916" t="n">
-        <v>4.58180952072144</v>
+        <v>4.58180999755859</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>4.88800001144409</v>
       </c>
       <c r="G917" t="n">
-        <v>4.65030860900879</v>
+        <v>4.65030813217163</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>4.60200023651123</v>
       </c>
       <c r="G918" t="n">
-        <v>4.37821626663208</v>
+        <v>4.37821578979492</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>4.56500005722046</v>
       </c>
       <c r="G923" t="n">
-        <v>4.34301567077637</v>
+        <v>4.34301519393921</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>4.47200012207031</v>
       </c>
       <c r="G924" t="n">
-        <v>4.25453758239746</v>
+        <v>4.25453805923462</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>4.59800004959106</v>
       </c>
       <c r="G926" t="n">
-        <v>4.3744101524353</v>
+        <v>4.37441062927246</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>4.52600002288818</v>
       </c>
       <c r="G927" t="n">
-        <v>4.30591154098511</v>
+        <v>4.30591201782227</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>4.92600011825562</v>
       </c>
       <c r="G935" t="n">
-        <v>4.68646097183228</v>
+        <v>4.68646049499512</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>4.91800022125244</v>
       </c>
       <c r="G936" t="n">
-        <v>4.67884969711304</v>
+        <v>4.6788501739502</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G942" t="n">
-        <v>4.9566502571106</v>
+        <v>4.95665073394775</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>5.16699981689453</v>
       </c>
       <c r="G943" t="n">
-        <v>4.91574096679688</v>
+        <v>4.91574144363403</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G946" t="n">
-        <v>4.985191822052</v>
+        <v>4.98519134521484</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>5.19700002670288</v>
       </c>
       <c r="G952" t="n">
-        <v>4.94428300857544</v>
+        <v>4.94428253173828</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>4.94199991226196</v>
       </c>
       <c r="G955" t="n">
-        <v>4.70168256759644</v>
+        <v>4.70168209075928</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>4.96799993515015</v>
       </c>
       <c r="G956" t="n">
-        <v>4.72641849517822</v>
+        <v>4.72641801834106</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>4.97599983215332</v>
       </c>
       <c r="G957" t="n">
-        <v>4.73402881622314</v>
+        <v>4.7340292930603</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>5.06599998474121</v>
       </c>
       <c r="G959" t="n">
-        <v>4.81965255737305</v>
+        <v>4.81965303421021</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G962" t="n">
-        <v>5.09935665130615</v>
+        <v>5.09935617446899</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>5.39400005340576</v>
       </c>
       <c r="G965" t="n">
-        <v>5.13170337677002</v>
+        <v>5.13170289993286</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>5.35400009155273</v>
       </c>
       <c r="G967" t="n">
-        <v>5.09364795684814</v>
+        <v>5.0936484336853</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G971" t="n">
-        <v>5.06130170822144</v>
+        <v>5.06130123138428</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G974" t="n">
-        <v>5.05178737640381</v>
+        <v>5.05178785324097</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>5.36299991607666</v>
       </c>
       <c r="G984" t="n">
-        <v>5.10221004486084</v>
+        <v>5.102210521698</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G985" t="n">
-        <v>5.09935665130615</v>
+        <v>5.09935617446899</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>5.41300010681152</v>
       </c>
       <c r="G986" t="n">
-        <v>5.14977931976318</v>
+        <v>5.14977884292603</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>5.44099998474121</v>
       </c>
       <c r="G987" t="n">
-        <v>5.17641735076904</v>
+        <v>5.1764178276062</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>5.51800012588501</v>
       </c>
       <c r="G989" t="n">
-        <v>5.24967336654663</v>
+        <v>5.24967288970947</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>5.65100002288818</v>
       </c>
       <c r="G990" t="n">
-        <v>5.37620544433594</v>
+        <v>5.3762059211731</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>5.83900022506714</v>
       </c>
       <c r="G993" t="n">
-        <v>5.55506420135498</v>
+        <v>5.55506372451782</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>5.73899984359741</v>
       </c>
       <c r="G995" t="n">
-        <v>5.45992660522461</v>
+        <v>5.45992612838745</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>5.68599987030029</v>
       </c>
       <c r="G996" t="n">
-        <v>5.40950393676758</v>
+        <v>5.40950345993042</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>5.51200008392334</v>
       </c>
       <c r="G999" t="n">
-        <v>5.24396467208862</v>
+        <v>5.24396514892578</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>5.54199981689453</v>
       </c>
       <c r="G1008" t="n">
-        <v>5.27250623703003</v>
+        <v>5.27250576019287</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1009" t="n">
-        <v>5.28963041305542</v>
+        <v>5.28963088989258</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>5.59499979019165</v>
       </c>
       <c r="G1010" t="n">
-        <v>5.32292890548706</v>
+        <v>5.3229284286499</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>5.59499979019165</v>
       </c>
       <c r="G1011" t="n">
-        <v>5.32292890548706</v>
+        <v>5.3229284286499</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>5.59499979019165</v>
       </c>
       <c r="G1016" t="n">
-        <v>5.32292890548706</v>
+        <v>5.3229284286499</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>5.26300001144409</v>
       </c>
       <c r="G1021" t="n">
-        <v>5.00707292556763</v>
+        <v>5.00707340240479</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1024" t="n">
-        <v>4.89956855773926</v>
+        <v>4.8995680809021</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>5.05900001525879</v>
       </c>
       <c r="G1025" t="n">
-        <v>4.81299352645874</v>
+        <v>4.81299304962158</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>5.1230001449585</v>
       </c>
       <c r="G1027" t="n">
-        <v>4.87388134002686</v>
+        <v>4.8738808631897</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>5.11399984359741</v>
       </c>
       <c r="G1028" t="n">
-        <v>4.86531829833984</v>
+        <v>4.865318775177</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>5.06599998474121</v>
       </c>
       <c r="G1029" t="n">
-        <v>4.81965255737305</v>
+        <v>4.81965303421021</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>4.94199991226196</v>
       </c>
       <c r="G1031" t="n">
-        <v>4.70168256759644</v>
+        <v>4.70168209075928</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>5.05399990081787</v>
       </c>
       <c r="G1036" t="n">
-        <v>4.80823659896851</v>
+        <v>4.80823612213135</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1038" t="n">
-        <v>4.58561563491821</v>
+        <v>4.58561515808105</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>4.91800022125244</v>
       </c>
       <c r="G1039" t="n">
-        <v>4.67884969711304</v>
+        <v>4.6788501739502</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1041" t="n">
-        <v>4.77588987350464</v>
+        <v>4.77588939666748</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>4.94799995422363</v>
       </c>
       <c r="G1042" t="n">
-        <v>4.70739126205444</v>
+        <v>4.70739078521729</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>5.25</v>
       </c>
       <c r="G1046" t="n">
-        <v>4.99470567703247</v>
+        <v>4.99470520019531</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>5.00099992752075</v>
       </c>
       <c r="G1057" t="n">
-        <v>4.75781393051147</v>
+        <v>4.75781345367432</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>4.77899980545044</v>
       </c>
       <c r="G1059" t="n">
-        <v>4.54660844802856</v>
+        <v>4.54660892486572</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>4.32100009918213</v>
       </c>
       <c r="G1062" t="n">
-        <v>4.11088085174561</v>
+        <v>4.11088037490845</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>3.67199993133545</v>
       </c>
       <c r="G1064" t="n">
-        <v>3.49343943595886</v>
+        <v>3.49343967437744</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>3.81699991226196</v>
       </c>
       <c r="G1065" t="n">
-        <v>3.63138866424561</v>
+        <v>3.63138842582703</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>3.7739999294281</v>
       </c>
       <c r="G1071" t="n">
-        <v>3.59047961235046</v>
+        <v>3.59047937393188</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>3.79299998283386</v>
       </c>
       <c r="G1081" t="n">
-        <v>3.60855579376221</v>
+        <v>3.60855555534363</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>3.92400002479553</v>
       </c>
       <c r="G1083" t="n">
-        <v>3.73318552970886</v>
+        <v>3.73318529129028</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G1085" t="n">
-        <v>3.61045837402344</v>
+        <v>3.61045861244202</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>3.53399991989136</v>
       </c>
       <c r="G1088" t="n">
-        <v>3.36214995384216</v>
+        <v>3.36215019226074</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>3.44600009918213</v>
       </c>
       <c r="G1097" t="n">
-        <v>3.27842974662781</v>
+        <v>3.27842950820923</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>3.64400005340576</v>
       </c>
       <c r="G1098" t="n">
-        <v>3.46680116653442</v>
+        <v>3.466801404953</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>3.6159999370575</v>
       </c>
       <c r="G1099" t="n">
-        <v>3.44016289710999</v>
+        <v>3.44016265869141</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>3.53399991989136</v>
       </c>
       <c r="G1101" t="n">
-        <v>3.36214995384216</v>
+        <v>3.36215019226074</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>3.50399994850159</v>
       </c>
       <c r="G1102" t="n">
-        <v>3.33360910415649</v>
+        <v>3.33360886573792</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>3.42799997329712</v>
       </c>
       <c r="G1103" t="n">
-        <v>3.2613046169281</v>
+        <v>3.26130485534668</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1104" t="n">
-        <v>3.29174852371216</v>
+        <v>3.29174876213074</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>3.20700001716614</v>
       </c>
       <c r="G1114" t="n">
-        <v>3.0510516166687</v>
+        <v>3.05105137825012</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>3.30399990081787</v>
       </c>
       <c r="G1116" t="n">
-        <v>3.14333438873291</v>
+        <v>3.14333462715149</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>3.3050000667572</v>
       </c>
       <c r="G1117" t="n">
-        <v>3.14428615570068</v>
+        <v>3.1442859172821</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>3.41400003433228</v>
       </c>
       <c r="G1120" t="n">
-        <v>3.24798560142517</v>
+        <v>3.24798536300659</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>3.52300000190735</v>
       </c>
       <c r="G1121" t="n">
-        <v>3.35168528556824</v>
+        <v>3.35168504714966</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>3.71600008010864</v>
       </c>
       <c r="G1127" t="n">
-        <v>3.5353000164032</v>
+        <v>3.53530025482178</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>3.53399991989136</v>
       </c>
       <c r="G1129" t="n">
-        <v>3.36214995384216</v>
+        <v>3.36215019226074</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1133" t="n">
-        <v>3.49153685569763</v>
+        <v>3.49153709411621</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -71222,6 +71222,32 @@
         <v>7.77600002288818</v>
       </c>
       <c r="H2725" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2726">
+      <c r="A2726" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B2726" t="n">
+        <v>14601558</v>
+      </c>
+      <c r="C2726" t="n">
+        <v>7.7649998664856</v>
+      </c>
+      <c r="D2726" t="n">
+        <v>7.48799991607666</v>
+      </c>
+      <c r="E2726" t="n">
+        <v>7.74499988555908</v>
+      </c>
+      <c r="F2726" t="n">
+        <v>7.51599979400635</v>
+      </c>
+      <c r="G2726" t="n">
+        <v>7.51599979400635</v>
+      </c>
+      <c r="H2726" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/TIT.MI.xlsx
+++ b/data/TIT.MI.xlsx
@@ -733,7 +733,7 @@
         <v>9.76500034332275</v>
       </c>
       <c r="G14" t="n">
-        <v>9.29015254974365</v>
+        <v>9.29015159606934</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>9.77000045776367</v>
       </c>
       <c r="G20" t="n">
-        <v>9.29490947723389</v>
+        <v>9.29490852355957</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G27" t="n">
-        <v>7.99152851104736</v>
+        <v>7.99152803421021</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G28" t="n">
-        <v>8.27693939208984</v>
+        <v>8.27694034576416</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>8.25500011444092</v>
       </c>
       <c r="G30" t="n">
-        <v>7.8535795211792</v>
+        <v>7.85357904434204</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G31" t="n">
-        <v>8.17228984832764</v>
+        <v>8.17228889465332</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>8.76500034332275</v>
       </c>
       <c r="G32" t="n">
-        <v>8.33878040313721</v>
+        <v>8.33877944946289</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G33" t="n">
-        <v>7.80125331878662</v>
+        <v>7.80125379562378</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>8.98999977111816</v>
       </c>
       <c r="G42" t="n">
-        <v>8.55283737182617</v>
+        <v>8.55283832550049</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G44" t="n">
-        <v>8.98095607757568</v>
+        <v>8.98095512390137</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G46" t="n">
-        <v>9.70399951934814</v>
+        <v>9.70399856567383</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>9.82499980926514</v>
       </c>
       <c r="G47" t="n">
-        <v>9.34723377227783</v>
+        <v>9.34723472595215</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G49" t="n">
-        <v>9.64691638946533</v>
+        <v>9.64691734313965</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G51" t="n">
-        <v>9.91330146789551</v>
+        <v>9.91330051422119</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G52" t="n">
-        <v>9.81816291809082</v>
+        <v>9.81816387176514</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>10.3299999237061</v>
       </c>
       <c r="G54" t="n">
-        <v>9.82767677307129</v>
+        <v>9.82767772674561</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>10.4099998474121</v>
       </c>
       <c r="G57" t="n">
-        <v>9.90378761291504</v>
+        <v>9.90378665924072</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G64" t="n">
-        <v>8.70505714416504</v>
+        <v>8.70505809783936</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>8.58500003814697</v>
       </c>
       <c r="G66" t="n">
-        <v>8.1675329208374</v>
+        <v>8.16753196716309</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G67" t="n">
-        <v>8.18180274963379</v>
+        <v>8.18180370330811</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G68" t="n">
-        <v>7.95347356796265</v>
+        <v>7.95347309112549</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>8.98999977111816</v>
       </c>
       <c r="G70" t="n">
-        <v>8.55283737182617</v>
+        <v>8.55283832550049</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>8.65499973297119</v>
       </c>
       <c r="G81" t="n">
-        <v>8.23412895202637</v>
+        <v>8.23412799835205</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G83" t="n">
-        <v>8.25791263580322</v>
+        <v>8.25791358947754</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>8.46500015258789</v>
       </c>
       <c r="G85" t="n">
-        <v>8.05336761474609</v>
+        <v>8.05336856842041</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>8.36499977111816</v>
       </c>
       <c r="G86" t="n">
-        <v>7.95823049545288</v>
+        <v>7.95823001861572</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G87" t="n">
-        <v>8.04861068725586</v>
+        <v>8.04861164093018</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G92" t="n">
-        <v>8.05812454223633</v>
+        <v>8.05812549591064</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>8.48999977111816</v>
       </c>
       <c r="G96" t="n">
-        <v>8.07715129852295</v>
+        <v>8.07715225219727</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>8.30500030517578</v>
       </c>
       <c r="G98" t="n">
-        <v>7.90114784240723</v>
+        <v>7.90114879608154</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G99" t="n">
-        <v>7.87736320495605</v>
+        <v>7.87736368179321</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G102" t="n">
-        <v>7.91541814804077</v>
+        <v>7.91541862487793</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G104" t="n">
-        <v>8.27693939208984</v>
+        <v>8.27694034576416</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G114" t="n">
-        <v>7.82028198242188</v>
+        <v>7.82028150558472</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>7.91499996185303</v>
       </c>
       <c r="G115" t="n">
-        <v>7.53011322021484</v>
+        <v>7.53011274337769</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>7.59499979019165</v>
       </c>
       <c r="G117" t="n">
-        <v>7.22567367553711</v>
+        <v>7.22567319869995</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G118" t="n">
-        <v>7.04015588760376</v>
+        <v>7.04015636444092</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>8.27499961853027</v>
       </c>
       <c r="G123" t="n">
-        <v>7.87260627746582</v>
+        <v>7.87260675430298</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>6.67500019073486</v>
       </c>
       <c r="G125" t="n">
-        <v>6.3504114151001</v>
+        <v>6.35041093826294</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>7.44500017166138</v>
       </c>
       <c r="G127" t="n">
-        <v>7.08296823501587</v>
+        <v>7.08296775817871</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G129" t="n">
-        <v>7.04015588760376</v>
+        <v>7.04015636444092</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>6.33500003814697</v>
       </c>
       <c r="G133" t="n">
-        <v>6.02694463729858</v>
+        <v>6.02694416046143</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G135" t="n">
-        <v>6.30759906768799</v>
+        <v>6.30759954452515</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>6.92500019073486</v>
       </c>
       <c r="G136" t="n">
-        <v>6.58825445175171</v>
+        <v>6.58825397491455</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G140" t="n">
-        <v>6.60252475738525</v>
+        <v>6.60252523422241</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>6.86499977111816</v>
       </c>
       <c r="G142" t="n">
-        <v>6.5311713218689</v>
+        <v>6.53117179870605</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>7</v>
       </c>
       <c r="G145" t="n">
-        <v>6.65960741043091</v>
+        <v>6.65960693359375</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>7.46999979019165</v>
       </c>
       <c r="G147" t="n">
-        <v>7.10675239562988</v>
+        <v>7.10675191879272</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>7.63500022888184</v>
       </c>
       <c r="G149" t="n">
-        <v>7.26372861862183</v>
+        <v>7.26372909545898</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>7.44500017166138</v>
       </c>
       <c r="G151" t="n">
-        <v>7.08296823501587</v>
+        <v>7.08296775817871</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G156" t="n">
-        <v>7.24945783615112</v>
+        <v>7.24945831298828</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>7.92999982833862</v>
       </c>
       <c r="G164" t="n">
-        <v>7.54438352584839</v>
+        <v>7.54438304901123</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>8.0649995803833</v>
       </c>
       <c r="G167" t="n">
-        <v>7.67281818389893</v>
+        <v>7.67281866073608</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>8.24499988555908</v>
       </c>
       <c r="G170" t="n">
-        <v>7.84406566619873</v>
+        <v>7.84406518936157</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>8.13500022888184</v>
       </c>
       <c r="G171" t="n">
-        <v>7.73941469192505</v>
+        <v>7.73941516876221</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>8.16499996185303</v>
       </c>
       <c r="G172" t="n">
-        <v>7.76795625686646</v>
+        <v>7.7679557800293</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G173" t="n">
-        <v>7.80125331878662</v>
+        <v>7.80125379562378</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>8.04500007629395</v>
       </c>
       <c r="G176" t="n">
-        <v>7.65379095077515</v>
+        <v>7.6537914276123</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>8.16499996185303</v>
       </c>
       <c r="G177" t="n">
-        <v>7.76795625686646</v>
+        <v>7.7679557800293</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G178" t="n">
-        <v>7.64903450012207</v>
+        <v>7.64903402328491</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>7.88500022888184</v>
       </c>
       <c r="G179" t="n">
-        <v>7.50157165527344</v>
+        <v>7.5015721321106</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>7.53499984741211</v>
       </c>
       <c r="G182" t="n">
-        <v>7.16859102249146</v>
+        <v>7.16859149932861</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>7.28499984741211</v>
       </c>
       <c r="G185" t="n">
-        <v>6.93074798583984</v>
+        <v>6.930748462677</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>7.63500022888184</v>
       </c>
       <c r="G188" t="n">
-        <v>7.26372861862183</v>
+        <v>7.26372909545898</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>7.34499979019165</v>
       </c>
       <c r="G190" t="n">
-        <v>6.9878306388855</v>
+        <v>6.98783016204834</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>7.49499988555908</v>
       </c>
       <c r="G191" t="n">
-        <v>7.13053607940674</v>
+        <v>7.1305365562439</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G193" t="n">
-        <v>7.03064203262329</v>
+        <v>7.03064250946045</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>7.29500007629395</v>
       </c>
       <c r="G196" t="n">
-        <v>6.94026184082031</v>
+        <v>6.94026231765747</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G199" t="n">
-        <v>7.04015588760376</v>
+        <v>7.04015636444092</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G200" t="n">
-        <v>6.86890840530396</v>
+        <v>6.86890888214111</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>6.94500017166138</v>
       </c>
       <c r="G202" t="n">
-        <v>6.60728168487549</v>
+        <v>6.60728216171265</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>7.57499980926514</v>
       </c>
       <c r="G205" t="n">
-        <v>7.20664644241333</v>
+        <v>7.20664596557617</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>7.59499979019165</v>
       </c>
       <c r="G207" t="n">
-        <v>7.22567367553711</v>
+        <v>7.22567319869995</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G208" t="n">
-        <v>7.3541088104248</v>
+        <v>7.35410928726196</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>7.92999982833862</v>
       </c>
       <c r="G209" t="n">
-        <v>7.54438352584839</v>
+        <v>7.54438304901123</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G216" t="n">
-        <v>7.3541088104248</v>
+        <v>7.35410928726196</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>7.70499992370605</v>
       </c>
       <c r="G217" t="n">
-        <v>7.33032417297363</v>
+        <v>7.33032464981079</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>7.45499992370605</v>
       </c>
       <c r="G221" t="n">
-        <v>7.09248113632202</v>
+        <v>7.09248161315918</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G227" t="n">
-        <v>6.67863464355469</v>
+        <v>6.67863416671753</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>6.86499977111816</v>
       </c>
       <c r="G228" t="n">
-        <v>6.5311713218689</v>
+        <v>6.53117179870605</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G232" t="n">
-        <v>6.70717573165894</v>
+        <v>6.70717620849609</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>7.14499998092651</v>
       </c>
       <c r="G233" t="n">
-        <v>6.79755640029907</v>
+        <v>6.79755592346191</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>7</v>
       </c>
       <c r="G239" t="n">
-        <v>6.65960741043091</v>
+        <v>6.65960693359375</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>7.54500007629395</v>
       </c>
       <c r="G241" t="n">
-        <v>7.17810487747192</v>
+        <v>7.17810535430908</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>7.625</v>
       </c>
       <c r="G243" t="n">
-        <v>7.25421476364136</v>
+        <v>7.25421524047852</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>8.06999969482422</v>
       </c>
       <c r="G248" t="n">
-        <v>7.67757511138916</v>
+        <v>7.67757558822632</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G251" t="n">
-        <v>7.99152851104736</v>
+        <v>7.99152803421021</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G254" t="n">
-        <v>8.27693939208984</v>
+        <v>8.27694034576416</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>8.42500019073486</v>
       </c>
       <c r="G255" t="n">
-        <v>8.01531314849854</v>
+        <v>8.01531219482422</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G257" t="n">
-        <v>7.96298742294312</v>
+        <v>7.96298694610596</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G258" t="n">
-        <v>8.16277599334717</v>
+        <v>8.16277503967285</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>8.42500019073486</v>
       </c>
       <c r="G261" t="n">
-        <v>8.01531314849854</v>
+        <v>8.01531219482422</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G263" t="n">
-        <v>7.82028198242188</v>
+        <v>7.82028150558472</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G264" t="n">
-        <v>7.87736320495605</v>
+        <v>7.87736368179321</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G265" t="n">
-        <v>8.04861068725586</v>
+        <v>8.04861164093018</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G266" t="n">
-        <v>7.93444681167603</v>
+        <v>7.93444633483887</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G268" t="n">
-        <v>8.10569286346436</v>
+        <v>8.10569381713867</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>8.375</v>
       </c>
       <c r="G269" t="n">
-        <v>7.96774482727051</v>
+        <v>7.96774387359619</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>8.3100004196167</v>
       </c>
       <c r="G270" t="n">
-        <v>7.90590524673462</v>
+        <v>7.90590572357178</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G271" t="n">
-        <v>7.99152851104736</v>
+        <v>7.99152803421021</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G272" t="n">
-        <v>8.04861068725586</v>
+        <v>8.04861164093018</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G273" t="n">
-        <v>7.99152851104736</v>
+        <v>7.99152803421021</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>8.3100004196167</v>
       </c>
       <c r="G274" t="n">
-        <v>7.90590524673462</v>
+        <v>7.90590572357178</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G275" t="n">
-        <v>7.82979536056519</v>
+        <v>7.82979440689087</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G281" t="n">
-        <v>7.59195184707642</v>
+        <v>7.59195232391357</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G285" t="n">
-        <v>7.79174041748047</v>
+        <v>7.79173994064331</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>8.25</v>
       </c>
       <c r="G286" t="n">
-        <v>7.84882259368896</v>
+        <v>7.84882211685181</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G287" t="n">
-        <v>7.64903450012207</v>
+        <v>7.64903402328491</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>7.97499990463257</v>
       </c>
       <c r="G289" t="n">
-        <v>7.58719491958618</v>
+        <v>7.58719539642334</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>7.91499996185303</v>
       </c>
       <c r="G291" t="n">
-        <v>7.53011322021484</v>
+        <v>7.53011274337769</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G294" t="n">
-        <v>7.32556772232056</v>
+        <v>7.3255672454834</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>7.59499979019165</v>
       </c>
       <c r="G295" t="n">
-        <v>7.22567367553711</v>
+        <v>7.22567319869995</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>7.79500007629395</v>
       </c>
       <c r="G304" t="n">
-        <v>7.41594791412354</v>
+        <v>7.41594839096069</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G305" t="n">
-        <v>7.3541088104248</v>
+        <v>7.35410928726196</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>7.83500003814697</v>
       </c>
       <c r="G306" t="n">
-        <v>7.45400285720825</v>
+        <v>7.45400333404541</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>7.88500022888184</v>
       </c>
       <c r="G310" t="n">
-        <v>7.50157165527344</v>
+        <v>7.5015721321106</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>8.125</v>
       </c>
       <c r="G314" t="n">
-        <v>7.72990131378174</v>
+        <v>7.72990083694458</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G317" t="n">
-        <v>7.93444681167603</v>
+        <v>7.93444633483887</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G319" t="n">
-        <v>8.10569286346436</v>
+        <v>8.10569381713867</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G320" t="n">
-        <v>8.0105562210083</v>
+        <v>8.01055526733398</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>8.45499992370605</v>
       </c>
       <c r="G321" t="n">
-        <v>8.04385375976562</v>
+        <v>8.04385471343994</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>8.13500022888184</v>
       </c>
       <c r="G325" t="n">
-        <v>7.73941469192505</v>
+        <v>7.73941516876221</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G329" t="n">
-        <v>7.64903450012207</v>
+        <v>7.64903402328491</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>8.04500007629395</v>
       </c>
       <c r="G330" t="n">
-        <v>7.65379095077515</v>
+        <v>7.6537914276123</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>7.875</v>
       </c>
       <c r="G335" t="n">
-        <v>7.49205780029297</v>
+        <v>7.49205827713013</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G337" t="n">
-        <v>7.87736320495605</v>
+        <v>7.87736368179321</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G346" t="n">
-        <v>8.50526905059814</v>
+        <v>8.50527000427246</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>9.14500045776367</v>
       </c>
       <c r="G351" t="n">
-        <v>8.70030117034912</v>
+        <v>8.70030212402344</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G358" t="n">
-        <v>8.2388858795166</v>
+        <v>8.23888492584229</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G360" t="n">
-        <v>8.05812454223633</v>
+        <v>8.05812549591064</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>8.3100004196167</v>
       </c>
       <c r="G361" t="n">
-        <v>7.90590524673462</v>
+        <v>7.90590572357178</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G363" t="n">
-        <v>7.93444681167603</v>
+        <v>7.93444633483887</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G367" t="n">
-        <v>7.88687753677368</v>
+        <v>7.88687801361084</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>8.3100004196167</v>
       </c>
       <c r="G368" t="n">
-        <v>7.90590524673462</v>
+        <v>7.90590572357178</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>8.25</v>
       </c>
       <c r="G369" t="n">
-        <v>7.84882259368896</v>
+        <v>7.84882211685181</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>8.27499961853027</v>
       </c>
       <c r="G370" t="n">
-        <v>7.87260627746582</v>
+        <v>7.87260675430298</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G371" t="n">
-        <v>7.91541814804077</v>
+        <v>7.91541862487793</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>8.33500003814697</v>
       </c>
       <c r="G372" t="n">
-        <v>7.92968988418579</v>
+        <v>7.92968940734863</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>8.25</v>
       </c>
       <c r="G373" t="n">
-        <v>7.84882259368896</v>
+        <v>7.84882211685181</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G376" t="n">
-        <v>7.88687753677368</v>
+        <v>7.88687801361084</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G377" t="n">
-        <v>7.91541814804077</v>
+        <v>7.91541862487793</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G378" t="n">
-        <v>7.82979536056519</v>
+        <v>7.82979440689087</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>8.0649995803833</v>
       </c>
       <c r="G381" t="n">
-        <v>7.67281818389893</v>
+        <v>7.67281866073608</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G385" t="n">
-        <v>7.82979536056519</v>
+        <v>7.82979440689087</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G387" t="n">
-        <v>7.63000774383545</v>
+        <v>7.63000726699829</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>8.04500007629395</v>
       </c>
       <c r="G388" t="n">
-        <v>7.65379095077515</v>
+        <v>7.6537914276123</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>7.88500022888184</v>
       </c>
       <c r="G391" t="n">
-        <v>7.50157165527344</v>
+        <v>7.5015721321106</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G393" t="n">
-        <v>7.8678503036499</v>
+        <v>7.86785078048706</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>8.04500007629395</v>
       </c>
       <c r="G394" t="n">
-        <v>7.65379095077515</v>
+        <v>7.6537914276123</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>8.125</v>
       </c>
       <c r="G399" t="n">
-        <v>7.72990131378174</v>
+        <v>7.72990083694458</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G403" t="n">
-        <v>8.2388858795166</v>
+        <v>8.23888492584229</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>8.70499992370605</v>
       </c>
       <c r="G405" t="n">
-        <v>8.28169631958008</v>
+        <v>8.28169727325439</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>8.70499992370605</v>
       </c>
       <c r="G408" t="n">
-        <v>8.28169631958008</v>
+        <v>8.28169727325439</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G415" t="n">
-        <v>8.05812454223633</v>
+        <v>8.05812549591064</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>8.33500003814697</v>
       </c>
       <c r="G418" t="n">
-        <v>7.92968988418579</v>
+        <v>7.92968940734863</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>8.27499961853027</v>
       </c>
       <c r="G419" t="n">
-        <v>7.87260627746582</v>
+        <v>7.87260675430298</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>8.04500007629395</v>
       </c>
       <c r="G427" t="n">
-        <v>7.65379095077515</v>
+        <v>7.6537914276123</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>7.83500003814697</v>
       </c>
       <c r="G429" t="n">
-        <v>7.45400285720825</v>
+        <v>7.45400333404541</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>7.88500022888184</v>
       </c>
       <c r="G435" t="n">
-        <v>7.50157165527344</v>
+        <v>7.5015721321106</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>8.02499961853027</v>
       </c>
       <c r="G440" t="n">
-        <v>7.63476371765137</v>
+        <v>7.63476324081421</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G442" t="n">
-        <v>7.57292461395264</v>
+        <v>7.57292509078979</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>7.93499994277954</v>
       </c>
       <c r="G445" t="n">
-        <v>7.54914045333862</v>
+        <v>7.54913997650146</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G447" t="n">
-        <v>7.59195184707642</v>
+        <v>7.59195232391357</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>7.63500022888184</v>
       </c>
       <c r="G454" t="n">
-        <v>7.26372861862183</v>
+        <v>7.26372909545898</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>7.54500007629395</v>
       </c>
       <c r="G455" t="n">
-        <v>7.17810487747192</v>
+        <v>7.17810535430908</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>7.625</v>
       </c>
       <c r="G459" t="n">
-        <v>7.25421476364136</v>
+        <v>7.25421524047852</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>7.68499994277954</v>
       </c>
       <c r="G463" t="n">
-        <v>7.31129741668701</v>
+        <v>7.31129693984985</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>7.63500022888184</v>
       </c>
       <c r="G472" t="n">
-        <v>7.26372861862183</v>
+        <v>7.26372909545898</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>7.35500001907349</v>
       </c>
       <c r="G476" t="n">
-        <v>6.99734449386597</v>
+        <v>6.99734401702881</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>6.89499998092651</v>
       </c>
       <c r="G479" t="n">
-        <v>6.55971336364746</v>
+        <v>6.5597128868103</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>6.81500005722046</v>
       </c>
       <c r="G481" t="n">
-        <v>6.48360347747803</v>
+        <v>6.48360300064087</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>6.89499998092651</v>
       </c>
       <c r="G482" t="n">
-        <v>6.55971336364746</v>
+        <v>6.5597128868103</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>7.04500007629395</v>
       </c>
       <c r="G490" t="n">
-        <v>6.7024188041687</v>
+        <v>6.70241928100586</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G494" t="n">
-        <v>6.71668910980225</v>
+        <v>6.7166895866394</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>7.46999979019165</v>
       </c>
       <c r="G497" t="n">
-        <v>7.10675239562988</v>
+        <v>7.10675191879272</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>7.54500007629395</v>
       </c>
       <c r="G498" t="n">
-        <v>7.17810487747192</v>
+        <v>7.17810535430908</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>7.2649998664856</v>
       </c>
       <c r="G502" t="n">
-        <v>6.91172075271606</v>
+        <v>6.91172027587891</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>7.34499979019165</v>
       </c>
       <c r="G504" t="n">
-        <v>6.9878306388855</v>
+        <v>6.98783016204834</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G505" t="n">
-        <v>7.04015588760376</v>
+        <v>7.04015636444092</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>7.34499979019165</v>
       </c>
       <c r="G507" t="n">
-        <v>6.9878306388855</v>
+        <v>6.98783016204834</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G508" t="n">
-        <v>7.02112913131714</v>
+        <v>7.02112865447998</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>7.29500007629395</v>
       </c>
       <c r="G510" t="n">
-        <v>6.94026184082031</v>
+        <v>6.94026231765747</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>7.20499992370605</v>
       </c>
       <c r="G511" t="n">
-        <v>6.85463809967041</v>
+        <v>6.85463857650757</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>7.25500011444092</v>
       </c>
       <c r="G512" t="n">
-        <v>6.90220737457275</v>
+        <v>6.9022068977356</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>7.25</v>
       </c>
       <c r="G513" t="n">
-        <v>6.89745044708252</v>
+        <v>6.89744997024536</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G514" t="n">
-        <v>6.98307418823242</v>
+        <v>6.98307371139526</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>7.38500022888184</v>
       </c>
       <c r="G515" t="n">
-        <v>7.02588558197021</v>
+        <v>7.02588605880737</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>7.43499994277954</v>
       </c>
       <c r="G520" t="n">
-        <v>7.0734543800354</v>
+        <v>7.07345390319824</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>7.38500022888184</v>
       </c>
       <c r="G521" t="n">
-        <v>7.02588558197021</v>
+        <v>7.02588605880737</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>7.20499992370605</v>
       </c>
       <c r="G530" t="n">
-        <v>6.85463809967041</v>
+        <v>6.85463857650757</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>7.21199989318848</v>
       </c>
       <c r="G538" t="n">
-        <v>6.86129808425903</v>
+        <v>6.86129760742188</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>6.98799991607666</v>
       </c>
       <c r="G540" t="n">
-        <v>6.64819049835205</v>
+        <v>6.64819097518921</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G543" t="n">
-        <v>6.5454421043396</v>
+        <v>6.54544258117676</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>7.19600009918213</v>
       </c>
       <c r="G548" t="n">
-        <v>6.84607648849487</v>
+        <v>6.84607601165771</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G551" t="n">
-        <v>7.02112913131714</v>
+        <v>7.02112865447998</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G553" t="n">
-        <v>7.04015588760376</v>
+        <v>7.04015636444092</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>7.39799976348877</v>
       </c>
       <c r="G554" t="n">
-        <v>7.03825330734253</v>
+        <v>7.03825283050537</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>7.24599981307983</v>
       </c>
       <c r="G555" t="n">
-        <v>6.89364433288574</v>
+        <v>6.8936448097229</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>7.28800010681152</v>
       </c>
       <c r="G556" t="n">
-        <v>6.93360280990601</v>
+        <v>6.93360233306885</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G559" t="n">
-        <v>7.82979536056519</v>
+        <v>7.82979440689087</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G560" t="n">
-        <v>7.91541814804077</v>
+        <v>7.91541862487793</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>8.20199966430664</v>
       </c>
       <c r="G561" t="n">
-        <v>7.80315589904785</v>
+        <v>7.80315637588501</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>8.00800037384033</v>
       </c>
       <c r="G562" t="n">
-        <v>7.61859130859375</v>
+        <v>7.61859083175659</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>7.83199977874756</v>
       </c>
       <c r="G563" t="n">
-        <v>7.45114850997925</v>
+        <v>7.45114898681641</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>8.08800029754639</v>
       </c>
       <c r="G565" t="n">
-        <v>7.69470071792603</v>
+        <v>7.69470024108887</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>8.11600017547607</v>
       </c>
       <c r="G566" t="n">
-        <v>7.72133922576904</v>
+        <v>7.72133874893188</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>7.72599983215332</v>
       </c>
       <c r="G570" t="n">
-        <v>7.35030317306519</v>
+        <v>7.35030364990234</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>7.61399984359741</v>
       </c>
       <c r="G572" t="n">
-        <v>7.24375009536743</v>
+        <v>7.24374961853027</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>7.58199977874756</v>
       </c>
       <c r="G576" t="n">
-        <v>7.21330547332764</v>
+        <v>7.21330595016479</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>8.61200046539307</v>
       </c>
       <c r="G582" t="n">
-        <v>8.1932201385498</v>
+        <v>8.19321918487549</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>8.38199996948242</v>
       </c>
       <c r="G585" t="n">
-        <v>7.97440338134766</v>
+        <v>7.97440385818481</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>8.76200008392334</v>
       </c>
       <c r="G588" t="n">
-        <v>8.3359260559082</v>
+        <v>8.33592510223389</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G589" t="n">
-        <v>8.27693939208984</v>
+        <v>8.27694034576416</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>8.26200008392334</v>
       </c>
       <c r="G591" t="n">
-        <v>7.86023950576782</v>
+        <v>7.86023902893066</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G596" t="n">
-        <v>7.96298742294312</v>
+        <v>7.96298694610596</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G599" t="n">
-        <v>8.0105562210083</v>
+        <v>8.01055526733398</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G600" t="n">
-        <v>7.88687753677368</v>
+        <v>7.88687801361084</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G605" t="n">
-        <v>7.3541088104248</v>
+        <v>7.35410928726196</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G606" t="n">
-        <v>7.30654048919678</v>
+        <v>7.30654001235962</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G609" t="n">
-        <v>7.02112913131714</v>
+        <v>7.02112865447998</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>7.31199979782104</v>
       </c>
       <c r="G610" t="n">
-        <v>6.95643472671509</v>
+        <v>6.95643520355225</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>7.30999994277954</v>
       </c>
       <c r="G611" t="n">
-        <v>6.95453214645386</v>
+        <v>6.95453262329102</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>7.14400005340576</v>
       </c>
       <c r="G613" t="n">
-        <v>6.79660511016846</v>
+        <v>6.7966046333313</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>7.01599979400635</v>
       </c>
       <c r="G615" t="n">
-        <v>6.67482900619507</v>
+        <v>6.67482852935791</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>6.87200021743774</v>
       </c>
       <c r="G616" t="n">
-        <v>6.53783178329468</v>
+        <v>6.53783130645752</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>6.98600006103516</v>
       </c>
       <c r="G618" t="n">
-        <v>6.64628839492798</v>
+        <v>6.64628791809082</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>6.91599988937378</v>
       </c>
       <c r="G620" t="n">
-        <v>6.5796914100647</v>
+        <v>6.57969188690186</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>6.72200012207031</v>
       </c>
       <c r="G622" t="n">
-        <v>6.39512538909912</v>
+        <v>6.39512586593628</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>6.87200021743774</v>
       </c>
       <c r="G623" t="n">
-        <v>6.53783178329468</v>
+        <v>6.53783130645752</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>6.85799980163574</v>
       </c>
       <c r="G624" t="n">
-        <v>6.52451229095459</v>
+        <v>6.52451181411743</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>6.7519998550415</v>
       </c>
       <c r="G627" t="n">
-        <v>6.42366695404053</v>
+        <v>6.42366647720337</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>6.76599979400635</v>
       </c>
       <c r="G628" t="n">
-        <v>6.43698596954346</v>
+        <v>6.4369854927063</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G631" t="n">
-        <v>6.33614063262939</v>
+        <v>6.33614015579224</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>6.45599985122681</v>
       </c>
       <c r="G635" t="n">
-        <v>6.14206027984619</v>
+        <v>6.14206075668335</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>6.37400007247925</v>
       </c>
       <c r="G637" t="n">
-        <v>6.06404829025269</v>
+        <v>6.06404781341553</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>6.28200006484985</v>
       </c>
       <c r="G638" t="n">
-        <v>5.97652196884155</v>
+        <v>5.97652149200439</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>6.52400016784668</v>
       </c>
       <c r="G640" t="n">
-        <v>6.20675373077393</v>
+        <v>6.20675420761108</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>6.55200004577637</v>
       </c>
       <c r="G642" t="n">
-        <v>6.23339223861694</v>
+        <v>6.2333927154541</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>6.36600017547607</v>
       </c>
       <c r="G644" t="n">
-        <v>6.05643701553345</v>
+        <v>6.05643749237061</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G645" t="n">
-        <v>6.01267433166504</v>
+        <v>6.01267385482788</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>6.14599990844727</v>
       </c>
       <c r="G646" t="n">
-        <v>5.84713459014893</v>
+        <v>5.84713506698608</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>6.07399988174438</v>
       </c>
       <c r="G648" t="n">
-        <v>5.77863597869873</v>
+        <v>5.77863645553589</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G658" t="n">
-        <v>6.27905797958374</v>
+        <v>6.2790584564209</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>6.50400018692017</v>
       </c>
       <c r="G660" t="n">
-        <v>6.18772649765015</v>
+        <v>6.1877269744873</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>6.38199996948242</v>
       </c>
       <c r="G661" t="n">
-        <v>6.07165861129761</v>
+        <v>6.07165908813477</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>6</v>
       </c>
       <c r="G675" t="n">
-        <v>5.7082347869873</v>
+        <v>5.70823431015015</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>5.98799991607666</v>
       </c>
       <c r="G676" t="n">
-        <v>5.69681787490845</v>
+        <v>5.69681835174561</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>6.0019998550415</v>
       </c>
       <c r="G677" t="n">
-        <v>5.71013689041138</v>
+        <v>5.71013736724854</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>5.93800020217896</v>
       </c>
       <c r="G678" t="n">
-        <v>5.64925003051758</v>
+        <v>5.64924955368042</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G681" t="n">
-        <v>5.22303438186646</v>
+        <v>5.22303485870361</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G682" t="n">
-        <v>5.28011751174927</v>
+        <v>5.28011703491211</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>5.25</v>
       </c>
       <c r="G683" t="n">
-        <v>4.99470520019531</v>
+        <v>4.99470567703247</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>5.4060001373291</v>
       </c>
       <c r="G689" t="n">
-        <v>5.14311981201172</v>
+        <v>5.14311933517456</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>5.71400022506714</v>
       </c>
       <c r="G693" t="n">
-        <v>5.43614196777344</v>
+        <v>5.4361424446106</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>5.68599987030029</v>
       </c>
       <c r="G695" t="n">
-        <v>5.40950345993042</v>
+        <v>5.40950393676758</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>5.68599987030029</v>
       </c>
       <c r="G696" t="n">
-        <v>5.40950345993042</v>
+        <v>5.40950393676758</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>5.60599994659424</v>
       </c>
       <c r="G697" t="n">
-        <v>5.33339357376099</v>
+        <v>5.33339405059814</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G698" t="n">
-        <v>5.30865812301636</v>
+        <v>5.30865859985352</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>4.95300006866455</v>
       </c>
       <c r="G702" t="n">
-        <v>4.71214771270752</v>
+        <v>4.71214818954468</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>4.95699977874756</v>
       </c>
       <c r="G705" t="n">
-        <v>4.71595335006714</v>
+        <v>4.71595287322998</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>5.03200006484985</v>
       </c>
       <c r="G709" t="n">
-        <v>4.78730583190918</v>
+        <v>4.78730630874634</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G710" t="n">
-        <v>4.77588939666748</v>
+        <v>4.77588987350464</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>4.98600006103516</v>
       </c>
       <c r="G716" t="n">
-        <v>4.74354314804077</v>
+        <v>4.74354267120361</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>5.19199991226196</v>
       </c>
       <c r="G724" t="n">
-        <v>4.93952608108521</v>
+        <v>4.93952560424805</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>5.35400009155273</v>
       </c>
       <c r="G727" t="n">
-        <v>5.0936484336853</v>
+        <v>5.09364795684814</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G729" t="n">
-        <v>5.08984279632568</v>
+        <v>5.08984231948853</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G731" t="n">
-        <v>4.90908145904541</v>
+        <v>4.90908193588257</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>5.30399990081787</v>
       </c>
       <c r="G732" t="n">
-        <v>5.04607915878296</v>
+        <v>5.04607963562012</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G734" t="n">
-        <v>4.95665073394775</v>
+        <v>4.9566502571106</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>5.16400003433228</v>
       </c>
       <c r="G735" t="n">
-        <v>4.91288709640503</v>
+        <v>4.91288757324219</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>5.26200008392334</v>
       </c>
       <c r="G736" t="n">
-        <v>5.00612211227417</v>
+        <v>5.00612163543701</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>5.74599981307983</v>
       </c>
       <c r="G747" t="n">
-        <v>5.46658611297607</v>
+        <v>5.46658563613892</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>5.69199991226196</v>
       </c>
       <c r="G748" t="n">
-        <v>5.41521215438843</v>
+        <v>5.41521167755127</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G754" t="n">
-        <v>5.42282247543335</v>
+        <v>5.42282295227051</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>5.4520001411438</v>
       </c>
       <c r="G759" t="n">
-        <v>5.18688249588013</v>
+        <v>5.18688297271729</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>5.2020001411438</v>
       </c>
       <c r="G760" t="n">
-        <v>4.94903945922852</v>
+        <v>4.94903993606567</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G762" t="n">
-        <v>4.58561515808105</v>
+        <v>4.58561563491821</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>4.83300018310547</v>
       </c>
       <c r="G763" t="n">
-        <v>4.59798336029053</v>
+        <v>4.59798288345337</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>5.06199979782104</v>
       </c>
       <c r="G768" t="n">
-        <v>4.81584739685059</v>
+        <v>4.81584692001343</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>4.95900011062622</v>
       </c>
       <c r="G769" t="n">
-        <v>4.71785640716553</v>
+        <v>4.71785593032837</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>5.00600004196167</v>
       </c>
       <c r="G771" t="n">
-        <v>4.76257038116455</v>
+        <v>4.76257085800171</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>5.01599979400635</v>
       </c>
       <c r="G772" t="n">
-        <v>4.77208375930786</v>
+        <v>4.77208423614502</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>5.02400016784668</v>
       </c>
       <c r="G773" t="n">
-        <v>4.77969551086426</v>
+        <v>4.7796950340271</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>4.88500022888184</v>
       </c>
       <c r="G776" t="n">
-        <v>4.64745473861694</v>
+        <v>4.64745426177979</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>4.48400020599365</v>
       </c>
       <c r="G779" t="n">
-        <v>4.26595401763916</v>
+        <v>4.26595449447632</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>4.52899980545044</v>
       </c>
       <c r="G780" t="n">
-        <v>4.30876588821411</v>
+        <v>4.30876541137695</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>4.58199977874756</v>
       </c>
       <c r="G783" t="n">
-        <v>4.35918855667114</v>
+        <v>4.35918807983398</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G784" t="n">
-        <v>4.4048547744751</v>
+        <v>4.40485429763794</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>5.02400016784668</v>
       </c>
       <c r="G788" t="n">
-        <v>4.77969551086426</v>
+        <v>4.7796950340271</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G791" t="n">
-        <v>4.49047803878784</v>
+        <v>4.49047756195068</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>4.81599998474121</v>
       </c>
       <c r="G793" t="n">
-        <v>4.58180999755859</v>
+        <v>4.58180952072144</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>4.8270001411438</v>
       </c>
       <c r="G795" t="n">
-        <v>4.59227514266968</v>
+        <v>4.59227466583252</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G797" t="n">
-        <v>5.04227447509766</v>
+        <v>5.0422739982605</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G802" t="n">
-        <v>5.09935617446899</v>
+        <v>5.09935665130615</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>5.32200002670288</v>
       </c>
       <c r="G806" t="n">
-        <v>5.06320381164551</v>
+        <v>5.06320428848267</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>5.5</v>
       </c>
       <c r="G808" t="n">
-        <v>5.23254823684692</v>
+        <v>5.23254871368408</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>5.64799976348877</v>
       </c>
       <c r="G809" t="n">
-        <v>5.37335109710693</v>
+        <v>5.37335157394409</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G810" t="n">
-        <v>5.33719921112061</v>
+        <v>5.33719968795776</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>5.35599994659424</v>
       </c>
       <c r="G818" t="n">
-        <v>5.09555053710938</v>
+        <v>5.09555101394653</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G820" t="n">
-        <v>5.04227447509766</v>
+        <v>5.0422739982605</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>5.25799989700317</v>
       </c>
       <c r="G821" t="n">
-        <v>5.00231647491455</v>
+        <v>5.00231599807739</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>5.31599998474121</v>
       </c>
       <c r="G823" t="n">
-        <v>5.05749607086182</v>
+        <v>5.05749559402466</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>5.35599994659424</v>
       </c>
       <c r="G824" t="n">
-        <v>5.09555053710938</v>
+        <v>5.09555101394653</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G825" t="n">
-        <v>5.14692449569702</v>
+        <v>5.14692497253418</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G828" t="n">
-        <v>5.08984279632568</v>
+        <v>5.08984231948853</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>5.40199995040894</v>
       </c>
       <c r="G829" t="n">
-        <v>5.1393141746521</v>
+        <v>5.13931369781494</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>5.36800003051758</v>
       </c>
       <c r="G831" t="n">
-        <v>5.10696744918823</v>
+        <v>5.10696697235107</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>5.33599996566772</v>
       </c>
       <c r="G832" t="n">
-        <v>5.07652378082275</v>
+        <v>5.0765233039856</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>5.34899997711182</v>
       </c>
       <c r="G833" t="n">
-        <v>5.08889150619507</v>
+        <v>5.08889102935791</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>5.25500011444092</v>
       </c>
       <c r="G838" t="n">
-        <v>4.99946212768555</v>
+        <v>4.99946260452271</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>4.98600006103516</v>
       </c>
       <c r="G846" t="n">
-        <v>4.74354314804077</v>
+        <v>4.74354267120361</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>4.95900011062622</v>
       </c>
       <c r="G847" t="n">
-        <v>4.71785640716553</v>
+        <v>4.71785593032837</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>4.67199993133545</v>
       </c>
       <c r="G853" t="n">
-        <v>4.44481229782104</v>
+        <v>4.44481182098389</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>4.45800018310547</v>
       </c>
       <c r="G856" t="n">
-        <v>4.24121809005737</v>
+        <v>4.24121856689453</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>4.57800006866455</v>
       </c>
       <c r="G859" t="n">
-        <v>4.35538339614868</v>
+        <v>4.35538291931152</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>4.38100004196167</v>
       </c>
       <c r="G863" t="n">
-        <v>4.1679630279541</v>
+        <v>4.16796255111694</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G870" t="n">
-        <v>4.32398796081543</v>
+        <v>4.32398748397827</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>4.63100004196167</v>
       </c>
       <c r="G877" t="n">
-        <v>4.40580606460571</v>
+        <v>4.40580558776855</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>4.84200000762939</v>
       </c>
       <c r="G882" t="n">
-        <v>4.60654544830322</v>
+        <v>4.60654497146606</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>5.00899982452393</v>
       </c>
       <c r="G883" t="n">
-        <v>4.76542472839355</v>
+        <v>4.7654242515564</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>4.82800006866455</v>
       </c>
       <c r="G889" t="n">
-        <v>4.59322643280029</v>
+        <v>4.59322595596313</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>4.78299999237061</v>
       </c>
       <c r="G890" t="n">
-        <v>4.55041408538818</v>
+        <v>4.55041456222534</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>4.92199993133545</v>
       </c>
       <c r="G891" t="n">
-        <v>4.68265533447266</v>
+        <v>4.6826548576355</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>4.96299982070923</v>
       </c>
       <c r="G893" t="n">
-        <v>4.72166109085083</v>
+        <v>4.72166156768799</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>5.01300001144409</v>
       </c>
       <c r="G898" t="n">
-        <v>4.76923036575317</v>
+        <v>4.76922988891602</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>5.06099987030029</v>
       </c>
       <c r="G902" t="n">
-        <v>4.81489610671997</v>
+        <v>4.81489562988281</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>4.91099977493286</v>
       </c>
       <c r="G903" t="n">
-        <v>4.67218971252441</v>
+        <v>4.67219018936157</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>4.95699977874756</v>
       </c>
       <c r="G905" t="n">
-        <v>4.71595335006714</v>
+        <v>4.71595287322998</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G909" t="n">
-        <v>4.98519134521484</v>
+        <v>4.985191822052</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>5.10599994659424</v>
       </c>
       <c r="G911" t="n">
-        <v>4.85770750045776</v>
+        <v>4.85770797729492</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>4.99599981307983</v>
       </c>
       <c r="G913" t="n">
-        <v>4.75305652618408</v>
+        <v>4.75305700302124</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>4.83400011062622</v>
       </c>
       <c r="G915" t="n">
-        <v>4.59893417358398</v>
+        <v>4.59893465042114</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>4.81599998474121</v>
       </c>
       <c r="G916" t="n">
-        <v>4.58180999755859</v>
+        <v>4.58180952072144</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>4.88800001144409</v>
       </c>
       <c r="G917" t="n">
-        <v>4.65030813217163</v>
+        <v>4.65030860900879</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>4.60200023651123</v>
       </c>
       <c r="G918" t="n">
-        <v>4.37821578979492</v>
+        <v>4.37821626663208</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>4.56500005722046</v>
       </c>
       <c r="G923" t="n">
-        <v>4.34301519393921</v>
+        <v>4.34301567077637</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>4.47200012207031</v>
       </c>
       <c r="G924" t="n">
-        <v>4.25453805923462</v>
+        <v>4.25453758239746</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>4.59800004959106</v>
       </c>
       <c r="G926" t="n">
-        <v>4.37441062927246</v>
+        <v>4.3744101524353</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>4.52600002288818</v>
       </c>
       <c r="G927" t="n">
-        <v>4.30591201782227</v>
+        <v>4.30591154098511</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>4.92600011825562</v>
       </c>
       <c r="G935" t="n">
-        <v>4.68646049499512</v>
+        <v>4.68646097183228</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>4.91800022125244</v>
       </c>
       <c r="G936" t="n">
-        <v>4.6788501739502</v>
+        <v>4.67884969711304</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G942" t="n">
-        <v>4.95665073394775</v>
+        <v>4.9566502571106</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>5.16699981689453</v>
       </c>
       <c r="G943" t="n">
-        <v>4.91574144363403</v>
+        <v>4.91574096679688</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G946" t="n">
-        <v>4.98519134521484</v>
+        <v>4.985191822052</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>5.19700002670288</v>
       </c>
       <c r="G952" t="n">
-        <v>4.94428253173828</v>
+        <v>4.94428300857544</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>4.94199991226196</v>
       </c>
       <c r="G955" t="n">
-        <v>4.70168209075928</v>
+        <v>4.70168256759644</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>4.96799993515015</v>
       </c>
       <c r="G956" t="n">
-        <v>4.72641801834106</v>
+        <v>4.72641849517822</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>4.97599983215332</v>
       </c>
       <c r="G957" t="n">
-        <v>4.7340292930603</v>
+        <v>4.73402881622314</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>5.06599998474121</v>
       </c>
       <c r="G959" t="n">
-        <v>4.81965303421021</v>
+        <v>4.81965255737305</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G962" t="n">
-        <v>5.09935617446899</v>
+        <v>5.09935665130615</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>5.39400005340576</v>
       </c>
       <c r="G965" t="n">
-        <v>5.13170289993286</v>
+        <v>5.13170337677002</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>5.35400009155273</v>
       </c>
       <c r="G967" t="n">
-        <v>5.0936484336853</v>
+        <v>5.09364795684814</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G971" t="n">
-        <v>5.06130123138428</v>
+        <v>5.06130170822144</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G974" t="n">
-        <v>5.05178785324097</v>
+        <v>5.05178737640381</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>5.36299991607666</v>
       </c>
       <c r="G984" t="n">
-        <v>5.102210521698</v>
+        <v>5.10221004486084</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G985" t="n">
-        <v>5.09935617446899</v>
+        <v>5.09935665130615</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>5.41300010681152</v>
       </c>
       <c r="G986" t="n">
-        <v>5.14977884292603</v>
+        <v>5.14977931976318</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>5.44099998474121</v>
       </c>
       <c r="G987" t="n">
-        <v>5.1764178276062</v>
+        <v>5.17641735076904</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>5.51800012588501</v>
       </c>
       <c r="G989" t="n">
-        <v>5.24967288970947</v>
+        <v>5.24967336654663</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>5.65100002288818</v>
       </c>
       <c r="G990" t="n">
-        <v>5.3762059211731</v>
+        <v>5.37620544433594</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>5.83900022506714</v>
       </c>
       <c r="G993" t="n">
-        <v>5.55506372451782</v>
+        <v>5.55506420135498</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>5.73899984359741</v>
       </c>
       <c r="G995" t="n">
-        <v>5.45992612838745</v>
+        <v>5.45992660522461</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>5.68599987030029</v>
       </c>
       <c r="G996" t="n">
-        <v>5.40950345993042</v>
+        <v>5.40950393676758</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>5.51200008392334</v>
       </c>
       <c r="G999" t="n">
-        <v>5.24396514892578</v>
+        <v>5.24396467208862</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>5.54199981689453</v>
       </c>
       <c r="G1008" t="n">
-        <v>5.27250576019287</v>
+        <v>5.27250623703003</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1009" t="n">
-        <v>5.28963088989258</v>
+        <v>5.28963041305542</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>5.59499979019165</v>
       </c>
       <c r="G1010" t="n">
-        <v>5.3229284286499</v>
+        <v>5.32292890548706</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>5.59499979019165</v>
       </c>
       <c r="G1011" t="n">
-        <v>5.3229284286499</v>
+        <v>5.32292890548706</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>5.59499979019165</v>
       </c>
       <c r="G1016" t="n">
-        <v>5.3229284286499</v>
+        <v>5.32292890548706</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>5.26300001144409</v>
       </c>
       <c r="G1021" t="n">
-        <v>5.00707340240479</v>
+        <v>5.00707292556763</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1024" t="n">
-        <v>4.8995680809021</v>
+        <v>4.89956855773926</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>5.05900001525879</v>
       </c>
       <c r="G1025" t="n">
-        <v>4.81299304962158</v>
+        <v>4.81299352645874</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>5.1230001449585</v>
       </c>
       <c r="G1027" t="n">
-        <v>4.8738808631897</v>
+        <v>4.87388134002686</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>5.11399984359741</v>
       </c>
       <c r="G1028" t="n">
-        <v>4.865318775177</v>
+        <v>4.86531829833984</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>5.06599998474121</v>
       </c>
       <c r="G1029" t="n">
-        <v>4.81965303421021</v>
+        <v>4.81965255737305</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>4.94199991226196</v>
       </c>
       <c r="G1031" t="n">
-        <v>4.70168209075928</v>
+        <v>4.70168256759644</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>5.05399990081787</v>
       </c>
       <c r="G1036" t="n">
-        <v>4.80823612213135</v>
+        <v>4.80823659896851</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1038" t="n">
-        <v>4.58561515808105</v>
+        <v>4.58561563491821</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>4.91800022125244</v>
       </c>
       <c r="G1039" t="n">
-        <v>4.6788501739502</v>
+        <v>4.67884969711304</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1041" t="n">
-        <v>4.77588939666748</v>
+        <v>4.77588987350464</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>4.94799995422363</v>
       </c>
       <c r="G1042" t="n">
-        <v>4.70739078521729</v>
+        <v>4.70739126205444</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>5.25</v>
       </c>
       <c r="G1046" t="n">
-        <v>4.99470520019531</v>
+        <v>4.99470567703247</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>5.00099992752075</v>
       </c>
       <c r="G1057" t="n">
-        <v>4.75781345367432</v>
+        <v>4.75781393051147</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>4.77899980545044</v>
       </c>
       <c r="G1059" t="n">
-        <v>4.54660892486572</v>
+        <v>4.54660844802856</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>4.32100009918213</v>
       </c>
       <c r="G1062" t="n">
-        <v>4.11088037490845</v>
+        <v>4.11088085174561</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>3.67199993133545</v>
       </c>
       <c r="G1064" t="n">
-        <v>3.49343967437744</v>
+        <v>3.49343943595886</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>3.81699991226196</v>
       </c>
       <c r="G1065" t="n">
-        <v>3.63138842582703</v>
+        <v>3.63138866424561</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>3.7739999294281</v>
       </c>
       <c r="G1071" t="n">
-        <v>3.59047937393188</v>
+        <v>3.59047961235046</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>3.79299998283386</v>
       </c>
       <c r="G1081" t="n">
-        <v>3.60855555534363</v>
+        <v>3.60855579376221</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>3.92400002479553</v>
       </c>
       <c r="G1083" t="n">
-        <v>3.73318529129028</v>
+        <v>3.73318552970886</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G1085" t="n">
-        <v>3.61045861244202</v>
+        <v>3.61045837402344</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>3.53399991989136</v>
       </c>
       <c r="G1088" t="n">
-        <v>3.36215019226074</v>
+        <v>3.36214995384216</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>3.44600009918213</v>
       </c>
       <c r="G1097" t="n">
-        <v>3.27842950820923</v>
+        <v>3.27842974662781</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>3.64400005340576</v>
       </c>
       <c r="G1098" t="n">
-        <v>3.466801404953</v>
+        <v>3.46680116653442</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>3.6159999370575</v>
       </c>
       <c r="G1099" t="n">
-        <v>3.44016265869141</v>
+        <v>3.44016289710999</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>3.53399991989136</v>
       </c>
       <c r="G1101" t="n">
-        <v>3.36215019226074</v>
+        <v>3.36214995384216</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>3.50399994850159</v>
       </c>
       <c r="G1102" t="n">
-        <v>3.33360886573792</v>
+        <v>3.33360910415649</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>3.42799997329712</v>
       </c>
       <c r="G1103" t="n">
-        <v>3.26130485534668</v>
+        <v>3.2613046169281</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1104" t="n">
-        <v>3.29174876213074</v>
+        <v>3.29174852371216</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>3.20700001716614</v>
       </c>
       <c r="G1114" t="n">
-        <v>3.05105137825012</v>
+        <v>3.0510516166687</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>3.30399990081787</v>
       </c>
       <c r="G1116" t="n">
-        <v>3.14333462715149</v>
+        <v>3.14333438873291</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>3.3050000667572</v>
       </c>
       <c r="G1117" t="n">
-        <v>3.1442859172821</v>
+        <v>3.14428615570068</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>3.41400003433228</v>
       </c>
       <c r="G1120" t="n">
-        <v>3.24798536300659</v>
+        <v>3.24798560142517</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>3.52300000190735</v>
       </c>
       <c r="G1121" t="n">
-        <v>3.35168504714966</v>
+        <v>3.35168528556824</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>3.71600008010864</v>
       </c>
       <c r="G1127" t="n">
-        <v>3.53530025482178</v>
+        <v>3.5353000164032</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>3.53399991989136</v>
       </c>
       <c r="G1129" t="n">
-        <v>3.36215019226074</v>
+        <v>3.36214995384216</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1133" t="n">
-        <v>3.49153709411621</v>
+        <v>3.49153685569763</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -71248,6 +71248,32 @@
         <v>7.51599979400635</v>
       </c>
       <c r="H2726" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2727">
+      <c r="A2727" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B2727" t="n">
+        <v>11489646</v>
+      </c>
+      <c r="C2727" t="n">
+        <v>7.56300020217896</v>
+      </c>
+      <c r="D2727" t="n">
+        <v>7.4210000038147</v>
+      </c>
+      <c r="E2727" t="n">
+        <v>7.49399995803833</v>
+      </c>
+      <c r="F2727" t="n">
+        <v>7.48899984359741</v>
+      </c>
+      <c r="G2727" t="n">
+        <v>7.48899984359741</v>
+      </c>
+      <c r="H2727" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/TIT.MI.xlsx
+++ b/data/TIT.MI.xlsx
@@ -71277,6 +71277,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2728">
+      <c r="A2728" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B2728" t="n">
+        <v>9996250</v>
+      </c>
+      <c r="C2728" t="n">
+        <v>7.52799987792969</v>
+      </c>
+      <c r="D2728" t="n">
+        <v>7.35099983215332</v>
+      </c>
+      <c r="E2728" t="n">
+        <v>7.42999982833862</v>
+      </c>
+      <c r="F2728" t="n">
+        <v>7.44099998474121</v>
+      </c>
+      <c r="G2728" t="n">
+        <v>7.44099998474121</v>
+      </c>
+      <c r="H2728" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TIT.MI.xlsx
+++ b/data/TIT.MI.xlsx
@@ -733,7 +733,7 @@
         <v>9.76500034332275</v>
       </c>
       <c r="G14" t="n">
-        <v>9.29015159606934</v>
+        <v>9.29015254974365</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>9.77000045776367</v>
       </c>
       <c r="G20" t="n">
-        <v>9.29490852355957</v>
+        <v>9.29490947723389</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G27" t="n">
-        <v>7.99152803421021</v>
+        <v>7.99152851104736</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G28" t="n">
-        <v>8.27694034576416</v>
+        <v>8.27693939208984</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>8.25500011444092</v>
       </c>
       <c r="G30" t="n">
-        <v>7.85357904434204</v>
+        <v>7.8535795211792</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G31" t="n">
-        <v>8.17228889465332</v>
+        <v>8.17228984832764</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>8.76500034332275</v>
       </c>
       <c r="G32" t="n">
-        <v>8.33877944946289</v>
+        <v>8.33878040313721</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G33" t="n">
-        <v>7.80125379562378</v>
+        <v>7.80125331878662</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>8.98999977111816</v>
       </c>
       <c r="G42" t="n">
-        <v>8.55283832550049</v>
+        <v>8.55283737182617</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G44" t="n">
-        <v>8.98095512390137</v>
+        <v>8.98095607757568</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G46" t="n">
-        <v>9.70399856567383</v>
+        <v>9.70399951934814</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>9.82499980926514</v>
       </c>
       <c r="G47" t="n">
-        <v>9.34723472595215</v>
+        <v>9.34723377227783</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G49" t="n">
-        <v>9.64691734313965</v>
+        <v>9.64691638946533</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G51" t="n">
-        <v>9.91330051422119</v>
+        <v>9.91330146789551</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G52" t="n">
-        <v>9.81816387176514</v>
+        <v>9.81816291809082</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>10.3299999237061</v>
       </c>
       <c r="G54" t="n">
-        <v>9.82767772674561</v>
+        <v>9.82767677307129</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>10.4099998474121</v>
       </c>
       <c r="G57" t="n">
-        <v>9.90378665924072</v>
+        <v>9.90378761291504</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G64" t="n">
-        <v>8.70505809783936</v>
+        <v>8.70505714416504</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>8.58500003814697</v>
       </c>
       <c r="G66" t="n">
-        <v>8.16753196716309</v>
+        <v>8.1675329208374</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G67" t="n">
-        <v>8.18180370330811</v>
+        <v>8.18180274963379</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G68" t="n">
-        <v>7.95347309112549</v>
+        <v>7.95347356796265</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>8.98999977111816</v>
       </c>
       <c r="G70" t="n">
-        <v>8.55283832550049</v>
+        <v>8.55283737182617</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>8.65499973297119</v>
       </c>
       <c r="G81" t="n">
-        <v>8.23412799835205</v>
+        <v>8.23412895202637</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G83" t="n">
-        <v>8.25791358947754</v>
+        <v>8.25791263580322</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>8.46500015258789</v>
       </c>
       <c r="G85" t="n">
-        <v>8.05336856842041</v>
+        <v>8.05336761474609</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>8.36499977111816</v>
       </c>
       <c r="G86" t="n">
-        <v>7.95823001861572</v>
+        <v>7.95823049545288</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G87" t="n">
-        <v>8.04861164093018</v>
+        <v>8.04861068725586</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G92" t="n">
-        <v>8.05812549591064</v>
+        <v>8.05812454223633</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>8.48999977111816</v>
       </c>
       <c r="G96" t="n">
-        <v>8.07715225219727</v>
+        <v>8.07715129852295</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>8.30500030517578</v>
       </c>
       <c r="G98" t="n">
-        <v>7.90114879608154</v>
+        <v>7.90114784240723</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G99" t="n">
-        <v>7.87736368179321</v>
+        <v>7.87736320495605</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G102" t="n">
-        <v>7.91541862487793</v>
+        <v>7.91541814804077</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G104" t="n">
-        <v>8.27694034576416</v>
+        <v>8.27693939208984</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G114" t="n">
-        <v>7.82028150558472</v>
+        <v>7.82028198242188</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>7.91499996185303</v>
       </c>
       <c r="G115" t="n">
-        <v>7.53011274337769</v>
+        <v>7.53011322021484</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>7.59499979019165</v>
       </c>
       <c r="G117" t="n">
-        <v>7.22567319869995</v>
+        <v>7.22567367553711</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G118" t="n">
-        <v>7.04015636444092</v>
+        <v>7.04015588760376</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>8.27499961853027</v>
       </c>
       <c r="G123" t="n">
-        <v>7.87260675430298</v>
+        <v>7.87260627746582</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>6.67500019073486</v>
       </c>
       <c r="G125" t="n">
-        <v>6.35041093826294</v>
+        <v>6.3504114151001</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>7.44500017166138</v>
       </c>
       <c r="G127" t="n">
-        <v>7.08296775817871</v>
+        <v>7.08296823501587</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G129" t="n">
-        <v>7.04015636444092</v>
+        <v>7.04015588760376</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>6.33500003814697</v>
       </c>
       <c r="G133" t="n">
-        <v>6.02694416046143</v>
+        <v>6.02694463729858</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G135" t="n">
-        <v>6.30759954452515</v>
+        <v>6.30759906768799</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>6.92500019073486</v>
       </c>
       <c r="G136" t="n">
-        <v>6.58825397491455</v>
+        <v>6.58825445175171</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G140" t="n">
-        <v>6.60252523422241</v>
+        <v>6.60252475738525</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>6.86499977111816</v>
       </c>
       <c r="G142" t="n">
-        <v>6.53117179870605</v>
+        <v>6.5311713218689</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>7</v>
       </c>
       <c r="G145" t="n">
-        <v>6.65960693359375</v>
+        <v>6.65960741043091</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>7.46999979019165</v>
       </c>
       <c r="G147" t="n">
-        <v>7.10675191879272</v>
+        <v>7.10675239562988</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>7.63500022888184</v>
       </c>
       <c r="G149" t="n">
-        <v>7.26372909545898</v>
+        <v>7.26372861862183</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>7.44500017166138</v>
       </c>
       <c r="G151" t="n">
-        <v>7.08296775817871</v>
+        <v>7.08296823501587</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G156" t="n">
-        <v>7.24945831298828</v>
+        <v>7.24945783615112</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>7.92999982833862</v>
       </c>
       <c r="G164" t="n">
-        <v>7.54438304901123</v>
+        <v>7.54438352584839</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>8.0649995803833</v>
       </c>
       <c r="G167" t="n">
-        <v>7.67281866073608</v>
+        <v>7.67281818389893</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>8.24499988555908</v>
       </c>
       <c r="G170" t="n">
-        <v>7.84406518936157</v>
+        <v>7.84406566619873</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>8.13500022888184</v>
       </c>
       <c r="G171" t="n">
-        <v>7.73941516876221</v>
+        <v>7.73941469192505</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>8.16499996185303</v>
       </c>
       <c r="G172" t="n">
-        <v>7.7679557800293</v>
+        <v>7.76795625686646</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G173" t="n">
-        <v>7.80125379562378</v>
+        <v>7.80125331878662</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>8.04500007629395</v>
       </c>
       <c r="G176" t="n">
-        <v>7.6537914276123</v>
+        <v>7.65379095077515</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>8.16499996185303</v>
       </c>
       <c r="G177" t="n">
-        <v>7.7679557800293</v>
+        <v>7.76795625686646</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G178" t="n">
-        <v>7.64903402328491</v>
+        <v>7.64903450012207</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>7.88500022888184</v>
       </c>
       <c r="G179" t="n">
-        <v>7.5015721321106</v>
+        <v>7.50157165527344</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>7.53499984741211</v>
       </c>
       <c r="G182" t="n">
-        <v>7.16859149932861</v>
+        <v>7.16859102249146</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>7.28499984741211</v>
       </c>
       <c r="G185" t="n">
-        <v>6.930748462677</v>
+        <v>6.93074798583984</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>7.63500022888184</v>
       </c>
       <c r="G188" t="n">
-        <v>7.26372909545898</v>
+        <v>7.26372861862183</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>7.34499979019165</v>
       </c>
       <c r="G190" t="n">
-        <v>6.98783016204834</v>
+        <v>6.9878306388855</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>7.49499988555908</v>
       </c>
       <c r="G191" t="n">
-        <v>7.1305365562439</v>
+        <v>7.13053607940674</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G193" t="n">
-        <v>7.03064250946045</v>
+        <v>7.03064203262329</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>7.29500007629395</v>
       </c>
       <c r="G196" t="n">
-        <v>6.94026231765747</v>
+        <v>6.94026184082031</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G199" t="n">
-        <v>7.04015636444092</v>
+        <v>7.04015588760376</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G200" t="n">
-        <v>6.86890888214111</v>
+        <v>6.86890840530396</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>6.94500017166138</v>
       </c>
       <c r="G202" t="n">
-        <v>6.60728216171265</v>
+        <v>6.60728168487549</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>7.57499980926514</v>
       </c>
       <c r="G205" t="n">
-        <v>7.20664596557617</v>
+        <v>7.20664644241333</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>7.59499979019165</v>
       </c>
       <c r="G207" t="n">
-        <v>7.22567319869995</v>
+        <v>7.22567367553711</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G208" t="n">
-        <v>7.35410928726196</v>
+        <v>7.3541088104248</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>7.92999982833862</v>
       </c>
       <c r="G209" t="n">
-        <v>7.54438304901123</v>
+        <v>7.54438352584839</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G216" t="n">
-        <v>7.35410928726196</v>
+        <v>7.3541088104248</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>7.70499992370605</v>
       </c>
       <c r="G217" t="n">
-        <v>7.33032464981079</v>
+        <v>7.33032417297363</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>7.45499992370605</v>
       </c>
       <c r="G221" t="n">
-        <v>7.09248161315918</v>
+        <v>7.09248113632202</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G227" t="n">
-        <v>6.67863416671753</v>
+        <v>6.67863464355469</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>6.86499977111816</v>
       </c>
       <c r="G228" t="n">
-        <v>6.53117179870605</v>
+        <v>6.5311713218689</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G232" t="n">
-        <v>6.70717620849609</v>
+        <v>6.70717573165894</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>7.14499998092651</v>
       </c>
       <c r="G233" t="n">
-        <v>6.79755592346191</v>
+        <v>6.79755640029907</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>7</v>
       </c>
       <c r="G239" t="n">
-        <v>6.65960693359375</v>
+        <v>6.65960741043091</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>7.54500007629395</v>
       </c>
       <c r="G241" t="n">
-        <v>7.17810535430908</v>
+        <v>7.17810487747192</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>7.625</v>
       </c>
       <c r="G243" t="n">
-        <v>7.25421524047852</v>
+        <v>7.25421476364136</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>8.06999969482422</v>
       </c>
       <c r="G248" t="n">
-        <v>7.67757558822632</v>
+        <v>7.67757511138916</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G251" t="n">
-        <v>7.99152803421021</v>
+        <v>7.99152851104736</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G254" t="n">
-        <v>8.27694034576416</v>
+        <v>8.27693939208984</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>8.42500019073486</v>
       </c>
       <c r="G255" t="n">
-        <v>8.01531219482422</v>
+        <v>8.01531314849854</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G257" t="n">
-        <v>7.96298694610596</v>
+        <v>7.96298742294312</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G258" t="n">
-        <v>8.16277503967285</v>
+        <v>8.16277599334717</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>8.42500019073486</v>
       </c>
       <c r="G261" t="n">
-        <v>8.01531219482422</v>
+        <v>8.01531314849854</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G263" t="n">
-        <v>7.82028150558472</v>
+        <v>7.82028198242188</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G264" t="n">
-        <v>7.87736368179321</v>
+        <v>7.87736320495605</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G265" t="n">
-        <v>8.04861164093018</v>
+        <v>8.04861068725586</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G266" t="n">
-        <v>7.93444633483887</v>
+        <v>7.93444681167603</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G268" t="n">
-        <v>8.10569381713867</v>
+        <v>8.10569286346436</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>8.375</v>
       </c>
       <c r="G269" t="n">
-        <v>7.96774387359619</v>
+        <v>7.96774482727051</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>8.3100004196167</v>
       </c>
       <c r="G270" t="n">
-        <v>7.90590572357178</v>
+        <v>7.90590524673462</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G271" t="n">
-        <v>7.99152803421021</v>
+        <v>7.99152851104736</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G272" t="n">
-        <v>8.04861164093018</v>
+        <v>8.04861068725586</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G273" t="n">
-        <v>7.99152803421021</v>
+        <v>7.99152851104736</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>8.3100004196167</v>
       </c>
       <c r="G274" t="n">
-        <v>7.90590572357178</v>
+        <v>7.90590524673462</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G275" t="n">
-        <v>7.82979440689087</v>
+        <v>7.82979536056519</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G281" t="n">
-        <v>7.59195232391357</v>
+        <v>7.59195184707642</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G285" t="n">
-        <v>7.79173994064331</v>
+        <v>7.79174041748047</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>8.25</v>
       </c>
       <c r="G286" t="n">
-        <v>7.84882211685181</v>
+        <v>7.84882259368896</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G287" t="n">
-        <v>7.64903402328491</v>
+        <v>7.64903450012207</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>7.97499990463257</v>
       </c>
       <c r="G289" t="n">
-        <v>7.58719539642334</v>
+        <v>7.58719491958618</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>7.91499996185303</v>
       </c>
       <c r="G291" t="n">
-        <v>7.53011274337769</v>
+        <v>7.53011322021484</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G294" t="n">
-        <v>7.3255672454834</v>
+        <v>7.32556772232056</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>7.59499979019165</v>
       </c>
       <c r="G295" t="n">
-        <v>7.22567319869995</v>
+        <v>7.22567367553711</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>7.79500007629395</v>
       </c>
       <c r="G304" t="n">
-        <v>7.41594839096069</v>
+        <v>7.41594791412354</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G305" t="n">
-        <v>7.35410928726196</v>
+        <v>7.3541088104248</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>7.83500003814697</v>
       </c>
       <c r="G306" t="n">
-        <v>7.45400333404541</v>
+        <v>7.45400285720825</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>7.88500022888184</v>
       </c>
       <c r="G310" t="n">
-        <v>7.5015721321106</v>
+        <v>7.50157165527344</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>8.125</v>
       </c>
       <c r="G314" t="n">
-        <v>7.72990083694458</v>
+        <v>7.72990131378174</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G317" t="n">
-        <v>7.93444633483887</v>
+        <v>7.93444681167603</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G319" t="n">
-        <v>8.10569381713867</v>
+        <v>8.10569286346436</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G320" t="n">
-        <v>8.01055526733398</v>
+        <v>8.0105562210083</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>8.45499992370605</v>
       </c>
       <c r="G321" t="n">
-        <v>8.04385471343994</v>
+        <v>8.04385375976562</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>8.13500022888184</v>
       </c>
       <c r="G325" t="n">
-        <v>7.73941516876221</v>
+        <v>7.73941469192505</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G329" t="n">
-        <v>7.64903402328491</v>
+        <v>7.64903450012207</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>8.04500007629395</v>
       </c>
       <c r="G330" t="n">
-        <v>7.6537914276123</v>
+        <v>7.65379095077515</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>7.875</v>
       </c>
       <c r="G335" t="n">
-        <v>7.49205827713013</v>
+        <v>7.49205780029297</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G337" t="n">
-        <v>7.87736368179321</v>
+        <v>7.87736320495605</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G346" t="n">
-        <v>8.50527000427246</v>
+        <v>8.50526905059814</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>9.14500045776367</v>
       </c>
       <c r="G351" t="n">
-        <v>8.70030212402344</v>
+        <v>8.70030117034912</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G358" t="n">
-        <v>8.23888492584229</v>
+        <v>8.2388858795166</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G360" t="n">
-        <v>8.05812549591064</v>
+        <v>8.05812454223633</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>8.3100004196167</v>
       </c>
       <c r="G361" t="n">
-        <v>7.90590572357178</v>
+        <v>7.90590524673462</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G363" t="n">
-        <v>7.93444633483887</v>
+        <v>7.93444681167603</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G367" t="n">
-        <v>7.88687801361084</v>
+        <v>7.88687753677368</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>8.3100004196167</v>
       </c>
       <c r="G368" t="n">
-        <v>7.90590572357178</v>
+        <v>7.90590524673462</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>8.25</v>
       </c>
       <c r="G369" t="n">
-        <v>7.84882211685181</v>
+        <v>7.84882259368896</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>8.27499961853027</v>
       </c>
       <c r="G370" t="n">
-        <v>7.87260675430298</v>
+        <v>7.87260627746582</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G371" t="n">
-        <v>7.91541862487793</v>
+        <v>7.91541814804077</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>8.33500003814697</v>
       </c>
       <c r="G372" t="n">
-        <v>7.92968940734863</v>
+        <v>7.92968988418579</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>8.25</v>
       </c>
       <c r="G373" t="n">
-        <v>7.84882211685181</v>
+        <v>7.84882259368896</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G376" t="n">
-        <v>7.88687801361084</v>
+        <v>7.88687753677368</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G377" t="n">
-        <v>7.91541862487793</v>
+        <v>7.91541814804077</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G378" t="n">
-        <v>7.82979440689087</v>
+        <v>7.82979536056519</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>8.0649995803833</v>
       </c>
       <c r="G381" t="n">
-        <v>7.67281866073608</v>
+        <v>7.67281818389893</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G385" t="n">
-        <v>7.82979440689087</v>
+        <v>7.82979536056519</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G387" t="n">
-        <v>7.63000726699829</v>
+        <v>7.63000774383545</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>8.04500007629395</v>
       </c>
       <c r="G388" t="n">
-        <v>7.6537914276123</v>
+        <v>7.65379095077515</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>7.88500022888184</v>
       </c>
       <c r="G391" t="n">
-        <v>7.5015721321106</v>
+        <v>7.50157165527344</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G393" t="n">
-        <v>7.86785078048706</v>
+        <v>7.8678503036499</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>8.04500007629395</v>
       </c>
       <c r="G394" t="n">
-        <v>7.6537914276123</v>
+        <v>7.65379095077515</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>8.125</v>
       </c>
       <c r="G399" t="n">
-        <v>7.72990083694458</v>
+        <v>7.72990131378174</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G403" t="n">
-        <v>8.23888492584229</v>
+        <v>8.2388858795166</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>8.70499992370605</v>
       </c>
       <c r="G405" t="n">
-        <v>8.28169727325439</v>
+        <v>8.28169631958008</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>8.70499992370605</v>
       </c>
       <c r="G408" t="n">
-        <v>8.28169727325439</v>
+        <v>8.28169631958008</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G415" t="n">
-        <v>8.05812549591064</v>
+        <v>8.05812454223633</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>8.33500003814697</v>
       </c>
       <c r="G418" t="n">
-        <v>7.92968940734863</v>
+        <v>7.92968988418579</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>8.27499961853027</v>
       </c>
       <c r="G419" t="n">
-        <v>7.87260675430298</v>
+        <v>7.87260627746582</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>8.04500007629395</v>
       </c>
       <c r="G427" t="n">
-        <v>7.6537914276123</v>
+        <v>7.65379095077515</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>7.83500003814697</v>
       </c>
       <c r="G429" t="n">
-        <v>7.45400333404541</v>
+        <v>7.45400285720825</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>7.88500022888184</v>
       </c>
       <c r="G435" t="n">
-        <v>7.5015721321106</v>
+        <v>7.50157165527344</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>8.02499961853027</v>
       </c>
       <c r="G440" t="n">
-        <v>7.63476324081421</v>
+        <v>7.63476371765137</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G442" t="n">
-        <v>7.57292509078979</v>
+        <v>7.57292461395264</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>7.93499994277954</v>
       </c>
       <c r="G445" t="n">
-        <v>7.54913997650146</v>
+        <v>7.54914045333862</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G447" t="n">
-        <v>7.59195232391357</v>
+        <v>7.59195184707642</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>7.63500022888184</v>
       </c>
       <c r="G454" t="n">
-        <v>7.26372909545898</v>
+        <v>7.26372861862183</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>7.54500007629395</v>
       </c>
       <c r="G455" t="n">
-        <v>7.17810535430908</v>
+        <v>7.17810487747192</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>7.625</v>
       </c>
       <c r="G459" t="n">
-        <v>7.25421524047852</v>
+        <v>7.25421476364136</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>7.68499994277954</v>
       </c>
       <c r="G463" t="n">
-        <v>7.31129693984985</v>
+        <v>7.31129741668701</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>7.63500022888184</v>
       </c>
       <c r="G472" t="n">
-        <v>7.26372909545898</v>
+        <v>7.26372861862183</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>7.35500001907349</v>
       </c>
       <c r="G476" t="n">
-        <v>6.99734401702881</v>
+        <v>6.99734449386597</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>6.89499998092651</v>
       </c>
       <c r="G479" t="n">
-        <v>6.5597128868103</v>
+        <v>6.55971336364746</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>6.81500005722046</v>
       </c>
       <c r="G481" t="n">
-        <v>6.48360300064087</v>
+        <v>6.48360347747803</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>6.89499998092651</v>
       </c>
       <c r="G482" t="n">
-        <v>6.5597128868103</v>
+        <v>6.55971336364746</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>7.04500007629395</v>
       </c>
       <c r="G490" t="n">
-        <v>6.70241928100586</v>
+        <v>6.7024188041687</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G494" t="n">
-        <v>6.7166895866394</v>
+        <v>6.71668910980225</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>7.46999979019165</v>
       </c>
       <c r="G497" t="n">
-        <v>7.10675191879272</v>
+        <v>7.10675239562988</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>7.54500007629395</v>
       </c>
       <c r="G498" t="n">
-        <v>7.17810535430908</v>
+        <v>7.17810487747192</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>7.2649998664856</v>
       </c>
       <c r="G502" t="n">
-        <v>6.91172027587891</v>
+        <v>6.91172075271606</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>7.34499979019165</v>
       </c>
       <c r="G504" t="n">
-        <v>6.98783016204834</v>
+        <v>6.9878306388855</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G505" t="n">
-        <v>7.04015636444092</v>
+        <v>7.04015588760376</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>7.34499979019165</v>
       </c>
       <c r="G507" t="n">
-        <v>6.98783016204834</v>
+        <v>6.9878306388855</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G508" t="n">
-        <v>7.02112865447998</v>
+        <v>7.02112913131714</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>7.29500007629395</v>
       </c>
       <c r="G510" t="n">
-        <v>6.94026231765747</v>
+        <v>6.94026184082031</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>7.20499992370605</v>
       </c>
       <c r="G511" t="n">
-        <v>6.85463857650757</v>
+        <v>6.85463809967041</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>7.25500011444092</v>
       </c>
       <c r="G512" t="n">
-        <v>6.9022068977356</v>
+        <v>6.90220737457275</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>7.25</v>
       </c>
       <c r="G513" t="n">
-        <v>6.89744997024536</v>
+        <v>6.89745044708252</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G514" t="n">
-        <v>6.98307371139526</v>
+        <v>6.98307418823242</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>7.38500022888184</v>
       </c>
       <c r="G515" t="n">
-        <v>7.02588605880737</v>
+        <v>7.02588558197021</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>7.43499994277954</v>
       </c>
       <c r="G520" t="n">
-        <v>7.07345390319824</v>
+        <v>7.0734543800354</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>7.38500022888184</v>
       </c>
       <c r="G521" t="n">
-        <v>7.02588605880737</v>
+        <v>7.02588558197021</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>7.20499992370605</v>
       </c>
       <c r="G530" t="n">
-        <v>6.85463857650757</v>
+        <v>6.85463809967041</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>7.21199989318848</v>
       </c>
       <c r="G538" t="n">
-        <v>6.86129760742188</v>
+        <v>6.86129808425903</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>6.98799991607666</v>
       </c>
       <c r="G540" t="n">
-        <v>6.64819097518921</v>
+        <v>6.64819049835205</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G543" t="n">
-        <v>6.54544258117676</v>
+        <v>6.5454421043396</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>7.19600009918213</v>
       </c>
       <c r="G548" t="n">
-        <v>6.84607601165771</v>
+        <v>6.84607648849487</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G551" t="n">
-        <v>7.02112865447998</v>
+        <v>7.02112913131714</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G553" t="n">
-        <v>7.04015636444092</v>
+        <v>7.04015588760376</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>7.39799976348877</v>
       </c>
       <c r="G554" t="n">
-        <v>7.03825283050537</v>
+        <v>7.03825330734253</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>7.24599981307983</v>
       </c>
       <c r="G555" t="n">
-        <v>6.8936448097229</v>
+        <v>6.89364433288574</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>7.28800010681152</v>
       </c>
       <c r="G556" t="n">
-        <v>6.93360233306885</v>
+        <v>6.93360280990601</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G559" t="n">
-        <v>7.82979440689087</v>
+        <v>7.82979536056519</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G560" t="n">
-        <v>7.91541862487793</v>
+        <v>7.91541814804077</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>8.20199966430664</v>
       </c>
       <c r="G561" t="n">
-        <v>7.80315637588501</v>
+        <v>7.80315589904785</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>8.00800037384033</v>
       </c>
       <c r="G562" t="n">
-        <v>7.61859083175659</v>
+        <v>7.61859130859375</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>7.83199977874756</v>
       </c>
       <c r="G563" t="n">
-        <v>7.45114898681641</v>
+        <v>7.45114850997925</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>8.08800029754639</v>
       </c>
       <c r="G565" t="n">
-        <v>7.69470024108887</v>
+        <v>7.69470071792603</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>8.11600017547607</v>
       </c>
       <c r="G566" t="n">
-        <v>7.72133874893188</v>
+        <v>7.72133922576904</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>7.72599983215332</v>
       </c>
       <c r="G570" t="n">
-        <v>7.35030364990234</v>
+        <v>7.35030317306519</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>7.61399984359741</v>
       </c>
       <c r="G572" t="n">
-        <v>7.24374961853027</v>
+        <v>7.24375009536743</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>7.58199977874756</v>
       </c>
       <c r="G576" t="n">
-        <v>7.21330595016479</v>
+        <v>7.21330547332764</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>8.61200046539307</v>
       </c>
       <c r="G582" t="n">
-        <v>8.19321918487549</v>
+        <v>8.1932201385498</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>8.38199996948242</v>
       </c>
       <c r="G585" t="n">
-        <v>7.97440385818481</v>
+        <v>7.97440338134766</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>8.76200008392334</v>
       </c>
       <c r="G588" t="n">
-        <v>8.33592510223389</v>
+        <v>8.3359260559082</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G589" t="n">
-        <v>8.27694034576416</v>
+        <v>8.27693939208984</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>8.26200008392334</v>
       </c>
       <c r="G591" t="n">
-        <v>7.86023902893066</v>
+        <v>7.86023950576782</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G596" t="n">
-        <v>7.96298694610596</v>
+        <v>7.96298742294312</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G599" t="n">
-        <v>8.01055526733398</v>
+        <v>8.0105562210083</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G600" t="n">
-        <v>7.88687801361084</v>
+        <v>7.88687753677368</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G605" t="n">
-        <v>7.35410928726196</v>
+        <v>7.3541088104248</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G606" t="n">
-        <v>7.30654001235962</v>
+        <v>7.30654048919678</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G609" t="n">
-        <v>7.02112865447998</v>
+        <v>7.02112913131714</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>7.31199979782104</v>
       </c>
       <c r="G610" t="n">
-        <v>6.95643520355225</v>
+        <v>6.95643472671509</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>7.30999994277954</v>
       </c>
       <c r="G611" t="n">
-        <v>6.95453262329102</v>
+        <v>6.95453214645386</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>7.14400005340576</v>
       </c>
       <c r="G613" t="n">
-        <v>6.7966046333313</v>
+        <v>6.79660511016846</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>7.01599979400635</v>
       </c>
       <c r="G615" t="n">
-        <v>6.67482852935791</v>
+        <v>6.67482900619507</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>6.87200021743774</v>
       </c>
       <c r="G616" t="n">
-        <v>6.53783130645752</v>
+        <v>6.53783178329468</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>6.98600006103516</v>
       </c>
       <c r="G618" t="n">
-        <v>6.64628791809082</v>
+        <v>6.64628839492798</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>6.91599988937378</v>
       </c>
       <c r="G620" t="n">
-        <v>6.57969188690186</v>
+        <v>6.5796914100647</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>6.72200012207031</v>
       </c>
       <c r="G622" t="n">
-        <v>6.39512586593628</v>
+        <v>6.39512538909912</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>6.87200021743774</v>
       </c>
       <c r="G623" t="n">
-        <v>6.53783130645752</v>
+        <v>6.53783178329468</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>6.85799980163574</v>
       </c>
       <c r="G624" t="n">
-        <v>6.52451181411743</v>
+        <v>6.52451229095459</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>6.7519998550415</v>
       </c>
       <c r="G627" t="n">
-        <v>6.42366647720337</v>
+        <v>6.42366695404053</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>6.76599979400635</v>
       </c>
       <c r="G628" t="n">
-        <v>6.4369854927063</v>
+        <v>6.43698596954346</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G631" t="n">
-        <v>6.33614015579224</v>
+        <v>6.33614063262939</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>6.45599985122681</v>
       </c>
       <c r="G635" t="n">
-        <v>6.14206075668335</v>
+        <v>6.14206027984619</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>6.37400007247925</v>
       </c>
       <c r="G637" t="n">
-        <v>6.06404781341553</v>
+        <v>6.06404829025269</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>6.28200006484985</v>
       </c>
       <c r="G638" t="n">
-        <v>5.97652149200439</v>
+        <v>5.97652196884155</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>6.52400016784668</v>
       </c>
       <c r="G640" t="n">
-        <v>6.20675420761108</v>
+        <v>6.20675373077393</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>6.55200004577637</v>
       </c>
       <c r="G642" t="n">
-        <v>6.2333927154541</v>
+        <v>6.23339223861694</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>6.36600017547607</v>
       </c>
       <c r="G644" t="n">
-        <v>6.05643749237061</v>
+        <v>6.05643701553345</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G645" t="n">
-        <v>6.01267385482788</v>
+        <v>6.01267433166504</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>6.14599990844727</v>
       </c>
       <c r="G646" t="n">
-        <v>5.84713506698608</v>
+        <v>5.84713459014893</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>6.07399988174438</v>
       </c>
       <c r="G648" t="n">
-        <v>5.77863645553589</v>
+        <v>5.77863597869873</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G658" t="n">
-        <v>6.2790584564209</v>
+        <v>6.27905797958374</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>6.50400018692017</v>
       </c>
       <c r="G660" t="n">
-        <v>6.1877269744873</v>
+        <v>6.18772649765015</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>6.38199996948242</v>
       </c>
       <c r="G661" t="n">
-        <v>6.07165908813477</v>
+        <v>6.07165861129761</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>6</v>
       </c>
       <c r="G675" t="n">
-        <v>5.70823431015015</v>
+        <v>5.7082347869873</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>5.98799991607666</v>
       </c>
       <c r="G676" t="n">
-        <v>5.69681835174561</v>
+        <v>5.69681787490845</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>6.0019998550415</v>
       </c>
       <c r="G677" t="n">
-        <v>5.71013736724854</v>
+        <v>5.71013689041138</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>5.93800020217896</v>
       </c>
       <c r="G678" t="n">
-        <v>5.64924955368042</v>
+        <v>5.64925003051758</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G681" t="n">
-        <v>5.22303485870361</v>
+        <v>5.22303438186646</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G682" t="n">
-        <v>5.28011703491211</v>
+        <v>5.28011751174927</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>5.25</v>
       </c>
       <c r="G683" t="n">
-        <v>4.99470567703247</v>
+        <v>4.99470520019531</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>5.4060001373291</v>
       </c>
       <c r="G689" t="n">
-        <v>5.14311933517456</v>
+        <v>5.14311981201172</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>5.71400022506714</v>
       </c>
       <c r="G693" t="n">
-        <v>5.4361424446106</v>
+        <v>5.43614196777344</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>5.68599987030029</v>
       </c>
       <c r="G695" t="n">
-        <v>5.40950393676758</v>
+        <v>5.40950345993042</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>5.68599987030029</v>
       </c>
       <c r="G696" t="n">
-        <v>5.40950393676758</v>
+        <v>5.40950345993042</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>5.60599994659424</v>
       </c>
       <c r="G697" t="n">
-        <v>5.33339405059814</v>
+        <v>5.33339357376099</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G698" t="n">
-        <v>5.30865859985352</v>
+        <v>5.30865812301636</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>4.95300006866455</v>
       </c>
       <c r="G702" t="n">
-        <v>4.71214818954468</v>
+        <v>4.71214771270752</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>4.95699977874756</v>
       </c>
       <c r="G705" t="n">
-        <v>4.71595287322998</v>
+        <v>4.71595335006714</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>5.03200006484985</v>
       </c>
       <c r="G709" t="n">
-        <v>4.78730630874634</v>
+        <v>4.78730583190918</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G710" t="n">
-        <v>4.77588987350464</v>
+        <v>4.77588939666748</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>4.98600006103516</v>
       </c>
       <c r="G716" t="n">
-        <v>4.74354267120361</v>
+        <v>4.74354314804077</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>5.19199991226196</v>
       </c>
       <c r="G724" t="n">
-        <v>4.93952560424805</v>
+        <v>4.93952608108521</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>5.35400009155273</v>
       </c>
       <c r="G727" t="n">
-        <v>5.09364795684814</v>
+        <v>5.0936484336853</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G729" t="n">
-        <v>5.08984231948853</v>
+        <v>5.08984279632568</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G731" t="n">
-        <v>4.90908193588257</v>
+        <v>4.90908145904541</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>5.30399990081787</v>
       </c>
       <c r="G732" t="n">
-        <v>5.04607963562012</v>
+        <v>5.04607915878296</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G734" t="n">
-        <v>4.9566502571106</v>
+        <v>4.95665073394775</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>5.16400003433228</v>
       </c>
       <c r="G735" t="n">
-        <v>4.91288757324219</v>
+        <v>4.91288709640503</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>5.26200008392334</v>
       </c>
       <c r="G736" t="n">
-        <v>5.00612163543701</v>
+        <v>5.00612211227417</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>5.74599981307983</v>
       </c>
       <c r="G747" t="n">
-        <v>5.46658563613892</v>
+        <v>5.46658611297607</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>5.69199991226196</v>
       </c>
       <c r="G748" t="n">
-        <v>5.41521167755127</v>
+        <v>5.41521215438843</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G754" t="n">
-        <v>5.42282295227051</v>
+        <v>5.42282247543335</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>5.4520001411438</v>
       </c>
       <c r="G759" t="n">
-        <v>5.18688297271729</v>
+        <v>5.18688249588013</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>5.2020001411438</v>
       </c>
       <c r="G760" t="n">
-        <v>4.94903993606567</v>
+        <v>4.94903945922852</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G762" t="n">
-        <v>4.58561563491821</v>
+        <v>4.58561515808105</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>4.83300018310547</v>
       </c>
       <c r="G763" t="n">
-        <v>4.59798288345337</v>
+        <v>4.59798336029053</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>5.06199979782104</v>
       </c>
       <c r="G768" t="n">
-        <v>4.81584692001343</v>
+        <v>4.81584739685059</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>4.95900011062622</v>
       </c>
       <c r="G769" t="n">
-        <v>4.71785593032837</v>
+        <v>4.71785640716553</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>5.00600004196167</v>
       </c>
       <c r="G771" t="n">
-        <v>4.76257085800171</v>
+        <v>4.76257038116455</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>5.01599979400635</v>
       </c>
       <c r="G772" t="n">
-        <v>4.77208423614502</v>
+        <v>4.77208375930786</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>5.02400016784668</v>
       </c>
       <c r="G773" t="n">
-        <v>4.7796950340271</v>
+        <v>4.77969551086426</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>4.88500022888184</v>
       </c>
       <c r="G776" t="n">
-        <v>4.64745426177979</v>
+        <v>4.64745473861694</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>4.48400020599365</v>
       </c>
       <c r="G779" t="n">
-        <v>4.26595449447632</v>
+        <v>4.26595401763916</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>4.52899980545044</v>
       </c>
       <c r="G780" t="n">
-        <v>4.30876541137695</v>
+        <v>4.30876588821411</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>4.58199977874756</v>
       </c>
       <c r="G783" t="n">
-        <v>4.35918807983398</v>
+        <v>4.35918855667114</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G784" t="n">
-        <v>4.40485429763794</v>
+        <v>4.4048547744751</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>5.02400016784668</v>
       </c>
       <c r="G788" t="n">
-        <v>4.7796950340271</v>
+        <v>4.77969551086426</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G791" t="n">
-        <v>4.49047756195068</v>
+        <v>4.49047803878784</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>4.81599998474121</v>
       </c>
       <c r="G793" t="n">
-        <v>4.58180952072144</v>
+        <v>4.58180999755859</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>4.8270001411438</v>
       </c>
       <c r="G795" t="n">
-        <v>4.59227466583252</v>
+        <v>4.59227514266968</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G797" t="n">
-        <v>5.0422739982605</v>
+        <v>5.04227447509766</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G802" t="n">
-        <v>5.09935665130615</v>
+        <v>5.09935617446899</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>5.32200002670288</v>
       </c>
       <c r="G806" t="n">
-        <v>5.06320428848267</v>
+        <v>5.06320381164551</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>5.5</v>
       </c>
       <c r="G808" t="n">
-        <v>5.23254871368408</v>
+        <v>5.23254823684692</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>5.64799976348877</v>
       </c>
       <c r="G809" t="n">
-        <v>5.37335157394409</v>
+        <v>5.37335109710693</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G810" t="n">
-        <v>5.33719968795776</v>
+        <v>5.33719921112061</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>5.35599994659424</v>
       </c>
       <c r="G818" t="n">
-        <v>5.09555101394653</v>
+        <v>5.09555053710938</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G820" t="n">
-        <v>5.0422739982605</v>
+        <v>5.04227447509766</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>5.25799989700317</v>
       </c>
       <c r="G821" t="n">
-        <v>5.00231599807739</v>
+        <v>5.00231647491455</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>5.31599998474121</v>
       </c>
       <c r="G823" t="n">
-        <v>5.05749559402466</v>
+        <v>5.05749607086182</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>5.35599994659424</v>
       </c>
       <c r="G824" t="n">
-        <v>5.09555101394653</v>
+        <v>5.09555053710938</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G825" t="n">
-        <v>5.14692497253418</v>
+        <v>5.14692449569702</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G828" t="n">
-        <v>5.08984231948853</v>
+        <v>5.08984279632568</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>5.40199995040894</v>
       </c>
       <c r="G829" t="n">
-        <v>5.13931369781494</v>
+        <v>5.1393141746521</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>5.36800003051758</v>
       </c>
       <c r="G831" t="n">
-        <v>5.10696697235107</v>
+        <v>5.10696744918823</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>5.33599996566772</v>
       </c>
       <c r="G832" t="n">
-        <v>5.0765233039856</v>
+        <v>5.07652378082275</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>5.34899997711182</v>
       </c>
       <c r="G833" t="n">
-        <v>5.08889102935791</v>
+        <v>5.08889150619507</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>5.25500011444092</v>
       </c>
       <c r="G838" t="n">
-        <v>4.99946260452271</v>
+        <v>4.99946212768555</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>4.98600006103516</v>
       </c>
       <c r="G846" t="n">
-        <v>4.74354267120361</v>
+        <v>4.74354314804077</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>4.95900011062622</v>
       </c>
       <c r="G847" t="n">
-        <v>4.71785593032837</v>
+        <v>4.71785640716553</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>4.67199993133545</v>
       </c>
       <c r="G853" t="n">
-        <v>4.44481182098389</v>
+        <v>4.44481229782104</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>4.45800018310547</v>
       </c>
       <c r="G856" t="n">
-        <v>4.24121856689453</v>
+        <v>4.24121809005737</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>4.57800006866455</v>
       </c>
       <c r="G859" t="n">
-        <v>4.35538291931152</v>
+        <v>4.35538339614868</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>4.38100004196167</v>
       </c>
       <c r="G863" t="n">
-        <v>4.16796255111694</v>
+        <v>4.1679630279541</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G870" t="n">
-        <v>4.32398748397827</v>
+        <v>4.32398796081543</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>4.63100004196167</v>
       </c>
       <c r="G877" t="n">
-        <v>4.40580558776855</v>
+        <v>4.40580606460571</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>4.84200000762939</v>
       </c>
       <c r="G882" t="n">
-        <v>4.60654497146606</v>
+        <v>4.60654544830322</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>5.00899982452393</v>
       </c>
       <c r="G883" t="n">
-        <v>4.7654242515564</v>
+        <v>4.76542472839355</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>4.82800006866455</v>
       </c>
       <c r="G889" t="n">
-        <v>4.59322595596313</v>
+        <v>4.59322643280029</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>4.78299999237061</v>
       </c>
       <c r="G890" t="n">
-        <v>4.55041456222534</v>
+        <v>4.55041408538818</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>4.92199993133545</v>
       </c>
       <c r="G891" t="n">
-        <v>4.6826548576355</v>
+        <v>4.68265533447266</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>4.96299982070923</v>
       </c>
       <c r="G893" t="n">
-        <v>4.72166156768799</v>
+        <v>4.72166109085083</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>5.01300001144409</v>
       </c>
       <c r="G898" t="n">
-        <v>4.76922988891602</v>
+        <v>4.76923036575317</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>5.06099987030029</v>
       </c>
       <c r="G902" t="n">
-        <v>4.81489562988281</v>
+        <v>4.81489610671997</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>4.91099977493286</v>
       </c>
       <c r="G903" t="n">
-        <v>4.67219018936157</v>
+        <v>4.67218971252441</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>4.95699977874756</v>
       </c>
       <c r="G905" t="n">
-        <v>4.71595287322998</v>
+        <v>4.71595335006714</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G909" t="n">
-        <v>4.985191822052</v>
+        <v>4.98519134521484</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>5.10599994659424</v>
       </c>
       <c r="G911" t="n">
-        <v>4.85770797729492</v>
+        <v>4.85770750045776</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>4.99599981307983</v>
       </c>
       <c r="G913" t="n">
-        <v>4.75305700302124</v>
+        <v>4.75305652618408</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>4.83400011062622</v>
       </c>
       <c r="G915" t="n">
-        <v>4.59893465042114</v>
+        <v>4.59893417358398</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>4.81599998474121</v>
       </c>
       <c r="G916" t="n">
-        <v>4.58180952072144</v>
+        <v>4.58180999755859</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>4.88800001144409</v>
       </c>
       <c r="G917" t="n">
-        <v>4.65030860900879</v>
+        <v>4.65030813217163</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>4.60200023651123</v>
       </c>
       <c r="G918" t="n">
-        <v>4.37821626663208</v>
+        <v>4.37821578979492</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>4.56500005722046</v>
       </c>
       <c r="G923" t="n">
-        <v>4.34301567077637</v>
+        <v>4.34301519393921</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>4.47200012207031</v>
       </c>
       <c r="G924" t="n">
-        <v>4.25453758239746</v>
+        <v>4.25453805923462</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>4.59800004959106</v>
       </c>
       <c r="G926" t="n">
-        <v>4.3744101524353</v>
+        <v>4.37441062927246</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>4.52600002288818</v>
       </c>
       <c r="G927" t="n">
-        <v>4.30591154098511</v>
+        <v>4.30591201782227</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>4.92600011825562</v>
       </c>
       <c r="G935" t="n">
-        <v>4.68646097183228</v>
+        <v>4.68646049499512</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>4.91800022125244</v>
       </c>
       <c r="G936" t="n">
-        <v>4.67884969711304</v>
+        <v>4.6788501739502</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G942" t="n">
-        <v>4.9566502571106</v>
+        <v>4.95665073394775</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>5.16699981689453</v>
       </c>
       <c r="G943" t="n">
-        <v>4.91574096679688</v>
+        <v>4.91574144363403</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G946" t="n">
-        <v>4.985191822052</v>
+        <v>4.98519134521484</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>5.19700002670288</v>
       </c>
       <c r="G952" t="n">
-        <v>4.94428300857544</v>
+        <v>4.94428253173828</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>4.94199991226196</v>
       </c>
       <c r="G955" t="n">
-        <v>4.70168256759644</v>
+        <v>4.70168209075928</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>4.96799993515015</v>
       </c>
       <c r="G956" t="n">
-        <v>4.72641849517822</v>
+        <v>4.72641801834106</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>4.97599983215332</v>
       </c>
       <c r="G957" t="n">
-        <v>4.73402881622314</v>
+        <v>4.7340292930603</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>5.06599998474121</v>
       </c>
       <c r="G959" t="n">
-        <v>4.81965255737305</v>
+        <v>4.81965303421021</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G962" t="n">
-        <v>5.09935665130615</v>
+        <v>5.09935617446899</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>5.39400005340576</v>
       </c>
       <c r="G965" t="n">
-        <v>5.13170337677002</v>
+        <v>5.13170289993286</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>5.35400009155273</v>
       </c>
       <c r="G967" t="n">
-        <v>5.09364795684814</v>
+        <v>5.0936484336853</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G971" t="n">
-        <v>5.06130170822144</v>
+        <v>5.06130123138428</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G974" t="n">
-        <v>5.05178737640381</v>
+        <v>5.05178785324097</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>5.36299991607666</v>
       </c>
       <c r="G984" t="n">
-        <v>5.10221004486084</v>
+        <v>5.102210521698</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G985" t="n">
-        <v>5.09935665130615</v>
+        <v>5.09935617446899</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>5.41300010681152</v>
       </c>
       <c r="G986" t="n">
-        <v>5.14977931976318</v>
+        <v>5.14977884292603</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>5.44099998474121</v>
       </c>
       <c r="G987" t="n">
-        <v>5.17641735076904</v>
+        <v>5.1764178276062</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>5.51800012588501</v>
       </c>
       <c r="G989" t="n">
-        <v>5.24967336654663</v>
+        <v>5.24967288970947</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>5.65100002288818</v>
       </c>
       <c r="G990" t="n">
-        <v>5.37620544433594</v>
+        <v>5.3762059211731</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>5.83900022506714</v>
       </c>
       <c r="G993" t="n">
-        <v>5.55506420135498</v>
+        <v>5.55506372451782</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>5.73899984359741</v>
       </c>
       <c r="G995" t="n">
-        <v>5.45992660522461</v>
+        <v>5.45992612838745</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>5.68599987030029</v>
       </c>
       <c r="G996" t="n">
-        <v>5.40950393676758</v>
+        <v>5.40950345993042</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>5.51200008392334</v>
       </c>
       <c r="G999" t="n">
-        <v>5.24396467208862</v>
+        <v>5.24396514892578</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>5.54199981689453</v>
       </c>
       <c r="G1008" t="n">
-        <v>5.27250623703003</v>
+        <v>5.27250576019287</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1009" t="n">
-        <v>5.28963041305542</v>
+        <v>5.28963088989258</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>5.59499979019165</v>
       </c>
       <c r="G1010" t="n">
-        <v>5.32292890548706</v>
+        <v>5.3229284286499</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>5.59499979019165</v>
       </c>
       <c r="G1011" t="n">
-        <v>5.32292890548706</v>
+        <v>5.3229284286499</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>5.59499979019165</v>
       </c>
       <c r="G1016" t="n">
-        <v>5.32292890548706</v>
+        <v>5.3229284286499</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>5.26300001144409</v>
       </c>
       <c r="G1021" t="n">
-        <v>5.00707292556763</v>
+        <v>5.00707340240479</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1024" t="n">
-        <v>4.89956855773926</v>
+        <v>4.8995680809021</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>5.05900001525879</v>
       </c>
       <c r="G1025" t="n">
-        <v>4.81299352645874</v>
+        <v>4.81299304962158</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>5.1230001449585</v>
       </c>
       <c r="G1027" t="n">
-        <v>4.87388134002686</v>
+        <v>4.8738808631897</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>5.11399984359741</v>
       </c>
       <c r="G1028" t="n">
-        <v>4.86531829833984</v>
+        <v>4.865318775177</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>5.06599998474121</v>
       </c>
       <c r="G1029" t="n">
-        <v>4.81965255737305</v>
+        <v>4.81965303421021</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>4.94199991226196</v>
       </c>
       <c r="G1031" t="n">
-        <v>4.70168256759644</v>
+        <v>4.70168209075928</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>5.05399990081787</v>
       </c>
       <c r="G1036" t="n">
-        <v>4.80823659896851</v>
+        <v>4.80823612213135</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1038" t="n">
-        <v>4.58561563491821</v>
+        <v>4.58561515808105</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>4.91800022125244</v>
       </c>
       <c r="G1039" t="n">
-        <v>4.67884969711304</v>
+        <v>4.6788501739502</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1041" t="n">
-        <v>4.77588987350464</v>
+        <v>4.77588939666748</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>4.94799995422363</v>
       </c>
       <c r="G1042" t="n">
-        <v>4.70739126205444</v>
+        <v>4.70739078521729</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>5.25</v>
       </c>
       <c r="G1046" t="n">
-        <v>4.99470567703247</v>
+        <v>4.99470520019531</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>5.00099992752075</v>
       </c>
       <c r="G1057" t="n">
-        <v>4.75781393051147</v>
+        <v>4.75781345367432</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>4.77899980545044</v>
       </c>
       <c r="G1059" t="n">
-        <v>4.54660844802856</v>
+        <v>4.54660892486572</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>4.32100009918213</v>
       </c>
       <c r="G1062" t="n">
-        <v>4.11088085174561</v>
+        <v>4.11088037490845</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>3.67199993133545</v>
       </c>
       <c r="G1064" t="n">
-        <v>3.49343943595886</v>
+        <v>3.49343967437744</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>3.81699991226196</v>
       </c>
       <c r="G1065" t="n">
-        <v>3.63138866424561</v>
+        <v>3.63138842582703</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>3.7739999294281</v>
       </c>
       <c r="G1071" t="n">
-        <v>3.59047961235046</v>
+        <v>3.59047937393188</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>3.79299998283386</v>
       </c>
       <c r="G1081" t="n">
-        <v>3.60855579376221</v>
+        <v>3.60855555534363</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>3.92400002479553</v>
       </c>
       <c r="G1083" t="n">
-        <v>3.73318552970886</v>
+        <v>3.73318529129028</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G1085" t="n">
-        <v>3.61045837402344</v>
+        <v>3.61045861244202</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>3.53399991989136</v>
       </c>
       <c r="G1088" t="n">
-        <v>3.36214995384216</v>
+        <v>3.36215019226074</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>3.44600009918213</v>
       </c>
       <c r="G1097" t="n">
-        <v>3.27842974662781</v>
+        <v>3.27842950820923</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>3.64400005340576</v>
       </c>
       <c r="G1098" t="n">
-        <v>3.46680116653442</v>
+        <v>3.466801404953</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>3.6159999370575</v>
       </c>
       <c r="G1099" t="n">
-        <v>3.44016289710999</v>
+        <v>3.44016265869141</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>3.53399991989136</v>
       </c>
       <c r="G1101" t="n">
-        <v>3.36214995384216</v>
+        <v>3.36215019226074</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>3.50399994850159</v>
       </c>
       <c r="G1102" t="n">
-        <v>3.33360910415649</v>
+        <v>3.33360886573792</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>3.42799997329712</v>
       </c>
       <c r="G1103" t="n">
-        <v>3.2613046169281</v>
+        <v>3.26130485534668</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1104" t="n">
-        <v>3.29174852371216</v>
+        <v>3.29174876213074</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>3.20700001716614</v>
       </c>
       <c r="G1114" t="n">
-        <v>3.0510516166687</v>
+        <v>3.05105137825012</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>3.30399990081787</v>
       </c>
       <c r="G1116" t="n">
-        <v>3.14333438873291</v>
+        <v>3.14333462715149</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>3.3050000667572</v>
       </c>
       <c r="G1117" t="n">
-        <v>3.14428615570068</v>
+        <v>3.1442859172821</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>3.41400003433228</v>
       </c>
       <c r="G1120" t="n">
-        <v>3.24798560142517</v>
+        <v>3.24798536300659</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>3.52300000190735</v>
       </c>
       <c r="G1121" t="n">
-        <v>3.35168528556824</v>
+        <v>3.35168504714966</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>3.71600008010864</v>
       </c>
       <c r="G1127" t="n">
-        <v>3.5353000164032</v>
+        <v>3.53530025482178</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>3.53399991989136</v>
       </c>
       <c r="G1129" t="n">
-        <v>3.36214995384216</v>
+        <v>3.36215019226074</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1133" t="n">
-        <v>3.49153685569763</v>
+        <v>3.49153709411621</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -71300,6 +71300,32 @@
         <v>7.44099998474121</v>
       </c>
       <c r="H2728" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2729">
+      <c r="A2729" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B2729" t="n">
+        <v>8379207</v>
+      </c>
+      <c r="C2729" t="n">
+        <v>7.53299999237061</v>
+      </c>
+      <c r="D2729" t="n">
+        <v>7.15299987792969</v>
+      </c>
+      <c r="E2729" t="n">
+        <v>7.51999998092651</v>
+      </c>
+      <c r="F2729" t="n">
+        <v>7.24100017547607</v>
+      </c>
+      <c r="G2729" t="n">
+        <v>7.24100017547607</v>
+      </c>
+      <c r="H2729" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/TIT.MI.xlsx
+++ b/data/TIT.MI.xlsx
@@ -71381,6 +71381,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2732">
+      <c r="A2732" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B2732" t="n">
+        <v>120682136</v>
+      </c>
+      <c r="C2732" t="n">
+        <v>6.96999979019165</v>
+      </c>
+      <c r="D2732" t="n">
+        <v>6.67799997329712</v>
+      </c>
+      <c r="E2732" t="n">
+        <v>6.85500001907349</v>
+      </c>
+      <c r="F2732" t="n">
+        <v>6.67799997329712</v>
+      </c>
+      <c r="G2732" t="n">
+        <v>6.67799997329712</v>
+      </c>
+      <c r="H2732" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TIT.MI.xlsx
+++ b/data/TIT.MI.xlsx
@@ -63270,8 +63270,31 @@
       <c r="E2735" t="n">
         <v>6.40000009536743</v>
       </c>
-      <c r="F2735"/>
+      <c r="F2735" t="n">
+        <v>6.26000022888184</v>
+      </c>
       <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>15101025</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>5.92799997329712</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>6.23999977111816</v>
+      </c>
+      <c r="F2736"/>
+      <c r="G2736" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/TIT.MI.xlsx
+++ b/data/TIT.MI.xlsx
@@ -63293,8 +63293,31 @@
       <c r="E2736" t="n">
         <v>6.23999977111816</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>6.0310001373291</v>
+      </c>
       <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>12407554</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>6.21999979019165</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>5.83699989318848</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>6.01200008392334</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/TIT.MI.xlsx
+++ b/data/TIT.MI.xlsx
@@ -63316,8 +63316,31 @@
       <c r="E2737" t="n">
         <v>6.01200008392334</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>5.83699989318848</v>
+      </c>
       <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>11141334</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>5.83500003814697</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>5.5789999961853</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>5.81500005722046</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/TIT.MI.xlsx
+++ b/data/TIT.MI.xlsx
@@ -63339,8 +63339,31 @@
       <c r="E2738" t="n">
         <v>5.81500005722046</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>5.625</v>
+      </c>
       <c r="G2738" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2739" t="n">
+        <v>7851498</v>
+      </c>
+      <c r="C2739" t="n">
+        <v>5.73400020599365</v>
+      </c>
+      <c r="D2739" t="n">
+        <v>5.54699993133545</v>
+      </c>
+      <c r="E2739" t="n">
+        <v>5.63000011444092</v>
+      </c>
+      <c r="F2739"/>
+      <c r="G2739" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/TIT.MI.xlsx
+++ b/data/TIT.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>5950328</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>5.6230001449585</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>5.42199993133545</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>5.59000015258789</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>5.48600006103516</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TIT.MI.xlsx
+++ b/data/TIT.MI.xlsx
@@ -733,7 +733,7 @@
         <v>9.76500034332275</v>
       </c>
       <c r="G14" t="n">
-        <v>9.29015159606934</v>
+        <v>9.29015254974365</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>9.77000045776367</v>
       </c>
       <c r="G20" t="n">
-        <v>9.29490852355957</v>
+        <v>9.29490947723389</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G27" t="n">
-        <v>7.99152803421021</v>
+        <v>7.99152851104736</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G28" t="n">
-        <v>8.27694034576416</v>
+        <v>8.27693939208984</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>8.25500011444092</v>
       </c>
       <c r="G30" t="n">
-        <v>7.85357904434204</v>
+        <v>7.8535795211792</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G31" t="n">
-        <v>8.17228889465332</v>
+        <v>8.17228984832764</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>8.76500034332275</v>
       </c>
       <c r="G32" t="n">
-        <v>8.33877944946289</v>
+        <v>8.33878040313721</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G33" t="n">
-        <v>7.80125379562378</v>
+        <v>7.80125331878662</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>8.98999977111816</v>
       </c>
       <c r="G42" t="n">
-        <v>8.55283832550049</v>
+        <v>8.55283737182617</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G44" t="n">
-        <v>8.98095512390137</v>
+        <v>8.98095607757568</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G46" t="n">
-        <v>9.70399856567383</v>
+        <v>9.70399951934814</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>9.82499980926514</v>
       </c>
       <c r="G47" t="n">
-        <v>9.34723472595215</v>
+        <v>9.34723377227783</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G49" t="n">
-        <v>9.64691734313965</v>
+        <v>9.64691638946533</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G51" t="n">
-        <v>9.91330051422119</v>
+        <v>9.91330146789551</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G52" t="n">
-        <v>9.81816387176514</v>
+        <v>9.81816291809082</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>10.3299999237061</v>
       </c>
       <c r="G54" t="n">
-        <v>9.82767772674561</v>
+        <v>9.82767677307129</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>10.4099998474121</v>
       </c>
       <c r="G57" t="n">
-        <v>9.90378665924072</v>
+        <v>9.90378761291504</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G64" t="n">
-        <v>8.70505809783936</v>
+        <v>8.70505714416504</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>8.58500003814697</v>
       </c>
       <c r="G66" t="n">
-        <v>8.16753196716309</v>
+        <v>8.1675329208374</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G67" t="n">
-        <v>8.18180370330811</v>
+        <v>8.18180274963379</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G68" t="n">
-        <v>7.95347309112549</v>
+        <v>7.95347356796265</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>8.98999977111816</v>
       </c>
       <c r="G70" t="n">
-        <v>8.55283832550049</v>
+        <v>8.55283737182617</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>8.65499973297119</v>
       </c>
       <c r="G81" t="n">
-        <v>8.23412799835205</v>
+        <v>8.23412895202637</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G83" t="n">
-        <v>8.25791358947754</v>
+        <v>8.25791263580322</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>8.46500015258789</v>
       </c>
       <c r="G85" t="n">
-        <v>8.05336856842041</v>
+        <v>8.05336761474609</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>8.36499977111816</v>
       </c>
       <c r="G86" t="n">
-        <v>7.95823001861572</v>
+        <v>7.95823049545288</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G87" t="n">
-        <v>8.04861164093018</v>
+        <v>8.04861068725586</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G92" t="n">
-        <v>8.05812549591064</v>
+        <v>8.05812454223633</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>8.48999977111816</v>
       </c>
       <c r="G96" t="n">
-        <v>8.07715225219727</v>
+        <v>8.07715129852295</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>8.30500030517578</v>
       </c>
       <c r="G98" t="n">
-        <v>7.90114879608154</v>
+        <v>7.90114784240723</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G99" t="n">
-        <v>7.87736368179321</v>
+        <v>7.87736320495605</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G102" t="n">
-        <v>7.91541862487793</v>
+        <v>7.91541814804077</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G104" t="n">
-        <v>8.27694034576416</v>
+        <v>8.27693939208984</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G114" t="n">
-        <v>7.82028150558472</v>
+        <v>7.82028198242188</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>7.91499996185303</v>
       </c>
       <c r="G115" t="n">
-        <v>7.53011274337769</v>
+        <v>7.53011322021484</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>7.59499979019165</v>
       </c>
       <c r="G117" t="n">
-        <v>7.22567319869995</v>
+        <v>7.22567367553711</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G118" t="n">
-        <v>7.04015636444092</v>
+        <v>7.04015588760376</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>8.27499961853027</v>
       </c>
       <c r="G123" t="n">
-        <v>7.87260675430298</v>
+        <v>7.87260627746582</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>6.67500019073486</v>
       </c>
       <c r="G125" t="n">
-        <v>6.35041093826294</v>
+        <v>6.3504114151001</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>7.44500017166138</v>
       </c>
       <c r="G127" t="n">
-        <v>7.08296775817871</v>
+        <v>7.08296823501587</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G129" t="n">
-        <v>7.04015636444092</v>
+        <v>7.04015588760376</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>6.33500003814697</v>
       </c>
       <c r="G133" t="n">
-        <v>6.02694416046143</v>
+        <v>6.02694463729858</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G135" t="n">
-        <v>6.30759954452515</v>
+        <v>6.30759906768799</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>6.92500019073486</v>
       </c>
       <c r="G136" t="n">
-        <v>6.58825397491455</v>
+        <v>6.58825445175171</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G140" t="n">
-        <v>6.60252523422241</v>
+        <v>6.60252475738525</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>6.86499977111816</v>
       </c>
       <c r="G142" t="n">
-        <v>6.53117179870605</v>
+        <v>6.5311713218689</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>7</v>
       </c>
       <c r="G145" t="n">
-        <v>6.65960693359375</v>
+        <v>6.65960741043091</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>7.46999979019165</v>
       </c>
       <c r="G147" t="n">
-        <v>7.10675191879272</v>
+        <v>7.10675239562988</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>7.63500022888184</v>
       </c>
       <c r="G149" t="n">
-        <v>7.26372909545898</v>
+        <v>7.26372861862183</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>7.44500017166138</v>
       </c>
       <c r="G151" t="n">
-        <v>7.08296775817871</v>
+        <v>7.08296823501587</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G156" t="n">
-        <v>7.24945831298828</v>
+        <v>7.24945783615112</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>7.92999982833862</v>
       </c>
       <c r="G164" t="n">
-        <v>7.54438304901123</v>
+        <v>7.54438352584839</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>8.0649995803833</v>
       </c>
       <c r="G167" t="n">
-        <v>7.67281866073608</v>
+        <v>7.67281818389893</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>8.24499988555908</v>
       </c>
       <c r="G170" t="n">
-        <v>7.84406518936157</v>
+        <v>7.84406566619873</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>8.13500022888184</v>
       </c>
       <c r="G171" t="n">
-        <v>7.73941516876221</v>
+        <v>7.73941469192505</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>8.16499996185303</v>
       </c>
       <c r="G172" t="n">
-        <v>7.7679557800293</v>
+        <v>7.76795625686646</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G173" t="n">
-        <v>7.80125379562378</v>
+        <v>7.80125331878662</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>8.04500007629395</v>
       </c>
       <c r="G176" t="n">
-        <v>7.6537914276123</v>
+        <v>7.65379095077515</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>8.16499996185303</v>
       </c>
       <c r="G177" t="n">
-        <v>7.7679557800293</v>
+        <v>7.76795625686646</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G178" t="n">
-        <v>7.64903402328491</v>
+        <v>7.64903450012207</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>7.88500022888184</v>
       </c>
       <c r="G179" t="n">
-        <v>7.5015721321106</v>
+        <v>7.50157165527344</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>7.53499984741211</v>
       </c>
       <c r="G182" t="n">
-        <v>7.16859149932861</v>
+        <v>7.16859102249146</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>7.28499984741211</v>
       </c>
       <c r="G185" t="n">
-        <v>6.930748462677</v>
+        <v>6.93074798583984</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>7.63500022888184</v>
       </c>
       <c r="G188" t="n">
-        <v>7.26372909545898</v>
+        <v>7.26372861862183</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>7.34499979019165</v>
       </c>
       <c r="G190" t="n">
-        <v>6.98783016204834</v>
+        <v>6.9878306388855</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>7.49499988555908</v>
       </c>
       <c r="G191" t="n">
-        <v>7.1305365562439</v>
+        <v>7.13053607940674</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G193" t="n">
-        <v>7.03064250946045</v>
+        <v>7.03064203262329</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>7.29500007629395</v>
       </c>
       <c r="G196" t="n">
-        <v>6.94026231765747</v>
+        <v>6.94026184082031</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G199" t="n">
-        <v>7.04015636444092</v>
+        <v>7.04015588760376</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G200" t="n">
-        <v>6.86890888214111</v>
+        <v>6.86890840530396</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>6.94500017166138</v>
       </c>
       <c r="G202" t="n">
-        <v>6.60728216171265</v>
+        <v>6.60728168487549</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>7.57499980926514</v>
       </c>
       <c r="G205" t="n">
-        <v>7.20664596557617</v>
+        <v>7.20664644241333</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>7.59499979019165</v>
       </c>
       <c r="G207" t="n">
-        <v>7.22567319869995</v>
+        <v>7.22567367553711</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G208" t="n">
-        <v>7.35410928726196</v>
+        <v>7.3541088104248</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>7.92999982833862</v>
       </c>
       <c r="G209" t="n">
-        <v>7.54438304901123</v>
+        <v>7.54438352584839</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G216" t="n">
-        <v>7.35410928726196</v>
+        <v>7.3541088104248</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>7.70499992370605</v>
       </c>
       <c r="G217" t="n">
-        <v>7.33032464981079</v>
+        <v>7.33032417297363</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>7.45499992370605</v>
       </c>
       <c r="G221" t="n">
-        <v>7.09248161315918</v>
+        <v>7.09248113632202</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G227" t="n">
-        <v>6.67863416671753</v>
+        <v>6.67863464355469</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>6.86499977111816</v>
       </c>
       <c r="G228" t="n">
-        <v>6.53117179870605</v>
+        <v>6.5311713218689</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G232" t="n">
-        <v>6.70717620849609</v>
+        <v>6.70717573165894</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>7.14499998092651</v>
       </c>
       <c r="G233" t="n">
-        <v>6.79755592346191</v>
+        <v>6.79755640029907</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>7</v>
       </c>
       <c r="G239" t="n">
-        <v>6.65960693359375</v>
+        <v>6.65960741043091</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>7.54500007629395</v>
       </c>
       <c r="G241" t="n">
-        <v>7.17810535430908</v>
+        <v>7.17810487747192</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>7.625</v>
       </c>
       <c r="G243" t="n">
-        <v>7.25421524047852</v>
+        <v>7.25421476364136</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>8.06999969482422</v>
       </c>
       <c r="G248" t="n">
-        <v>7.67757558822632</v>
+        <v>7.67757511138916</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G251" t="n">
-        <v>7.99152803421021</v>
+        <v>7.99152851104736</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G254" t="n">
-        <v>8.27694034576416</v>
+        <v>8.27693939208984</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>8.42500019073486</v>
       </c>
       <c r="G255" t="n">
-        <v>8.01531219482422</v>
+        <v>8.01531314849854</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G257" t="n">
-        <v>7.96298694610596</v>
+        <v>7.96298742294312</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G258" t="n">
-        <v>8.16277503967285</v>
+        <v>8.16277599334717</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>8.42500019073486</v>
       </c>
       <c r="G261" t="n">
-        <v>8.01531219482422</v>
+        <v>8.01531314849854</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G263" t="n">
-        <v>7.82028150558472</v>
+        <v>7.82028198242188</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G264" t="n">
-        <v>7.87736368179321</v>
+        <v>7.87736320495605</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G265" t="n">
-        <v>8.04861164093018</v>
+        <v>8.04861068725586</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G266" t="n">
-        <v>7.93444633483887</v>
+        <v>7.93444681167603</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G268" t="n">
-        <v>8.10569381713867</v>
+        <v>8.10569286346436</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>8.375</v>
       </c>
       <c r="G269" t="n">
-        <v>7.96774387359619</v>
+        <v>7.96774482727051</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>8.3100004196167</v>
       </c>
       <c r="G270" t="n">
-        <v>7.90590572357178</v>
+        <v>7.90590524673462</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G271" t="n">
-        <v>7.99152803421021</v>
+        <v>7.99152851104736</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G272" t="n">
-        <v>8.04861164093018</v>
+        <v>8.04861068725586</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G273" t="n">
-        <v>7.99152803421021</v>
+        <v>7.99152851104736</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>8.3100004196167</v>
       </c>
       <c r="G274" t="n">
-        <v>7.90590572357178</v>
+        <v>7.90590524673462</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G275" t="n">
-        <v>7.82979440689087</v>
+        <v>7.82979536056519</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G281" t="n">
-        <v>7.59195232391357</v>
+        <v>7.59195184707642</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G285" t="n">
-        <v>7.79173994064331</v>
+        <v>7.79174041748047</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>8.25</v>
       </c>
       <c r="G286" t="n">
-        <v>7.84882211685181</v>
+        <v>7.84882259368896</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G287" t="n">
-        <v>7.64903402328491</v>
+        <v>7.64903450012207</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>7.97499990463257</v>
       </c>
       <c r="G289" t="n">
-        <v>7.58719539642334</v>
+        <v>7.58719491958618</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>7.91499996185303</v>
       </c>
       <c r="G291" t="n">
-        <v>7.53011274337769</v>
+        <v>7.53011322021484</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G294" t="n">
-        <v>7.3255672454834</v>
+        <v>7.32556772232056</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>7.59499979019165</v>
       </c>
       <c r="G295" t="n">
-        <v>7.22567319869995</v>
+        <v>7.22567367553711</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>7.79500007629395</v>
       </c>
       <c r="G304" t="n">
-        <v>7.41594839096069</v>
+        <v>7.41594791412354</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G305" t="n">
-        <v>7.35410928726196</v>
+        <v>7.3541088104248</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>7.83500003814697</v>
       </c>
       <c r="G306" t="n">
-        <v>7.45400333404541</v>
+        <v>7.45400285720825</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>7.88500022888184</v>
       </c>
       <c r="G310" t="n">
-        <v>7.5015721321106</v>
+        <v>7.50157165527344</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>8.125</v>
       </c>
       <c r="G314" t="n">
-        <v>7.72990083694458</v>
+        <v>7.72990131378174</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G317" t="n">
-        <v>7.93444633483887</v>
+        <v>7.93444681167603</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G319" t="n">
-        <v>8.10569381713867</v>
+        <v>8.10569286346436</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G320" t="n">
-        <v>8.01055526733398</v>
+        <v>8.0105562210083</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>8.45499992370605</v>
       </c>
       <c r="G321" t="n">
-        <v>8.04385471343994</v>
+        <v>8.04385375976562</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>8.13500022888184</v>
       </c>
       <c r="G325" t="n">
-        <v>7.73941516876221</v>
+        <v>7.73941469192505</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G329" t="n">
-        <v>7.64903402328491</v>
+        <v>7.64903450012207</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>8.04500007629395</v>
       </c>
       <c r="G330" t="n">
-        <v>7.6537914276123</v>
+        <v>7.65379095077515</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>7.875</v>
       </c>
       <c r="G335" t="n">
-        <v>7.49205827713013</v>
+        <v>7.49205780029297</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G337" t="n">
-        <v>7.87736368179321</v>
+        <v>7.87736320495605</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G346" t="n">
-        <v>8.50527000427246</v>
+        <v>8.50526905059814</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>9.14500045776367</v>
       </c>
       <c r="G351" t="n">
-        <v>8.70030212402344</v>
+        <v>8.70030117034912</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G358" t="n">
-        <v>8.23888492584229</v>
+        <v>8.2388858795166</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G360" t="n">
-        <v>8.05812549591064</v>
+        <v>8.05812454223633</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>8.3100004196167</v>
       </c>
       <c r="G361" t="n">
-        <v>7.90590572357178</v>
+        <v>7.90590524673462</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G363" t="n">
-        <v>7.93444633483887</v>
+        <v>7.93444681167603</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G367" t="n">
-        <v>7.88687801361084</v>
+        <v>7.88687753677368</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>8.3100004196167</v>
       </c>
       <c r="G368" t="n">
-        <v>7.90590572357178</v>
+        <v>7.90590524673462</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>8.25</v>
       </c>
       <c r="G369" t="n">
-        <v>7.84882211685181</v>
+        <v>7.84882259368896</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>8.27499961853027</v>
       </c>
       <c r="G370" t="n">
-        <v>7.87260675430298</v>
+        <v>7.87260627746582</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G371" t="n">
-        <v>7.91541862487793</v>
+        <v>7.91541814804077</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>8.33500003814697</v>
       </c>
       <c r="G372" t="n">
-        <v>7.92968940734863</v>
+        <v>7.92968988418579</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>8.25</v>
       </c>
       <c r="G373" t="n">
-        <v>7.84882211685181</v>
+        <v>7.84882259368896</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G376" t="n">
-        <v>7.88687801361084</v>
+        <v>7.88687753677368</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G377" t="n">
-        <v>7.91541862487793</v>
+        <v>7.91541814804077</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G378" t="n">
-        <v>7.82979440689087</v>
+        <v>7.82979536056519</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>8.0649995803833</v>
       </c>
       <c r="G381" t="n">
-        <v>7.67281866073608</v>
+        <v>7.67281818389893</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G385" t="n">
-        <v>7.82979440689087</v>
+        <v>7.82979536056519</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G387" t="n">
-        <v>7.63000726699829</v>
+        <v>7.63000774383545</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>8.04500007629395</v>
       </c>
       <c r="G388" t="n">
-        <v>7.6537914276123</v>
+        <v>7.65379095077515</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>7.88500022888184</v>
       </c>
       <c r="G391" t="n">
-        <v>7.5015721321106</v>
+        <v>7.50157165527344</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G393" t="n">
-        <v>7.86785078048706</v>
+        <v>7.8678503036499</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>8.04500007629395</v>
       </c>
       <c r="G394" t="n">
-        <v>7.6537914276123</v>
+        <v>7.65379095077515</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>8.125</v>
       </c>
       <c r="G399" t="n">
-        <v>7.72990083694458</v>
+        <v>7.72990131378174</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G403" t="n">
-        <v>8.23888492584229</v>
+        <v>8.2388858795166</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>8.70499992370605</v>
       </c>
       <c r="G405" t="n">
-        <v>8.28169727325439</v>
+        <v>8.28169631958008</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>8.70499992370605</v>
       </c>
       <c r="G408" t="n">
-        <v>8.28169727325439</v>
+        <v>8.28169631958008</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G415" t="n">
-        <v>8.05812549591064</v>
+        <v>8.05812454223633</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>8.33500003814697</v>
       </c>
       <c r="G418" t="n">
-        <v>7.92968940734863</v>
+        <v>7.92968988418579</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>8.27499961853027</v>
       </c>
       <c r="G419" t="n">
-        <v>7.87260675430298</v>
+        <v>7.87260627746582</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>8.04500007629395</v>
       </c>
       <c r="G427" t="n">
-        <v>7.6537914276123</v>
+        <v>7.65379095077515</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>7.83500003814697</v>
       </c>
       <c r="G429" t="n">
-        <v>7.45400333404541</v>
+        <v>7.45400285720825</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>7.88500022888184</v>
       </c>
       <c r="G435" t="n">
-        <v>7.5015721321106</v>
+        <v>7.50157165527344</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>8.02499961853027</v>
       </c>
       <c r="G440" t="n">
-        <v>7.63476324081421</v>
+        <v>7.63476371765137</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G442" t="n">
-        <v>7.57292509078979</v>
+        <v>7.57292461395264</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>7.93499994277954</v>
       </c>
       <c r="G445" t="n">
-        <v>7.54913997650146</v>
+        <v>7.54914045333862</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G447" t="n">
-        <v>7.59195232391357</v>
+        <v>7.59195184707642</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>7.63500022888184</v>
       </c>
       <c r="G454" t="n">
-        <v>7.26372909545898</v>
+        <v>7.26372861862183</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>7.54500007629395</v>
       </c>
       <c r="G455" t="n">
-        <v>7.17810535430908</v>
+        <v>7.17810487747192</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>7.625</v>
       </c>
       <c r="G459" t="n">
-        <v>7.25421524047852</v>
+        <v>7.25421476364136</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>7.68499994277954</v>
       </c>
       <c r="G463" t="n">
-        <v>7.31129693984985</v>
+        <v>7.31129741668701</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>7.63500022888184</v>
       </c>
       <c r="G472" t="n">
-        <v>7.26372909545898</v>
+        <v>7.26372861862183</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>7.35500001907349</v>
       </c>
       <c r="G476" t="n">
-        <v>6.99734401702881</v>
+        <v>6.99734449386597</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>6.89499998092651</v>
       </c>
       <c r="G479" t="n">
-        <v>6.5597128868103</v>
+        <v>6.55971336364746</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>6.81500005722046</v>
       </c>
       <c r="G481" t="n">
-        <v>6.48360300064087</v>
+        <v>6.48360347747803</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>6.89499998092651</v>
       </c>
       <c r="G482" t="n">
-        <v>6.5597128868103</v>
+        <v>6.55971336364746</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>7.04500007629395</v>
       </c>
       <c r="G490" t="n">
-        <v>6.70241928100586</v>
+        <v>6.7024188041687</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G494" t="n">
-        <v>6.7166895866394</v>
+        <v>6.71668910980225</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>7.46999979019165</v>
       </c>
       <c r="G497" t="n">
-        <v>7.10675191879272</v>
+        <v>7.10675239562988</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>7.54500007629395</v>
       </c>
       <c r="G498" t="n">
-        <v>7.17810535430908</v>
+        <v>7.17810487747192</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>7.2649998664856</v>
       </c>
       <c r="G502" t="n">
-        <v>6.91172027587891</v>
+        <v>6.91172075271606</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>7.34499979019165</v>
       </c>
       <c r="G504" t="n">
-        <v>6.98783016204834</v>
+        <v>6.9878306388855</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G505" t="n">
-        <v>7.04015636444092</v>
+        <v>7.04015588760376</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>7.34499979019165</v>
       </c>
       <c r="G507" t="n">
-        <v>6.98783016204834</v>
+        <v>6.9878306388855</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G508" t="n">
-        <v>7.02112865447998</v>
+        <v>7.02112913131714</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>7.29500007629395</v>
       </c>
       <c r="G510" t="n">
-        <v>6.94026231765747</v>
+        <v>6.94026184082031</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>7.20499992370605</v>
       </c>
       <c r="G511" t="n">
-        <v>6.85463857650757</v>
+        <v>6.85463809967041</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>7.25500011444092</v>
       </c>
       <c r="G512" t="n">
-        <v>6.9022068977356</v>
+        <v>6.90220737457275</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>7.25</v>
       </c>
       <c r="G513" t="n">
-        <v>6.89744997024536</v>
+        <v>6.89745044708252</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G514" t="n">
-        <v>6.98307371139526</v>
+        <v>6.98307418823242</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>7.38500022888184</v>
       </c>
       <c r="G515" t="n">
-        <v>7.02588605880737</v>
+        <v>7.02588558197021</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>7.43499994277954</v>
       </c>
       <c r="G520" t="n">
-        <v>7.07345390319824</v>
+        <v>7.0734543800354</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>7.38500022888184</v>
       </c>
       <c r="G521" t="n">
-        <v>7.02588605880737</v>
+        <v>7.02588558197021</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>7.20499992370605</v>
       </c>
       <c r="G530" t="n">
-        <v>6.85463857650757</v>
+        <v>6.85463809967041</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>7.21199989318848</v>
       </c>
       <c r="G538" t="n">
-        <v>6.86129760742188</v>
+        <v>6.86129808425903</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>6.98799991607666</v>
       </c>
       <c r="G540" t="n">
-        <v>6.64819097518921</v>
+        <v>6.64819049835205</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G543" t="n">
-        <v>6.54544258117676</v>
+        <v>6.5454421043396</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>7.19600009918213</v>
       </c>
       <c r="G548" t="n">
-        <v>6.84607601165771</v>
+        <v>6.84607648849487</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G551" t="n">
-        <v>7.02112865447998</v>
+        <v>7.02112913131714</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G553" t="n">
-        <v>7.04015636444092</v>
+        <v>7.04015588760376</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>7.39799976348877</v>
       </c>
       <c r="G554" t="n">
-        <v>7.03825283050537</v>
+        <v>7.03825330734253</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>7.24599981307983</v>
       </c>
       <c r="G555" t="n">
-        <v>6.8936448097229</v>
+        <v>6.89364433288574</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>7.28800010681152</v>
       </c>
       <c r="G556" t="n">
-        <v>6.93360233306885</v>
+        <v>6.93360280990601</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G559" t="n">
-        <v>7.82979440689087</v>
+        <v>7.82979536056519</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G560" t="n">
-        <v>7.91541862487793</v>
+        <v>7.91541814804077</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>8.20199966430664</v>
       </c>
       <c r="G561" t="n">
-        <v>7.80315637588501</v>
+        <v>7.80315589904785</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>8.00800037384033</v>
       </c>
       <c r="G562" t="n">
-        <v>7.61859083175659</v>
+        <v>7.61859130859375</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>7.83199977874756</v>
       </c>
       <c r="G563" t="n">
-        <v>7.45114898681641</v>
+        <v>7.45114850997925</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>8.08800029754639</v>
       </c>
       <c r="G565" t="n">
-        <v>7.69470024108887</v>
+        <v>7.69470071792603</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>8.11600017547607</v>
       </c>
       <c r="G566" t="n">
-        <v>7.72133874893188</v>
+        <v>7.72133922576904</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>7.72599983215332</v>
       </c>
       <c r="G570" t="n">
-        <v>7.35030364990234</v>
+        <v>7.35030317306519</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>7.61399984359741</v>
       </c>
       <c r="G572" t="n">
-        <v>7.24374961853027</v>
+        <v>7.24375009536743</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>7.58199977874756</v>
       </c>
       <c r="G576" t="n">
-        <v>7.21330595016479</v>
+        <v>7.21330547332764</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>8.61200046539307</v>
       </c>
       <c r="G582" t="n">
-        <v>8.19321918487549</v>
+        <v>8.1932201385498</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>8.38199996948242</v>
       </c>
       <c r="G585" t="n">
-        <v>7.97440385818481</v>
+        <v>7.97440338134766</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>8.76200008392334</v>
       </c>
       <c r="G588" t="n">
-        <v>8.33592510223389</v>
+        <v>8.3359260559082</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G589" t="n">
-        <v>8.27694034576416</v>
+        <v>8.27693939208984</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>8.26200008392334</v>
       </c>
       <c r="G591" t="n">
-        <v>7.86023902893066</v>
+        <v>7.86023950576782</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G596" t="n">
-        <v>7.96298694610596</v>
+        <v>7.96298742294312</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G599" t="n">
-        <v>8.01055526733398</v>
+        <v>8.0105562210083</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G600" t="n">
-        <v>7.88687801361084</v>
+        <v>7.88687753677368</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G605" t="n">
-        <v>7.35410928726196</v>
+        <v>7.3541088104248</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G606" t="n">
-        <v>7.30654001235962</v>
+        <v>7.30654048919678</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G609" t="n">
-        <v>7.02112865447998</v>
+        <v>7.02112913131714</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>7.31199979782104</v>
       </c>
       <c r="G610" t="n">
-        <v>6.95643520355225</v>
+        <v>6.95643472671509</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>7.30999994277954</v>
       </c>
       <c r="G611" t="n">
-        <v>6.95453262329102</v>
+        <v>6.95453214645386</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>7.14400005340576</v>
       </c>
       <c r="G613" t="n">
-        <v>6.7966046333313</v>
+        <v>6.79660511016846</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>7.01599979400635</v>
       </c>
       <c r="G615" t="n">
-        <v>6.67482852935791</v>
+        <v>6.67482900619507</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>6.87200021743774</v>
       </c>
       <c r="G616" t="n">
-        <v>6.53783130645752</v>
+        <v>6.53783178329468</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>6.98600006103516</v>
       </c>
       <c r="G618" t="n">
-        <v>6.64628791809082</v>
+        <v>6.64628839492798</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>6.91599988937378</v>
       </c>
       <c r="G620" t="n">
-        <v>6.57969188690186</v>
+        <v>6.5796914100647</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>6.72200012207031</v>
       </c>
       <c r="G622" t="n">
-        <v>6.39512586593628</v>
+        <v>6.39512538909912</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>6.87200021743774</v>
       </c>
       <c r="G623" t="n">
-        <v>6.53783130645752</v>
+        <v>6.53783178329468</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>6.85799980163574</v>
       </c>
       <c r="G624" t="n">
-        <v>6.52451181411743</v>
+        <v>6.52451229095459</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>6.7519998550415</v>
       </c>
       <c r="G627" t="n">
-        <v>6.42366647720337</v>
+        <v>6.42366695404053</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>6.76599979400635</v>
       </c>
       <c r="G628" t="n">
-        <v>6.4369854927063</v>
+        <v>6.43698596954346</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G631" t="n">
-        <v>6.33614015579224</v>
+        <v>6.33614063262939</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>6.45599985122681</v>
       </c>
       <c r="G635" t="n">
-        <v>6.14206075668335</v>
+        <v>6.14206027984619</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>6.37400007247925</v>
       </c>
       <c r="G637" t="n">
-        <v>6.06404781341553</v>
+        <v>6.06404829025269</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>6.28200006484985</v>
       </c>
       <c r="G638" t="n">
-        <v>5.97652149200439</v>
+        <v>5.97652196884155</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>6.52400016784668</v>
       </c>
       <c r="G640" t="n">
-        <v>6.20675420761108</v>
+        <v>6.20675373077393</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>6.55200004577637</v>
       </c>
       <c r="G642" t="n">
-        <v>6.2333927154541</v>
+        <v>6.23339223861694</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>6.36600017547607</v>
       </c>
       <c r="G644" t="n">
-        <v>6.05643749237061</v>
+        <v>6.05643701553345</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G645" t="n">
-        <v>6.01267385482788</v>
+        <v>6.01267433166504</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>6.14599990844727</v>
       </c>
       <c r="G646" t="n">
-        <v>5.84713506698608</v>
+        <v>5.84713459014893</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>6.07399988174438</v>
       </c>
       <c r="G648" t="n">
-        <v>5.77863645553589</v>
+        <v>5.77863597869873</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G658" t="n">
-        <v>6.2790584564209</v>
+        <v>6.27905797958374</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>6.50400018692017</v>
       </c>
       <c r="G660" t="n">
-        <v>6.1877269744873</v>
+        <v>6.18772649765015</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>6.38199996948242</v>
       </c>
       <c r="G661" t="n">
-        <v>6.07165908813477</v>
+        <v>6.07165861129761</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>6</v>
       </c>
       <c r="G675" t="n">
-        <v>5.70823431015015</v>
+        <v>5.7082347869873</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>5.98799991607666</v>
       </c>
       <c r="G676" t="n">
-        <v>5.69681835174561</v>
+        <v>5.69681787490845</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>6.0019998550415</v>
       </c>
       <c r="G677" t="n">
-        <v>5.71013736724854</v>
+        <v>5.71013689041138</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>5.93800020217896</v>
       </c>
       <c r="G678" t="n">
-        <v>5.64924955368042</v>
+        <v>5.64925003051758</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G681" t="n">
-        <v>5.22303485870361</v>
+        <v>5.22303438186646</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G682" t="n">
-        <v>5.28011703491211</v>
+        <v>5.28011751174927</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>5.25</v>
       </c>
       <c r="G683" t="n">
-        <v>4.99470567703247</v>
+        <v>4.99470520019531</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>5.4060001373291</v>
       </c>
       <c r="G689" t="n">
-        <v>5.14311933517456</v>
+        <v>5.14311981201172</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>5.71400022506714</v>
       </c>
       <c r="G693" t="n">
-        <v>5.4361424446106</v>
+        <v>5.43614196777344</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>5.68599987030029</v>
       </c>
       <c r="G695" t="n">
-        <v>5.40950393676758</v>
+        <v>5.40950345993042</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>5.68599987030029</v>
       </c>
       <c r="G696" t="n">
-        <v>5.40950393676758</v>
+        <v>5.40950345993042</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>5.60599994659424</v>
       </c>
       <c r="G697" t="n">
-        <v>5.33339405059814</v>
+        <v>5.33339357376099</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G698" t="n">
-        <v>5.30865859985352</v>
+        <v>5.30865812301636</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>4.95300006866455</v>
       </c>
       <c r="G702" t="n">
-        <v>4.71214818954468</v>
+        <v>4.71214771270752</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>4.95699977874756</v>
       </c>
       <c r="G705" t="n">
-        <v>4.71595287322998</v>
+        <v>4.71595335006714</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>5.03200006484985</v>
       </c>
       <c r="G709" t="n">
-        <v>4.78730630874634</v>
+        <v>4.78730583190918</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G710" t="n">
-        <v>4.77588987350464</v>
+        <v>4.77588939666748</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>4.98600006103516</v>
       </c>
       <c r="G716" t="n">
-        <v>4.74354267120361</v>
+        <v>4.74354314804077</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>5.19199991226196</v>
       </c>
       <c r="G724" t="n">
-        <v>4.93952560424805</v>
+        <v>4.93952608108521</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>5.35400009155273</v>
       </c>
       <c r="G727" t="n">
-        <v>5.09364795684814</v>
+        <v>5.0936484336853</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G729" t="n">
-        <v>5.08984231948853</v>
+        <v>5.08984279632568</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G731" t="n">
-        <v>4.90908193588257</v>
+        <v>4.90908145904541</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>5.30399990081787</v>
       </c>
       <c r="G732" t="n">
-        <v>5.04607963562012</v>
+        <v>5.04607915878296</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G734" t="n">
-        <v>4.9566502571106</v>
+        <v>4.95665073394775</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>5.16400003433228</v>
       </c>
       <c r="G735" t="n">
-        <v>4.91288757324219</v>
+        <v>4.91288709640503</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>5.26200008392334</v>
       </c>
       <c r="G736" t="n">
-        <v>5.00612163543701</v>
+        <v>5.00612211227417</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>5.74599981307983</v>
       </c>
       <c r="G747" t="n">
-        <v>5.46658563613892</v>
+        <v>5.46658611297607</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>5.69199991226196</v>
       </c>
       <c r="G748" t="n">
-        <v>5.41521167755127</v>
+        <v>5.41521215438843</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G754" t="n">
-        <v>5.42282295227051</v>
+        <v>5.42282247543335</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>5.4520001411438</v>
       </c>
       <c r="G759" t="n">
-        <v>5.18688297271729</v>
+        <v>5.18688249588013</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>5.2020001411438</v>
       </c>
       <c r="G760" t="n">
-        <v>4.94903993606567</v>
+        <v>4.94903945922852</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G762" t="n">
-        <v>4.58561563491821</v>
+        <v>4.58561515808105</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>4.83300018310547</v>
       </c>
       <c r="G763" t="n">
-        <v>4.59798288345337</v>
+        <v>4.59798336029053</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>5.06199979782104</v>
       </c>
       <c r="G768" t="n">
-        <v>4.81584692001343</v>
+        <v>4.81584739685059</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>4.95900011062622</v>
       </c>
       <c r="G769" t="n">
-        <v>4.71785593032837</v>
+        <v>4.71785640716553</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>5.00600004196167</v>
       </c>
       <c r="G771" t="n">
-        <v>4.76257085800171</v>
+        <v>4.76257038116455</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>5.01599979400635</v>
       </c>
       <c r="G772" t="n">
-        <v>4.77208423614502</v>
+        <v>4.77208375930786</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>5.02400016784668</v>
       </c>
       <c r="G773" t="n">
-        <v>4.7796950340271</v>
+        <v>4.77969551086426</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>4.88500022888184</v>
       </c>
       <c r="G776" t="n">
-        <v>4.64745426177979</v>
+        <v>4.64745473861694</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>4.48400020599365</v>
       </c>
       <c r="G779" t="n">
-        <v>4.26595449447632</v>
+        <v>4.26595401763916</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>4.52899980545044</v>
       </c>
       <c r="G780" t="n">
-        <v>4.30876541137695</v>
+        <v>4.30876588821411</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>4.58199977874756</v>
       </c>
       <c r="G783" t="n">
-        <v>4.35918807983398</v>
+        <v>4.35918855667114</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G784" t="n">
-        <v>4.40485429763794</v>
+        <v>4.4048547744751</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>5.02400016784668</v>
       </c>
       <c r="G788" t="n">
-        <v>4.7796950340271</v>
+        <v>4.77969551086426</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G791" t="n">
-        <v>4.49047756195068</v>
+        <v>4.49047803878784</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>4.81599998474121</v>
       </c>
       <c r="G793" t="n">
-        <v>4.58180952072144</v>
+        <v>4.58180999755859</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>4.8270001411438</v>
       </c>
       <c r="G795" t="n">
-        <v>4.59227466583252</v>
+        <v>4.59227514266968</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G797" t="n">
-        <v>5.0422739982605</v>
+        <v>5.04227447509766</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G802" t="n">
-        <v>5.09935665130615</v>
+        <v>5.09935617446899</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>5.32200002670288</v>
       </c>
       <c r="G806" t="n">
-        <v>5.06320428848267</v>
+        <v>5.06320381164551</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>5.5</v>
       </c>
       <c r="G808" t="n">
-        <v>5.23254871368408</v>
+        <v>5.23254823684692</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>5.64799976348877</v>
       </c>
       <c r="G809" t="n">
-        <v>5.37335157394409</v>
+        <v>5.37335109710693</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G810" t="n">
-        <v>5.33719968795776</v>
+        <v>5.33719921112061</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>5.35599994659424</v>
       </c>
       <c r="G818" t="n">
-        <v>5.09555101394653</v>
+        <v>5.09555053710938</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G820" t="n">
-        <v>5.0422739982605</v>
+        <v>5.04227447509766</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>5.25799989700317</v>
       </c>
       <c r="G821" t="n">
-        <v>5.00231599807739</v>
+        <v>5.00231647491455</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>5.31599998474121</v>
       </c>
       <c r="G823" t="n">
-        <v>5.05749559402466</v>
+        <v>5.05749607086182</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>5.35599994659424</v>
       </c>
       <c r="G824" t="n">
-        <v>5.09555101394653</v>
+        <v>5.09555053710938</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G825" t="n">
-        <v>5.14692497253418</v>
+        <v>5.14692449569702</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G828" t="n">
-        <v>5.08984231948853</v>
+        <v>5.08984279632568</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>5.40199995040894</v>
       </c>
       <c r="G829" t="n">
-        <v>5.13931369781494</v>
+        <v>5.1393141746521</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>5.36800003051758</v>
       </c>
       <c r="G831" t="n">
-        <v>5.10696697235107</v>
+        <v>5.10696744918823</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>5.33599996566772</v>
       </c>
       <c r="G832" t="n">
-        <v>5.0765233039856</v>
+        <v>5.07652378082275</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>5.34899997711182</v>
       </c>
       <c r="G833" t="n">
-        <v>5.08889102935791</v>
+        <v>5.08889150619507</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>5.25500011444092</v>
       </c>
       <c r="G838" t="n">
-        <v>4.99946260452271</v>
+        <v>4.99946212768555</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>4.98600006103516</v>
       </c>
       <c r="G846" t="n">
-        <v>4.74354267120361</v>
+        <v>4.74354314804077</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>4.95900011062622</v>
       </c>
       <c r="G847" t="n">
-        <v>4.71785593032837</v>
+        <v>4.71785640716553</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>4.67199993133545</v>
       </c>
       <c r="G853" t="n">
-        <v>4.44481182098389</v>
+        <v>4.44481229782104</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>4.45800018310547</v>
       </c>
       <c r="G856" t="n">
-        <v>4.24121856689453</v>
+        <v>4.24121809005737</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>4.57800006866455</v>
       </c>
       <c r="G859" t="n">
-        <v>4.35538291931152</v>
+        <v>4.35538339614868</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>4.38100004196167</v>
       </c>
       <c r="G863" t="n">
-        <v>4.16796255111694</v>
+        <v>4.1679630279541</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G870" t="n">
-        <v>4.32398748397827</v>
+        <v>4.32398796081543</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>4.63100004196167</v>
       </c>
       <c r="G877" t="n">
-        <v>4.40580558776855</v>
+        <v>4.40580606460571</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>4.84200000762939</v>
       </c>
       <c r="G882" t="n">
-        <v>4.60654497146606</v>
+        <v>4.60654544830322</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>5.00899982452393</v>
       </c>
       <c r="G883" t="n">
-        <v>4.7654242515564</v>
+        <v>4.76542472839355</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>4.82800006866455</v>
       </c>
       <c r="G889" t="n">
-        <v>4.59322595596313</v>
+        <v>4.59322643280029</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>4.78299999237061</v>
       </c>
       <c r="G890" t="n">
-        <v>4.55041456222534</v>
+        <v>4.55041408538818</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>4.92199993133545</v>
       </c>
       <c r="G891" t="n">
-        <v>4.6826548576355</v>
+        <v>4.68265533447266</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>4.96299982070923</v>
       </c>
       <c r="G893" t="n">
-        <v>4.72166156768799</v>
+        <v>4.72166109085083</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>5.01300001144409</v>
       </c>
       <c r="G898" t="n">
-        <v>4.76922988891602</v>
+        <v>4.76923036575317</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>5.06099987030029</v>
       </c>
       <c r="G902" t="n">
-        <v>4.81489562988281</v>
+        <v>4.81489610671997</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>4.91099977493286</v>
       </c>
       <c r="G903" t="n">
-        <v>4.67219018936157</v>
+        <v>4.67218971252441</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>4.95699977874756</v>
       </c>
       <c r="G905" t="n">
-        <v>4.71595287322998</v>
+        <v>4.71595335006714</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G909" t="n">
-        <v>4.985191822052</v>
+        <v>4.98519134521484</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>5.10599994659424</v>
       </c>
       <c r="G911" t="n">
-        <v>4.85770797729492</v>
+        <v>4.85770750045776</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>4.99599981307983</v>
       </c>
       <c r="G913" t="n">
-        <v>4.75305700302124</v>
+        <v>4.75305652618408</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>4.83400011062622</v>
       </c>
       <c r="G915" t="n">
-        <v>4.59893465042114</v>
+        <v>4.59893417358398</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>4.81599998474121</v>
       </c>
       <c r="G916" t="n">
-        <v>4.58180952072144</v>
+        <v>4.58180999755859</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>4.88800001144409</v>
       </c>
       <c r="G917" t="n">
-        <v>4.65030860900879</v>
+        <v>4.65030813217163</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>4.60200023651123</v>
       </c>
       <c r="G918" t="n">
-        <v>4.37821626663208</v>
+        <v>4.37821578979492</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>4.56500005722046</v>
       </c>
       <c r="G923" t="n">
-        <v>4.34301567077637</v>
+        <v>4.34301519393921</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>4.47200012207031</v>
       </c>
       <c r="G924" t="n">
-        <v>4.25453758239746</v>
+        <v>4.25453805923462</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>4.59800004959106</v>
       </c>
       <c r="G926" t="n">
-        <v>4.3744101524353</v>
+        <v>4.37441062927246</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>4.52600002288818</v>
       </c>
       <c r="G927" t="n">
-        <v>4.30591154098511</v>
+        <v>4.30591201782227</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>4.92600011825562</v>
       </c>
       <c r="G935" t="n">
-        <v>4.68646097183228</v>
+        <v>4.68646049499512</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>4.91800022125244</v>
       </c>
       <c r="G936" t="n">
-        <v>4.67884969711304</v>
+        <v>4.6788501739502</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G942" t="n">
-        <v>4.9566502571106</v>
+        <v>4.95665073394775</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>5.16699981689453</v>
       </c>
       <c r="G943" t="n">
-        <v>4.91574096679688</v>
+        <v>4.91574144363403</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G946" t="n">
-        <v>4.985191822052</v>
+        <v>4.98519134521484</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>5.19700002670288</v>
       </c>
       <c r="G952" t="n">
-        <v>4.94428300857544</v>
+        <v>4.94428253173828</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>4.94199991226196</v>
       </c>
       <c r="G955" t="n">
-        <v>4.70168256759644</v>
+        <v>4.70168209075928</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>4.96799993515015</v>
       </c>
       <c r="G956" t="n">
-        <v>4.72641849517822</v>
+        <v>4.72641801834106</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>4.97599983215332</v>
       </c>
       <c r="G957" t="n">
-        <v>4.73402881622314</v>
+        <v>4.7340292930603</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>5.06599998474121</v>
       </c>
       <c r="G959" t="n">
-        <v>4.81965255737305</v>
+        <v>4.81965303421021</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G962" t="n">
-        <v>5.09935665130615</v>
+        <v>5.09935617446899</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>5.39400005340576</v>
       </c>
       <c r="G965" t="n">
-        <v>5.13170337677002</v>
+        <v>5.13170289993286</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>5.35400009155273</v>
       </c>
       <c r="G967" t="n">
-        <v>5.09364795684814</v>
+        <v>5.0936484336853</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G971" t="n">
-        <v>5.06130170822144</v>
+        <v>5.06130123138428</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G974" t="n">
-        <v>5.05178737640381</v>
+        <v>5.05178785324097</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>5.36299991607666</v>
       </c>
       <c r="G984" t="n">
-        <v>5.10221004486084</v>
+        <v>5.102210521698</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G985" t="n">
-        <v>5.09935665130615</v>
+        <v>5.09935617446899</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>5.41300010681152</v>
       </c>
       <c r="G986" t="n">
-        <v>5.14977931976318</v>
+        <v>5.14977884292603</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>5.44099998474121</v>
       </c>
       <c r="G987" t="n">
-        <v>5.17641735076904</v>
+        <v>5.1764178276062</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>5.51800012588501</v>
       </c>
       <c r="G989" t="n">
-        <v>5.24967336654663</v>
+        <v>5.24967288970947</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>5.65100002288818</v>
       </c>
       <c r="G990" t="n">
-        <v>5.37620544433594</v>
+        <v>5.3762059211731</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>5.83900022506714</v>
       </c>
       <c r="G993" t="n">
-        <v>5.55506420135498</v>
+        <v>5.55506372451782</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>5.73899984359741</v>
       </c>
       <c r="G995" t="n">
-        <v>5.45992660522461</v>
+        <v>5.45992612838745</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>5.68599987030029</v>
       </c>
       <c r="G996" t="n">
-        <v>5.40950393676758</v>
+        <v>5.40950345993042</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>5.51200008392334</v>
       </c>
       <c r="G999" t="n">
-        <v>5.24396467208862</v>
+        <v>5.24396514892578</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>5.54199981689453</v>
       </c>
       <c r="G1008" t="n">
-        <v>5.27250623703003</v>
+        <v>5.27250576019287</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1009" t="n">
-        <v>5.28963041305542</v>
+        <v>5.28963088989258</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>5.59499979019165</v>
       </c>
       <c r="G1010" t="n">
-        <v>5.32292890548706</v>
+        <v>5.3229284286499</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>5.59499979019165</v>
       </c>
       <c r="G1011" t="n">
-        <v>5.32292890548706</v>
+        <v>5.3229284286499</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>5.59499979019165</v>
       </c>
       <c r="G1016" t="n">
-        <v>5.32292890548706</v>
+        <v>5.3229284286499</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>5.26300001144409</v>
       </c>
       <c r="G1021" t="n">
-        <v>5.00707292556763</v>
+        <v>5.00707340240479</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1024" t="n">
-        <v>4.89956855773926</v>
+        <v>4.8995680809021</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>5.05900001525879</v>
       </c>
       <c r="G1025" t="n">
-        <v>4.81299352645874</v>
+        <v>4.81299304962158</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>5.1230001449585</v>
       </c>
       <c r="G1027" t="n">
-        <v>4.87388134002686</v>
+        <v>4.8738808631897</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>5.11399984359741</v>
       </c>
       <c r="G1028" t="n">
-        <v>4.86531829833984</v>
+        <v>4.865318775177</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>5.06599998474121</v>
       </c>
       <c r="G1029" t="n">
-        <v>4.81965255737305</v>
+        <v>4.81965303421021</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>4.94199991226196</v>
       </c>
       <c r="G1031" t="n">
-        <v>4.70168256759644</v>
+        <v>4.70168209075928</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>5.05399990081787</v>
       </c>
       <c r="G1036" t="n">
-        <v>4.80823659896851</v>
+        <v>4.80823612213135</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1038" t="n">
-        <v>4.58561563491821</v>
+        <v>4.58561515808105</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>4.91800022125244</v>
       </c>
       <c r="G1039" t="n">
-        <v>4.67884969711304</v>
+        <v>4.6788501739502</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1041" t="n">
-        <v>4.77588987350464</v>
+        <v>4.77588939666748</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>4.94799995422363</v>
       </c>
       <c r="G1042" t="n">
-        <v>4.70739126205444</v>
+        <v>4.70739078521729</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>5.25</v>
       </c>
       <c r="G1046" t="n">
-        <v>4.99470567703247</v>
+        <v>4.99470520019531</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>5.00099992752075</v>
       </c>
       <c r="G1057" t="n">
-        <v>4.75781393051147</v>
+        <v>4.75781345367432</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>4.77899980545044</v>
       </c>
       <c r="G1059" t="n">
-        <v>4.54660844802856</v>
+        <v>4.54660892486572</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>4.32100009918213</v>
       </c>
       <c r="G1062" t="n">
-        <v>4.11088085174561</v>
+        <v>4.11088037490845</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>3.67199993133545</v>
       </c>
       <c r="G1064" t="n">
-        <v>3.49343943595886</v>
+        <v>3.49343967437744</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>3.81699991226196</v>
       </c>
       <c r="G1065" t="n">
-        <v>3.63138866424561</v>
+        <v>3.63138842582703</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>3.7739999294281</v>
       </c>
       <c r="G1071" t="n">
-        <v>3.59047961235046</v>
+        <v>3.59047937393188</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>3.79299998283386</v>
       </c>
       <c r="G1081" t="n">
-        <v>3.60855579376221</v>
+        <v>3.60855555534363</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>3.92400002479553</v>
       </c>
       <c r="G1083" t="n">
-        <v>3.73318552970886</v>
+        <v>3.73318529129028</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G1085" t="n">
-        <v>3.61045837402344</v>
+        <v>3.61045861244202</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>3.53399991989136</v>
       </c>
       <c r="G1088" t="n">
-        <v>3.36214995384216</v>
+        <v>3.36215019226074</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>3.44600009918213</v>
       </c>
       <c r="G1097" t="n">
-        <v>3.27842974662781</v>
+        <v>3.27842950820923</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>3.64400005340576</v>
       </c>
       <c r="G1098" t="n">
-        <v>3.46680116653442</v>
+        <v>3.466801404953</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>3.6159999370575</v>
       </c>
       <c r="G1099" t="n">
-        <v>3.44016289710999</v>
+        <v>3.44016265869141</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>3.53399991989136</v>
       </c>
       <c r="G1101" t="n">
-        <v>3.36214995384216</v>
+        <v>3.36215019226074</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>3.50399994850159</v>
       </c>
       <c r="G1102" t="n">
-        <v>3.33360910415649</v>
+        <v>3.33360886573792</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>3.42799997329712</v>
       </c>
       <c r="G1103" t="n">
-        <v>3.2613046169281</v>
+        <v>3.26130485534668</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1104" t="n">
-        <v>3.29174852371216</v>
+        <v>3.29174876213074</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>3.20700001716614</v>
       </c>
       <c r="G1114" t="n">
-        <v>3.0510516166687</v>
+        <v>3.05105137825012</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>3.30399990081787</v>
       </c>
       <c r="G1116" t="n">
-        <v>3.14333438873291</v>
+        <v>3.14333462715149</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>3.3050000667572</v>
       </c>
       <c r="G1117" t="n">
-        <v>3.14428615570068</v>
+        <v>3.1442859172821</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>3.41400003433228</v>
       </c>
       <c r="G1120" t="n">
-        <v>3.24798560142517</v>
+        <v>3.24798536300659</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>3.52300000190735</v>
       </c>
       <c r="G1121" t="n">
-        <v>3.35168528556824</v>
+        <v>3.35168504714966</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>3.71600008010864</v>
       </c>
       <c r="G1127" t="n">
-        <v>3.5353000164032</v>
+        <v>3.53530025482178</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>3.53399991989136</v>
       </c>
       <c r="G1129" t="n">
-        <v>3.36214995384216</v>
+        <v>3.36215019226074</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1133" t="n">
-        <v>3.49153685569763</v>
+        <v>3.49153709411621</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -71664,6 +71664,32 @@
         <v>5.56300020217896</v>
       </c>
       <c r="H2742" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2743">
+      <c r="A2743" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B2743" t="n">
+        <v>4704627</v>
+      </c>
+      <c r="C2743" t="n">
+        <v>5.71500015258789</v>
+      </c>
+      <c r="D2743" t="n">
+        <v>5.5770001411438</v>
+      </c>
+      <c r="E2743" t="n">
+        <v>5.59000015258789</v>
+      </c>
+      <c r="F2743" t="n">
+        <v>5.67000007629395</v>
+      </c>
+      <c r="G2743" t="n">
+        <v>5.67000007629395</v>
+      </c>
+      <c r="H2743" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/TIT.MI.xlsx
+++ b/data/TIT.MI.xlsx
@@ -71693,6 +71693,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2744">
+      <c r="A2744" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B2744" t="n">
+        <v>3247389</v>
+      </c>
+      <c r="C2744" t="n">
+        <v>5.73000001907349</v>
+      </c>
+      <c r="D2744" t="n">
+        <v>5.59200000762939</v>
+      </c>
+      <c r="E2744" t="n">
+        <v>5.65899991989136</v>
+      </c>
+      <c r="F2744" t="n">
+        <v>5.59200000762939</v>
+      </c>
+      <c r="G2744" t="n">
+        <v>5.59200000762939</v>
+      </c>
+      <c r="H2744" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TIT.MI.xlsx
+++ b/data/TIT.MI.xlsx
@@ -775,7 +775,7 @@
         <v>9.76500034332275</v>
       </c>
       <c r="G14" t="n">
-        <v>9.29015159606934</v>
+        <v>9.29015254974365</v>
       </c>
       <c r="H14" t="n">
         <v>12465433</v>
@@ -949,7 +949,7 @@
         <v>9.77000045776367</v>
       </c>
       <c r="G20" t="n">
-        <v>9.29490852355957</v>
+        <v>9.29490947723389</v>
       </c>
       <c r="H20" t="n">
         <v>21107831</v>
@@ -1152,7 +1152,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G27" t="n">
-        <v>7.99152803421021</v>
+        <v>7.99152851104736</v>
       </c>
       <c r="H27" t="n">
         <v>18362675</v>
@@ -1181,7 +1181,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G28" t="n">
-        <v>8.27694034576416</v>
+        <v>8.27693939208984</v>
       </c>
       <c r="H28" t="n">
         <v>22554264</v>
@@ -1239,7 +1239,7 @@
         <v>8.25500011444092</v>
       </c>
       <c r="G30" t="n">
-        <v>7.85357904434204</v>
+        <v>7.8535795211792</v>
       </c>
       <c r="H30" t="n">
         <v>17371217</v>
@@ -1268,7 +1268,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G31" t="n">
-        <v>8.17228889465332</v>
+        <v>8.17228984832764</v>
       </c>
       <c r="H31" t="n">
         <v>10187944</v>
@@ -1297,7 +1297,7 @@
         <v>8.76500034332275</v>
       </c>
       <c r="G32" t="n">
-        <v>8.33877944946289</v>
+        <v>8.33878040313721</v>
       </c>
       <c r="H32" t="n">
         <v>9462652</v>
@@ -1326,7 +1326,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G33" t="n">
-        <v>7.80125379562378</v>
+        <v>7.80125331878662</v>
       </c>
       <c r="H33" t="n">
         <v>28696243</v>
@@ -1587,7 +1587,7 @@
         <v>8.98999977111816</v>
       </c>
       <c r="G42" t="n">
-        <v>8.55283832550049</v>
+        <v>8.55283737182617</v>
       </c>
       <c r="H42" t="n">
         <v>10915001</v>
@@ -1645,7 +1645,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G44" t="n">
-        <v>8.98095512390137</v>
+        <v>8.98095607757568</v>
       </c>
       <c r="H44" t="n">
         <v>13756209</v>
@@ -1703,7 +1703,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G46" t="n">
-        <v>9.70399856567383</v>
+        <v>9.70399951934814</v>
       </c>
       <c r="H46" t="n">
         <v>20342560</v>
@@ -1732,7 +1732,7 @@
         <v>9.82499980926514</v>
       </c>
       <c r="G47" t="n">
-        <v>9.34723472595215</v>
+        <v>9.34723377227783</v>
       </c>
       <c r="H47" t="n">
         <v>11169591</v>
@@ -1790,7 +1790,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G49" t="n">
-        <v>9.64691734313965</v>
+        <v>9.64691638946533</v>
       </c>
       <c r="H49" t="n">
         <v>18523100</v>
@@ -1848,7 +1848,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G51" t="n">
-        <v>9.91330051422119</v>
+        <v>9.91330146789551</v>
       </c>
       <c r="H51" t="n">
         <v>10987806</v>
@@ -1877,7 +1877,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G52" t="n">
-        <v>9.81816387176514</v>
+        <v>9.81816291809082</v>
       </c>
       <c r="H52" t="n">
         <v>6496305</v>
@@ -1935,7 +1935,7 @@
         <v>10.3299999237061</v>
       </c>
       <c r="G54" t="n">
-        <v>9.82767772674561</v>
+        <v>9.82767677307129</v>
       </c>
       <c r="H54" t="n">
         <v>5795315</v>
@@ -2022,7 +2022,7 @@
         <v>10.4099998474121</v>
       </c>
       <c r="G57" t="n">
-        <v>9.90378665924072</v>
+        <v>9.90378761291504</v>
       </c>
       <c r="H57" t="n">
         <v>9694375</v>
@@ -2225,7 +2225,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G64" t="n">
-        <v>8.70505809783936</v>
+        <v>8.70505714416504</v>
       </c>
       <c r="H64" t="n">
         <v>14609221</v>
@@ -2283,7 +2283,7 @@
         <v>8.58500003814697</v>
       </c>
       <c r="G66" t="n">
-        <v>8.16753196716309</v>
+        <v>8.1675329208374</v>
       </c>
       <c r="H66" t="n">
         <v>11386012</v>
@@ -2312,7 +2312,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G67" t="n">
-        <v>8.18180370330811</v>
+        <v>8.18180274963379</v>
       </c>
       <c r="H67" t="n">
         <v>8994634</v>
@@ -2341,7 +2341,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G68" t="n">
-        <v>7.95347309112549</v>
+        <v>7.95347356796265</v>
       </c>
       <c r="H68" t="n">
         <v>8054619</v>
@@ -2399,7 +2399,7 @@
         <v>8.98999977111816</v>
       </c>
       <c r="G70" t="n">
-        <v>8.55283832550049</v>
+        <v>8.55283737182617</v>
       </c>
       <c r="H70" t="n">
         <v>7769877</v>
@@ -2718,7 +2718,7 @@
         <v>8.65499973297119</v>
       </c>
       <c r="G81" t="n">
-        <v>8.23412799835205</v>
+        <v>8.23412895202637</v>
       </c>
       <c r="H81" t="n">
         <v>11095524</v>
@@ -2776,7 +2776,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G83" t="n">
-        <v>8.25791358947754</v>
+        <v>8.25791263580322</v>
       </c>
       <c r="H83" t="n">
         <v>15796951</v>
@@ -2834,7 +2834,7 @@
         <v>8.46500015258789</v>
       </c>
       <c r="G85" t="n">
-        <v>8.05336856842041</v>
+        <v>8.05336761474609</v>
       </c>
       <c r="H85" t="n">
         <v>6739223</v>
@@ -2863,7 +2863,7 @@
         <v>8.36499977111816</v>
       </c>
       <c r="G86" t="n">
-        <v>7.95823001861572</v>
+        <v>7.95823049545288</v>
       </c>
       <c r="H86" t="n">
         <v>7439860</v>
@@ -2892,7 +2892,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G87" t="n">
-        <v>8.04861164093018</v>
+        <v>8.04861068725586</v>
       </c>
       <c r="H87" t="n">
         <v>6088332</v>
@@ -3037,7 +3037,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G92" t="n">
-        <v>8.05812549591064</v>
+        <v>8.05812454223633</v>
       </c>
       <c r="H92" t="n">
         <v>7818052</v>
@@ -3153,7 +3153,7 @@
         <v>8.48999977111816</v>
       </c>
       <c r="G96" t="n">
-        <v>8.07715225219727</v>
+        <v>8.07715129852295</v>
       </c>
       <c r="H96" t="n">
         <v>11841822</v>
@@ -3211,7 +3211,7 @@
         <v>8.30500030517578</v>
       </c>
       <c r="G98" t="n">
-        <v>7.90114879608154</v>
+        <v>7.90114784240723</v>
       </c>
       <c r="H98" t="n">
         <v>9583225</v>
@@ -3240,7 +3240,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G99" t="n">
-        <v>7.87736368179321</v>
+        <v>7.87736320495605</v>
       </c>
       <c r="H99" t="n">
         <v>7171888</v>
@@ -3327,7 +3327,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G102" t="n">
-        <v>7.91541862487793</v>
+        <v>7.91541814804077</v>
       </c>
       <c r="H102" t="n">
         <v>15847474</v>
@@ -3385,7 +3385,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G104" t="n">
-        <v>8.27694034576416</v>
+        <v>8.27693939208984</v>
       </c>
       <c r="H104" t="n">
         <v>8314517</v>
@@ -3675,7 +3675,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G114" t="n">
-        <v>7.82028150558472</v>
+        <v>7.82028198242188</v>
       </c>
       <c r="H114" t="n">
         <v>14068153</v>
@@ -3704,7 +3704,7 @@
         <v>7.91499996185303</v>
       </c>
       <c r="G115" t="n">
-        <v>7.53011274337769</v>
+        <v>7.53011322021484</v>
       </c>
       <c r="H115" t="n">
         <v>12688239</v>
@@ -3762,7 +3762,7 @@
         <v>7.59499979019165</v>
       </c>
       <c r="G117" t="n">
-        <v>7.22567319869995</v>
+        <v>7.22567367553711</v>
       </c>
       <c r="H117" t="n">
         <v>14127681</v>
@@ -3791,7 +3791,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G118" t="n">
-        <v>7.04015636444092</v>
+        <v>7.04015588760376</v>
       </c>
       <c r="H118" t="n">
         <v>12062526</v>
@@ -3936,7 +3936,7 @@
         <v>8.27499961853027</v>
       </c>
       <c r="G123" t="n">
-        <v>7.87260675430298</v>
+        <v>7.87260627746582</v>
       </c>
       <c r="H123" t="n">
         <v>12615589</v>
@@ -3994,7 +3994,7 @@
         <v>6.67500019073486</v>
       </c>
       <c r="G125" t="n">
-        <v>6.35041093826294</v>
+        <v>6.3504114151001</v>
       </c>
       <c r="H125" t="n">
         <v>23209498</v>
@@ -4052,7 +4052,7 @@
         <v>7.44500017166138</v>
       </c>
       <c r="G127" t="n">
-        <v>7.08296775817871</v>
+        <v>7.08296823501587</v>
       </c>
       <c r="H127" t="n">
         <v>14352211</v>
@@ -4110,7 +4110,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G129" t="n">
-        <v>7.04015636444092</v>
+        <v>7.04015588760376</v>
       </c>
       <c r="H129" t="n">
         <v>8980366</v>
@@ -4226,7 +4226,7 @@
         <v>6.33500003814697</v>
       </c>
       <c r="G133" t="n">
-        <v>6.02694416046143</v>
+        <v>6.02694463729858</v>
       </c>
       <c r="H133" t="n">
         <v>13905809</v>
@@ -4284,7 +4284,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G135" t="n">
-        <v>6.30759954452515</v>
+        <v>6.30759906768799</v>
       </c>
       <c r="H135" t="n">
         <v>6922559</v>
@@ -4313,7 +4313,7 @@
         <v>6.92500019073486</v>
       </c>
       <c r="G136" t="n">
-        <v>6.58825397491455</v>
+        <v>6.58825445175171</v>
       </c>
       <c r="H136" t="n">
         <v>10111814</v>
@@ -4429,7 +4429,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G140" t="n">
-        <v>6.60252523422241</v>
+        <v>6.60252475738525</v>
       </c>
       <c r="H140" t="n">
         <v>13382865</v>
@@ -4487,7 +4487,7 @@
         <v>6.86499977111816</v>
       </c>
       <c r="G142" t="n">
-        <v>6.53117179870605</v>
+        <v>6.5311713218689</v>
       </c>
       <c r="H142" t="n">
         <v>8811876</v>
@@ -4574,7 +4574,7 @@
         <v>7</v>
       </c>
       <c r="G145" t="n">
-        <v>6.65960693359375</v>
+        <v>6.65960741043091</v>
       </c>
       <c r="H145" t="n">
         <v>8398609</v>
@@ -4632,7 +4632,7 @@
         <v>7.46999979019165</v>
       </c>
       <c r="G147" t="n">
-        <v>7.10675191879272</v>
+        <v>7.10675239562988</v>
       </c>
       <c r="H147" t="n">
         <v>29073903</v>
@@ -4690,7 +4690,7 @@
         <v>7.63500022888184</v>
       </c>
       <c r="G149" t="n">
-        <v>7.26372909545898</v>
+        <v>7.26372861862183</v>
       </c>
       <c r="H149" t="n">
         <v>10594903</v>
@@ -4748,7 +4748,7 @@
         <v>7.44500017166138</v>
       </c>
       <c r="G151" t="n">
-        <v>7.08296775817871</v>
+        <v>7.08296823501587</v>
       </c>
       <c r="H151" t="n">
         <v>8748243</v>
@@ -4893,7 +4893,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G156" t="n">
-        <v>7.24945831298828</v>
+        <v>7.24945783615112</v>
       </c>
       <c r="H156" t="n">
         <v>4135572</v>
@@ -5125,7 +5125,7 @@
         <v>7.92999982833862</v>
       </c>
       <c r="G164" t="n">
-        <v>7.54438304901123</v>
+        <v>7.54438352584839</v>
       </c>
       <c r="H164" t="n">
         <v>4924973</v>
@@ -5212,7 +5212,7 @@
         <v>8.0649995803833</v>
       </c>
       <c r="G167" t="n">
-        <v>7.67281866073608</v>
+        <v>7.67281818389893</v>
       </c>
       <c r="H167" t="n">
         <v>5554419</v>
@@ -5299,7 +5299,7 @@
         <v>8.24499988555908</v>
       </c>
       <c r="G170" t="n">
-        <v>7.84406518936157</v>
+        <v>7.84406566619873</v>
       </c>
       <c r="H170" t="n">
         <v>6352724</v>
@@ -5328,7 +5328,7 @@
         <v>8.13500022888184</v>
       </c>
       <c r="G171" t="n">
-        <v>7.73941516876221</v>
+        <v>7.73941469192505</v>
       </c>
       <c r="H171" t="n">
         <v>7750471</v>
@@ -5357,7 +5357,7 @@
         <v>8.16499996185303</v>
       </c>
       <c r="G172" t="n">
-        <v>7.7679557800293</v>
+        <v>7.76795625686646</v>
       </c>
       <c r="H172" t="n">
         <v>8273298</v>
@@ -5386,7 +5386,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G173" t="n">
-        <v>7.80125379562378</v>
+        <v>7.80125331878662</v>
       </c>
       <c r="H173" t="n">
         <v>5239033</v>
@@ -5473,7 +5473,7 @@
         <v>8.04500007629395</v>
       </c>
       <c r="G176" t="n">
-        <v>7.6537914276123</v>
+        <v>7.65379095077515</v>
       </c>
       <c r="H176" t="n">
         <v>7646216</v>
@@ -5502,7 +5502,7 @@
         <v>8.16499996185303</v>
       </c>
       <c r="G177" t="n">
-        <v>7.7679557800293</v>
+        <v>7.76795625686646</v>
       </c>
       <c r="H177" t="n">
         <v>6137326</v>
@@ -5531,7 +5531,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G178" t="n">
-        <v>7.64903402328491</v>
+        <v>7.64903450012207</v>
       </c>
       <c r="H178" t="n">
         <v>7450630</v>
@@ -5560,7 +5560,7 @@
         <v>7.88500022888184</v>
       </c>
       <c r="G179" t="n">
-        <v>7.5015721321106</v>
+        <v>7.50157165527344</v>
       </c>
       <c r="H179" t="n">
         <v>10968844</v>
@@ -5647,7 +5647,7 @@
         <v>7.53499984741211</v>
       </c>
       <c r="G182" t="n">
-        <v>7.16859149932861</v>
+        <v>7.16859102249146</v>
       </c>
       <c r="H182" t="n">
         <v>8919248</v>
@@ -5734,7 +5734,7 @@
         <v>7.28499984741211</v>
       </c>
       <c r="G185" t="n">
-        <v>6.930748462677</v>
+        <v>6.93074798583984</v>
       </c>
       <c r="H185" t="n">
         <v>7139176</v>
@@ -5821,7 +5821,7 @@
         <v>7.63500022888184</v>
       </c>
       <c r="G188" t="n">
-        <v>7.26372909545898</v>
+        <v>7.26372861862183</v>
       </c>
       <c r="H188" t="n">
         <v>4604142</v>
@@ -5879,7 +5879,7 @@
         <v>7.34499979019165</v>
       </c>
       <c r="G190" t="n">
-        <v>6.98783016204834</v>
+        <v>6.9878306388855</v>
       </c>
       <c r="H190" t="n">
         <v>5769993</v>
@@ -5908,7 +5908,7 @@
         <v>7.49499988555908</v>
       </c>
       <c r="G191" t="n">
-        <v>7.1305365562439</v>
+        <v>7.13053607940674</v>
       </c>
       <c r="H191" t="n">
         <v>4422318</v>
@@ -5966,7 +5966,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G193" t="n">
-        <v>7.03064250946045</v>
+        <v>7.03064203262329</v>
       </c>
       <c r="H193" t="n">
         <v>9011031</v>
@@ -6053,7 +6053,7 @@
         <v>7.29500007629395</v>
       </c>
       <c r="G196" t="n">
-        <v>6.94026231765747</v>
+        <v>6.94026184082031</v>
       </c>
       <c r="H196" t="n">
         <v>10575030</v>
@@ -6140,7 +6140,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G199" t="n">
-        <v>7.04015636444092</v>
+        <v>7.04015588760376</v>
       </c>
       <c r="H199" t="n">
         <v>8616275</v>
@@ -6169,7 +6169,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G200" t="n">
-        <v>6.86890888214111</v>
+        <v>6.86890840530396</v>
       </c>
       <c r="H200" t="n">
         <v>8236131</v>
@@ -6227,7 +6227,7 @@
         <v>6.94500017166138</v>
       </c>
       <c r="G202" t="n">
-        <v>6.60728216171265</v>
+        <v>6.60728168487549</v>
       </c>
       <c r="H202" t="n">
         <v>17317483</v>
@@ -6314,7 +6314,7 @@
         <v>7.57499980926514</v>
       </c>
       <c r="G205" t="n">
-        <v>7.20664596557617</v>
+        <v>7.20664644241333</v>
       </c>
       <c r="H205" t="n">
         <v>13042674</v>
@@ -6372,7 +6372,7 @@
         <v>7.59499979019165</v>
       </c>
       <c r="G207" t="n">
-        <v>7.22567319869995</v>
+        <v>7.22567367553711</v>
       </c>
       <c r="H207" t="n">
         <v>5770682</v>
@@ -6401,7 +6401,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G208" t="n">
-        <v>7.35410928726196</v>
+        <v>7.3541088104248</v>
       </c>
       <c r="H208" t="n">
         <v>11041706</v>
@@ -6430,7 +6430,7 @@
         <v>7.92999982833862</v>
       </c>
       <c r="G209" t="n">
-        <v>7.54438304901123</v>
+        <v>7.54438352584839</v>
       </c>
       <c r="H209" t="n">
         <v>12562957</v>
@@ -6633,7 +6633,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G216" t="n">
-        <v>7.35410928726196</v>
+        <v>7.3541088104248</v>
       </c>
       <c r="H216" t="n">
         <v>11074256</v>
@@ -6662,7 +6662,7 @@
         <v>7.70499992370605</v>
       </c>
       <c r="G217" t="n">
-        <v>7.33032464981079</v>
+        <v>7.33032417297363</v>
       </c>
       <c r="H217" t="n">
         <v>6751462</v>
@@ -6778,7 +6778,7 @@
         <v>7.45499992370605</v>
       </c>
       <c r="G221" t="n">
-        <v>7.09248161315918</v>
+        <v>7.09248113632202</v>
       </c>
       <c r="H221" t="n">
         <v>19305315</v>
@@ -6952,7 +6952,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G227" t="n">
-        <v>6.67863416671753</v>
+        <v>6.67863464355469</v>
       </c>
       <c r="H227" t="n">
         <v>15148923</v>
@@ -6981,7 +6981,7 @@
         <v>6.86499977111816</v>
       </c>
       <c r="G228" t="n">
-        <v>6.53117179870605</v>
+        <v>6.5311713218689</v>
       </c>
       <c r="H228" t="n">
         <v>15141472</v>
@@ -7097,7 +7097,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G232" t="n">
-        <v>6.70717620849609</v>
+        <v>6.70717573165894</v>
       </c>
       <c r="H232" t="n">
         <v>6631825</v>
@@ -7126,7 +7126,7 @@
         <v>7.14499998092651</v>
       </c>
       <c r="G233" t="n">
-        <v>6.79755592346191</v>
+        <v>6.79755640029907</v>
       </c>
       <c r="H233" t="n">
         <v>7685848</v>
@@ -7300,7 +7300,7 @@
         <v>7</v>
       </c>
       <c r="G239" t="n">
-        <v>6.65960693359375</v>
+        <v>6.65960741043091</v>
       </c>
       <c r="H239" t="n">
         <v>16092872</v>
@@ -7358,7 +7358,7 @@
         <v>7.54500007629395</v>
       </c>
       <c r="G241" t="n">
-        <v>7.17810535430908</v>
+        <v>7.17810487747192</v>
       </c>
       <c r="H241" t="n">
         <v>14162922</v>
@@ -7416,7 +7416,7 @@
         <v>7.625</v>
       </c>
       <c r="G243" t="n">
-        <v>7.25421524047852</v>
+        <v>7.25421476364136</v>
       </c>
       <c r="H243" t="n">
         <v>7313055</v>
@@ -7561,7 +7561,7 @@
         <v>8.06999969482422</v>
       </c>
       <c r="G248" t="n">
-        <v>7.67757558822632</v>
+        <v>7.67757511138916</v>
       </c>
       <c r="H248" t="n">
         <v>19683266</v>
@@ -7648,7 +7648,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G251" t="n">
-        <v>7.99152803421021</v>
+        <v>7.99152851104736</v>
       </c>
       <c r="H251" t="n">
         <v>10995964</v>
@@ -7735,7 +7735,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G254" t="n">
-        <v>8.27694034576416</v>
+        <v>8.27693939208984</v>
       </c>
       <c r="H254" t="n">
         <v>7105744</v>
@@ -7764,7 +7764,7 @@
         <v>8.42500019073486</v>
       </c>
       <c r="G255" t="n">
-        <v>8.01531219482422</v>
+        <v>8.01531314849854</v>
       </c>
       <c r="H255" t="n">
         <v>7953684</v>
@@ -7822,7 +7822,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G257" t="n">
-        <v>7.96298694610596</v>
+        <v>7.96298742294312</v>
       </c>
       <c r="H257" t="n">
         <v>4473749</v>
@@ -7851,7 +7851,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G258" t="n">
-        <v>8.16277503967285</v>
+        <v>8.16277599334717</v>
       </c>
       <c r="H258" t="n">
         <v>6919849</v>
@@ -7938,7 +7938,7 @@
         <v>8.42500019073486</v>
       </c>
       <c r="G261" t="n">
-        <v>8.01531219482422</v>
+        <v>8.01531314849854</v>
       </c>
       <c r="H261" t="n">
         <v>8691609</v>
@@ -7996,7 +7996,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G263" t="n">
-        <v>7.82028150558472</v>
+        <v>7.82028198242188</v>
       </c>
       <c r="H263" t="n">
         <v>9698154</v>
@@ -8025,7 +8025,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G264" t="n">
-        <v>7.87736368179321</v>
+        <v>7.87736320495605</v>
       </c>
       <c r="H264" t="n">
         <v>8049414</v>
@@ -8054,7 +8054,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G265" t="n">
-        <v>8.04861164093018</v>
+        <v>8.04861068725586</v>
       </c>
       <c r="H265" t="n">
         <v>10193124</v>
@@ -8083,7 +8083,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G266" t="n">
-        <v>7.93444633483887</v>
+        <v>7.93444681167603</v>
       </c>
       <c r="H266" t="n">
         <v>5591385</v>
@@ -8141,7 +8141,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G268" t="n">
-        <v>8.10569381713867</v>
+        <v>8.10569286346436</v>
       </c>
       <c r="H268" t="n">
         <v>4819501</v>
@@ -8170,7 +8170,7 @@
         <v>8.375</v>
       </c>
       <c r="G269" t="n">
-        <v>7.96774387359619</v>
+        <v>7.96774482727051</v>
       </c>
       <c r="H269" t="n">
         <v>6854564</v>
@@ -8199,7 +8199,7 @@
         <v>8.3100004196167</v>
       </c>
       <c r="G270" t="n">
-        <v>7.90590572357178</v>
+        <v>7.90590524673462</v>
       </c>
       <c r="H270" t="n">
         <v>7624065</v>
@@ -8228,7 +8228,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G271" t="n">
-        <v>7.99152803421021</v>
+        <v>7.99152851104736</v>
       </c>
       <c r="H271" t="n">
         <v>15001217</v>
@@ -8257,7 +8257,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G272" t="n">
-        <v>8.04861164093018</v>
+        <v>8.04861068725586</v>
       </c>
       <c r="H272" t="n">
         <v>7357311</v>
@@ -8286,7 +8286,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G273" t="n">
-        <v>7.99152803421021</v>
+        <v>7.99152851104736</v>
       </c>
       <c r="H273" t="n">
         <v>6892052</v>
@@ -8315,7 +8315,7 @@
         <v>8.3100004196167</v>
       </c>
       <c r="G274" t="n">
-        <v>7.90590572357178</v>
+        <v>7.90590524673462</v>
       </c>
       <c r="H274" t="n">
         <v>10051498</v>
@@ -8344,7 +8344,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G275" t="n">
-        <v>7.82979440689087</v>
+        <v>7.82979536056519</v>
       </c>
       <c r="H275" t="n">
         <v>9477679</v>
@@ -8518,7 +8518,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G281" t="n">
-        <v>7.59195232391357</v>
+        <v>7.59195184707642</v>
       </c>
       <c r="H281" t="n">
         <v>6833809</v>
@@ -8634,7 +8634,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G285" t="n">
-        <v>7.79173994064331</v>
+        <v>7.79174041748047</v>
       </c>
       <c r="H285" t="n">
         <v>8180031</v>
@@ -8663,7 +8663,7 @@
         <v>8.25</v>
       </c>
       <c r="G286" t="n">
-        <v>7.84882211685181</v>
+        <v>7.84882259368896</v>
       </c>
       <c r="H286" t="n">
         <v>8035948</v>
@@ -8692,7 +8692,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G287" t="n">
-        <v>7.64903402328491</v>
+        <v>7.64903450012207</v>
       </c>
       <c r="H287" t="n">
         <v>9027559</v>
@@ -8750,7 +8750,7 @@
         <v>7.97499990463257</v>
       </c>
       <c r="G289" t="n">
-        <v>7.58719539642334</v>
+        <v>7.58719491958618</v>
       </c>
       <c r="H289" t="n">
         <v>7815676</v>
@@ -8808,7 +8808,7 @@
         <v>7.91499996185303</v>
       </c>
       <c r="G291" t="n">
-        <v>7.53011274337769</v>
+        <v>7.53011322021484</v>
       </c>
       <c r="H291" t="n">
         <v>6709166</v>
@@ -8895,7 +8895,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G294" t="n">
-        <v>7.3255672454834</v>
+        <v>7.32556772232056</v>
       </c>
       <c r="H294" t="n">
         <v>10570127</v>
@@ -8924,7 +8924,7 @@
         <v>7.59499979019165</v>
       </c>
       <c r="G295" t="n">
-        <v>7.22567319869995</v>
+        <v>7.22567367553711</v>
       </c>
       <c r="H295" t="n">
         <v>15446807</v>
@@ -9185,7 +9185,7 @@
         <v>7.79500007629395</v>
       </c>
       <c r="G304" t="n">
-        <v>7.41594839096069</v>
+        <v>7.41594791412354</v>
       </c>
       <c r="H304" t="n">
         <v>5768451</v>
@@ -9214,7 +9214,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G305" t="n">
-        <v>7.35410928726196</v>
+        <v>7.3541088104248</v>
       </c>
       <c r="H305" t="n">
         <v>8662340</v>
@@ -9243,7 +9243,7 @@
         <v>7.83500003814697</v>
       </c>
       <c r="G306" t="n">
-        <v>7.45400333404541</v>
+        <v>7.45400285720825</v>
       </c>
       <c r="H306" t="n">
         <v>8558245</v>
@@ -9359,7 +9359,7 @@
         <v>7.88500022888184</v>
       </c>
       <c r="G310" t="n">
-        <v>7.5015721321106</v>
+        <v>7.50157165527344</v>
       </c>
       <c r="H310" t="n">
         <v>9967793</v>
@@ -9475,7 +9475,7 @@
         <v>8.125</v>
       </c>
       <c r="G314" t="n">
-        <v>7.72990083694458</v>
+        <v>7.72990131378174</v>
       </c>
       <c r="H314" t="n">
         <v>8729316</v>
@@ -9562,7 +9562,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G317" t="n">
-        <v>7.93444633483887</v>
+        <v>7.93444681167603</v>
       </c>
       <c r="H317" t="n">
         <v>9638120</v>
@@ -9620,7 +9620,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G319" t="n">
-        <v>8.10569381713867</v>
+        <v>8.10569286346436</v>
       </c>
       <c r="H319" t="n">
         <v>9247079</v>
@@ -9649,7 +9649,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G320" t="n">
-        <v>8.01055526733398</v>
+        <v>8.0105562210083</v>
       </c>
       <c r="H320" t="n">
         <v>7285311</v>
@@ -9678,7 +9678,7 @@
         <v>8.45499992370605</v>
       </c>
       <c r="G321" t="n">
-        <v>8.04385471343994</v>
+        <v>8.04385375976562</v>
       </c>
       <c r="H321" t="n">
         <v>8408909</v>
@@ -9794,7 +9794,7 @@
         <v>8.13500022888184</v>
       </c>
       <c r="G325" t="n">
-        <v>7.73941516876221</v>
+        <v>7.73941469192505</v>
       </c>
       <c r="H325" t="n">
         <v>6312505</v>
@@ -9910,7 +9910,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G329" t="n">
-        <v>7.64903402328491</v>
+        <v>7.64903450012207</v>
       </c>
       <c r="H329" t="n">
         <v>5813093</v>
@@ -9939,7 +9939,7 @@
         <v>8.04500007629395</v>
       </c>
       <c r="G330" t="n">
-        <v>7.6537914276123</v>
+        <v>7.65379095077515</v>
       </c>
       <c r="H330" t="n">
         <v>5005452</v>
@@ -10084,7 +10084,7 @@
         <v>7.875</v>
       </c>
       <c r="G335" t="n">
-        <v>7.49205827713013</v>
+        <v>7.49205780029297</v>
       </c>
       <c r="H335" t="n">
         <v>7752172</v>
@@ -10142,7 +10142,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G337" t="n">
-        <v>7.87736368179321</v>
+        <v>7.87736320495605</v>
       </c>
       <c r="H337" t="n">
         <v>9607132</v>
@@ -10403,7 +10403,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G346" t="n">
-        <v>8.50527000427246</v>
+        <v>8.50526905059814</v>
       </c>
       <c r="H346" t="n">
         <v>9675664</v>
@@ -10548,7 +10548,7 @@
         <v>9.14500045776367</v>
       </c>
       <c r="G351" t="n">
-        <v>8.70030212402344</v>
+        <v>8.70030117034912</v>
       </c>
       <c r="H351" t="n">
         <v>9357770</v>
@@ -10751,7 +10751,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G358" t="n">
-        <v>8.23888492584229</v>
+        <v>8.2388858795166</v>
       </c>
       <c r="H358" t="n">
         <v>7073837</v>
@@ -10809,7 +10809,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G360" t="n">
-        <v>8.05812549591064</v>
+        <v>8.05812454223633</v>
       </c>
       <c r="H360" t="n">
         <v>6620743</v>
@@ -10838,7 +10838,7 @@
         <v>8.3100004196167</v>
       </c>
       <c r="G361" t="n">
-        <v>7.90590572357178</v>
+        <v>7.90590524673462</v>
       </c>
       <c r="H361" t="n">
         <v>14291998</v>
@@ -10896,7 +10896,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G363" t="n">
-        <v>7.93444633483887</v>
+        <v>7.93444681167603</v>
       </c>
       <c r="H363" t="n">
         <v>6865591</v>
@@ -11012,7 +11012,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G367" t="n">
-        <v>7.88687801361084</v>
+        <v>7.88687753677368</v>
       </c>
       <c r="H367" t="n">
         <v>7688881</v>
@@ -11041,7 +11041,7 @@
         <v>8.3100004196167</v>
       </c>
       <c r="G368" t="n">
-        <v>7.90590572357178</v>
+        <v>7.90590524673462</v>
       </c>
       <c r="H368" t="n">
         <v>8382176</v>
@@ -11070,7 +11070,7 @@
         <v>8.25</v>
       </c>
       <c r="G369" t="n">
-        <v>7.84882211685181</v>
+        <v>7.84882259368896</v>
       </c>
       <c r="H369" t="n">
         <v>8979733</v>
@@ -11099,7 +11099,7 @@
         <v>8.27499961853027</v>
       </c>
       <c r="G370" t="n">
-        <v>7.87260675430298</v>
+        <v>7.87260627746582</v>
       </c>
       <c r="H370" t="n">
         <v>7573261</v>
@@ -11128,7 +11128,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G371" t="n">
-        <v>7.91541862487793</v>
+        <v>7.91541814804077</v>
       </c>
       <c r="H371" t="n">
         <v>7773160</v>
@@ -11157,7 +11157,7 @@
         <v>8.33500003814697</v>
       </c>
       <c r="G372" t="n">
-        <v>7.92968940734863</v>
+        <v>7.92968988418579</v>
       </c>
       <c r="H372" t="n">
         <v>10290370</v>
@@ -11186,7 +11186,7 @@
         <v>8.25</v>
       </c>
       <c r="G373" t="n">
-        <v>7.84882211685181</v>
+        <v>7.84882259368896</v>
       </c>
       <c r="H373" t="n">
         <v>7754055</v>
@@ -11273,7 +11273,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G376" t="n">
-        <v>7.88687801361084</v>
+        <v>7.88687753677368</v>
       </c>
       <c r="H376" t="n">
         <v>5684368</v>
@@ -11302,7 +11302,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G377" t="n">
-        <v>7.91541862487793</v>
+        <v>7.91541814804077</v>
       </c>
       <c r="H377" t="n">
         <v>7730283</v>
@@ -11331,7 +11331,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G378" t="n">
-        <v>7.82979440689087</v>
+        <v>7.82979536056519</v>
       </c>
       <c r="H378" t="n">
         <v>6359602</v>
@@ -11418,7 +11418,7 @@
         <v>8.0649995803833</v>
       </c>
       <c r="G381" t="n">
-        <v>7.67281866073608</v>
+        <v>7.67281818389893</v>
       </c>
       <c r="H381" t="n">
         <v>6950390</v>
@@ -11534,7 +11534,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G385" t="n">
-        <v>7.82979440689087</v>
+        <v>7.82979536056519</v>
       </c>
       <c r="H385" t="n">
         <v>6247925</v>
@@ -11592,7 +11592,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G387" t="n">
-        <v>7.63000726699829</v>
+        <v>7.63000774383545</v>
       </c>
       <c r="H387" t="n">
         <v>5489232</v>
@@ -11621,7 +11621,7 @@
         <v>8.04500007629395</v>
       </c>
       <c r="G388" t="n">
-        <v>7.6537914276123</v>
+        <v>7.65379095077515</v>
       </c>
       <c r="H388" t="n">
         <v>6520553</v>
@@ -11708,7 +11708,7 @@
         <v>7.88500022888184</v>
       </c>
       <c r="G391" t="n">
-        <v>7.5015721321106</v>
+        <v>7.50157165527344</v>
       </c>
       <c r="H391" t="n">
         <v>13737506</v>
@@ -11766,7 +11766,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G393" t="n">
-        <v>7.86785078048706</v>
+        <v>7.8678503036499</v>
       </c>
       <c r="H393" t="n">
         <v>13345067</v>
@@ -11795,7 +11795,7 @@
         <v>8.04500007629395</v>
       </c>
       <c r="G394" t="n">
-        <v>7.6537914276123</v>
+        <v>7.65379095077515</v>
       </c>
       <c r="H394" t="n">
         <v>12204969</v>
@@ -11940,7 +11940,7 @@
         <v>8.125</v>
       </c>
       <c r="G399" t="n">
-        <v>7.72990083694458</v>
+        <v>7.72990131378174</v>
       </c>
       <c r="H399" t="n">
         <v>8832091</v>
@@ -12056,7 +12056,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G403" t="n">
-        <v>8.23888492584229</v>
+        <v>8.2388858795166</v>
       </c>
       <c r="H403" t="n">
         <v>8102311</v>
@@ -12114,7 +12114,7 @@
         <v>8.70499992370605</v>
       </c>
       <c r="G405" t="n">
-        <v>8.28169727325439</v>
+        <v>8.28169631958008</v>
       </c>
       <c r="H405" t="n">
         <v>9759736</v>
@@ -12201,7 +12201,7 @@
         <v>8.70499992370605</v>
       </c>
       <c r="G408" t="n">
-        <v>8.28169727325439</v>
+        <v>8.28169631958008</v>
       </c>
       <c r="H408" t="n">
         <v>5695609</v>
@@ -12404,7 +12404,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G415" t="n">
-        <v>8.05812549591064</v>
+        <v>8.05812454223633</v>
       </c>
       <c r="H415" t="n">
         <v>4472224</v>
@@ -12491,7 +12491,7 @@
         <v>8.33500003814697</v>
       </c>
       <c r="G418" t="n">
-        <v>7.92968940734863</v>
+        <v>7.92968988418579</v>
       </c>
       <c r="H418" t="n">
         <v>4935773</v>
@@ -12520,7 +12520,7 @@
         <v>8.27499961853027</v>
       </c>
       <c r="G419" t="n">
-        <v>7.87260675430298</v>
+        <v>7.87260627746582</v>
       </c>
       <c r="H419" t="n">
         <v>4715292</v>
@@ -12752,7 +12752,7 @@
         <v>8.04500007629395</v>
       </c>
       <c r="G427" t="n">
-        <v>7.6537914276123</v>
+        <v>7.65379095077515</v>
       </c>
       <c r="H427" t="n">
         <v>6232506</v>
@@ -12810,7 +12810,7 @@
         <v>7.83500003814697</v>
       </c>
       <c r="G429" t="n">
-        <v>7.45400333404541</v>
+        <v>7.45400285720825</v>
       </c>
       <c r="H429" t="n">
         <v>6232104</v>
@@ -12984,7 +12984,7 @@
         <v>7.88500022888184</v>
       </c>
       <c r="G435" t="n">
-        <v>7.5015721321106</v>
+        <v>7.50157165527344</v>
       </c>
       <c r="H435" t="n">
         <v>6028869</v>
@@ -13129,7 +13129,7 @@
         <v>8.02499961853027</v>
       </c>
       <c r="G440" t="n">
-        <v>7.63476324081421</v>
+        <v>7.63476371765137</v>
       </c>
       <c r="H440" t="n">
         <v>11093394</v>
@@ -13187,7 +13187,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G442" t="n">
-        <v>7.57292509078979</v>
+        <v>7.57292461395264</v>
       </c>
       <c r="H442" t="n">
         <v>6659325</v>
@@ -13274,7 +13274,7 @@
         <v>7.93499994277954</v>
       </c>
       <c r="G445" t="n">
-        <v>7.54913997650146</v>
+        <v>7.54914045333862</v>
       </c>
       <c r="H445" t="n">
         <v>4915478</v>
@@ -13332,7 +13332,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G447" t="n">
-        <v>7.59195232391357</v>
+        <v>7.59195184707642</v>
       </c>
       <c r="H447" t="n">
         <v>9449306</v>
@@ -13535,7 +13535,7 @@
         <v>7.63500022888184</v>
       </c>
       <c r="G454" t="n">
-        <v>7.26372909545898</v>
+        <v>7.26372861862183</v>
       </c>
       <c r="H454" t="n">
         <v>6637000</v>
@@ -13564,7 +13564,7 @@
         <v>7.54500007629395</v>
       </c>
       <c r="G455" t="n">
-        <v>7.17810535430908</v>
+        <v>7.17810487747192</v>
       </c>
       <c r="H455" t="n">
         <v>8006633</v>
@@ -13680,7 +13680,7 @@
         <v>7.625</v>
       </c>
       <c r="G459" t="n">
-        <v>7.25421524047852</v>
+        <v>7.25421476364136</v>
       </c>
       <c r="H459" t="n">
         <v>9352175</v>
@@ -13796,7 +13796,7 @@
         <v>7.68499994277954</v>
       </c>
       <c r="G463" t="n">
-        <v>7.31129693984985</v>
+        <v>7.31129741668701</v>
       </c>
       <c r="H463" t="n">
         <v>11433018</v>
@@ -14057,7 +14057,7 @@
         <v>7.63500022888184</v>
       </c>
       <c r="G472" t="n">
-        <v>7.26372909545898</v>
+        <v>7.26372861862183</v>
       </c>
       <c r="H472" t="n">
         <v>12393241</v>
@@ -14173,7 +14173,7 @@
         <v>7.35500001907349</v>
       </c>
       <c r="G476" t="n">
-        <v>6.99734401702881</v>
+        <v>6.99734449386597</v>
       </c>
       <c r="H476" t="n">
         <v>10343796</v>
@@ -14260,7 +14260,7 @@
         <v>6.89499998092651</v>
       </c>
       <c r="G479" t="n">
-        <v>6.5597128868103</v>
+        <v>6.55971336364746</v>
       </c>
       <c r="H479" t="n">
         <v>18049941</v>
@@ -14318,7 +14318,7 @@
         <v>6.81500005722046</v>
       </c>
       <c r="G481" t="n">
-        <v>6.48360300064087</v>
+        <v>6.48360347747803</v>
       </c>
       <c r="H481" t="n">
         <v>19321011</v>
@@ -14347,7 +14347,7 @@
         <v>6.89499998092651</v>
       </c>
       <c r="G482" t="n">
-        <v>6.5597128868103</v>
+        <v>6.55971336364746</v>
       </c>
       <c r="H482" t="n">
         <v>13873115</v>
@@ -14579,7 +14579,7 @@
         <v>7.04500007629395</v>
       </c>
       <c r="G490" t="n">
-        <v>6.70241928100586</v>
+        <v>6.7024188041687</v>
       </c>
       <c r="H490" t="n">
         <v>8224257</v>
@@ -14695,7 +14695,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G494" t="n">
-        <v>6.7166895866394</v>
+        <v>6.71668910980225</v>
       </c>
       <c r="H494" t="n">
         <v>7676027</v>
@@ -14782,7 +14782,7 @@
         <v>7.46999979019165</v>
       </c>
       <c r="G497" t="n">
-        <v>7.10675191879272</v>
+        <v>7.10675239562988</v>
       </c>
       <c r="H497" t="n">
         <v>16327353</v>
@@ -14811,7 +14811,7 @@
         <v>7.54500007629395</v>
       </c>
       <c r="G498" t="n">
-        <v>7.17810535430908</v>
+        <v>7.17810487747192</v>
       </c>
       <c r="H498" t="n">
         <v>9765474</v>
@@ -14927,7 +14927,7 @@
         <v>7.2649998664856</v>
       </c>
       <c r="G502" t="n">
-        <v>6.91172027587891</v>
+        <v>6.91172075271606</v>
       </c>
       <c r="H502" t="n">
         <v>12983601</v>
@@ -14985,7 +14985,7 @@
         <v>7.34499979019165</v>
       </c>
       <c r="G504" t="n">
-        <v>6.98783016204834</v>
+        <v>6.9878306388855</v>
       </c>
       <c r="H504" t="n">
         <v>8029365</v>
@@ -15014,7 +15014,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G505" t="n">
-        <v>7.04015636444092</v>
+        <v>7.04015588760376</v>
       </c>
       <c r="H505" t="n">
         <v>7758336</v>
@@ -15072,7 +15072,7 @@
         <v>7.34499979019165</v>
       </c>
       <c r="G507" t="n">
-        <v>6.98783016204834</v>
+        <v>6.9878306388855</v>
       </c>
       <c r="H507" t="n">
         <v>8653660</v>
@@ -15101,7 +15101,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G508" t="n">
-        <v>7.02112865447998</v>
+        <v>7.02112913131714</v>
       </c>
       <c r="H508" t="n">
         <v>5233596</v>
@@ -15159,7 +15159,7 @@
         <v>7.29500007629395</v>
       </c>
       <c r="G510" t="n">
-        <v>6.94026231765747</v>
+        <v>6.94026184082031</v>
       </c>
       <c r="H510" t="n">
         <v>4579894</v>
@@ -15188,7 +15188,7 @@
         <v>7.20499992370605</v>
       </c>
       <c r="G511" t="n">
-        <v>6.85463857650757</v>
+        <v>6.85463809967041</v>
       </c>
       <c r="H511" t="n">
         <v>4245157</v>
@@ -15217,7 +15217,7 @@
         <v>7.25500011444092</v>
       </c>
       <c r="G512" t="n">
-        <v>6.9022068977356</v>
+        <v>6.90220737457275</v>
       </c>
       <c r="H512" t="n">
         <v>6607233</v>
@@ -15246,7 +15246,7 @@
         <v>7.25</v>
       </c>
       <c r="G513" t="n">
-        <v>6.89744997024536</v>
+        <v>6.89745044708252</v>
       </c>
       <c r="H513" t="n">
         <v>5483915</v>
@@ -15275,7 +15275,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G514" t="n">
-        <v>6.98307371139526</v>
+        <v>6.98307418823242</v>
       </c>
       <c r="H514" t="n">
         <v>5974047</v>
@@ -15304,7 +15304,7 @@
         <v>7.38500022888184</v>
       </c>
       <c r="G515" t="n">
-        <v>7.02588605880737</v>
+        <v>7.02588558197021</v>
       </c>
       <c r="H515" t="n">
         <v>5887106</v>
@@ -15449,7 +15449,7 @@
         <v>7.43499994277954</v>
       </c>
       <c r="G520" t="n">
-        <v>7.07345390319824</v>
+        <v>7.0734543800354</v>
       </c>
       <c r="H520" t="n">
         <v>6198087</v>
@@ -15478,7 +15478,7 @@
         <v>7.38500022888184</v>
       </c>
       <c r="G521" t="n">
-        <v>7.02588605880737</v>
+        <v>7.02588558197021</v>
       </c>
       <c r="H521" t="n">
         <v>5952155</v>
@@ -15739,7 +15739,7 @@
         <v>7.20499992370605</v>
       </c>
       <c r="G530" t="n">
-        <v>6.85463857650757</v>
+        <v>6.85463809967041</v>
       </c>
       <c r="H530" t="n">
         <v>8180429</v>
@@ -15971,7 +15971,7 @@
         <v>7.21199989318848</v>
       </c>
       <c r="G538" t="n">
-        <v>6.86129760742188</v>
+        <v>6.86129808425903</v>
       </c>
       <c r="H538" t="n">
         <v>18503191</v>
@@ -16029,7 +16029,7 @@
         <v>6.98799991607666</v>
       </c>
       <c r="G540" t="n">
-        <v>6.64819097518921</v>
+        <v>6.64819049835205</v>
       </c>
       <c r="H540" t="n">
         <v>10998838</v>
@@ -16116,7 +16116,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G543" t="n">
-        <v>6.54544258117676</v>
+        <v>6.5454421043396</v>
       </c>
       <c r="H543" t="n">
         <v>9422768</v>
@@ -16261,7 +16261,7 @@
         <v>7.19600009918213</v>
       </c>
       <c r="G548" t="n">
-        <v>6.84607601165771</v>
+        <v>6.84607648849487</v>
       </c>
       <c r="H548" t="n">
         <v>13117904</v>
@@ -16348,7 +16348,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G551" t="n">
-        <v>7.02112865447998</v>
+        <v>7.02112913131714</v>
       </c>
       <c r="H551" t="n">
         <v>9959256</v>
@@ -16406,7 +16406,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G553" t="n">
-        <v>7.04015636444092</v>
+        <v>7.04015588760376</v>
       </c>
       <c r="H553" t="n">
         <v>10517150</v>
@@ -16435,7 +16435,7 @@
         <v>7.39799976348877</v>
       </c>
       <c r="G554" t="n">
-        <v>7.03825283050537</v>
+        <v>7.03825330734253</v>
       </c>
       <c r="H554" t="n">
         <v>10319173</v>
@@ -16464,7 +16464,7 @@
         <v>7.24599981307983</v>
       </c>
       <c r="G555" t="n">
-        <v>6.8936448097229</v>
+        <v>6.89364433288574</v>
       </c>
       <c r="H555" t="n">
         <v>12031756</v>
@@ -16493,7 +16493,7 @@
         <v>7.28800010681152</v>
       </c>
       <c r="G556" t="n">
-        <v>6.93360233306885</v>
+        <v>6.93360280990601</v>
       </c>
       <c r="H556" t="n">
         <v>9797279</v>
@@ -16580,7 +16580,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G559" t="n">
-        <v>7.82979440689087</v>
+        <v>7.82979536056519</v>
       </c>
       <c r="H559" t="n">
         <v>38979913</v>
@@ -16609,7 +16609,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G560" t="n">
-        <v>7.91541862487793</v>
+        <v>7.91541814804077</v>
       </c>
       <c r="H560" t="n">
         <v>29766429</v>
@@ -16638,7 +16638,7 @@
         <v>8.20199966430664</v>
       </c>
       <c r="G561" t="n">
-        <v>7.80315637588501</v>
+        <v>7.80315589904785</v>
       </c>
       <c r="H561" t="n">
         <v>15070704</v>
@@ -16667,7 +16667,7 @@
         <v>8.00800037384033</v>
       </c>
       <c r="G562" t="n">
-        <v>7.61859083175659</v>
+        <v>7.61859130859375</v>
       </c>
       <c r="H562" t="n">
         <v>17830195</v>
@@ -16696,7 +16696,7 @@
         <v>7.83199977874756</v>
       </c>
       <c r="G563" t="n">
-        <v>7.45114898681641</v>
+        <v>7.45114850997925</v>
       </c>
       <c r="H563" t="n">
         <v>15531686</v>
@@ -16754,7 +16754,7 @@
         <v>8.08800029754639</v>
       </c>
       <c r="G565" t="n">
-        <v>7.69470024108887</v>
+        <v>7.69470071792603</v>
       </c>
       <c r="H565" t="n">
         <v>13814697</v>
@@ -16783,7 +16783,7 @@
         <v>8.11600017547607</v>
       </c>
       <c r="G566" t="n">
-        <v>7.72133874893188</v>
+        <v>7.72133922576904</v>
       </c>
       <c r="H566" t="n">
         <v>11221597</v>
@@ -16899,7 +16899,7 @@
         <v>7.72599983215332</v>
       </c>
       <c r="G570" t="n">
-        <v>7.35030364990234</v>
+        <v>7.35030317306519</v>
       </c>
       <c r="H570" t="n">
         <v>11293097</v>
@@ -16957,7 +16957,7 @@
         <v>7.61399984359741</v>
       </c>
       <c r="G572" t="n">
-        <v>7.24374961853027</v>
+        <v>7.24375009536743</v>
       </c>
       <c r="H572" t="n">
         <v>8793021</v>
@@ -17073,7 +17073,7 @@
         <v>7.58199977874756</v>
       </c>
       <c r="G576" t="n">
-        <v>7.21330595016479</v>
+        <v>7.21330547332764</v>
       </c>
       <c r="H576" t="n">
         <v>7516325</v>
@@ -17247,7 +17247,7 @@
         <v>8.61200046539307</v>
       </c>
       <c r="G582" t="n">
-        <v>8.19321918487549</v>
+        <v>8.1932201385498</v>
       </c>
       <c r="H582" t="n">
         <v>21024100</v>
@@ -17334,7 +17334,7 @@
         <v>8.38199996948242</v>
       </c>
       <c r="G585" t="n">
-        <v>7.97440385818481</v>
+        <v>7.97440338134766</v>
       </c>
       <c r="H585" t="n">
         <v>16885220</v>
@@ -17421,7 +17421,7 @@
         <v>8.76200008392334</v>
       </c>
       <c r="G588" t="n">
-        <v>8.33592510223389</v>
+        <v>8.3359260559082</v>
       </c>
       <c r="H588" t="n">
         <v>19699701</v>
@@ -17450,7 +17450,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G589" t="n">
-        <v>8.27694034576416</v>
+        <v>8.27693939208984</v>
       </c>
       <c r="H589" t="n">
         <v>14602170</v>
@@ -17508,7 +17508,7 @@
         <v>8.26200008392334</v>
       </c>
       <c r="G591" t="n">
-        <v>7.86023902893066</v>
+        <v>7.86023950576782</v>
       </c>
       <c r="H591" t="n">
         <v>15384354</v>
@@ -17653,7 +17653,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G596" t="n">
-        <v>7.96298694610596</v>
+        <v>7.96298742294312</v>
       </c>
       <c r="H596" t="n">
         <v>11477450</v>
@@ -17740,7 +17740,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G599" t="n">
-        <v>8.01055526733398</v>
+        <v>8.0105562210083</v>
       </c>
       <c r="H599" t="n">
         <v>20166769</v>
@@ -17769,7 +17769,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G600" t="n">
-        <v>7.88687801361084</v>
+        <v>7.88687753677368</v>
       </c>
       <c r="H600" t="n">
         <v>10308492</v>
@@ -17914,7 +17914,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G605" t="n">
-        <v>7.35410928726196</v>
+        <v>7.3541088104248</v>
       </c>
       <c r="H605" t="n">
         <v>19807914</v>
@@ -17943,7 +17943,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G606" t="n">
-        <v>7.30654001235962</v>
+        <v>7.30654048919678</v>
       </c>
       <c r="H606" t="n">
         <v>13820402</v>
@@ -18030,7 +18030,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G609" t="n">
-        <v>7.02112865447998</v>
+        <v>7.02112913131714</v>
       </c>
       <c r="H609" t="n">
         <v>12987765</v>
@@ -18059,7 +18059,7 @@
         <v>7.31199979782104</v>
       </c>
       <c r="G610" t="n">
-        <v>6.95643520355225</v>
+        <v>6.95643472671509</v>
       </c>
       <c r="H610" t="n">
         <v>9821711</v>
@@ -18088,7 +18088,7 @@
         <v>7.30999994277954</v>
       </c>
       <c r="G611" t="n">
-        <v>6.95453262329102</v>
+        <v>6.95453214645386</v>
       </c>
       <c r="H611" t="n">
         <v>10969407</v>
@@ -18146,7 +18146,7 @@
         <v>7.14400005340576</v>
       </c>
       <c r="G613" t="n">
-        <v>6.7966046333313</v>
+        <v>6.79660511016846</v>
       </c>
       <c r="H613" t="n">
         <v>15383630</v>
@@ -18204,7 +18204,7 @@
         <v>7.01599979400635</v>
       </c>
       <c r="G615" t="n">
-        <v>6.67482852935791</v>
+        <v>6.67482900619507</v>
       </c>
       <c r="H615" t="n">
         <v>10762161</v>
@@ -18233,7 +18233,7 @@
         <v>6.87200021743774</v>
       </c>
       <c r="G616" t="n">
-        <v>6.53783130645752</v>
+        <v>6.53783178329468</v>
       </c>
       <c r="H616" t="n">
         <v>13644902</v>
@@ -18291,7 +18291,7 @@
         <v>6.98600006103516</v>
       </c>
       <c r="G618" t="n">
-        <v>6.64628791809082</v>
+        <v>6.64628839492798</v>
       </c>
       <c r="H618" t="n">
         <v>6146232</v>
@@ -18349,7 +18349,7 @@
         <v>6.91599988937378</v>
       </c>
       <c r="G620" t="n">
-        <v>6.57969188690186</v>
+        <v>6.5796914100647</v>
       </c>
       <c r="H620" t="n">
         <v>11484221</v>
@@ -18407,7 +18407,7 @@
         <v>6.72200012207031</v>
       </c>
       <c r="G622" t="n">
-        <v>6.39512586593628</v>
+        <v>6.39512538909912</v>
       </c>
       <c r="H622" t="n">
         <v>8616778</v>
@@ -18436,7 +18436,7 @@
         <v>6.87200021743774</v>
       </c>
       <c r="G623" t="n">
-        <v>6.53783130645752</v>
+        <v>6.53783178329468</v>
       </c>
       <c r="H623" t="n">
         <v>11592172</v>
@@ -18465,7 +18465,7 @@
         <v>6.85799980163574</v>
       </c>
       <c r="G624" t="n">
-        <v>6.52451181411743</v>
+        <v>6.52451229095459</v>
       </c>
       <c r="H624" t="n">
         <v>6763306</v>
@@ -18552,7 +18552,7 @@
         <v>6.7519998550415</v>
       </c>
       <c r="G627" t="n">
-        <v>6.42366647720337</v>
+        <v>6.42366695404053</v>
       </c>
       <c r="H627" t="n">
         <v>11827362</v>
@@ -18581,7 +18581,7 @@
         <v>6.76599979400635</v>
       </c>
       <c r="G628" t="n">
-        <v>6.4369854927063</v>
+        <v>6.43698596954346</v>
       </c>
       <c r="H628" t="n">
         <v>9517293</v>
@@ -18668,7 +18668,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G631" t="n">
-        <v>6.33614015579224</v>
+        <v>6.33614063262939</v>
       </c>
       <c r="H631" t="n">
         <v>8779408</v>
@@ -18784,7 +18784,7 @@
         <v>6.45599985122681</v>
       </c>
       <c r="G635" t="n">
-        <v>6.14206075668335</v>
+        <v>6.14206027984619</v>
       </c>
       <c r="H635" t="n">
         <v>13273047</v>
@@ -18842,7 +18842,7 @@
         <v>6.37400007247925</v>
       </c>
       <c r="G637" t="n">
-        <v>6.06404781341553</v>
+        <v>6.06404829025269</v>
       </c>
       <c r="H637" t="n">
         <v>8023540</v>
@@ -18871,7 +18871,7 @@
         <v>6.28200006484985</v>
       </c>
       <c r="G638" t="n">
-        <v>5.97652149200439</v>
+        <v>5.97652196884155</v>
       </c>
       <c r="H638" t="n">
         <v>5846091</v>
@@ -18929,7 +18929,7 @@
         <v>6.52400016784668</v>
       </c>
       <c r="G640" t="n">
-        <v>6.20675420761108</v>
+        <v>6.20675373077393</v>
       </c>
       <c r="H640" t="n">
         <v>5707740</v>
@@ -18987,7 +18987,7 @@
         <v>6.55200004577637</v>
       </c>
       <c r="G642" t="n">
-        <v>6.2333927154541</v>
+        <v>6.23339223861694</v>
       </c>
       <c r="H642" t="n">
         <v>6589583</v>
@@ -19045,7 +19045,7 @@
         <v>6.36600017547607</v>
       </c>
       <c r="G644" t="n">
-        <v>6.05643749237061</v>
+        <v>6.05643701553345</v>
       </c>
       <c r="H644" t="n">
         <v>10253469</v>
@@ -19074,7 +19074,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G645" t="n">
-        <v>6.01267385482788</v>
+        <v>6.01267433166504</v>
       </c>
       <c r="H645" t="n">
         <v>7151777</v>
@@ -19103,7 +19103,7 @@
         <v>6.14599990844727</v>
       </c>
       <c r="G646" t="n">
-        <v>5.84713506698608</v>
+        <v>5.84713459014893</v>
       </c>
       <c r="H646" t="n">
         <v>10297948</v>
@@ -19161,7 +19161,7 @@
         <v>6.07399988174438</v>
       </c>
       <c r="G648" t="n">
-        <v>5.77863645553589</v>
+        <v>5.77863597869873</v>
       </c>
       <c r="H648" t="n">
         <v>9314960</v>
@@ -19451,7 +19451,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G658" t="n">
-        <v>6.2790584564209</v>
+        <v>6.27905797958374</v>
       </c>
       <c r="H658" t="n">
         <v>10357178</v>
@@ -19509,7 +19509,7 @@
         <v>6.50400018692017</v>
       </c>
       <c r="G660" t="n">
-        <v>6.1877269744873</v>
+        <v>6.18772649765015</v>
       </c>
       <c r="H660" t="n">
         <v>7068352</v>
@@ -19538,7 +19538,7 @@
         <v>6.38199996948242</v>
       </c>
       <c r="G661" t="n">
-        <v>6.07165908813477</v>
+        <v>6.07165861129761</v>
       </c>
       <c r="H661" t="n">
         <v>7651712</v>
@@ -19944,7 +19944,7 @@
         <v>6</v>
       </c>
       <c r="G675" t="n">
-        <v>5.70823431015015</v>
+        <v>5.7082347869873</v>
       </c>
       <c r="H675" t="n">
         <v>8439947</v>
@@ -19973,7 +19973,7 @@
         <v>5.98799991607666</v>
       </c>
       <c r="G676" t="n">
-        <v>5.69681835174561</v>
+        <v>5.69681787490845</v>
       </c>
       <c r="H676" t="n">
         <v>6952501</v>
@@ -20002,7 +20002,7 @@
         <v>6.0019998550415</v>
       </c>
       <c r="G677" t="n">
-        <v>5.71013736724854</v>
+        <v>5.71013689041138</v>
       </c>
       <c r="H677" t="n">
         <v>3495139</v>
@@ -20031,7 +20031,7 @@
         <v>5.93800020217896</v>
       </c>
       <c r="G678" t="n">
-        <v>5.64924955368042</v>
+        <v>5.64925003051758</v>
       </c>
       <c r="H678" t="n">
         <v>6479576</v>
@@ -20118,7 +20118,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G681" t="n">
-        <v>5.22303485870361</v>
+        <v>5.22303438186646</v>
       </c>
       <c r="H681" t="n">
         <v>21485023</v>
@@ -20147,7 +20147,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G682" t="n">
-        <v>5.28011703491211</v>
+        <v>5.28011751174927</v>
       </c>
       <c r="H682" t="n">
         <v>7364755</v>
@@ -20176,7 +20176,7 @@
         <v>5.25</v>
       </c>
       <c r="G683" t="n">
-        <v>4.99470567703247</v>
+        <v>4.99470520019531</v>
       </c>
       <c r="H683" t="n">
         <v>33784406</v>
@@ -20350,7 +20350,7 @@
         <v>5.4060001373291</v>
       </c>
       <c r="G689" t="n">
-        <v>5.14311933517456</v>
+        <v>5.14311981201172</v>
       </c>
       <c r="H689" t="n">
         <v>9097960</v>
@@ -20466,7 +20466,7 @@
         <v>5.71400022506714</v>
       </c>
       <c r="G693" t="n">
-        <v>5.4361424446106</v>
+        <v>5.43614196777344</v>
       </c>
       <c r="H693" t="n">
         <v>14951668</v>
@@ -20524,7 +20524,7 @@
         <v>5.68599987030029</v>
       </c>
       <c r="G695" t="n">
-        <v>5.40950393676758</v>
+        <v>5.40950345993042</v>
       </c>
       <c r="H695" t="n">
         <v>8514680</v>
@@ -20553,7 +20553,7 @@
         <v>5.68599987030029</v>
       </c>
       <c r="G696" t="n">
-        <v>5.40950393676758</v>
+        <v>5.40950345993042</v>
       </c>
       <c r="H696" t="n">
         <v>11073700</v>
@@ -20582,7 +20582,7 @@
         <v>5.60599994659424</v>
       </c>
       <c r="G697" t="n">
-        <v>5.33339405059814</v>
+        <v>5.33339357376099</v>
       </c>
       <c r="H697" t="n">
         <v>9256009</v>
@@ -20611,7 +20611,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G698" t="n">
-        <v>5.30865859985352</v>
+        <v>5.30865812301636</v>
       </c>
       <c r="H698" t="n">
         <v>8345160</v>
@@ -20727,7 +20727,7 @@
         <v>4.95300006866455</v>
       </c>
       <c r="G702" t="n">
-        <v>4.71214818954468</v>
+        <v>4.71214771270752</v>
       </c>
       <c r="H702" t="n">
         <v>21571910</v>
@@ -20814,7 +20814,7 @@
         <v>4.95699977874756</v>
       </c>
       <c r="G705" t="n">
-        <v>4.71595287322998</v>
+        <v>4.71595335006714</v>
       </c>
       <c r="H705" t="n">
         <v>12269784</v>
@@ -20930,7 +20930,7 @@
         <v>5.03200006484985</v>
       </c>
       <c r="G709" t="n">
-        <v>4.78730630874634</v>
+        <v>4.78730583190918</v>
       </c>
       <c r="H709" t="n">
         <v>16574528</v>
@@ -20959,7 +20959,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G710" t="n">
-        <v>4.77588987350464</v>
+        <v>4.77588939666748</v>
       </c>
       <c r="H710" t="n">
         <v>13466859</v>
@@ -21133,7 +21133,7 @@
         <v>4.98600006103516</v>
       </c>
       <c r="G716" t="n">
-        <v>4.74354267120361</v>
+        <v>4.74354314804077</v>
       </c>
       <c r="H716" t="n">
         <v>11883638</v>
@@ -21365,7 +21365,7 @@
         <v>5.19199991226196</v>
       </c>
       <c r="G724" t="n">
-        <v>4.93952560424805</v>
+        <v>4.93952608108521</v>
       </c>
       <c r="H724" t="n">
         <v>11611382</v>
@@ -21452,7 +21452,7 @@
         <v>5.35400009155273</v>
       </c>
       <c r="G727" t="n">
-        <v>5.09364795684814</v>
+        <v>5.0936484336853</v>
       </c>
       <c r="H727" t="n">
         <v>5004868</v>
@@ -21510,7 +21510,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G729" t="n">
-        <v>5.08984231948853</v>
+        <v>5.08984279632568</v>
       </c>
       <c r="H729" t="n">
         <v>4502292</v>
@@ -21568,7 +21568,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G731" t="n">
-        <v>4.90908193588257</v>
+        <v>4.90908145904541</v>
       </c>
       <c r="H731" t="n">
         <v>20215708</v>
@@ -21597,7 +21597,7 @@
         <v>5.30399990081787</v>
       </c>
       <c r="G732" t="n">
-        <v>5.04607963562012</v>
+        <v>5.04607915878296</v>
       </c>
       <c r="H732" t="n">
         <v>21192969</v>
@@ -21655,7 +21655,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G734" t="n">
-        <v>4.9566502571106</v>
+        <v>4.95665073394775</v>
       </c>
       <c r="H734" t="n">
         <v>13016824</v>
@@ -21684,7 +21684,7 @@
         <v>5.16400003433228</v>
       </c>
       <c r="G735" t="n">
-        <v>4.91288757324219</v>
+        <v>4.91288709640503</v>
       </c>
       <c r="H735" t="n">
         <v>7858565</v>
@@ -21713,7 +21713,7 @@
         <v>5.26200008392334</v>
       </c>
       <c r="G736" t="n">
-        <v>5.00612163543701</v>
+        <v>5.00612211227417</v>
       </c>
       <c r="H736" t="n">
         <v>9329889</v>
@@ -22032,7 +22032,7 @@
         <v>5.74599981307983</v>
       </c>
       <c r="G747" t="n">
-        <v>5.46658563613892</v>
+        <v>5.46658611297607</v>
       </c>
       <c r="H747" t="n">
         <v>8767299</v>
@@ -22061,7 +22061,7 @@
         <v>5.69199991226196</v>
       </c>
       <c r="G748" t="n">
-        <v>5.41521167755127</v>
+        <v>5.41521215438843</v>
       </c>
       <c r="H748" t="n">
         <v>5268321</v>
@@ -22235,7 +22235,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G754" t="n">
-        <v>5.42282295227051</v>
+        <v>5.42282247543335</v>
       </c>
       <c r="H754" t="n">
         <v>8739136</v>
@@ -22380,7 +22380,7 @@
         <v>5.4520001411438</v>
       </c>
       <c r="G759" t="n">
-        <v>5.18688297271729</v>
+        <v>5.18688249588013</v>
       </c>
       <c r="H759" t="n">
         <v>9181301</v>
@@ -22409,7 +22409,7 @@
         <v>5.2020001411438</v>
       </c>
       <c r="G760" t="n">
-        <v>4.94903993606567</v>
+        <v>4.94903945922852</v>
       </c>
       <c r="H760" t="n">
         <v>11959404</v>
@@ -22467,7 +22467,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G762" t="n">
-        <v>4.58561563491821</v>
+        <v>4.58561515808105</v>
       </c>
       <c r="H762" t="n">
         <v>10213287</v>
@@ -22496,7 +22496,7 @@
         <v>4.83300018310547</v>
       </c>
       <c r="G763" t="n">
-        <v>4.59798288345337</v>
+        <v>4.59798336029053</v>
       </c>
       <c r="H763" t="n">
         <v>6812527</v>
@@ -22641,7 +22641,7 @@
         <v>5.06199979782104</v>
       </c>
       <c r="G768" t="n">
-        <v>4.81584692001343</v>
+        <v>4.81584739685059</v>
       </c>
       <c r="H768" t="n">
         <v>6948538</v>
@@ -22670,7 +22670,7 @@
         <v>4.95900011062622</v>
       </c>
       <c r="G769" t="n">
-        <v>4.71785593032837</v>
+        <v>4.71785640716553</v>
       </c>
       <c r="H769" t="n">
         <v>10542869</v>
@@ -22728,7 +22728,7 @@
         <v>5.00600004196167</v>
       </c>
       <c r="G771" t="n">
-        <v>4.76257085800171</v>
+        <v>4.76257038116455</v>
       </c>
       <c r="H771" t="n">
         <v>7037218</v>
@@ -22757,7 +22757,7 @@
         <v>5.01599979400635</v>
       </c>
       <c r="G772" t="n">
-        <v>4.77208423614502</v>
+        <v>4.77208375930786</v>
       </c>
       <c r="H772" t="n">
         <v>5703804</v>
@@ -22786,7 +22786,7 @@
         <v>5.02400016784668</v>
       </c>
       <c r="G773" t="n">
-        <v>4.7796950340271</v>
+        <v>4.77969551086426</v>
       </c>
       <c r="H773" t="n">
         <v>5160678</v>
@@ -22873,7 +22873,7 @@
         <v>4.88500022888184</v>
       </c>
       <c r="G776" t="n">
-        <v>4.64745426177979</v>
+        <v>4.64745473861694</v>
       </c>
       <c r="H776" t="n">
         <v>41676407</v>
@@ -22960,7 +22960,7 @@
         <v>4.48400020599365</v>
       </c>
       <c r="G779" t="n">
-        <v>4.26595449447632</v>
+        <v>4.26595401763916</v>
       </c>
       <c r="H779" t="n">
         <v>18215988</v>
@@ -22989,7 +22989,7 @@
         <v>4.52899980545044</v>
       </c>
       <c r="G780" t="n">
-        <v>4.30876541137695</v>
+        <v>4.30876588821411</v>
       </c>
       <c r="H780" t="n">
         <v>16117024</v>
@@ -23076,7 +23076,7 @@
         <v>4.58199977874756</v>
       </c>
       <c r="G783" t="n">
-        <v>4.35918807983398</v>
+        <v>4.35918855667114</v>
       </c>
       <c r="H783" t="n">
         <v>7847751</v>
@@ -23105,7 +23105,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G784" t="n">
-        <v>4.40485429763794</v>
+        <v>4.4048547744751</v>
       </c>
       <c r="H784" t="n">
         <v>11137135</v>
@@ -23221,7 +23221,7 @@
         <v>5.02400016784668</v>
       </c>
       <c r="G788" t="n">
-        <v>4.7796950340271</v>
+        <v>4.77969551086426</v>
       </c>
       <c r="H788" t="n">
         <v>9181552</v>
@@ -23308,7 +23308,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G791" t="n">
-        <v>4.49047756195068</v>
+        <v>4.49047803878784</v>
       </c>
       <c r="H791" t="n">
         <v>10923993</v>
@@ -23366,7 +23366,7 @@
         <v>4.81599998474121</v>
       </c>
       <c r="G793" t="n">
-        <v>4.58180952072144</v>
+        <v>4.58180999755859</v>
       </c>
       <c r="H793" t="n">
         <v>6859684</v>
@@ -23424,7 +23424,7 @@
         <v>4.8270001411438</v>
       </c>
       <c r="G795" t="n">
-        <v>4.59227466583252</v>
+        <v>4.59227514266968</v>
       </c>
       <c r="H795" t="n">
         <v>10108349</v>
@@ -23482,7 +23482,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G797" t="n">
-        <v>5.0422739982605</v>
+        <v>5.04227447509766</v>
       </c>
       <c r="H797" t="n">
         <v>14228495</v>
@@ -23627,7 +23627,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G802" t="n">
-        <v>5.09935665130615</v>
+        <v>5.09935617446899</v>
       </c>
       <c r="H802" t="n">
         <v>13548252</v>
@@ -23743,7 +23743,7 @@
         <v>5.32200002670288</v>
       </c>
       <c r="G806" t="n">
-        <v>5.06320428848267</v>
+        <v>5.06320381164551</v>
       </c>
       <c r="H806" t="n">
         <v>10595102</v>
@@ -23801,7 +23801,7 @@
         <v>5.5</v>
       </c>
       <c r="G808" t="n">
-        <v>5.23254871368408</v>
+        <v>5.23254823684692</v>
       </c>
       <c r="H808" t="n">
         <v>15904611</v>
@@ -23830,7 +23830,7 @@
         <v>5.64799976348877</v>
       </c>
       <c r="G809" t="n">
-        <v>5.37335157394409</v>
+        <v>5.37335109710693</v>
       </c>
       <c r="H809" t="n">
         <v>20711461</v>
@@ -23859,7 +23859,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G810" t="n">
-        <v>5.33719968795776</v>
+        <v>5.33719921112061</v>
       </c>
       <c r="H810" t="n">
         <v>21767982</v>
@@ -24091,7 +24091,7 @@
         <v>5.35599994659424</v>
       </c>
       <c r="G818" t="n">
-        <v>5.09555101394653</v>
+        <v>5.09555053710938</v>
       </c>
       <c r="H818" t="n">
         <v>10767173</v>
@@ -24149,7 +24149,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G820" t="n">
-        <v>5.0422739982605</v>
+        <v>5.04227447509766</v>
       </c>
       <c r="H820" t="n">
         <v>6355484</v>
@@ -24178,7 +24178,7 @@
         <v>5.25799989700317</v>
       </c>
       <c r="G821" t="n">
-        <v>5.00231599807739</v>
+        <v>5.00231647491455</v>
       </c>
       <c r="H821" t="n">
         <v>8320301</v>
@@ -24236,7 +24236,7 @@
         <v>5.31599998474121</v>
       </c>
       <c r="G823" t="n">
-        <v>5.05749559402466</v>
+        <v>5.05749607086182</v>
       </c>
       <c r="H823" t="n">
         <v>5741634</v>
@@ -24265,7 +24265,7 @@
         <v>5.35599994659424</v>
       </c>
       <c r="G824" t="n">
-        <v>5.09555101394653</v>
+        <v>5.09555053710938</v>
       </c>
       <c r="H824" t="n">
         <v>7192964</v>
@@ -24294,7 +24294,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G825" t="n">
-        <v>5.14692497253418</v>
+        <v>5.14692449569702</v>
       </c>
       <c r="H825" t="n">
         <v>6837351</v>
@@ -24381,7 +24381,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G828" t="n">
-        <v>5.08984231948853</v>
+        <v>5.08984279632568</v>
       </c>
       <c r="H828" t="n">
         <v>11314863</v>
@@ -24410,7 +24410,7 @@
         <v>5.40199995040894</v>
       </c>
       <c r="G829" t="n">
-        <v>5.13931369781494</v>
+        <v>5.1393141746521</v>
       </c>
       <c r="H829" t="n">
         <v>9915940</v>
@@ -24468,7 +24468,7 @@
         <v>5.36800003051758</v>
       </c>
       <c r="G831" t="n">
-        <v>5.10696697235107</v>
+        <v>5.10696744918823</v>
       </c>
       <c r="H831" t="n">
         <v>8336278</v>
@@ -24497,7 +24497,7 @@
         <v>5.33599996566772</v>
       </c>
       <c r="G832" t="n">
-        <v>5.0765233039856</v>
+        <v>5.07652378082275</v>
       </c>
       <c r="H832" t="n">
         <v>10088831</v>
@@ -24526,7 +24526,7 @@
         <v>5.34899997711182</v>
       </c>
       <c r="G833" t="n">
-        <v>5.08889102935791</v>
+        <v>5.08889150619507</v>
       </c>
       <c r="H833" t="n">
         <v>6378866</v>
@@ -24671,7 +24671,7 @@
         <v>5.25500011444092</v>
       </c>
       <c r="G838" t="n">
-        <v>4.99946260452271</v>
+        <v>4.99946212768555</v>
       </c>
       <c r="H838" t="n">
         <v>4873965</v>
@@ -24903,7 +24903,7 @@
         <v>4.98600006103516</v>
       </c>
       <c r="G846" t="n">
-        <v>4.74354267120361</v>
+        <v>4.74354314804077</v>
       </c>
       <c r="H846" t="n">
         <v>4443838</v>
@@ -24932,7 +24932,7 @@
         <v>4.95900011062622</v>
       </c>
       <c r="G847" t="n">
-        <v>4.71785593032837</v>
+        <v>4.71785640716553</v>
       </c>
       <c r="H847" t="n">
         <v>6501356</v>
@@ -25106,7 +25106,7 @@
         <v>4.67199993133545</v>
       </c>
       <c r="G853" t="n">
-        <v>4.44481182098389</v>
+        <v>4.44481229782104</v>
       </c>
       <c r="H853" t="n">
         <v>6493676</v>
@@ -25193,7 +25193,7 @@
         <v>4.45800018310547</v>
       </c>
       <c r="G856" t="n">
-        <v>4.24121856689453</v>
+        <v>4.24121809005737</v>
       </c>
       <c r="H856" t="n">
         <v>16786730</v>
@@ -25280,7 +25280,7 @@
         <v>4.57800006866455</v>
       </c>
       <c r="G859" t="n">
-        <v>4.35538291931152</v>
+        <v>4.35538339614868</v>
       </c>
       <c r="H859" t="n">
         <v>8359793</v>
@@ -25396,7 +25396,7 @@
         <v>4.38100004196167</v>
       </c>
       <c r="G863" t="n">
-        <v>4.16796255111694</v>
+        <v>4.1679630279541</v>
       </c>
       <c r="H863" t="n">
         <v>10295663</v>
@@ -25599,7 +25599,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G870" t="n">
-        <v>4.32398748397827</v>
+        <v>4.32398796081543</v>
       </c>
       <c r="H870" t="n">
         <v>10022461</v>
@@ -25802,7 +25802,7 @@
         <v>4.63100004196167</v>
       </c>
       <c r="G877" t="n">
-        <v>4.40580558776855</v>
+        <v>4.40580606460571</v>
       </c>
       <c r="H877" t="n">
         <v>6029498</v>
@@ -25947,7 +25947,7 @@
         <v>4.84200000762939</v>
       </c>
       <c r="G882" t="n">
-        <v>4.60654497146606</v>
+        <v>4.60654544830322</v>
       </c>
       <c r="H882" t="n">
         <v>15402357</v>
@@ -25976,7 +25976,7 @@
         <v>5.00899982452393</v>
       </c>
       <c r="G883" t="n">
-        <v>4.7654242515564</v>
+        <v>4.76542472839355</v>
       </c>
       <c r="H883" t="n">
         <v>21769809</v>
@@ -26150,7 +26150,7 @@
         <v>4.82800006866455</v>
       </c>
       <c r="G889" t="n">
-        <v>4.59322595596313</v>
+        <v>4.59322643280029</v>
       </c>
       <c r="H889" t="n">
         <v>7098552</v>
@@ -26179,7 +26179,7 @@
         <v>4.78299999237061</v>
       </c>
       <c r="G890" t="n">
-        <v>4.55041456222534</v>
+        <v>4.55041408538818</v>
       </c>
       <c r="H890" t="n">
         <v>4787528</v>
@@ -26208,7 +26208,7 @@
         <v>4.92199993133545</v>
       </c>
       <c r="G891" t="n">
-        <v>4.6826548576355</v>
+        <v>4.68265533447266</v>
       </c>
       <c r="H891" t="n">
         <v>9003798</v>
@@ -26266,7 +26266,7 @@
         <v>4.96299982070923</v>
       </c>
       <c r="G893" t="n">
-        <v>4.72166156768799</v>
+        <v>4.72166109085083</v>
       </c>
       <c r="H893" t="n">
         <v>6516566</v>
@@ -26411,7 +26411,7 @@
         <v>5.01300001144409</v>
       </c>
       <c r="G898" t="n">
-        <v>4.76922988891602</v>
+        <v>4.76923036575317</v>
       </c>
       <c r="H898" t="n">
         <v>5422412</v>
@@ -26527,7 +26527,7 @@
         <v>5.06099987030029</v>
       </c>
       <c r="G902" t="n">
-        <v>4.81489562988281</v>
+        <v>4.81489610671997</v>
       </c>
       <c r="H902" t="n">
         <v>4829287</v>
@@ -26556,7 +26556,7 @@
         <v>4.91099977493286</v>
       </c>
       <c r="G903" t="n">
-        <v>4.67219018936157</v>
+        <v>4.67218971252441</v>
       </c>
       <c r="H903" t="n">
         <v>8017443</v>
@@ -26614,7 +26614,7 @@
         <v>4.95699977874756</v>
       </c>
       <c r="G905" t="n">
-        <v>4.71595287322998</v>
+        <v>4.71595335006714</v>
       </c>
       <c r="H905" t="n">
         <v>5337026</v>
@@ -26730,7 +26730,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G909" t="n">
-        <v>4.985191822052</v>
+        <v>4.98519134521484</v>
       </c>
       <c r="H909" t="n">
         <v>10810457</v>
@@ -26788,7 +26788,7 @@
         <v>5.10599994659424</v>
       </c>
       <c r="G911" t="n">
-        <v>4.85770797729492</v>
+        <v>4.85770750045776</v>
       </c>
       <c r="H911" t="n">
         <v>5112107</v>
@@ -26846,7 +26846,7 @@
         <v>4.99599981307983</v>
       </c>
       <c r="G913" t="n">
-        <v>4.75305700302124</v>
+        <v>4.75305652618408</v>
       </c>
       <c r="H913" t="n">
         <v>6486219</v>
@@ -26904,7 +26904,7 @@
         <v>4.83400011062622</v>
       </c>
       <c r="G915" t="n">
-        <v>4.59893465042114</v>
+        <v>4.59893417358398</v>
       </c>
       <c r="H915" t="n">
         <v>6262907</v>
@@ -26933,7 +26933,7 @@
         <v>4.81599998474121</v>
       </c>
       <c r="G916" t="n">
-        <v>4.58180952072144</v>
+        <v>4.58180999755859</v>
       </c>
       <c r="H916" t="n">
         <v>4733278</v>
@@ -26962,7 +26962,7 @@
         <v>4.88800001144409</v>
       </c>
       <c r="G917" t="n">
-        <v>4.65030860900879</v>
+        <v>4.65030813217163</v>
       </c>
       <c r="H917" t="n">
         <v>5260695</v>
@@ -26991,7 +26991,7 @@
         <v>4.60200023651123</v>
       </c>
       <c r="G918" t="n">
-        <v>4.37821626663208</v>
+        <v>4.37821578979492</v>
       </c>
       <c r="H918" t="n">
         <v>11153136</v>
@@ -27136,7 +27136,7 @@
         <v>4.56500005722046</v>
       </c>
       <c r="G923" t="n">
-        <v>4.34301567077637</v>
+        <v>4.34301519393921</v>
       </c>
       <c r="H923" t="n">
         <v>5051334</v>
@@ -27165,7 +27165,7 @@
         <v>4.47200012207031</v>
       </c>
       <c r="G924" t="n">
-        <v>4.25453758239746</v>
+        <v>4.25453805923462</v>
       </c>
       <c r="H924" t="n">
         <v>5236518</v>
@@ -27223,7 +27223,7 @@
         <v>4.59800004959106</v>
       </c>
       <c r="G926" t="n">
-        <v>4.3744101524353</v>
+        <v>4.37441062927246</v>
       </c>
       <c r="H926" t="n">
         <v>5193190</v>
@@ -27252,7 +27252,7 @@
         <v>4.52600002288818</v>
       </c>
       <c r="G927" t="n">
-        <v>4.30591154098511</v>
+        <v>4.30591201782227</v>
       </c>
       <c r="H927" t="n">
         <v>4843476</v>
@@ -27484,7 +27484,7 @@
         <v>4.92600011825562</v>
       </c>
       <c r="G935" t="n">
-        <v>4.68646097183228</v>
+        <v>4.68646049499512</v>
       </c>
       <c r="H935" t="n">
         <v>7598993</v>
@@ -27513,7 +27513,7 @@
         <v>4.91800022125244</v>
       </c>
       <c r="G936" t="n">
-        <v>4.67884969711304</v>
+        <v>4.6788501739502</v>
       </c>
       <c r="H936" t="n">
         <v>8686085</v>
@@ -27687,7 +27687,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G942" t="n">
-        <v>4.9566502571106</v>
+        <v>4.95665073394775</v>
       </c>
       <c r="H942" t="n">
         <v>9765274</v>
@@ -27716,7 +27716,7 @@
         <v>5.16699981689453</v>
       </c>
       <c r="G943" t="n">
-        <v>4.91574096679688</v>
+        <v>4.91574144363403</v>
       </c>
       <c r="H943" t="n">
         <v>5370870</v>
@@ -27803,7 +27803,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G946" t="n">
-        <v>4.985191822052</v>
+        <v>4.98519134521484</v>
       </c>
       <c r="H946" t="n">
         <v>8525656</v>
@@ -27977,7 +27977,7 @@
         <v>5.19700002670288</v>
       </c>
       <c r="G952" t="n">
-        <v>4.94428300857544</v>
+        <v>4.94428253173828</v>
       </c>
       <c r="H952" t="n">
         <v>6264433</v>
@@ -28064,7 +28064,7 @@
         <v>4.94199991226196</v>
       </c>
       <c r="G955" t="n">
-        <v>4.70168256759644</v>
+        <v>4.70168209075928</v>
       </c>
       <c r="H955" t="n">
         <v>14155269</v>
@@ -28093,7 +28093,7 @@
         <v>4.96799993515015</v>
       </c>
       <c r="G956" t="n">
-        <v>4.72641849517822</v>
+        <v>4.72641801834106</v>
       </c>
       <c r="H956" t="n">
         <v>7492745</v>
@@ -28122,7 +28122,7 @@
         <v>4.97599983215332</v>
       </c>
       <c r="G957" t="n">
-        <v>4.73402881622314</v>
+        <v>4.7340292930603</v>
       </c>
       <c r="H957" t="n">
         <v>8539212</v>
@@ -28180,7 +28180,7 @@
         <v>5.06599998474121</v>
       </c>
       <c r="G959" t="n">
-        <v>4.81965255737305</v>
+        <v>4.81965303421021</v>
       </c>
       <c r="H959" t="n">
         <v>7079628</v>
@@ -28267,7 +28267,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G962" t="n">
-        <v>5.09935665130615</v>
+        <v>5.09935617446899</v>
       </c>
       <c r="H962" t="n">
         <v>9513376</v>
@@ -28354,7 +28354,7 @@
         <v>5.39400005340576</v>
       </c>
       <c r="G965" t="n">
-        <v>5.13170337677002</v>
+        <v>5.13170289993286</v>
       </c>
       <c r="H965" t="n">
         <v>7271483</v>
@@ -28412,7 +28412,7 @@
         <v>5.35400009155273</v>
       </c>
       <c r="G967" t="n">
-        <v>5.09364795684814</v>
+        <v>5.0936484336853</v>
       </c>
       <c r="H967" t="n">
         <v>7366786</v>
@@ -28528,7 +28528,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G971" t="n">
-        <v>5.06130170822144</v>
+        <v>5.06130123138428</v>
       </c>
       <c r="H971" t="n">
         <v>8251907</v>
@@ -28615,7 +28615,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G974" t="n">
-        <v>5.05178737640381</v>
+        <v>5.05178785324097</v>
       </c>
       <c r="H974" t="n">
         <v>5670673</v>
@@ -28905,7 +28905,7 @@
         <v>5.36299991607666</v>
       </c>
       <c r="G984" t="n">
-        <v>5.10221004486084</v>
+        <v>5.102210521698</v>
       </c>
       <c r="H984" t="n">
         <v>8375880</v>
@@ -28934,7 +28934,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G985" t="n">
-        <v>5.09935665130615</v>
+        <v>5.09935617446899</v>
       </c>
       <c r="H985" t="n">
         <v>6100265</v>
@@ -28963,7 +28963,7 @@
         <v>5.41300010681152</v>
       </c>
       <c r="G986" t="n">
-        <v>5.14977931976318</v>
+        <v>5.14977884292603</v>
       </c>
       <c r="H986" t="n">
         <v>11408179</v>
@@ -28992,7 +28992,7 @@
         <v>5.44099998474121</v>
       </c>
       <c r="G987" t="n">
-        <v>5.17641735076904</v>
+        <v>5.1764178276062</v>
       </c>
       <c r="H987" t="n">
         <v>5867671</v>
@@ -29050,7 +29050,7 @@
         <v>5.51800012588501</v>
       </c>
       <c r="G989" t="n">
-        <v>5.24967336654663</v>
+        <v>5.24967288970947</v>
       </c>
       <c r="H989" t="n">
         <v>8024179</v>
@@ -29079,7 +29079,7 @@
         <v>5.65100002288818</v>
       </c>
       <c r="G990" t="n">
-        <v>5.37620544433594</v>
+        <v>5.3762059211731</v>
       </c>
       <c r="H990" t="n">
         <v>12871995</v>
@@ -29166,7 +29166,7 @@
         <v>5.83900022506714</v>
       </c>
       <c r="G993" t="n">
-        <v>5.55506420135498</v>
+        <v>5.55506372451782</v>
       </c>
       <c r="H993" t="n">
         <v>5594077</v>
@@ -29224,7 +29224,7 @@
         <v>5.73899984359741</v>
       </c>
       <c r="G995" t="n">
-        <v>5.45992660522461</v>
+        <v>5.45992612838745</v>
       </c>
       <c r="H995" t="n">
         <v>8653313</v>
@@ -29253,7 +29253,7 @@
         <v>5.68599987030029</v>
       </c>
       <c r="G996" t="n">
-        <v>5.40950393676758</v>
+        <v>5.40950345993042</v>
       </c>
       <c r="H996" t="n">
         <v>4200712</v>
@@ -29340,7 +29340,7 @@
         <v>5.51200008392334</v>
       </c>
       <c r="G999" t="n">
-        <v>5.24396467208862</v>
+        <v>5.24396514892578</v>
       </c>
       <c r="H999" t="n">
         <v>5722620</v>
@@ -29601,7 +29601,7 @@
         <v>5.54199981689453</v>
       </c>
       <c r="G1008" t="n">
-        <v>5.27250623703003</v>
+        <v>5.27250576019287</v>
       </c>
       <c r="H1008" t="n">
         <v>4337873</v>
@@ -29630,7 +29630,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1009" t="n">
-        <v>5.28963041305542</v>
+        <v>5.28963088989258</v>
       </c>
       <c r="H1009" t="n">
         <v>5422481</v>
@@ -29659,7 +29659,7 @@
         <v>5.59499979019165</v>
       </c>
       <c r="G1010" t="n">
-        <v>5.32292890548706</v>
+        <v>5.3229284286499</v>
       </c>
       <c r="H1010" t="n">
         <v>7120475</v>
@@ -29688,7 +29688,7 @@
         <v>5.59499979019165</v>
       </c>
       <c r="G1011" t="n">
-        <v>5.32292890548706</v>
+        <v>5.3229284286499</v>
       </c>
       <c r="H1011" t="n">
         <v>8358777</v>
@@ -29833,7 +29833,7 @@
         <v>5.59499979019165</v>
       </c>
       <c r="G1016" t="n">
-        <v>5.32292890548706</v>
+        <v>5.3229284286499</v>
       </c>
       <c r="H1016" t="n">
         <v>3767783</v>
@@ -29978,7 +29978,7 @@
         <v>5.26300001144409</v>
       </c>
       <c r="G1021" t="n">
-        <v>5.00707292556763</v>
+        <v>5.00707340240479</v>
       </c>
       <c r="H1021" t="n">
         <v>11895409</v>
@@ -30065,7 +30065,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1024" t="n">
-        <v>4.89956855773926</v>
+        <v>4.8995680809021</v>
       </c>
       <c r="H1024" t="n">
         <v>9609886</v>
@@ -30094,7 +30094,7 @@
         <v>5.05900001525879</v>
       </c>
       <c r="G1025" t="n">
-        <v>4.81299352645874</v>
+        <v>4.81299304962158</v>
       </c>
       <c r="H1025" t="n">
         <v>6906988</v>
@@ -30152,7 +30152,7 @@
         <v>5.1230001449585</v>
       </c>
       <c r="G1027" t="n">
-        <v>4.87388134002686</v>
+        <v>4.8738808631897</v>
       </c>
       <c r="H1027" t="n">
         <v>5426424</v>
@@ -30181,7 +30181,7 @@
         <v>5.11399984359741</v>
       </c>
       <c r="G1028" t="n">
-        <v>4.86531829833984</v>
+        <v>4.865318775177</v>
       </c>
       <c r="H1028" t="n">
         <v>3560102</v>
@@ -30210,7 +30210,7 @@
         <v>5.06599998474121</v>
       </c>
       <c r="G1029" t="n">
-        <v>4.81965255737305</v>
+        <v>4.81965303421021</v>
       </c>
       <c r="H1029" t="n">
         <v>7067344</v>
@@ -30268,7 +30268,7 @@
         <v>4.94199991226196</v>
       </c>
       <c r="G1031" t="n">
-        <v>4.70168256759644</v>
+        <v>4.70168209075928</v>
       </c>
       <c r="H1031" t="n">
         <v>8681679</v>
@@ -30413,7 +30413,7 @@
         <v>5.05399990081787</v>
       </c>
       <c r="G1036" t="n">
-        <v>4.80823659896851</v>
+        <v>4.80823612213135</v>
       </c>
       <c r="H1036" t="n">
         <v>8898900</v>
@@ -30471,7 +30471,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1038" t="n">
-        <v>4.58561563491821</v>
+        <v>4.58561515808105</v>
       </c>
       <c r="H1038" t="n">
         <v>8979335</v>
@@ -30500,7 +30500,7 @@
         <v>4.91800022125244</v>
       </c>
       <c r="G1039" t="n">
-        <v>4.67884969711304</v>
+        <v>4.6788501739502</v>
       </c>
       <c r="H1039" t="n">
         <v>8140590</v>
@@ -30558,7 +30558,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1041" t="n">
-        <v>4.77588987350464</v>
+        <v>4.77588939666748</v>
       </c>
       <c r="H1041" t="n">
         <v>6949040</v>
@@ -30587,7 +30587,7 @@
         <v>4.94799995422363</v>
       </c>
       <c r="G1042" t="n">
-        <v>4.70739126205444</v>
+        <v>4.70739078521729</v>
       </c>
       <c r="H1042" t="n">
         <v>6830332</v>
@@ -30703,7 +30703,7 @@
         <v>5.25</v>
       </c>
       <c r="G1046" t="n">
-        <v>4.99470567703247</v>
+        <v>4.99470520019531</v>
       </c>
       <c r="H1046" t="n">
         <v>18341830</v>
@@ -31022,7 +31022,7 @@
         <v>5.00099992752075</v>
       </c>
       <c r="G1057" t="n">
-        <v>4.75781393051147</v>
+        <v>4.75781345367432</v>
       </c>
       <c r="H1057" t="n">
         <v>18342696</v>
@@ -31080,7 +31080,7 @@
         <v>4.77899980545044</v>
       </c>
       <c r="G1059" t="n">
-        <v>4.54660844802856</v>
+        <v>4.54660892486572</v>
       </c>
       <c r="H1059" t="n">
         <v>14134380</v>
@@ -31167,7 +31167,7 @@
         <v>4.32100009918213</v>
       </c>
       <c r="G1062" t="n">
-        <v>4.11088085174561</v>
+        <v>4.11088037490845</v>
       </c>
       <c r="H1062" t="n">
         <v>15034059</v>
@@ -31225,7 +31225,7 @@
         <v>3.67199993133545</v>
       </c>
       <c r="G1064" t="n">
-        <v>3.49343943595886</v>
+        <v>3.49343967437744</v>
       </c>
       <c r="H1064" t="n">
         <v>15459498</v>
@@ -31254,7 +31254,7 @@
         <v>3.81699991226196</v>
       </c>
       <c r="G1065" t="n">
-        <v>3.63138866424561</v>
+        <v>3.63138842582703</v>
       </c>
       <c r="H1065" t="n">
         <v>20006610</v>
@@ -31428,7 +31428,7 @@
         <v>3.7739999294281</v>
       </c>
       <c r="G1071" t="n">
-        <v>3.59047961235046</v>
+        <v>3.59047937393188</v>
       </c>
       <c r="H1071" t="n">
         <v>20539960</v>
@@ -31718,7 +31718,7 @@
         <v>3.79299998283386</v>
       </c>
       <c r="G1081" t="n">
-        <v>3.60855579376221</v>
+        <v>3.60855555534363</v>
       </c>
       <c r="H1081" t="n">
         <v>9112585</v>
@@ -31776,7 +31776,7 @@
         <v>3.92400002479553</v>
       </c>
       <c r="G1083" t="n">
-        <v>3.73318552970886</v>
+        <v>3.73318529129028</v>
       </c>
       <c r="H1083" t="n">
         <v>8125581</v>
@@ -31834,7 +31834,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G1085" t="n">
-        <v>3.61045837402344</v>
+        <v>3.61045861244202</v>
       </c>
       <c r="H1085" t="n">
         <v>9133043</v>
@@ -31921,7 +31921,7 @@
         <v>3.53399991989136</v>
       </c>
       <c r="G1088" t="n">
-        <v>3.36214995384216</v>
+        <v>3.36215019226074</v>
       </c>
       <c r="H1088" t="n">
         <v>10081010</v>
@@ -32182,7 +32182,7 @@
         <v>3.44600009918213</v>
       </c>
       <c r="G1097" t="n">
-        <v>3.27842974662781</v>
+        <v>3.27842950820923</v>
       </c>
       <c r="H1097" t="n">
         <v>7252885</v>
@@ -32211,7 +32211,7 @@
         <v>3.64400005340576</v>
       </c>
       <c r="G1098" t="n">
-        <v>3.46680116653442</v>
+        <v>3.466801404953</v>
       </c>
       <c r="H1098" t="n">
         <v>11382035</v>
@@ -32240,7 +32240,7 @@
         <v>3.6159999370575</v>
       </c>
       <c r="G1099" t="n">
-        <v>3.44016289710999</v>
+        <v>3.44016265869141</v>
       </c>
       <c r="H1099" t="n">
         <v>12293070</v>
@@ -32298,7 +32298,7 @@
         <v>3.53399991989136</v>
       </c>
       <c r="G1101" t="n">
-        <v>3.36214995384216</v>
+        <v>3.36215019226074</v>
       </c>
       <c r="H1101" t="n">
         <v>6018678</v>
@@ -32327,7 +32327,7 @@
         <v>3.50399994850159</v>
       </c>
       <c r="G1102" t="n">
-        <v>3.33360910415649</v>
+        <v>3.33360886573792</v>
       </c>
       <c r="H1102" t="n">
         <v>4601154</v>
@@ -32356,7 +32356,7 @@
         <v>3.42799997329712</v>
       </c>
       <c r="G1103" t="n">
-        <v>3.2613046169281</v>
+        <v>3.26130485534668</v>
       </c>
       <c r="H1103" t="n">
         <v>7123473</v>
@@ -32385,7 +32385,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1104" t="n">
-        <v>3.29174852371216</v>
+        <v>3.29174876213074</v>
       </c>
       <c r="H1104" t="n">
         <v>3356216</v>
@@ -32675,7 +32675,7 @@
         <v>3.20700001716614</v>
       </c>
       <c r="G1114" t="n">
-        <v>3.0510516166687</v>
+        <v>3.05105137825012</v>
       </c>
       <c r="H1114" t="n">
         <v>12499911</v>
@@ -32733,7 +32733,7 @@
         <v>3.30399990081787</v>
       </c>
       <c r="G1116" t="n">
-        <v>3.14333438873291</v>
+        <v>3.14333462715149</v>
       </c>
       <c r="H1116" t="n">
         <v>12389541</v>
@@ -32762,7 +32762,7 @@
         <v>3.3050000667572</v>
       </c>
       <c r="G1117" t="n">
-        <v>3.14428615570068</v>
+        <v>3.1442859172821</v>
       </c>
       <c r="H1117" t="n">
         <v>16377885</v>
@@ -32849,7 +32849,7 @@
         <v>3.41400003433228</v>
       </c>
       <c r="G1120" t="n">
-        <v>3.24798560142517</v>
+        <v>3.24798536300659</v>
       </c>
       <c r="H1120" t="n">
         <v>10515189</v>
@@ -32878,7 +32878,7 @@
         <v>3.52300000190735</v>
       </c>
       <c r="G1121" t="n">
-        <v>3.35168528556824</v>
+        <v>3.35168504714966</v>
       </c>
       <c r="H1121" t="n">
         <v>14830770</v>
@@ -33052,7 +33052,7 @@
         <v>3.71600008010864</v>
       </c>
       <c r="G1127" t="n">
-        <v>3.5353000164032</v>
+        <v>3.53530025482178</v>
       </c>
       <c r="H1127" t="n">
         <v>26938169</v>
@@ -33110,7 +33110,7 @@
         <v>3.53399991989136</v>
       </c>
       <c r="G1129" t="n">
-        <v>3.36214995384216</v>
+        <v>3.36215019226074</v>
       </c>
       <c r="H1129" t="n">
         <v>19235451</v>
@@ -33226,7 +33226,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1133" t="n">
-        <v>3.49153685569763</v>
+        <v>3.49153709411621</v>
       </c>
       <c r="H1133" t="n">
         <v>10659918</v>
@@ -79951,6 +79951,64 @@
         <v>3276530</v>
       </c>
       <c r="I2744" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2745">
+      <c r="A2745" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2745" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C2745" t="n">
+        <v>5.59000015258789</v>
+      </c>
+      <c r="D2745" t="n">
+        <v>5.61199998855591</v>
+      </c>
+      <c r="E2745" t="n">
+        <v>5.51999998092651</v>
+      </c>
+      <c r="F2745" t="n">
+        <v>5.58099985122681</v>
+      </c>
+      <c r="G2745" t="n">
+        <v>5.58099985122681</v>
+      </c>
+      <c r="H2745" t="n">
+        <v>2287483</v>
+      </c>
+      <c r="I2745" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2746">
+      <c r="A2746" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2746" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C2746" t="n">
+        <v>5.5789999961853</v>
+      </c>
+      <c r="D2746" t="n">
+        <v>5.6560001373291</v>
+      </c>
+      <c r="E2746" t="n">
+        <v>5.51599979400635</v>
+      </c>
+      <c r="F2746" t="n">
+        <v>5.63000011444092</v>
+      </c>
+      <c r="G2746" t="n">
+        <v>5.63000011444092</v>
+      </c>
+      <c r="H2746" t="n">
+        <v>3331974</v>
+      </c>
+      <c r="I2746" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TIT.MI.xlsx
+++ b/data/TIT.MI.xlsx
@@ -79994,7 +79994,7 @@
         <v>5.5789999961853</v>
       </c>
       <c r="D2746" t="n">
-        <v>5.6560001373291</v>
+        <v>5.65700006484985</v>
       </c>
       <c r="E2746" t="n">
         <v>5.51599979400635</v>
@@ -80009,6 +80009,35 @@
         <v>3331974</v>
       </c>
       <c r="I2746" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2747">
+      <c r="A2747" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2747" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C2747" t="n">
+        <v>5.62799978256226</v>
+      </c>
+      <c r="D2747" t="n">
+        <v>5.83400011062622</v>
+      </c>
+      <c r="E2747" t="n">
+        <v>5.60400009155273</v>
+      </c>
+      <c r="F2747" t="n">
+        <v>5.75799989700317</v>
+      </c>
+      <c r="G2747" t="n">
+        <v>5.75799989700317</v>
+      </c>
+      <c r="H2747" t="n">
+        <v>5263440</v>
+      </c>
+      <c r="I2747" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TIT.MI.xlsx
+++ b/data/TIT.MI.xlsx
@@ -80041,6 +80041,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2748">
+      <c r="A2748" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2748" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C2748" t="n">
+        <v>5.74900007247925</v>
+      </c>
+      <c r="D2748" t="n">
+        <v>5.84600019454956</v>
+      </c>
+      <c r="E2748" t="n">
+        <v>5.72200012207031</v>
+      </c>
+      <c r="F2748" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="G2748" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="H2748" t="n">
+        <v>3779210</v>
+      </c>
+      <c r="I2748" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TIT.MI.xlsx
+++ b/data/TIT.MI.xlsx
@@ -775,7 +775,7 @@
         <v>9.76500034332275</v>
       </c>
       <c r="G14" t="n">
-        <v>9.29015254974365</v>
+        <v>9.29015159606934</v>
       </c>
       <c r="H14" t="n">
         <v>12465433</v>
@@ -949,7 +949,7 @@
         <v>9.77000045776367</v>
       </c>
       <c r="G20" t="n">
-        <v>9.29490947723389</v>
+        <v>9.29490852355957</v>
       </c>
       <c r="H20" t="n">
         <v>21107831</v>
@@ -1152,7 +1152,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G27" t="n">
-        <v>7.99152851104736</v>
+        <v>7.99152803421021</v>
       </c>
       <c r="H27" t="n">
         <v>18362675</v>
@@ -1181,7 +1181,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G28" t="n">
-        <v>8.27693939208984</v>
+        <v>8.27694034576416</v>
       </c>
       <c r="H28" t="n">
         <v>22554264</v>
@@ -1239,7 +1239,7 @@
         <v>8.25500011444092</v>
       </c>
       <c r="G30" t="n">
-        <v>7.8535795211792</v>
+        <v>7.85357904434204</v>
       </c>
       <c r="H30" t="n">
         <v>17371217</v>
@@ -1268,7 +1268,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G31" t="n">
-        <v>8.17228984832764</v>
+        <v>8.17228889465332</v>
       </c>
       <c r="H31" t="n">
         <v>10187944</v>
@@ -1297,7 +1297,7 @@
         <v>8.76500034332275</v>
       </c>
       <c r="G32" t="n">
-        <v>8.33878040313721</v>
+        <v>8.33877944946289</v>
       </c>
       <c r="H32" t="n">
         <v>9462652</v>
@@ -1326,7 +1326,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G33" t="n">
-        <v>7.80125331878662</v>
+        <v>7.80125379562378</v>
       </c>
       <c r="H33" t="n">
         <v>28696243</v>
@@ -1587,7 +1587,7 @@
         <v>8.98999977111816</v>
       </c>
       <c r="G42" t="n">
-        <v>8.55283737182617</v>
+        <v>8.55283832550049</v>
       </c>
       <c r="H42" t="n">
         <v>10915001</v>
@@ -1645,7 +1645,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G44" t="n">
-        <v>8.98095607757568</v>
+        <v>8.98095512390137</v>
       </c>
       <c r="H44" t="n">
         <v>13756209</v>
@@ -1703,7 +1703,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G46" t="n">
-        <v>9.70399951934814</v>
+        <v>9.70399856567383</v>
       </c>
       <c r="H46" t="n">
         <v>20342560</v>
@@ -1732,7 +1732,7 @@
         <v>9.82499980926514</v>
       </c>
       <c r="G47" t="n">
-        <v>9.34723377227783</v>
+        <v>9.34723472595215</v>
       </c>
       <c r="H47" t="n">
         <v>11169591</v>
@@ -1790,7 +1790,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G49" t="n">
-        <v>9.64691638946533</v>
+        <v>9.64691734313965</v>
       </c>
       <c r="H49" t="n">
         <v>18523100</v>
@@ -1848,7 +1848,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G51" t="n">
-        <v>9.91330146789551</v>
+        <v>9.91330051422119</v>
       </c>
       <c r="H51" t="n">
         <v>10987806</v>
@@ -1877,7 +1877,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G52" t="n">
-        <v>9.81816291809082</v>
+        <v>9.81816387176514</v>
       </c>
       <c r="H52" t="n">
         <v>6496305</v>
@@ -1935,7 +1935,7 @@
         <v>10.3299999237061</v>
       </c>
       <c r="G54" t="n">
-        <v>9.82767677307129</v>
+        <v>9.82767772674561</v>
       </c>
       <c r="H54" t="n">
         <v>5795315</v>
@@ -2022,7 +2022,7 @@
         <v>10.4099998474121</v>
       </c>
       <c r="G57" t="n">
-        <v>9.90378761291504</v>
+        <v>9.90378665924072</v>
       </c>
       <c r="H57" t="n">
         <v>9694375</v>
@@ -2225,7 +2225,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G64" t="n">
-        <v>8.70505714416504</v>
+        <v>8.70505809783936</v>
       </c>
       <c r="H64" t="n">
         <v>14609221</v>
@@ -2283,7 +2283,7 @@
         <v>8.58500003814697</v>
       </c>
       <c r="G66" t="n">
-        <v>8.1675329208374</v>
+        <v>8.16753196716309</v>
       </c>
       <c r="H66" t="n">
         <v>11386012</v>
@@ -2312,7 +2312,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G67" t="n">
-        <v>8.18180274963379</v>
+        <v>8.18180370330811</v>
       </c>
       <c r="H67" t="n">
         <v>8994634</v>
@@ -2341,7 +2341,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G68" t="n">
-        <v>7.95347356796265</v>
+        <v>7.95347309112549</v>
       </c>
       <c r="H68" t="n">
         <v>8054619</v>
@@ -2399,7 +2399,7 @@
         <v>8.98999977111816</v>
       </c>
       <c r="G70" t="n">
-        <v>8.55283737182617</v>
+        <v>8.55283832550049</v>
       </c>
       <c r="H70" t="n">
         <v>7769877</v>
@@ -2718,7 +2718,7 @@
         <v>8.65499973297119</v>
       </c>
       <c r="G81" t="n">
-        <v>8.23412895202637</v>
+        <v>8.23412799835205</v>
       </c>
       <c r="H81" t="n">
         <v>11095524</v>
@@ -2776,7 +2776,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G83" t="n">
-        <v>8.25791263580322</v>
+        <v>8.25791358947754</v>
       </c>
       <c r="H83" t="n">
         <v>15796951</v>
@@ -2834,7 +2834,7 @@
         <v>8.46500015258789</v>
       </c>
       <c r="G85" t="n">
-        <v>8.05336761474609</v>
+        <v>8.05336856842041</v>
       </c>
       <c r="H85" t="n">
         <v>6739223</v>
@@ -2863,7 +2863,7 @@
         <v>8.36499977111816</v>
       </c>
       <c r="G86" t="n">
-        <v>7.95823049545288</v>
+        <v>7.95823001861572</v>
       </c>
       <c r="H86" t="n">
         <v>7439860</v>
@@ -2892,7 +2892,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G87" t="n">
-        <v>8.04861068725586</v>
+        <v>8.04861164093018</v>
       </c>
       <c r="H87" t="n">
         <v>6088332</v>
@@ -3037,7 +3037,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G92" t="n">
-        <v>8.05812454223633</v>
+        <v>8.05812549591064</v>
       </c>
       <c r="H92" t="n">
         <v>7818052</v>
@@ -3153,7 +3153,7 @@
         <v>8.48999977111816</v>
       </c>
       <c r="G96" t="n">
-        <v>8.07715129852295</v>
+        <v>8.07715225219727</v>
       </c>
       <c r="H96" t="n">
         <v>11841822</v>
@@ -3211,7 +3211,7 @@
         <v>8.30500030517578</v>
       </c>
       <c r="G98" t="n">
-        <v>7.90114784240723</v>
+        <v>7.90114879608154</v>
       </c>
       <c r="H98" t="n">
         <v>9583225</v>
@@ -3240,7 +3240,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G99" t="n">
-        <v>7.87736320495605</v>
+        <v>7.87736368179321</v>
       </c>
       <c r="H99" t="n">
         <v>7171888</v>
@@ -3327,7 +3327,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G102" t="n">
-        <v>7.91541814804077</v>
+        <v>7.91541862487793</v>
       </c>
       <c r="H102" t="n">
         <v>15847474</v>
@@ -3385,7 +3385,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G104" t="n">
-        <v>8.27693939208984</v>
+        <v>8.27694034576416</v>
       </c>
       <c r="H104" t="n">
         <v>8314517</v>
@@ -3675,7 +3675,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G114" t="n">
-        <v>7.82028198242188</v>
+        <v>7.82028150558472</v>
       </c>
       <c r="H114" t="n">
         <v>14068153</v>
@@ -3704,7 +3704,7 @@
         <v>7.91499996185303</v>
       </c>
       <c r="G115" t="n">
-        <v>7.53011322021484</v>
+        <v>7.53011274337769</v>
       </c>
       <c r="H115" t="n">
         <v>12688239</v>
@@ -3762,7 +3762,7 @@
         <v>7.59499979019165</v>
       </c>
       <c r="G117" t="n">
-        <v>7.22567367553711</v>
+        <v>7.22567319869995</v>
       </c>
       <c r="H117" t="n">
         <v>14127681</v>
@@ -3791,7 +3791,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G118" t="n">
-        <v>7.04015588760376</v>
+        <v>7.04015636444092</v>
       </c>
       <c r="H118" t="n">
         <v>12062526</v>
@@ -3936,7 +3936,7 @@
         <v>8.27499961853027</v>
       </c>
       <c r="G123" t="n">
-        <v>7.87260627746582</v>
+        <v>7.87260675430298</v>
       </c>
       <c r="H123" t="n">
         <v>12615589</v>
@@ -3994,7 +3994,7 @@
         <v>6.67500019073486</v>
       </c>
       <c r="G125" t="n">
-        <v>6.3504114151001</v>
+        <v>6.35041093826294</v>
       </c>
       <c r="H125" t="n">
         <v>23209498</v>
@@ -4052,7 +4052,7 @@
         <v>7.44500017166138</v>
       </c>
       <c r="G127" t="n">
-        <v>7.08296823501587</v>
+        <v>7.08296775817871</v>
       </c>
       <c r="H127" t="n">
         <v>14352211</v>
@@ -4110,7 +4110,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G129" t="n">
-        <v>7.04015588760376</v>
+        <v>7.04015636444092</v>
       </c>
       <c r="H129" t="n">
         <v>8980366</v>
@@ -4226,7 +4226,7 @@
         <v>6.33500003814697</v>
       </c>
       <c r="G133" t="n">
-        <v>6.02694463729858</v>
+        <v>6.02694416046143</v>
       </c>
       <c r="H133" t="n">
         <v>13905809</v>
@@ -4284,7 +4284,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G135" t="n">
-        <v>6.30759906768799</v>
+        <v>6.30759954452515</v>
       </c>
       <c r="H135" t="n">
         <v>6922559</v>
@@ -4313,7 +4313,7 @@
         <v>6.92500019073486</v>
       </c>
       <c r="G136" t="n">
-        <v>6.58825445175171</v>
+        <v>6.58825397491455</v>
       </c>
       <c r="H136" t="n">
         <v>10111814</v>
@@ -4429,7 +4429,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G140" t="n">
-        <v>6.60252475738525</v>
+        <v>6.60252523422241</v>
       </c>
       <c r="H140" t="n">
         <v>13382865</v>
@@ -4487,7 +4487,7 @@
         <v>6.86499977111816</v>
       </c>
       <c r="G142" t="n">
-        <v>6.5311713218689</v>
+        <v>6.53117179870605</v>
       </c>
       <c r="H142" t="n">
         <v>8811876</v>
@@ -4574,7 +4574,7 @@
         <v>7</v>
       </c>
       <c r="G145" t="n">
-        <v>6.65960741043091</v>
+        <v>6.65960693359375</v>
       </c>
       <c r="H145" t="n">
         <v>8398609</v>
@@ -4632,7 +4632,7 @@
         <v>7.46999979019165</v>
       </c>
       <c r="G147" t="n">
-        <v>7.10675239562988</v>
+        <v>7.10675191879272</v>
       </c>
       <c r="H147" t="n">
         <v>29073903</v>
@@ -4690,7 +4690,7 @@
         <v>7.63500022888184</v>
       </c>
       <c r="G149" t="n">
-        <v>7.26372861862183</v>
+        <v>7.26372909545898</v>
       </c>
       <c r="H149" t="n">
         <v>10594903</v>
@@ -4748,7 +4748,7 @@
         <v>7.44500017166138</v>
       </c>
       <c r="G151" t="n">
-        <v>7.08296823501587</v>
+        <v>7.08296775817871</v>
       </c>
       <c r="H151" t="n">
         <v>8748243</v>
@@ -4893,7 +4893,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G156" t="n">
-        <v>7.24945783615112</v>
+        <v>7.24945831298828</v>
       </c>
       <c r="H156" t="n">
         <v>4135572</v>
@@ -5125,7 +5125,7 @@
         <v>7.92999982833862</v>
       </c>
       <c r="G164" t="n">
-        <v>7.54438352584839</v>
+        <v>7.54438304901123</v>
       </c>
       <c r="H164" t="n">
         <v>4924973</v>
@@ -5212,7 +5212,7 @@
         <v>8.0649995803833</v>
       </c>
       <c r="G167" t="n">
-        <v>7.67281818389893</v>
+        <v>7.67281866073608</v>
       </c>
       <c r="H167" t="n">
         <v>5554419</v>
@@ -5299,7 +5299,7 @@
         <v>8.24499988555908</v>
       </c>
       <c r="G170" t="n">
-        <v>7.84406566619873</v>
+        <v>7.84406518936157</v>
       </c>
       <c r="H170" t="n">
         <v>6352724</v>
@@ -5328,7 +5328,7 @@
         <v>8.13500022888184</v>
       </c>
       <c r="G171" t="n">
-        <v>7.73941469192505</v>
+        <v>7.73941516876221</v>
       </c>
       <c r="H171" t="n">
         <v>7750471</v>
@@ -5357,7 +5357,7 @@
         <v>8.16499996185303</v>
       </c>
       <c r="G172" t="n">
-        <v>7.76795625686646</v>
+        <v>7.7679557800293</v>
       </c>
       <c r="H172" t="n">
         <v>8273298</v>
@@ -5386,7 +5386,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G173" t="n">
-        <v>7.80125331878662</v>
+        <v>7.80125379562378</v>
       </c>
       <c r="H173" t="n">
         <v>5239033</v>
@@ -5473,7 +5473,7 @@
         <v>8.04500007629395</v>
       </c>
       <c r="G176" t="n">
-        <v>7.65379095077515</v>
+        <v>7.6537914276123</v>
       </c>
       <c r="H176" t="n">
         <v>7646216</v>
@@ -5502,7 +5502,7 @@
         <v>8.16499996185303</v>
       </c>
       <c r="G177" t="n">
-        <v>7.76795625686646</v>
+        <v>7.7679557800293</v>
       </c>
       <c r="H177" t="n">
         <v>6137326</v>
@@ -5531,7 +5531,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G178" t="n">
-        <v>7.64903450012207</v>
+        <v>7.64903402328491</v>
       </c>
       <c r="H178" t="n">
         <v>7450630</v>
@@ -5560,7 +5560,7 @@
         <v>7.88500022888184</v>
       </c>
       <c r="G179" t="n">
-        <v>7.50157165527344</v>
+        <v>7.5015721321106</v>
       </c>
       <c r="H179" t="n">
         <v>10968844</v>
@@ -5647,7 +5647,7 @@
         <v>7.53499984741211</v>
       </c>
       <c r="G182" t="n">
-        <v>7.16859102249146</v>
+        <v>7.16859149932861</v>
       </c>
       <c r="H182" t="n">
         <v>8919248</v>
@@ -5734,7 +5734,7 @@
         <v>7.28499984741211</v>
       </c>
       <c r="G185" t="n">
-        <v>6.93074798583984</v>
+        <v>6.930748462677</v>
       </c>
       <c r="H185" t="n">
         <v>7139176</v>
@@ -5821,7 +5821,7 @@
         <v>7.63500022888184</v>
       </c>
       <c r="G188" t="n">
-        <v>7.26372861862183</v>
+        <v>7.26372909545898</v>
       </c>
       <c r="H188" t="n">
         <v>4604142</v>
@@ -5879,7 +5879,7 @@
         <v>7.34499979019165</v>
       </c>
       <c r="G190" t="n">
-        <v>6.9878306388855</v>
+        <v>6.98783016204834</v>
       </c>
       <c r="H190" t="n">
         <v>5769993</v>
@@ -5908,7 +5908,7 @@
         <v>7.49499988555908</v>
       </c>
       <c r="G191" t="n">
-        <v>7.13053607940674</v>
+        <v>7.1305365562439</v>
       </c>
       <c r="H191" t="n">
         <v>4422318</v>
@@ -5966,7 +5966,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G193" t="n">
-        <v>7.03064203262329</v>
+        <v>7.03064250946045</v>
       </c>
       <c r="H193" t="n">
         <v>9011031</v>
@@ -6053,7 +6053,7 @@
         <v>7.29500007629395</v>
       </c>
       <c r="G196" t="n">
-        <v>6.94026184082031</v>
+        <v>6.94026231765747</v>
       </c>
       <c r="H196" t="n">
         <v>10575030</v>
@@ -6140,7 +6140,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G199" t="n">
-        <v>7.04015588760376</v>
+        <v>7.04015636444092</v>
       </c>
       <c r="H199" t="n">
         <v>8616275</v>
@@ -6169,7 +6169,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G200" t="n">
-        <v>6.86890840530396</v>
+        <v>6.86890888214111</v>
       </c>
       <c r="H200" t="n">
         <v>8236131</v>
@@ -6227,7 +6227,7 @@
         <v>6.94500017166138</v>
       </c>
       <c r="G202" t="n">
-        <v>6.60728168487549</v>
+        <v>6.60728216171265</v>
       </c>
       <c r="H202" t="n">
         <v>17317483</v>
@@ -6314,7 +6314,7 @@
         <v>7.57499980926514</v>
       </c>
       <c r="G205" t="n">
-        <v>7.20664644241333</v>
+        <v>7.20664596557617</v>
       </c>
       <c r="H205" t="n">
         <v>13042674</v>
@@ -6372,7 +6372,7 @@
         <v>7.59499979019165</v>
       </c>
       <c r="G207" t="n">
-        <v>7.22567367553711</v>
+        <v>7.22567319869995</v>
       </c>
       <c r="H207" t="n">
         <v>5770682</v>
@@ -6401,7 +6401,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G208" t="n">
-        <v>7.3541088104248</v>
+        <v>7.35410928726196</v>
       </c>
       <c r="H208" t="n">
         <v>11041706</v>
@@ -6430,7 +6430,7 @@
         <v>7.92999982833862</v>
       </c>
       <c r="G209" t="n">
-        <v>7.54438352584839</v>
+        <v>7.54438304901123</v>
       </c>
       <c r="H209" t="n">
         <v>12562957</v>
@@ -6633,7 +6633,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G216" t="n">
-        <v>7.3541088104248</v>
+        <v>7.35410928726196</v>
       </c>
       <c r="H216" t="n">
         <v>11074256</v>
@@ -6662,7 +6662,7 @@
         <v>7.70499992370605</v>
       </c>
       <c r="G217" t="n">
-        <v>7.33032417297363</v>
+        <v>7.33032464981079</v>
       </c>
       <c r="H217" t="n">
         <v>6751462</v>
@@ -6778,7 +6778,7 @@
         <v>7.45499992370605</v>
       </c>
       <c r="G221" t="n">
-        <v>7.09248113632202</v>
+        <v>7.09248161315918</v>
       </c>
       <c r="H221" t="n">
         <v>19305315</v>
@@ -6952,7 +6952,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G227" t="n">
-        <v>6.67863464355469</v>
+        <v>6.67863416671753</v>
       </c>
       <c r="H227" t="n">
         <v>15148923</v>
@@ -6981,7 +6981,7 @@
         <v>6.86499977111816</v>
       </c>
       <c r="G228" t="n">
-        <v>6.5311713218689</v>
+        <v>6.53117179870605</v>
       </c>
       <c r="H228" t="n">
         <v>15141472</v>
@@ -7097,7 +7097,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G232" t="n">
-        <v>6.70717573165894</v>
+        <v>6.70717620849609</v>
       </c>
       <c r="H232" t="n">
         <v>6631825</v>
@@ -7126,7 +7126,7 @@
         <v>7.14499998092651</v>
       </c>
       <c r="G233" t="n">
-        <v>6.79755640029907</v>
+        <v>6.79755592346191</v>
       </c>
       <c r="H233" t="n">
         <v>7685848</v>
@@ -7300,7 +7300,7 @@
         <v>7</v>
       </c>
       <c r="G239" t="n">
-        <v>6.65960741043091</v>
+        <v>6.65960693359375</v>
       </c>
       <c r="H239" t="n">
         <v>16092872</v>
@@ -7358,7 +7358,7 @@
         <v>7.54500007629395</v>
       </c>
       <c r="G241" t="n">
-        <v>7.17810487747192</v>
+        <v>7.17810535430908</v>
       </c>
       <c r="H241" t="n">
         <v>14162922</v>
@@ -7416,7 +7416,7 @@
         <v>7.625</v>
       </c>
       <c r="G243" t="n">
-        <v>7.25421476364136</v>
+        <v>7.25421524047852</v>
       </c>
       <c r="H243" t="n">
         <v>7313055</v>
@@ -7561,7 +7561,7 @@
         <v>8.06999969482422</v>
       </c>
       <c r="G248" t="n">
-        <v>7.67757511138916</v>
+        <v>7.67757558822632</v>
       </c>
       <c r="H248" t="n">
         <v>19683266</v>
@@ -7648,7 +7648,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G251" t="n">
-        <v>7.99152851104736</v>
+        <v>7.99152803421021</v>
       </c>
       <c r="H251" t="n">
         <v>10995964</v>
@@ -7735,7 +7735,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G254" t="n">
-        <v>8.27693939208984</v>
+        <v>8.27694034576416</v>
       </c>
       <c r="H254" t="n">
         <v>7105744</v>
@@ -7764,7 +7764,7 @@
         <v>8.42500019073486</v>
       </c>
       <c r="G255" t="n">
-        <v>8.01531314849854</v>
+        <v>8.01531219482422</v>
       </c>
       <c r="H255" t="n">
         <v>7953684</v>
@@ -7822,7 +7822,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G257" t="n">
-        <v>7.96298742294312</v>
+        <v>7.96298694610596</v>
       </c>
       <c r="H257" t="n">
         <v>4473749</v>
@@ -7851,7 +7851,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G258" t="n">
-        <v>8.16277599334717</v>
+        <v>8.16277503967285</v>
       </c>
       <c r="H258" t="n">
         <v>6919849</v>
@@ -7938,7 +7938,7 @@
         <v>8.42500019073486</v>
       </c>
       <c r="G261" t="n">
-        <v>8.01531314849854</v>
+        <v>8.01531219482422</v>
       </c>
       <c r="H261" t="n">
         <v>8691609</v>
@@ -7996,7 +7996,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G263" t="n">
-        <v>7.82028198242188</v>
+        <v>7.82028150558472</v>
       </c>
       <c r="H263" t="n">
         <v>9698154</v>
@@ -8025,7 +8025,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G264" t="n">
-        <v>7.87736320495605</v>
+        <v>7.87736368179321</v>
       </c>
       <c r="H264" t="n">
         <v>8049414</v>
@@ -8054,7 +8054,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G265" t="n">
-        <v>8.04861068725586</v>
+        <v>8.04861164093018</v>
       </c>
       <c r="H265" t="n">
         <v>10193124</v>
@@ -8083,7 +8083,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G266" t="n">
-        <v>7.93444681167603</v>
+        <v>7.93444633483887</v>
       </c>
       <c r="H266" t="n">
         <v>5591385</v>
@@ -8141,7 +8141,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G268" t="n">
-        <v>8.10569286346436</v>
+        <v>8.10569381713867</v>
       </c>
       <c r="H268" t="n">
         <v>4819501</v>
@@ -8170,7 +8170,7 @@
         <v>8.375</v>
       </c>
       <c r="G269" t="n">
-        <v>7.96774482727051</v>
+        <v>7.96774387359619</v>
       </c>
       <c r="H269" t="n">
         <v>6854564</v>
@@ -8199,7 +8199,7 @@
         <v>8.3100004196167</v>
       </c>
       <c r="G270" t="n">
-        <v>7.90590524673462</v>
+        <v>7.90590572357178</v>
       </c>
       <c r="H270" t="n">
         <v>7624065</v>
@@ -8228,7 +8228,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G271" t="n">
-        <v>7.99152851104736</v>
+        <v>7.99152803421021</v>
       </c>
       <c r="H271" t="n">
         <v>15001217</v>
@@ -8257,7 +8257,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G272" t="n">
-        <v>8.04861068725586</v>
+        <v>8.04861164093018</v>
       </c>
       <c r="H272" t="n">
         <v>7357311</v>
@@ -8286,7 +8286,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G273" t="n">
-        <v>7.99152851104736</v>
+        <v>7.99152803421021</v>
       </c>
       <c r="H273" t="n">
         <v>6892052</v>
@@ -8315,7 +8315,7 @@
         <v>8.3100004196167</v>
       </c>
       <c r="G274" t="n">
-        <v>7.90590524673462</v>
+        <v>7.90590572357178</v>
       </c>
       <c r="H274" t="n">
         <v>10051498</v>
@@ -8344,7 +8344,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G275" t="n">
-        <v>7.82979536056519</v>
+        <v>7.82979440689087</v>
       </c>
       <c r="H275" t="n">
         <v>9477679</v>
@@ -8518,7 +8518,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G281" t="n">
-        <v>7.59195184707642</v>
+        <v>7.59195232391357</v>
       </c>
       <c r="H281" t="n">
         <v>6833809</v>
@@ -8634,7 +8634,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G285" t="n">
-        <v>7.79174041748047</v>
+        <v>7.79173994064331</v>
       </c>
       <c r="H285" t="n">
         <v>8180031</v>
@@ -8663,7 +8663,7 @@
         <v>8.25</v>
       </c>
       <c r="G286" t="n">
-        <v>7.84882259368896</v>
+        <v>7.84882211685181</v>
       </c>
       <c r="H286" t="n">
         <v>8035948</v>
@@ -8692,7 +8692,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G287" t="n">
-        <v>7.64903450012207</v>
+        <v>7.64903402328491</v>
       </c>
       <c r="H287" t="n">
         <v>9027559</v>
@@ -8750,7 +8750,7 @@
         <v>7.97499990463257</v>
       </c>
       <c r="G289" t="n">
-        <v>7.58719491958618</v>
+        <v>7.58719539642334</v>
       </c>
       <c r="H289" t="n">
         <v>7815676</v>
@@ -8808,7 +8808,7 @@
         <v>7.91499996185303</v>
       </c>
       <c r="G291" t="n">
-        <v>7.53011322021484</v>
+        <v>7.53011274337769</v>
       </c>
       <c r="H291" t="n">
         <v>6709166</v>
@@ -8895,7 +8895,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G294" t="n">
-        <v>7.32556772232056</v>
+        <v>7.3255672454834</v>
       </c>
       <c r="H294" t="n">
         <v>10570127</v>
@@ -8924,7 +8924,7 @@
         <v>7.59499979019165</v>
       </c>
       <c r="G295" t="n">
-        <v>7.22567367553711</v>
+        <v>7.22567319869995</v>
       </c>
       <c r="H295" t="n">
         <v>15446807</v>
@@ -9185,7 +9185,7 @@
         <v>7.79500007629395</v>
       </c>
       <c r="G304" t="n">
-        <v>7.41594791412354</v>
+        <v>7.41594839096069</v>
       </c>
       <c r="H304" t="n">
         <v>5768451</v>
@@ -9214,7 +9214,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G305" t="n">
-        <v>7.3541088104248</v>
+        <v>7.35410928726196</v>
       </c>
       <c r="H305" t="n">
         <v>8662340</v>
@@ -9243,7 +9243,7 @@
         <v>7.83500003814697</v>
       </c>
       <c r="G306" t="n">
-        <v>7.45400285720825</v>
+        <v>7.45400333404541</v>
       </c>
       <c r="H306" t="n">
         <v>8558245</v>
@@ -9359,7 +9359,7 @@
         <v>7.88500022888184</v>
       </c>
       <c r="G310" t="n">
-        <v>7.50157165527344</v>
+        <v>7.5015721321106</v>
       </c>
       <c r="H310" t="n">
         <v>9967793</v>
@@ -9475,7 +9475,7 @@
         <v>8.125</v>
       </c>
       <c r="G314" t="n">
-        <v>7.72990131378174</v>
+        <v>7.72990083694458</v>
       </c>
       <c r="H314" t="n">
         <v>8729316</v>
@@ -9562,7 +9562,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G317" t="n">
-        <v>7.93444681167603</v>
+        <v>7.93444633483887</v>
       </c>
       <c r="H317" t="n">
         <v>9638120</v>
@@ -9620,7 +9620,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G319" t="n">
-        <v>8.10569286346436</v>
+        <v>8.10569381713867</v>
       </c>
       <c r="H319" t="n">
         <v>9247079</v>
@@ -9649,7 +9649,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G320" t="n">
-        <v>8.0105562210083</v>
+        <v>8.01055526733398</v>
       </c>
       <c r="H320" t="n">
         <v>7285311</v>
@@ -9678,7 +9678,7 @@
         <v>8.45499992370605</v>
       </c>
       <c r="G321" t="n">
-        <v>8.04385375976562</v>
+        <v>8.04385471343994</v>
       </c>
       <c r="H321" t="n">
         <v>8408909</v>
@@ -9794,7 +9794,7 @@
         <v>8.13500022888184</v>
       </c>
       <c r="G325" t="n">
-        <v>7.73941469192505</v>
+        <v>7.73941516876221</v>
       </c>
       <c r="H325" t="n">
         <v>6312505</v>
@@ -9910,7 +9910,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G329" t="n">
-        <v>7.64903450012207</v>
+        <v>7.64903402328491</v>
       </c>
       <c r="H329" t="n">
         <v>5813093</v>
@@ -9939,7 +9939,7 @@
         <v>8.04500007629395</v>
       </c>
       <c r="G330" t="n">
-        <v>7.65379095077515</v>
+        <v>7.6537914276123</v>
       </c>
       <c r="H330" t="n">
         <v>5005452</v>
@@ -10084,7 +10084,7 @@
         <v>7.875</v>
       </c>
       <c r="G335" t="n">
-        <v>7.49205780029297</v>
+        <v>7.49205827713013</v>
       </c>
       <c r="H335" t="n">
         <v>7752172</v>
@@ -10142,7 +10142,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G337" t="n">
-        <v>7.87736320495605</v>
+        <v>7.87736368179321</v>
       </c>
       <c r="H337" t="n">
         <v>9607132</v>
@@ -10403,7 +10403,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G346" t="n">
-        <v>8.50526905059814</v>
+        <v>8.50527000427246</v>
       </c>
       <c r="H346" t="n">
         <v>9675664</v>
@@ -10548,7 +10548,7 @@
         <v>9.14500045776367</v>
       </c>
       <c r="G351" t="n">
-        <v>8.70030117034912</v>
+        <v>8.70030212402344</v>
       </c>
       <c r="H351" t="n">
         <v>9357770</v>
@@ -10751,7 +10751,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G358" t="n">
-        <v>8.2388858795166</v>
+        <v>8.23888492584229</v>
       </c>
       <c r="H358" t="n">
         <v>7073837</v>
@@ -10809,7 +10809,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G360" t="n">
-        <v>8.05812454223633</v>
+        <v>8.05812549591064</v>
       </c>
       <c r="H360" t="n">
         <v>6620743</v>
@@ -10838,7 +10838,7 @@
         <v>8.3100004196167</v>
       </c>
       <c r="G361" t="n">
-        <v>7.90590524673462</v>
+        <v>7.90590572357178</v>
       </c>
       <c r="H361" t="n">
         <v>14291998</v>
@@ -10896,7 +10896,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G363" t="n">
-        <v>7.93444681167603</v>
+        <v>7.93444633483887</v>
       </c>
       <c r="H363" t="n">
         <v>6865591</v>
@@ -11012,7 +11012,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G367" t="n">
-        <v>7.88687753677368</v>
+        <v>7.88687801361084</v>
       </c>
       <c r="H367" t="n">
         <v>7688881</v>
@@ -11041,7 +11041,7 @@
         <v>8.3100004196167</v>
       </c>
       <c r="G368" t="n">
-        <v>7.90590524673462</v>
+        <v>7.90590572357178</v>
       </c>
       <c r="H368" t="n">
         <v>8382176</v>
@@ -11070,7 +11070,7 @@
         <v>8.25</v>
       </c>
       <c r="G369" t="n">
-        <v>7.84882259368896</v>
+        <v>7.84882211685181</v>
       </c>
       <c r="H369" t="n">
         <v>8979733</v>
@@ -11099,7 +11099,7 @@
         <v>8.27499961853027</v>
       </c>
       <c r="G370" t="n">
-        <v>7.87260627746582</v>
+        <v>7.87260675430298</v>
       </c>
       <c r="H370" t="n">
         <v>7573261</v>
@@ -11128,7 +11128,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G371" t="n">
-        <v>7.91541814804077</v>
+        <v>7.91541862487793</v>
       </c>
       <c r="H371" t="n">
         <v>7773160</v>
@@ -11157,7 +11157,7 @@
         <v>8.33500003814697</v>
       </c>
       <c r="G372" t="n">
-        <v>7.92968988418579</v>
+        <v>7.92968940734863</v>
       </c>
       <c r="H372" t="n">
         <v>10290370</v>
@@ -11186,7 +11186,7 @@
         <v>8.25</v>
       </c>
       <c r="G373" t="n">
-        <v>7.84882259368896</v>
+        <v>7.84882211685181</v>
       </c>
       <c r="H373" t="n">
         <v>7754055</v>
@@ -11273,7 +11273,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G376" t="n">
-        <v>7.88687753677368</v>
+        <v>7.88687801361084</v>
       </c>
       <c r="H376" t="n">
         <v>5684368</v>
@@ -11302,7 +11302,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G377" t="n">
-        <v>7.91541814804077</v>
+        <v>7.91541862487793</v>
       </c>
       <c r="H377" t="n">
         <v>7730283</v>
@@ -11331,7 +11331,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G378" t="n">
-        <v>7.82979536056519</v>
+        <v>7.82979440689087</v>
       </c>
       <c r="H378" t="n">
         <v>6359602</v>
@@ -11418,7 +11418,7 @@
         <v>8.0649995803833</v>
       </c>
       <c r="G381" t="n">
-        <v>7.67281818389893</v>
+        <v>7.67281866073608</v>
       </c>
       <c r="H381" t="n">
         <v>6950390</v>
@@ -11534,7 +11534,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G385" t="n">
-        <v>7.82979536056519</v>
+        <v>7.82979440689087</v>
       </c>
       <c r="H385" t="n">
         <v>6247925</v>
@@ -11592,7 +11592,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G387" t="n">
-        <v>7.63000774383545</v>
+        <v>7.63000726699829</v>
       </c>
       <c r="H387" t="n">
         <v>5489232</v>
@@ -11621,7 +11621,7 @@
         <v>8.04500007629395</v>
       </c>
       <c r="G388" t="n">
-        <v>7.65379095077515</v>
+        <v>7.6537914276123</v>
       </c>
       <c r="H388" t="n">
         <v>6520553</v>
@@ -11708,7 +11708,7 @@
         <v>7.88500022888184</v>
       </c>
       <c r="G391" t="n">
-        <v>7.50157165527344</v>
+        <v>7.5015721321106</v>
       </c>
       <c r="H391" t="n">
         <v>13737506</v>
@@ -11766,7 +11766,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G393" t="n">
-        <v>7.8678503036499</v>
+        <v>7.86785078048706</v>
       </c>
       <c r="H393" t="n">
         <v>13345067</v>
@@ -11795,7 +11795,7 @@
         <v>8.04500007629395</v>
       </c>
       <c r="G394" t="n">
-        <v>7.65379095077515</v>
+        <v>7.6537914276123</v>
       </c>
       <c r="H394" t="n">
         <v>12204969</v>
@@ -11940,7 +11940,7 @@
         <v>8.125</v>
       </c>
       <c r="G399" t="n">
-        <v>7.72990131378174</v>
+        <v>7.72990083694458</v>
       </c>
       <c r="H399" t="n">
         <v>8832091</v>
@@ -12056,7 +12056,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G403" t="n">
-        <v>8.2388858795166</v>
+        <v>8.23888492584229</v>
       </c>
       <c r="H403" t="n">
         <v>8102311</v>
@@ -12114,7 +12114,7 @@
         <v>8.70499992370605</v>
       </c>
       <c r="G405" t="n">
-        <v>8.28169631958008</v>
+        <v>8.28169727325439</v>
       </c>
       <c r="H405" t="n">
         <v>9759736</v>
@@ -12201,7 +12201,7 @@
         <v>8.70499992370605</v>
       </c>
       <c r="G408" t="n">
-        <v>8.28169631958008</v>
+        <v>8.28169727325439</v>
       </c>
       <c r="H408" t="n">
         <v>5695609</v>
@@ -12404,7 +12404,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G415" t="n">
-        <v>8.05812454223633</v>
+        <v>8.05812549591064</v>
       </c>
       <c r="H415" t="n">
         <v>4472224</v>
@@ -12491,7 +12491,7 @@
         <v>8.33500003814697</v>
       </c>
       <c r="G418" t="n">
-        <v>7.92968988418579</v>
+        <v>7.92968940734863</v>
       </c>
       <c r="H418" t="n">
         <v>4935773</v>
@@ -12520,7 +12520,7 @@
         <v>8.27499961853027</v>
       </c>
       <c r="G419" t="n">
-        <v>7.87260627746582</v>
+        <v>7.87260675430298</v>
       </c>
       <c r="H419" t="n">
         <v>4715292</v>
@@ -12752,7 +12752,7 @@
         <v>8.04500007629395</v>
       </c>
       <c r="G427" t="n">
-        <v>7.65379095077515</v>
+        <v>7.6537914276123</v>
       </c>
       <c r="H427" t="n">
         <v>6232506</v>
@@ -12810,7 +12810,7 @@
         <v>7.83500003814697</v>
       </c>
       <c r="G429" t="n">
-        <v>7.45400285720825</v>
+        <v>7.45400333404541</v>
       </c>
       <c r="H429" t="n">
         <v>6232104</v>
@@ -12984,7 +12984,7 @@
         <v>7.88500022888184</v>
       </c>
       <c r="G435" t="n">
-        <v>7.50157165527344</v>
+        <v>7.5015721321106</v>
       </c>
       <c r="H435" t="n">
         <v>6028869</v>
@@ -13129,7 +13129,7 @@
         <v>8.02499961853027</v>
       </c>
       <c r="G440" t="n">
-        <v>7.63476371765137</v>
+        <v>7.63476324081421</v>
       </c>
       <c r="H440" t="n">
         <v>11093394</v>
@@ -13187,7 +13187,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G442" t="n">
-        <v>7.57292461395264</v>
+        <v>7.57292509078979</v>
       </c>
       <c r="H442" t="n">
         <v>6659325</v>
@@ -13274,7 +13274,7 @@
         <v>7.93499994277954</v>
       </c>
       <c r="G445" t="n">
-        <v>7.54914045333862</v>
+        <v>7.54913997650146</v>
       </c>
       <c r="H445" t="n">
         <v>4915478</v>
@@ -13332,7 +13332,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G447" t="n">
-        <v>7.59195184707642</v>
+        <v>7.59195232391357</v>
       </c>
       <c r="H447" t="n">
         <v>9449306</v>
@@ -13535,7 +13535,7 @@
         <v>7.63500022888184</v>
       </c>
       <c r="G454" t="n">
-        <v>7.26372861862183</v>
+        <v>7.26372909545898</v>
       </c>
       <c r="H454" t="n">
         <v>6637000</v>
@@ -13564,7 +13564,7 @@
         <v>7.54500007629395</v>
       </c>
       <c r="G455" t="n">
-        <v>7.17810487747192</v>
+        <v>7.17810535430908</v>
       </c>
       <c r="H455" t="n">
         <v>8006633</v>
@@ -13680,7 +13680,7 @@
         <v>7.625</v>
       </c>
       <c r="G459" t="n">
-        <v>7.25421476364136</v>
+        <v>7.25421524047852</v>
       </c>
       <c r="H459" t="n">
         <v>9352175</v>
@@ -13796,7 +13796,7 @@
         <v>7.68499994277954</v>
       </c>
       <c r="G463" t="n">
-        <v>7.31129741668701</v>
+        <v>7.31129693984985</v>
       </c>
       <c r="H463" t="n">
         <v>11433018</v>
@@ -14057,7 +14057,7 @@
         <v>7.63500022888184</v>
       </c>
       <c r="G472" t="n">
-        <v>7.26372861862183</v>
+        <v>7.26372909545898</v>
       </c>
       <c r="H472" t="n">
         <v>12393241</v>
@@ -14173,7 +14173,7 @@
         <v>7.35500001907349</v>
       </c>
       <c r="G476" t="n">
-        <v>6.99734449386597</v>
+        <v>6.99734401702881</v>
       </c>
       <c r="H476" t="n">
         <v>10343796</v>
@@ -14260,7 +14260,7 @@
         <v>6.89499998092651</v>
       </c>
       <c r="G479" t="n">
-        <v>6.55971336364746</v>
+        <v>6.5597128868103</v>
       </c>
       <c r="H479" t="n">
         <v>18049941</v>
@@ -14318,7 +14318,7 @@
         <v>6.81500005722046</v>
       </c>
       <c r="G481" t="n">
-        <v>6.48360347747803</v>
+        <v>6.48360300064087</v>
       </c>
       <c r="H481" t="n">
         <v>19321011</v>
@@ -14347,7 +14347,7 @@
         <v>6.89499998092651</v>
       </c>
       <c r="G482" t="n">
-        <v>6.55971336364746</v>
+        <v>6.5597128868103</v>
       </c>
       <c r="H482" t="n">
         <v>13873115</v>
@@ -14579,7 +14579,7 @@
         <v>7.04500007629395</v>
       </c>
       <c r="G490" t="n">
-        <v>6.7024188041687</v>
+        <v>6.70241928100586</v>
       </c>
       <c r="H490" t="n">
         <v>8224257</v>
@@ -14695,7 +14695,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G494" t="n">
-        <v>6.71668910980225</v>
+        <v>6.7166895866394</v>
       </c>
       <c r="H494" t="n">
         <v>7676027</v>
@@ -14782,7 +14782,7 @@
         <v>7.46999979019165</v>
       </c>
       <c r="G497" t="n">
-        <v>7.10675239562988</v>
+        <v>7.10675191879272</v>
       </c>
       <c r="H497" t="n">
         <v>16327353</v>
@@ -14811,7 +14811,7 @@
         <v>7.54500007629395</v>
       </c>
       <c r="G498" t="n">
-        <v>7.17810487747192</v>
+        <v>7.17810535430908</v>
       </c>
       <c r="H498" t="n">
         <v>9765474</v>
@@ -14927,7 +14927,7 @@
         <v>7.2649998664856</v>
       </c>
       <c r="G502" t="n">
-        <v>6.91172075271606</v>
+        <v>6.91172027587891</v>
       </c>
       <c r="H502" t="n">
         <v>12983601</v>
@@ -14985,7 +14985,7 @@
         <v>7.34499979019165</v>
       </c>
       <c r="G504" t="n">
-        <v>6.9878306388855</v>
+        <v>6.98783016204834</v>
       </c>
       <c r="H504" t="n">
         <v>8029365</v>
@@ -15014,7 +15014,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G505" t="n">
-        <v>7.04015588760376</v>
+        <v>7.04015636444092</v>
       </c>
       <c r="H505" t="n">
         <v>7758336</v>
@@ -15072,7 +15072,7 @@
         <v>7.34499979019165</v>
       </c>
       <c r="G507" t="n">
-        <v>6.9878306388855</v>
+        <v>6.98783016204834</v>
       </c>
       <c r="H507" t="n">
         <v>8653660</v>
@@ -15101,7 +15101,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G508" t="n">
-        <v>7.02112913131714</v>
+        <v>7.02112865447998</v>
       </c>
       <c r="H508" t="n">
         <v>5233596</v>
@@ -15159,7 +15159,7 @@
         <v>7.29500007629395</v>
       </c>
       <c r="G510" t="n">
-        <v>6.94026184082031</v>
+        <v>6.94026231765747</v>
       </c>
       <c r="H510" t="n">
         <v>4579894</v>
@@ -15188,7 +15188,7 @@
         <v>7.20499992370605</v>
       </c>
       <c r="G511" t="n">
-        <v>6.85463809967041</v>
+        <v>6.85463857650757</v>
       </c>
       <c r="H511" t="n">
         <v>4245157</v>
@@ -15217,7 +15217,7 @@
         <v>7.25500011444092</v>
       </c>
       <c r="G512" t="n">
-        <v>6.90220737457275</v>
+        <v>6.9022068977356</v>
       </c>
       <c r="H512" t="n">
         <v>6607233</v>
@@ -15246,7 +15246,7 @@
         <v>7.25</v>
       </c>
       <c r="G513" t="n">
-        <v>6.89745044708252</v>
+        <v>6.89744997024536</v>
       </c>
       <c r="H513" t="n">
         <v>5483915</v>
@@ -15275,7 +15275,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G514" t="n">
-        <v>6.98307418823242</v>
+        <v>6.98307371139526</v>
       </c>
       <c r="H514" t="n">
         <v>5974047</v>
@@ -15304,7 +15304,7 @@
         <v>7.38500022888184</v>
       </c>
       <c r="G515" t="n">
-        <v>7.02588558197021</v>
+        <v>7.02588605880737</v>
       </c>
       <c r="H515" t="n">
         <v>5887106</v>
@@ -15449,7 +15449,7 @@
         <v>7.43499994277954</v>
       </c>
       <c r="G520" t="n">
-        <v>7.0734543800354</v>
+        <v>7.07345390319824</v>
       </c>
       <c r="H520" t="n">
         <v>6198087</v>
@@ -15478,7 +15478,7 @@
         <v>7.38500022888184</v>
       </c>
       <c r="G521" t="n">
-        <v>7.02588558197021</v>
+        <v>7.02588605880737</v>
       </c>
       <c r="H521" t="n">
         <v>5952155</v>
@@ -15739,7 +15739,7 @@
         <v>7.20499992370605</v>
       </c>
       <c r="G530" t="n">
-        <v>6.85463809967041</v>
+        <v>6.85463857650757</v>
       </c>
       <c r="H530" t="n">
         <v>8180429</v>
@@ -15971,7 +15971,7 @@
         <v>7.21199989318848</v>
       </c>
       <c r="G538" t="n">
-        <v>6.86129808425903</v>
+        <v>6.86129760742188</v>
       </c>
       <c r="H538" t="n">
         <v>18503191</v>
@@ -16029,7 +16029,7 @@
         <v>6.98799991607666</v>
       </c>
       <c r="G540" t="n">
-        <v>6.64819049835205</v>
+        <v>6.64819097518921</v>
       </c>
       <c r="H540" t="n">
         <v>10998838</v>
@@ -16116,7 +16116,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G543" t="n">
-        <v>6.5454421043396</v>
+        <v>6.54544258117676</v>
       </c>
       <c r="H543" t="n">
         <v>9422768</v>
@@ -16261,7 +16261,7 @@
         <v>7.19600009918213</v>
       </c>
       <c r="G548" t="n">
-        <v>6.84607648849487</v>
+        <v>6.84607601165771</v>
       </c>
       <c r="H548" t="n">
         <v>13117904</v>
@@ -16348,7 +16348,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G551" t="n">
-        <v>7.02112913131714</v>
+        <v>7.02112865447998</v>
       </c>
       <c r="H551" t="n">
         <v>9959256</v>
@@ -16406,7 +16406,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G553" t="n">
-        <v>7.04015588760376</v>
+        <v>7.04015636444092</v>
       </c>
       <c r="H553" t="n">
         <v>10517150</v>
@@ -16435,7 +16435,7 @@
         <v>7.39799976348877</v>
       </c>
       <c r="G554" t="n">
-        <v>7.03825330734253</v>
+        <v>7.03825283050537</v>
       </c>
       <c r="H554" t="n">
         <v>10319173</v>
@@ -16464,7 +16464,7 @@
         <v>7.24599981307983</v>
       </c>
       <c r="G555" t="n">
-        <v>6.89364433288574</v>
+        <v>6.8936448097229</v>
       </c>
       <c r="H555" t="n">
         <v>12031756</v>
@@ -16493,7 +16493,7 @@
         <v>7.28800010681152</v>
       </c>
       <c r="G556" t="n">
-        <v>6.93360280990601</v>
+        <v>6.93360233306885</v>
       </c>
       <c r="H556" t="n">
         <v>9797279</v>
@@ -16580,7 +16580,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G559" t="n">
-        <v>7.82979536056519</v>
+        <v>7.82979440689087</v>
       </c>
       <c r="H559" t="n">
         <v>38979913</v>
@@ -16609,7 +16609,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G560" t="n">
-        <v>7.91541814804077</v>
+        <v>7.91541862487793</v>
       </c>
       <c r="H560" t="n">
         <v>29766429</v>
@@ -16638,7 +16638,7 @@
         <v>8.20199966430664</v>
       </c>
       <c r="G561" t="n">
-        <v>7.80315589904785</v>
+        <v>7.80315637588501</v>
       </c>
       <c r="H561" t="n">
         <v>15070704</v>
@@ -16667,7 +16667,7 @@
         <v>8.00800037384033</v>
       </c>
       <c r="G562" t="n">
-        <v>7.61859130859375</v>
+        <v>7.61859083175659</v>
       </c>
       <c r="H562" t="n">
         <v>17830195</v>
@@ -16696,7 +16696,7 @@
         <v>7.83199977874756</v>
       </c>
       <c r="G563" t="n">
-        <v>7.45114850997925</v>
+        <v>7.45114898681641</v>
       </c>
       <c r="H563" t="n">
         <v>15531686</v>
@@ -16754,7 +16754,7 @@
         <v>8.08800029754639</v>
       </c>
       <c r="G565" t="n">
-        <v>7.69470071792603</v>
+        <v>7.69470024108887</v>
       </c>
       <c r="H565" t="n">
         <v>13814697</v>
@@ -16783,7 +16783,7 @@
         <v>8.11600017547607</v>
       </c>
       <c r="G566" t="n">
-        <v>7.72133922576904</v>
+        <v>7.72133874893188</v>
       </c>
       <c r="H566" t="n">
         <v>11221597</v>
@@ -16899,7 +16899,7 @@
         <v>7.72599983215332</v>
       </c>
       <c r="G570" t="n">
-        <v>7.35030317306519</v>
+        <v>7.35030364990234</v>
       </c>
       <c r="H570" t="n">
         <v>11293097</v>
@@ -16957,7 +16957,7 @@
         <v>7.61399984359741</v>
       </c>
       <c r="G572" t="n">
-        <v>7.24375009536743</v>
+        <v>7.24374961853027</v>
       </c>
       <c r="H572" t="n">
         <v>8793021</v>
@@ -17073,7 +17073,7 @@
         <v>7.58199977874756</v>
       </c>
       <c r="G576" t="n">
-        <v>7.21330547332764</v>
+        <v>7.21330595016479</v>
       </c>
       <c r="H576" t="n">
         <v>7516325</v>
@@ -17247,7 +17247,7 @@
         <v>8.61200046539307</v>
       </c>
       <c r="G582" t="n">
-        <v>8.1932201385498</v>
+        <v>8.19321918487549</v>
       </c>
       <c r="H582" t="n">
         <v>21024100</v>
@@ -17334,7 +17334,7 @@
         <v>8.38199996948242</v>
       </c>
       <c r="G585" t="n">
-        <v>7.97440338134766</v>
+        <v>7.97440385818481</v>
       </c>
       <c r="H585" t="n">
         <v>16885220</v>
@@ -17421,7 +17421,7 @@
         <v>8.76200008392334</v>
       </c>
       <c r="G588" t="n">
-        <v>8.3359260559082</v>
+        <v>8.33592510223389</v>
       </c>
       <c r="H588" t="n">
         <v>19699701</v>
@@ -17450,7 +17450,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G589" t="n">
-        <v>8.27693939208984</v>
+        <v>8.27694034576416</v>
       </c>
       <c r="H589" t="n">
         <v>14602170</v>
@@ -17508,7 +17508,7 @@
         <v>8.26200008392334</v>
       </c>
       <c r="G591" t="n">
-        <v>7.86023950576782</v>
+        <v>7.86023902893066</v>
       </c>
       <c r="H591" t="n">
         <v>15384354</v>
@@ -17653,7 +17653,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G596" t="n">
-        <v>7.96298742294312</v>
+        <v>7.96298694610596</v>
       </c>
       <c r="H596" t="n">
         <v>11477450</v>
@@ -17740,7 +17740,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G599" t="n">
-        <v>8.0105562210083</v>
+        <v>8.01055526733398</v>
       </c>
       <c r="H599" t="n">
         <v>20166769</v>
@@ -17769,7 +17769,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G600" t="n">
-        <v>7.88687753677368</v>
+        <v>7.88687801361084</v>
       </c>
       <c r="H600" t="n">
         <v>10308492</v>
@@ -17914,7 +17914,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G605" t="n">
-        <v>7.3541088104248</v>
+        <v>7.35410928726196</v>
       </c>
       <c r="H605" t="n">
         <v>19807914</v>
@@ -17943,7 +17943,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G606" t="n">
-        <v>7.30654048919678</v>
+        <v>7.30654001235962</v>
       </c>
       <c r="H606" t="n">
         <v>13820402</v>
@@ -18030,7 +18030,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G609" t="n">
-        <v>7.02112913131714</v>
+        <v>7.02112865447998</v>
       </c>
       <c r="H609" t="n">
         <v>12987765</v>
@@ -18059,7 +18059,7 @@
         <v>7.31199979782104</v>
       </c>
       <c r="G610" t="n">
-        <v>6.95643472671509</v>
+        <v>6.95643520355225</v>
       </c>
       <c r="H610" t="n">
         <v>9821711</v>
@@ -18088,7 +18088,7 @@
         <v>7.30999994277954</v>
       </c>
       <c r="G611" t="n">
-        <v>6.95453214645386</v>
+        <v>6.95453262329102</v>
       </c>
       <c r="H611" t="n">
         <v>10969407</v>
@@ -18146,7 +18146,7 @@
         <v>7.14400005340576</v>
       </c>
       <c r="G613" t="n">
-        <v>6.79660511016846</v>
+        <v>6.7966046333313</v>
       </c>
       <c r="H613" t="n">
         <v>15383630</v>
@@ -18204,7 +18204,7 @@
         <v>7.01599979400635</v>
       </c>
       <c r="G615" t="n">
-        <v>6.67482900619507</v>
+        <v>6.67482852935791</v>
       </c>
       <c r="H615" t="n">
         <v>10762161</v>
@@ -18233,7 +18233,7 @@
         <v>6.87200021743774</v>
       </c>
       <c r="G616" t="n">
-        <v>6.53783178329468</v>
+        <v>6.53783130645752</v>
       </c>
       <c r="H616" t="n">
         <v>13644902</v>
@@ -18291,7 +18291,7 @@
         <v>6.98600006103516</v>
       </c>
       <c r="G618" t="n">
-        <v>6.64628839492798</v>
+        <v>6.64628791809082</v>
       </c>
       <c r="H618" t="n">
         <v>6146232</v>
@@ -18349,7 +18349,7 @@
         <v>6.91599988937378</v>
       </c>
       <c r="G620" t="n">
-        <v>6.5796914100647</v>
+        <v>6.57969188690186</v>
       </c>
       <c r="H620" t="n">
         <v>11484221</v>
@@ -18407,7 +18407,7 @@
         <v>6.72200012207031</v>
       </c>
       <c r="G622" t="n">
-        <v>6.39512538909912</v>
+        <v>6.39512586593628</v>
       </c>
       <c r="H622" t="n">
         <v>8616778</v>
@@ -18436,7 +18436,7 @@
         <v>6.87200021743774</v>
       </c>
       <c r="G623" t="n">
-        <v>6.53783178329468</v>
+        <v>6.53783130645752</v>
       </c>
       <c r="H623" t="n">
         <v>11592172</v>
@@ -18465,7 +18465,7 @@
         <v>6.85799980163574</v>
       </c>
       <c r="G624" t="n">
-        <v>6.52451229095459</v>
+        <v>6.52451181411743</v>
       </c>
       <c r="H624" t="n">
         <v>6763306</v>
@@ -18552,7 +18552,7 @@
         <v>6.7519998550415</v>
       </c>
       <c r="G627" t="n">
-        <v>6.42366695404053</v>
+        <v>6.42366647720337</v>
       </c>
       <c r="H627" t="n">
         <v>11827362</v>
@@ -18581,7 +18581,7 @@
         <v>6.76599979400635</v>
       </c>
       <c r="G628" t="n">
-        <v>6.43698596954346</v>
+        <v>6.4369854927063</v>
       </c>
       <c r="H628" t="n">
         <v>9517293</v>
@@ -18668,7 +18668,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G631" t="n">
-        <v>6.33614063262939</v>
+        <v>6.33614015579224</v>
       </c>
       <c r="H631" t="n">
         <v>8779408</v>
@@ -18784,7 +18784,7 @@
         <v>6.45599985122681</v>
       </c>
       <c r="G635" t="n">
-        <v>6.14206027984619</v>
+        <v>6.14206075668335</v>
       </c>
       <c r="H635" t="n">
         <v>13273047</v>
@@ -18842,7 +18842,7 @@
         <v>6.37400007247925</v>
       </c>
       <c r="G637" t="n">
-        <v>6.06404829025269</v>
+        <v>6.06404781341553</v>
       </c>
       <c r="H637" t="n">
         <v>8023540</v>
@@ -18871,7 +18871,7 @@
         <v>6.28200006484985</v>
       </c>
       <c r="G638" t="n">
-        <v>5.97652196884155</v>
+        <v>5.97652149200439</v>
       </c>
       <c r="H638" t="n">
         <v>5846091</v>
@@ -18929,7 +18929,7 @@
         <v>6.52400016784668</v>
       </c>
       <c r="G640" t="n">
-        <v>6.20675373077393</v>
+        <v>6.20675420761108</v>
       </c>
       <c r="H640" t="n">
         <v>5707740</v>
@@ -18987,7 +18987,7 @@
         <v>6.55200004577637</v>
       </c>
       <c r="G642" t="n">
-        <v>6.23339223861694</v>
+        <v>6.2333927154541</v>
       </c>
       <c r="H642" t="n">
         <v>6589583</v>
@@ -19045,7 +19045,7 @@
         <v>6.36600017547607</v>
       </c>
       <c r="G644" t="n">
-        <v>6.05643701553345</v>
+        <v>6.05643749237061</v>
       </c>
       <c r="H644" t="n">
         <v>10253469</v>
@@ -19074,7 +19074,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G645" t="n">
-        <v>6.01267433166504</v>
+        <v>6.01267385482788</v>
       </c>
       <c r="H645" t="n">
         <v>7151777</v>
@@ -19103,7 +19103,7 @@
         <v>6.14599990844727</v>
       </c>
       <c r="G646" t="n">
-        <v>5.84713459014893</v>
+        <v>5.84713506698608</v>
       </c>
       <c r="H646" t="n">
         <v>10297948</v>
@@ -19161,7 +19161,7 @@
         <v>6.07399988174438</v>
       </c>
       <c r="G648" t="n">
-        <v>5.77863597869873</v>
+        <v>5.77863645553589</v>
       </c>
       <c r="H648" t="n">
         <v>9314960</v>
@@ -19451,7 +19451,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G658" t="n">
-        <v>6.27905797958374</v>
+        <v>6.2790584564209</v>
       </c>
       <c r="H658" t="n">
         <v>10357178</v>
@@ -19509,7 +19509,7 @@
         <v>6.50400018692017</v>
       </c>
       <c r="G660" t="n">
-        <v>6.18772649765015</v>
+        <v>6.1877269744873</v>
       </c>
       <c r="H660" t="n">
         <v>7068352</v>
@@ -19538,7 +19538,7 @@
         <v>6.38199996948242</v>
       </c>
       <c r="G661" t="n">
-        <v>6.07165861129761</v>
+        <v>6.07165908813477</v>
       </c>
       <c r="H661" t="n">
         <v>7651712</v>
@@ -19944,7 +19944,7 @@
         <v>6</v>
       </c>
       <c r="G675" t="n">
-        <v>5.7082347869873</v>
+        <v>5.70823431015015</v>
       </c>
       <c r="H675" t="n">
         <v>8439947</v>
@@ -19973,7 +19973,7 @@
         <v>5.98799991607666</v>
       </c>
       <c r="G676" t="n">
-        <v>5.69681787490845</v>
+        <v>5.69681835174561</v>
       </c>
       <c r="H676" t="n">
         <v>6952501</v>
@@ -20002,7 +20002,7 @@
         <v>6.0019998550415</v>
       </c>
       <c r="G677" t="n">
-        <v>5.71013689041138</v>
+        <v>5.71013736724854</v>
       </c>
       <c r="H677" t="n">
         <v>3495139</v>
@@ -20031,7 +20031,7 @@
         <v>5.93800020217896</v>
       </c>
       <c r="G678" t="n">
-        <v>5.64925003051758</v>
+        <v>5.64924955368042</v>
       </c>
       <c r="H678" t="n">
         <v>6479576</v>
@@ -20118,7 +20118,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G681" t="n">
-        <v>5.22303438186646</v>
+        <v>5.22303485870361</v>
       </c>
       <c r="H681" t="n">
         <v>21485023</v>
@@ -20147,7 +20147,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G682" t="n">
-        <v>5.28011751174927</v>
+        <v>5.28011703491211</v>
       </c>
       <c r="H682" t="n">
         <v>7364755</v>
@@ -20176,7 +20176,7 @@
         <v>5.25</v>
       </c>
       <c r="G683" t="n">
-        <v>4.99470520019531</v>
+        <v>4.99470567703247</v>
       </c>
       <c r="H683" t="n">
         <v>33784406</v>
@@ -20350,7 +20350,7 @@
         <v>5.4060001373291</v>
       </c>
       <c r="G689" t="n">
-        <v>5.14311981201172</v>
+        <v>5.14311933517456</v>
       </c>
       <c r="H689" t="n">
         <v>9097960</v>
@@ -20466,7 +20466,7 @@
         <v>5.71400022506714</v>
       </c>
       <c r="G693" t="n">
-        <v>5.43614196777344</v>
+        <v>5.4361424446106</v>
       </c>
       <c r="H693" t="n">
         <v>14951668</v>
@@ -20524,7 +20524,7 @@
         <v>5.68599987030029</v>
       </c>
       <c r="G695" t="n">
-        <v>5.40950345993042</v>
+        <v>5.40950393676758</v>
       </c>
       <c r="H695" t="n">
         <v>8514680</v>
@@ -20553,7 +20553,7 @@
         <v>5.68599987030029</v>
       </c>
       <c r="G696" t="n">
-        <v>5.40950345993042</v>
+        <v>5.40950393676758</v>
       </c>
       <c r="H696" t="n">
         <v>11073700</v>
@@ -20582,7 +20582,7 @@
         <v>5.60599994659424</v>
       </c>
       <c r="G697" t="n">
-        <v>5.33339357376099</v>
+        <v>5.33339405059814</v>
       </c>
       <c r="H697" t="n">
         <v>9256009</v>
@@ -20611,7 +20611,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G698" t="n">
-        <v>5.30865812301636</v>
+        <v>5.30865859985352</v>
       </c>
       <c r="H698" t="n">
         <v>8345160</v>
@@ -20727,7 +20727,7 @@
         <v>4.95300006866455</v>
       </c>
       <c r="G702" t="n">
-        <v>4.71214771270752</v>
+        <v>4.71214818954468</v>
       </c>
       <c r="H702" t="n">
         <v>21571910</v>
@@ -20814,7 +20814,7 @@
         <v>4.95699977874756</v>
       </c>
       <c r="G705" t="n">
-        <v>4.71595335006714</v>
+        <v>4.71595287322998</v>
       </c>
       <c r="H705" t="n">
         <v>12269784</v>
@@ -20930,7 +20930,7 @@
         <v>5.03200006484985</v>
       </c>
       <c r="G709" t="n">
-        <v>4.78730583190918</v>
+        <v>4.78730630874634</v>
       </c>
       <c r="H709" t="n">
         <v>16574528</v>
@@ -20959,7 +20959,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G710" t="n">
-        <v>4.77588939666748</v>
+        <v>4.77588987350464</v>
       </c>
       <c r="H710" t="n">
         <v>13466859</v>
@@ -21133,7 +21133,7 @@
         <v>4.98600006103516</v>
       </c>
       <c r="G716" t="n">
-        <v>4.74354314804077</v>
+        <v>4.74354267120361</v>
       </c>
       <c r="H716" t="n">
         <v>11883638</v>
@@ -21365,7 +21365,7 @@
         <v>5.19199991226196</v>
       </c>
       <c r="G724" t="n">
-        <v>4.93952608108521</v>
+        <v>4.93952560424805</v>
       </c>
       <c r="H724" t="n">
         <v>11611382</v>
@@ -21452,7 +21452,7 @@
         <v>5.35400009155273</v>
       </c>
       <c r="G727" t="n">
-        <v>5.0936484336853</v>
+        <v>5.09364795684814</v>
       </c>
       <c r="H727" t="n">
         <v>5004868</v>
@@ -21510,7 +21510,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G729" t="n">
-        <v>5.08984279632568</v>
+        <v>5.08984231948853</v>
       </c>
       <c r="H729" t="n">
         <v>4502292</v>
@@ -21568,7 +21568,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G731" t="n">
-        <v>4.90908145904541</v>
+        <v>4.90908193588257</v>
       </c>
       <c r="H731" t="n">
         <v>20215708</v>
@@ -21597,7 +21597,7 @@
         <v>5.30399990081787</v>
       </c>
       <c r="G732" t="n">
-        <v>5.04607915878296</v>
+        <v>5.04607963562012</v>
       </c>
       <c r="H732" t="n">
         <v>21192969</v>
@@ -21655,7 +21655,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G734" t="n">
-        <v>4.95665073394775</v>
+        <v>4.9566502571106</v>
       </c>
       <c r="H734" t="n">
         <v>13016824</v>
@@ -21684,7 +21684,7 @@
         <v>5.16400003433228</v>
       </c>
       <c r="G735" t="n">
-        <v>4.91288709640503</v>
+        <v>4.91288757324219</v>
       </c>
       <c r="H735" t="n">
         <v>7858565</v>
@@ -21713,7 +21713,7 @@
         <v>5.26200008392334</v>
       </c>
       <c r="G736" t="n">
-        <v>5.00612211227417</v>
+        <v>5.00612163543701</v>
       </c>
       <c r="H736" t="n">
         <v>9329889</v>
@@ -22032,7 +22032,7 @@
         <v>5.74599981307983</v>
       </c>
       <c r="G747" t="n">
-        <v>5.46658611297607</v>
+        <v>5.46658563613892</v>
       </c>
       <c r="H747" t="n">
         <v>8767299</v>
@@ -22061,7 +22061,7 @@
         <v>5.69199991226196</v>
       </c>
       <c r="G748" t="n">
-        <v>5.41521215438843</v>
+        <v>5.41521167755127</v>
       </c>
       <c r="H748" t="n">
         <v>5268321</v>
@@ -22235,7 +22235,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G754" t="n">
-        <v>5.42282247543335</v>
+        <v>5.42282295227051</v>
       </c>
       <c r="H754" t="n">
         <v>8739136</v>
@@ -22380,7 +22380,7 @@
         <v>5.4520001411438</v>
       </c>
       <c r="G759" t="n">
-        <v>5.18688249588013</v>
+        <v>5.18688297271729</v>
       </c>
       <c r="H759" t="n">
         <v>9181301</v>
@@ -22409,7 +22409,7 @@
         <v>5.2020001411438</v>
       </c>
       <c r="G760" t="n">
-        <v>4.94903945922852</v>
+        <v>4.94903993606567</v>
       </c>
       <c r="H760" t="n">
         <v>11959404</v>
@@ -22467,7 +22467,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G762" t="n">
-        <v>4.58561515808105</v>
+        <v>4.58561563491821</v>
       </c>
       <c r="H762" t="n">
         <v>10213287</v>
@@ -22496,7 +22496,7 @@
         <v>4.83300018310547</v>
       </c>
       <c r="G763" t="n">
-        <v>4.59798336029053</v>
+        <v>4.59798288345337</v>
       </c>
       <c r="H763" t="n">
         <v>6812527</v>
@@ -22641,7 +22641,7 @@
         <v>5.06199979782104</v>
       </c>
       <c r="G768" t="n">
-        <v>4.81584739685059</v>
+        <v>4.81584692001343</v>
       </c>
       <c r="H768" t="n">
         <v>6948538</v>
@@ -22670,7 +22670,7 @@
         <v>4.95900011062622</v>
       </c>
       <c r="G769" t="n">
-        <v>4.71785640716553</v>
+        <v>4.71785593032837</v>
       </c>
       <c r="H769" t="n">
         <v>10542869</v>
@@ -22728,7 +22728,7 @@
         <v>5.00600004196167</v>
       </c>
       <c r="G771" t="n">
-        <v>4.76257038116455</v>
+        <v>4.76257085800171</v>
       </c>
       <c r="H771" t="n">
         <v>7037218</v>
@@ -22757,7 +22757,7 @@
         <v>5.01599979400635</v>
       </c>
       <c r="G772" t="n">
-        <v>4.77208375930786</v>
+        <v>4.77208423614502</v>
       </c>
       <c r="H772" t="n">
         <v>5703804</v>
@@ -22786,7 +22786,7 @@
         <v>5.02400016784668</v>
       </c>
       <c r="G773" t="n">
-        <v>4.77969551086426</v>
+        <v>4.7796950340271</v>
       </c>
       <c r="H773" t="n">
         <v>5160678</v>
@@ -22873,7 +22873,7 @@
         <v>4.88500022888184</v>
       </c>
       <c r="G776" t="n">
-        <v>4.64745473861694</v>
+        <v>4.64745426177979</v>
       </c>
       <c r="H776" t="n">
         <v>41676407</v>
@@ -22960,7 +22960,7 @@
         <v>4.48400020599365</v>
       </c>
       <c r="G779" t="n">
-        <v>4.26595401763916</v>
+        <v>4.26595449447632</v>
       </c>
       <c r="H779" t="n">
         <v>18215988</v>
@@ -22989,7 +22989,7 @@
         <v>4.52899980545044</v>
       </c>
       <c r="G780" t="n">
-        <v>4.30876588821411</v>
+        <v>4.30876541137695</v>
       </c>
       <c r="H780" t="n">
         <v>16117024</v>
@@ -23076,7 +23076,7 @@
         <v>4.58199977874756</v>
       </c>
       <c r="G783" t="n">
-        <v>4.35918855667114</v>
+        <v>4.35918807983398</v>
       </c>
       <c r="H783" t="n">
         <v>7847751</v>
@@ -23105,7 +23105,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G784" t="n">
-        <v>4.4048547744751</v>
+        <v>4.40485429763794</v>
       </c>
       <c r="H784" t="n">
         <v>11137135</v>
@@ -23221,7 +23221,7 @@
         <v>5.02400016784668</v>
       </c>
       <c r="G788" t="n">
-        <v>4.77969551086426</v>
+        <v>4.7796950340271</v>
       </c>
       <c r="H788" t="n">
         <v>9181552</v>
@@ -23308,7 +23308,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G791" t="n">
-        <v>4.49047803878784</v>
+        <v>4.49047756195068</v>
       </c>
       <c r="H791" t="n">
         <v>10923993</v>
@@ -23366,7 +23366,7 @@
         <v>4.81599998474121</v>
       </c>
       <c r="G793" t="n">
-        <v>4.58180999755859</v>
+        <v>4.58180952072144</v>
       </c>
       <c r="H793" t="n">
         <v>6859684</v>
@@ -23424,7 +23424,7 @@
         <v>4.8270001411438</v>
       </c>
       <c r="G795" t="n">
-        <v>4.59227514266968</v>
+        <v>4.59227466583252</v>
       </c>
       <c r="H795" t="n">
         <v>10108349</v>
@@ -23482,7 +23482,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G797" t="n">
-        <v>5.04227447509766</v>
+        <v>5.0422739982605</v>
       </c>
       <c r="H797" t="n">
         <v>14228495</v>
@@ -23627,7 +23627,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G802" t="n">
-        <v>5.09935617446899</v>
+        <v>5.09935665130615</v>
       </c>
       <c r="H802" t="n">
         <v>13548252</v>
@@ -23743,7 +23743,7 @@
         <v>5.32200002670288</v>
       </c>
       <c r="G806" t="n">
-        <v>5.06320381164551</v>
+        <v>5.06320428848267</v>
       </c>
       <c r="H806" t="n">
         <v>10595102</v>
@@ -23801,7 +23801,7 @@
         <v>5.5</v>
       </c>
       <c r="G808" t="n">
-        <v>5.23254823684692</v>
+        <v>5.23254871368408</v>
       </c>
       <c r="H808" t="n">
         <v>15904611</v>
@@ -23830,7 +23830,7 @@
         <v>5.64799976348877</v>
       </c>
       <c r="G809" t="n">
-        <v>5.37335109710693</v>
+        <v>5.37335157394409</v>
       </c>
       <c r="H809" t="n">
         <v>20711461</v>
@@ -23859,7 +23859,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G810" t="n">
-        <v>5.33719921112061</v>
+        <v>5.33719968795776</v>
       </c>
       <c r="H810" t="n">
         <v>21767982</v>
@@ -24091,7 +24091,7 @@
         <v>5.35599994659424</v>
       </c>
       <c r="G818" t="n">
-        <v>5.09555053710938</v>
+        <v>5.09555101394653</v>
       </c>
       <c r="H818" t="n">
         <v>10767173</v>
@@ -24149,7 +24149,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G820" t="n">
-        <v>5.04227447509766</v>
+        <v>5.0422739982605</v>
       </c>
       <c r="H820" t="n">
         <v>6355484</v>
@@ -24178,7 +24178,7 @@
         <v>5.25799989700317</v>
       </c>
       <c r="G821" t="n">
-        <v>5.00231647491455</v>
+        <v>5.00231599807739</v>
       </c>
       <c r="H821" t="n">
         <v>8320301</v>
@@ -24236,7 +24236,7 @@
         <v>5.31599998474121</v>
       </c>
       <c r="G823" t="n">
-        <v>5.05749607086182</v>
+        <v>5.05749559402466</v>
       </c>
       <c r="H823" t="n">
         <v>5741634</v>
@@ -24265,7 +24265,7 @@
         <v>5.35599994659424</v>
       </c>
       <c r="G824" t="n">
-        <v>5.09555053710938</v>
+        <v>5.09555101394653</v>
       </c>
       <c r="H824" t="n">
         <v>7192964</v>
@@ -24294,7 +24294,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G825" t="n">
-        <v>5.14692449569702</v>
+        <v>5.14692497253418</v>
       </c>
       <c r="H825" t="n">
         <v>6837351</v>
@@ -24381,7 +24381,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G828" t="n">
-        <v>5.08984279632568</v>
+        <v>5.08984231948853</v>
       </c>
       <c r="H828" t="n">
         <v>11314863</v>
@@ -24410,7 +24410,7 @@
         <v>5.40199995040894</v>
       </c>
       <c r="G829" t="n">
-        <v>5.1393141746521</v>
+        <v>5.13931369781494</v>
       </c>
       <c r="H829" t="n">
         <v>9915940</v>
@@ -24468,7 +24468,7 @@
         <v>5.36800003051758</v>
       </c>
       <c r="G831" t="n">
-        <v>5.10696744918823</v>
+        <v>5.10696697235107</v>
       </c>
       <c r="H831" t="n">
         <v>8336278</v>
@@ -24497,7 +24497,7 @@
         <v>5.33599996566772</v>
       </c>
       <c r="G832" t="n">
-        <v>5.07652378082275</v>
+        <v>5.0765233039856</v>
       </c>
       <c r="H832" t="n">
         <v>10088831</v>
@@ -24526,7 +24526,7 @@
         <v>5.34899997711182</v>
       </c>
       <c r="G833" t="n">
-        <v>5.08889150619507</v>
+        <v>5.08889102935791</v>
       </c>
       <c r="H833" t="n">
         <v>6378866</v>
@@ -24671,7 +24671,7 @@
         <v>5.25500011444092</v>
       </c>
       <c r="G838" t="n">
-        <v>4.99946212768555</v>
+        <v>4.99946260452271</v>
       </c>
       <c r="H838" t="n">
         <v>4873965</v>
@@ -24903,7 +24903,7 @@
         <v>4.98600006103516</v>
       </c>
       <c r="G846" t="n">
-        <v>4.74354314804077</v>
+        <v>4.74354267120361</v>
       </c>
       <c r="H846" t="n">
         <v>4443838</v>
@@ -24932,7 +24932,7 @@
         <v>4.95900011062622</v>
       </c>
       <c r="G847" t="n">
-        <v>4.71785640716553</v>
+        <v>4.71785593032837</v>
       </c>
       <c r="H847" t="n">
         <v>6501356</v>
@@ -25106,7 +25106,7 @@
         <v>4.67199993133545</v>
       </c>
       <c r="G853" t="n">
-        <v>4.44481229782104</v>
+        <v>4.44481182098389</v>
       </c>
       <c r="H853" t="n">
         <v>6493676</v>
@@ -25193,7 +25193,7 @@
         <v>4.45800018310547</v>
       </c>
       <c r="G856" t="n">
-        <v>4.24121809005737</v>
+        <v>4.24121856689453</v>
       </c>
       <c r="H856" t="n">
         <v>16786730</v>
@@ -25280,7 +25280,7 @@
         <v>4.57800006866455</v>
       </c>
       <c r="G859" t="n">
-        <v>4.35538339614868</v>
+        <v>4.35538291931152</v>
       </c>
       <c r="H859" t="n">
         <v>8359793</v>
@@ -25396,7 +25396,7 @@
         <v>4.38100004196167</v>
       </c>
       <c r="G863" t="n">
-        <v>4.1679630279541</v>
+        <v>4.16796255111694</v>
       </c>
       <c r="H863" t="n">
         <v>10295663</v>
@@ -25599,7 +25599,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G870" t="n">
-        <v>4.32398796081543</v>
+        <v>4.32398748397827</v>
       </c>
       <c r="H870" t="n">
         <v>10022461</v>
@@ -25802,7 +25802,7 @@
         <v>4.63100004196167</v>
       </c>
       <c r="G877" t="n">
-        <v>4.40580606460571</v>
+        <v>4.40580558776855</v>
       </c>
       <c r="H877" t="n">
         <v>6029498</v>
@@ -25947,7 +25947,7 @@
         <v>4.84200000762939</v>
       </c>
       <c r="G882" t="n">
-        <v>4.60654544830322</v>
+        <v>4.60654497146606</v>
       </c>
       <c r="H882" t="n">
         <v>15402357</v>
@@ -25976,7 +25976,7 @@
         <v>5.00899982452393</v>
       </c>
       <c r="G883" t="n">
-        <v>4.76542472839355</v>
+        <v>4.7654242515564</v>
       </c>
       <c r="H883" t="n">
         <v>21769809</v>
@@ -26150,7 +26150,7 @@
         <v>4.82800006866455</v>
       </c>
       <c r="G889" t="n">
-        <v>4.59322643280029</v>
+        <v>4.59322595596313</v>
       </c>
       <c r="H889" t="n">
         <v>7098552</v>
@@ -26179,7 +26179,7 @@
         <v>4.78299999237061</v>
       </c>
       <c r="G890" t="n">
-        <v>4.55041408538818</v>
+        <v>4.55041456222534</v>
       </c>
       <c r="H890" t="n">
         <v>4787528</v>
@@ -26208,7 +26208,7 @@
         <v>4.92199993133545</v>
       </c>
       <c r="G891" t="n">
-        <v>4.68265533447266</v>
+        <v>4.6826548576355</v>
       </c>
       <c r="H891" t="n">
         <v>9003798</v>
@@ -26266,7 +26266,7 @@
         <v>4.96299982070923</v>
       </c>
       <c r="G893" t="n">
-        <v>4.72166109085083</v>
+        <v>4.72166156768799</v>
       </c>
       <c r="H893" t="n">
         <v>6516566</v>
@@ -26411,7 +26411,7 @@
         <v>5.01300001144409</v>
       </c>
       <c r="G898" t="n">
-        <v>4.76923036575317</v>
+        <v>4.76922988891602</v>
       </c>
       <c r="H898" t="n">
         <v>5422412</v>
@@ -26527,7 +26527,7 @@
         <v>5.06099987030029</v>
       </c>
       <c r="G902" t="n">
-        <v>4.81489610671997</v>
+        <v>4.81489562988281</v>
       </c>
       <c r="H902" t="n">
         <v>4829287</v>
@@ -26556,7 +26556,7 @@
         <v>4.91099977493286</v>
       </c>
       <c r="G903" t="n">
-        <v>4.67218971252441</v>
+        <v>4.67219018936157</v>
       </c>
       <c r="H903" t="n">
         <v>8017443</v>
@@ -26614,7 +26614,7 @@
         <v>4.95699977874756</v>
       </c>
       <c r="G905" t="n">
-        <v>4.71595335006714</v>
+        <v>4.71595287322998</v>
       </c>
       <c r="H905" t="n">
         <v>5337026</v>
@@ -26730,7 +26730,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G909" t="n">
-        <v>4.98519134521484</v>
+        <v>4.985191822052</v>
       </c>
       <c r="H909" t="n">
         <v>10810457</v>
@@ -26788,7 +26788,7 @@
         <v>5.10599994659424</v>
       </c>
       <c r="G911" t="n">
-        <v>4.85770750045776</v>
+        <v>4.85770797729492</v>
       </c>
       <c r="H911" t="n">
         <v>5112107</v>
@@ -26846,7 +26846,7 @@
         <v>4.99599981307983</v>
       </c>
       <c r="G913" t="n">
-        <v>4.75305652618408</v>
+        <v>4.75305700302124</v>
       </c>
       <c r="H913" t="n">
         <v>6486219</v>
@@ -26904,7 +26904,7 @@
         <v>4.83400011062622</v>
       </c>
       <c r="G915" t="n">
-        <v>4.59893417358398</v>
+        <v>4.59893465042114</v>
       </c>
       <c r="H915" t="n">
         <v>6262907</v>
@@ -26933,7 +26933,7 @@
         <v>4.81599998474121</v>
       </c>
       <c r="G916" t="n">
-        <v>4.58180999755859</v>
+        <v>4.58180952072144</v>
       </c>
       <c r="H916" t="n">
         <v>4733278</v>
@@ -26962,7 +26962,7 @@
         <v>4.88800001144409</v>
       </c>
       <c r="G917" t="n">
-        <v>4.65030813217163</v>
+        <v>4.65030860900879</v>
       </c>
       <c r="H917" t="n">
         <v>5260695</v>
@@ -26991,7 +26991,7 @@
         <v>4.60200023651123</v>
       </c>
       <c r="G918" t="n">
-        <v>4.37821578979492</v>
+        <v>4.37821626663208</v>
       </c>
       <c r="H918" t="n">
         <v>11153136</v>
@@ -27136,7 +27136,7 @@
         <v>4.56500005722046</v>
       </c>
       <c r="G923" t="n">
-        <v>4.34301519393921</v>
+        <v>4.34301567077637</v>
       </c>
       <c r="H923" t="n">
         <v>5051334</v>
@@ -27165,7 +27165,7 @@
         <v>4.47200012207031</v>
       </c>
       <c r="G924" t="n">
-        <v>4.25453805923462</v>
+        <v>4.25453758239746</v>
       </c>
       <c r="H924" t="n">
         <v>5236518</v>
@@ -27223,7 +27223,7 @@
         <v>4.59800004959106</v>
       </c>
       <c r="G926" t="n">
-        <v>4.37441062927246</v>
+        <v>4.3744101524353</v>
       </c>
       <c r="H926" t="n">
         <v>5193190</v>
@@ -27252,7 +27252,7 @@
         <v>4.52600002288818</v>
       </c>
       <c r="G927" t="n">
-        <v>4.30591201782227</v>
+        <v>4.30591154098511</v>
       </c>
       <c r="H927" t="n">
         <v>4843476</v>
@@ -27484,7 +27484,7 @@
         <v>4.92600011825562</v>
       </c>
       <c r="G935" t="n">
-        <v>4.68646049499512</v>
+        <v>4.68646097183228</v>
       </c>
       <c r="H935" t="n">
         <v>7598993</v>
@@ -27513,7 +27513,7 @@
         <v>4.91800022125244</v>
       </c>
       <c r="G936" t="n">
-        <v>4.6788501739502</v>
+        <v>4.67884969711304</v>
       </c>
       <c r="H936" t="n">
         <v>8686085</v>
@@ -27687,7 +27687,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G942" t="n">
-        <v>4.95665073394775</v>
+        <v>4.9566502571106</v>
       </c>
       <c r="H942" t="n">
         <v>9765274</v>
@@ -27716,7 +27716,7 @@
         <v>5.16699981689453</v>
       </c>
       <c r="G943" t="n">
-        <v>4.91574144363403</v>
+        <v>4.91574096679688</v>
       </c>
       <c r="H943" t="n">
         <v>5370870</v>
@@ -27803,7 +27803,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G946" t="n">
-        <v>4.98519134521484</v>
+        <v>4.985191822052</v>
       </c>
       <c r="H946" t="n">
         <v>8525656</v>
@@ -27977,7 +27977,7 @@
         <v>5.19700002670288</v>
       </c>
       <c r="G952" t="n">
-        <v>4.94428253173828</v>
+        <v>4.94428300857544</v>
       </c>
       <c r="H952" t="n">
         <v>6264433</v>
@@ -28064,7 +28064,7 @@
         <v>4.94199991226196</v>
       </c>
       <c r="G955" t="n">
-        <v>4.70168209075928</v>
+        <v>4.70168256759644</v>
       </c>
       <c r="H955" t="n">
         <v>14155269</v>
@@ -28093,7 +28093,7 @@
         <v>4.96799993515015</v>
       </c>
       <c r="G956" t="n">
-        <v>4.72641801834106</v>
+        <v>4.72641849517822</v>
       </c>
       <c r="H956" t="n">
         <v>7492745</v>
@@ -28122,7 +28122,7 @@
         <v>4.97599983215332</v>
       </c>
       <c r="G957" t="n">
-        <v>4.7340292930603</v>
+        <v>4.73402881622314</v>
       </c>
       <c r="H957" t="n">
         <v>8539212</v>
@@ -28180,7 +28180,7 @@
         <v>5.06599998474121</v>
       </c>
       <c r="G959" t="n">
-        <v>4.81965303421021</v>
+        <v>4.81965255737305</v>
       </c>
       <c r="H959" t="n">
         <v>7079628</v>
@@ -28267,7 +28267,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G962" t="n">
-        <v>5.09935617446899</v>
+        <v>5.09935665130615</v>
       </c>
       <c r="H962" t="n">
         <v>9513376</v>
@@ -28354,7 +28354,7 @@
         <v>5.39400005340576</v>
       </c>
       <c r="G965" t="n">
-        <v>5.13170289993286</v>
+        <v>5.13170337677002</v>
       </c>
       <c r="H965" t="n">
         <v>7271483</v>
@@ -28412,7 +28412,7 @@
         <v>5.35400009155273</v>
       </c>
       <c r="G967" t="n">
-        <v>5.0936484336853</v>
+        <v>5.09364795684814</v>
       </c>
       <c r="H967" t="n">
         <v>7366786</v>
@@ -28528,7 +28528,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G971" t="n">
-        <v>5.06130123138428</v>
+        <v>5.06130170822144</v>
       </c>
       <c r="H971" t="n">
         <v>8251907</v>
@@ -28615,7 +28615,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G974" t="n">
-        <v>5.05178785324097</v>
+        <v>5.05178737640381</v>
       </c>
       <c r="H974" t="n">
         <v>5670673</v>
@@ -28905,7 +28905,7 @@
         <v>5.36299991607666</v>
       </c>
       <c r="G984" t="n">
-        <v>5.102210521698</v>
+        <v>5.10221004486084</v>
       </c>
       <c r="H984" t="n">
         <v>8375880</v>
@@ -28934,7 +28934,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G985" t="n">
-        <v>5.09935617446899</v>
+        <v>5.09935665130615</v>
       </c>
       <c r="H985" t="n">
         <v>6100265</v>
@@ -28963,7 +28963,7 @@
         <v>5.41300010681152</v>
       </c>
       <c r="G986" t="n">
-        <v>5.14977884292603</v>
+        <v>5.14977931976318</v>
       </c>
       <c r="H986" t="n">
         <v>11408179</v>
@@ -28992,7 +28992,7 @@
         <v>5.44099998474121</v>
       </c>
       <c r="G987" t="n">
-        <v>5.1764178276062</v>
+        <v>5.17641735076904</v>
       </c>
       <c r="H987" t="n">
         <v>5867671</v>
@@ -29050,7 +29050,7 @@
         <v>5.51800012588501</v>
       </c>
       <c r="G989" t="n">
-        <v>5.24967288970947</v>
+        <v>5.24967336654663</v>
       </c>
       <c r="H989" t="n">
         <v>8024179</v>
@@ -29079,7 +29079,7 @@
         <v>5.65100002288818</v>
       </c>
       <c r="G990" t="n">
-        <v>5.3762059211731</v>
+        <v>5.37620544433594</v>
       </c>
       <c r="H990" t="n">
         <v>12871995</v>
@@ -29166,7 +29166,7 @@
         <v>5.83900022506714</v>
       </c>
       <c r="G993" t="n">
-        <v>5.55506372451782</v>
+        <v>5.55506420135498</v>
       </c>
       <c r="H993" t="n">
         <v>5594077</v>
@@ -29224,7 +29224,7 @@
         <v>5.73899984359741</v>
       </c>
       <c r="G995" t="n">
-        <v>5.45992612838745</v>
+        <v>5.45992660522461</v>
       </c>
       <c r="H995" t="n">
         <v>8653313</v>
@@ -29253,7 +29253,7 @@
         <v>5.68599987030029</v>
       </c>
       <c r="G996" t="n">
-        <v>5.40950345993042</v>
+        <v>5.40950393676758</v>
       </c>
       <c r="H996" t="n">
         <v>4200712</v>
@@ -29340,7 +29340,7 @@
         <v>5.51200008392334</v>
       </c>
       <c r="G999" t="n">
-        <v>5.24396514892578</v>
+        <v>5.24396467208862</v>
       </c>
       <c r="H999" t="n">
         <v>5722620</v>
@@ -29601,7 +29601,7 @@
         <v>5.54199981689453</v>
       </c>
       <c r="G1008" t="n">
-        <v>5.27250576019287</v>
+        <v>5.27250623703003</v>
       </c>
       <c r="H1008" t="n">
         <v>4337873</v>
@@ -29630,7 +29630,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1009" t="n">
-        <v>5.28963088989258</v>
+        <v>5.28963041305542</v>
       </c>
       <c r="H1009" t="n">
         <v>5422481</v>
@@ -29659,7 +29659,7 @@
         <v>5.59499979019165</v>
       </c>
       <c r="G1010" t="n">
-        <v>5.3229284286499</v>
+        <v>5.32292890548706</v>
       </c>
       <c r="H1010" t="n">
         <v>7120475</v>
@@ -29688,7 +29688,7 @@
         <v>5.59499979019165</v>
       </c>
       <c r="G1011" t="n">
-        <v>5.3229284286499</v>
+        <v>5.32292890548706</v>
       </c>
       <c r="H1011" t="n">
         <v>8358777</v>
@@ -29833,7 +29833,7 @@
         <v>5.59499979019165</v>
       </c>
       <c r="G1016" t="n">
-        <v>5.3229284286499</v>
+        <v>5.32292890548706</v>
       </c>
       <c r="H1016" t="n">
         <v>3767783</v>
@@ -29978,7 +29978,7 @@
         <v>5.26300001144409</v>
       </c>
       <c r="G1021" t="n">
-        <v>5.00707340240479</v>
+        <v>5.00707292556763</v>
       </c>
       <c r="H1021" t="n">
         <v>11895409</v>
@@ -30065,7 +30065,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1024" t="n">
-        <v>4.8995680809021</v>
+        <v>4.89956855773926</v>
       </c>
       <c r="H1024" t="n">
         <v>9609886</v>
@@ -30094,7 +30094,7 @@
         <v>5.05900001525879</v>
       </c>
       <c r="G1025" t="n">
-        <v>4.81299304962158</v>
+        <v>4.81299352645874</v>
       </c>
       <c r="H1025" t="n">
         <v>6906988</v>
@@ -30152,7 +30152,7 @@
         <v>5.1230001449585</v>
       </c>
       <c r="G1027" t="n">
-        <v>4.8738808631897</v>
+        <v>4.87388134002686</v>
       </c>
       <c r="H1027" t="n">
         <v>5426424</v>
@@ -30181,7 +30181,7 @@
         <v>5.11399984359741</v>
       </c>
       <c r="G1028" t="n">
-        <v>4.865318775177</v>
+        <v>4.86531829833984</v>
       </c>
       <c r="H1028" t="n">
         <v>3560102</v>
@@ -30210,7 +30210,7 @@
         <v>5.06599998474121</v>
       </c>
       <c r="G1029" t="n">
-        <v>4.81965303421021</v>
+        <v>4.81965255737305</v>
       </c>
       <c r="H1029" t="n">
         <v>7067344</v>
@@ -30268,7 +30268,7 @@
         <v>4.94199991226196</v>
       </c>
       <c r="G1031" t="n">
-        <v>4.70168209075928</v>
+        <v>4.70168256759644</v>
       </c>
       <c r="H1031" t="n">
         <v>8681679</v>
@@ -30413,7 +30413,7 @@
         <v>5.05399990081787</v>
       </c>
       <c r="G1036" t="n">
-        <v>4.80823612213135</v>
+        <v>4.80823659896851</v>
       </c>
       <c r="H1036" t="n">
         <v>8898900</v>
@@ -30471,7 +30471,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1038" t="n">
-        <v>4.58561515808105</v>
+        <v>4.58561563491821</v>
       </c>
       <c r="H1038" t="n">
         <v>8979335</v>
@@ -30500,7 +30500,7 @@
         <v>4.91800022125244</v>
       </c>
       <c r="G1039" t="n">
-        <v>4.6788501739502</v>
+        <v>4.67884969711304</v>
       </c>
       <c r="H1039" t="n">
         <v>8140590</v>
@@ -30558,7 +30558,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1041" t="n">
-        <v>4.77588939666748</v>
+        <v>4.77588987350464</v>
       </c>
       <c r="H1041" t="n">
         <v>6949040</v>
@@ -30587,7 +30587,7 @@
         <v>4.94799995422363</v>
       </c>
       <c r="G1042" t="n">
-        <v>4.70739078521729</v>
+        <v>4.70739126205444</v>
       </c>
       <c r="H1042" t="n">
         <v>6830332</v>
@@ -30703,7 +30703,7 @@
         <v>5.25</v>
       </c>
       <c r="G1046" t="n">
-        <v>4.99470520019531</v>
+        <v>4.99470567703247</v>
       </c>
       <c r="H1046" t="n">
         <v>18341830</v>
@@ -31022,7 +31022,7 @@
         <v>5.00099992752075</v>
       </c>
       <c r="G1057" t="n">
-        <v>4.75781345367432</v>
+        <v>4.75781393051147</v>
       </c>
       <c r="H1057" t="n">
         <v>18342696</v>
@@ -31080,7 +31080,7 @@
         <v>4.77899980545044</v>
       </c>
       <c r="G1059" t="n">
-        <v>4.54660892486572</v>
+        <v>4.54660844802856</v>
       </c>
       <c r="H1059" t="n">
         <v>14134380</v>
@@ -31167,7 +31167,7 @@
         <v>4.32100009918213</v>
       </c>
       <c r="G1062" t="n">
-        <v>4.11088037490845</v>
+        <v>4.11088085174561</v>
       </c>
       <c r="H1062" t="n">
         <v>15034059</v>
@@ -31225,7 +31225,7 @@
         <v>3.67199993133545</v>
       </c>
       <c r="G1064" t="n">
-        <v>3.49343967437744</v>
+        <v>3.49343943595886</v>
       </c>
       <c r="H1064" t="n">
         <v>15459498</v>
@@ -31254,7 +31254,7 @@
         <v>3.81699991226196</v>
       </c>
       <c r="G1065" t="n">
-        <v>3.63138842582703</v>
+        <v>3.63138866424561</v>
       </c>
       <c r="H1065" t="n">
         <v>20006610</v>
@@ -31428,7 +31428,7 @@
         <v>3.7739999294281</v>
       </c>
       <c r="G1071" t="n">
-        <v>3.59047937393188</v>
+        <v>3.59047961235046</v>
       </c>
       <c r="H1071" t="n">
         <v>20539960</v>
@@ -31718,7 +31718,7 @@
         <v>3.79299998283386</v>
       </c>
       <c r="G1081" t="n">
-        <v>3.60855555534363</v>
+        <v>3.60855579376221</v>
       </c>
       <c r="H1081" t="n">
         <v>9112585</v>
@@ -31776,7 +31776,7 @@
         <v>3.92400002479553</v>
       </c>
       <c r="G1083" t="n">
-        <v>3.73318529129028</v>
+        <v>3.73318552970886</v>
       </c>
       <c r="H1083" t="n">
         <v>8125581</v>
@@ -31834,7 +31834,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G1085" t="n">
-        <v>3.61045861244202</v>
+        <v>3.61045837402344</v>
       </c>
       <c r="H1085" t="n">
         <v>9133043</v>
@@ -31921,7 +31921,7 @@
         <v>3.53399991989136</v>
       </c>
       <c r="G1088" t="n">
-        <v>3.36215019226074</v>
+        <v>3.36214995384216</v>
       </c>
       <c r="H1088" t="n">
         <v>10081010</v>
@@ -32182,7 +32182,7 @@
         <v>3.44600009918213</v>
       </c>
       <c r="G1097" t="n">
-        <v>3.27842950820923</v>
+        <v>3.27842974662781</v>
       </c>
       <c r="H1097" t="n">
         <v>7252885</v>
@@ -32211,7 +32211,7 @@
         <v>3.64400005340576</v>
       </c>
       <c r="G1098" t="n">
-        <v>3.466801404953</v>
+        <v>3.46680116653442</v>
       </c>
       <c r="H1098" t="n">
         <v>11382035</v>
@@ -32240,7 +32240,7 @@
         <v>3.6159999370575</v>
       </c>
       <c r="G1099" t="n">
-        <v>3.44016265869141</v>
+        <v>3.44016289710999</v>
       </c>
       <c r="H1099" t="n">
         <v>12293070</v>
@@ -32298,7 +32298,7 @@
         <v>3.53399991989136</v>
       </c>
       <c r="G1101" t="n">
-        <v>3.36215019226074</v>
+        <v>3.36214995384216</v>
       </c>
       <c r="H1101" t="n">
         <v>6018678</v>
@@ -32327,7 +32327,7 @@
         <v>3.50399994850159</v>
       </c>
       <c r="G1102" t="n">
-        <v>3.33360886573792</v>
+        <v>3.33360910415649</v>
       </c>
       <c r="H1102" t="n">
         <v>4601154</v>
@@ -32356,7 +32356,7 @@
         <v>3.42799997329712</v>
       </c>
       <c r="G1103" t="n">
-        <v>3.26130485534668</v>
+        <v>3.2613046169281</v>
       </c>
       <c r="H1103" t="n">
         <v>7123473</v>
@@ -32385,7 +32385,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1104" t="n">
-        <v>3.29174876213074</v>
+        <v>3.29174852371216</v>
       </c>
       <c r="H1104" t="n">
         <v>3356216</v>
@@ -32675,7 +32675,7 @@
         <v>3.20700001716614</v>
       </c>
       <c r="G1114" t="n">
-        <v>3.05105137825012</v>
+        <v>3.0510516166687</v>
       </c>
       <c r="H1114" t="n">
         <v>12499911</v>
@@ -32733,7 +32733,7 @@
         <v>3.30399990081787</v>
       </c>
       <c r="G1116" t="n">
-        <v>3.14333462715149</v>
+        <v>3.14333438873291</v>
       </c>
       <c r="H1116" t="n">
         <v>12389541</v>
@@ -32762,7 +32762,7 @@
         <v>3.3050000667572</v>
       </c>
       <c r="G1117" t="n">
-        <v>3.1442859172821</v>
+        <v>3.14428615570068</v>
       </c>
       <c r="H1117" t="n">
         <v>16377885</v>
@@ -32849,7 +32849,7 @@
         <v>3.41400003433228</v>
       </c>
       <c r="G1120" t="n">
-        <v>3.24798536300659</v>
+        <v>3.24798560142517</v>
       </c>
       <c r="H1120" t="n">
         <v>10515189</v>
@@ -32878,7 +32878,7 @@
         <v>3.52300000190735</v>
       </c>
       <c r="G1121" t="n">
-        <v>3.35168504714966</v>
+        <v>3.35168528556824</v>
       </c>
       <c r="H1121" t="n">
         <v>14830770</v>
@@ -33052,7 +33052,7 @@
         <v>3.71600008010864</v>
       </c>
       <c r="G1127" t="n">
-        <v>3.53530025482178</v>
+        <v>3.5353000164032</v>
       </c>
       <c r="H1127" t="n">
         <v>26938169</v>
@@ -33110,7 +33110,7 @@
         <v>3.53399991989136</v>
       </c>
       <c r="G1129" t="n">
-        <v>3.36215019226074</v>
+        <v>3.36214995384216</v>
       </c>
       <c r="H1129" t="n">
         <v>19235451</v>
@@ -33226,7 +33226,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1133" t="n">
-        <v>3.49153709411621</v>
+        <v>3.49153685569763</v>
       </c>
       <c r="H1133" t="n">
         <v>10659918</v>
@@ -80067,6 +80067,35 @@
         <v>3779210</v>
       </c>
       <c r="I2748" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2749">
+      <c r="A2749" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2749" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C2749" t="n">
+        <v>5.76000022888184</v>
+      </c>
+      <c r="D2749" t="n">
+        <v>5.76100015640259</v>
+      </c>
+      <c r="E2749" t="n">
+        <v>5.60400009155273</v>
+      </c>
+      <c r="F2749" t="n">
+        <v>5.72399997711182</v>
+      </c>
+      <c r="G2749" t="n">
+        <v>5.72399997711182</v>
+      </c>
+      <c r="H2749" t="n">
+        <v>2620080</v>
+      </c>
+      <c r="I2749" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TIT.MI.xlsx
+++ b/data/TIT.MI.xlsx
@@ -80099,6 +80099,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2750">
+      <c r="A2750" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2750" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C2750" t="n">
+        <v>5.69999980926514</v>
+      </c>
+      <c r="D2750" t="n">
+        <v>5.70900011062622</v>
+      </c>
+      <c r="E2750" t="n">
+        <v>5.53399991989136</v>
+      </c>
+      <c r="F2750" t="n">
+        <v>5.58400011062622</v>
+      </c>
+      <c r="G2750" t="n">
+        <v>5.58400011062622</v>
+      </c>
+      <c r="H2750" t="n">
+        <v>5802552</v>
+      </c>
+      <c r="I2750" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TIT.MI.xlsx
+++ b/data/TIT.MI.xlsx
@@ -775,7 +775,7 @@
         <v>9.76500034332275</v>
       </c>
       <c r="G14" t="n">
-        <v>9.29015159606934</v>
+        <v>9.29015254974365</v>
       </c>
       <c r="H14" t="n">
         <v>12465433</v>
@@ -949,7 +949,7 @@
         <v>9.77000045776367</v>
       </c>
       <c r="G20" t="n">
-        <v>9.29490852355957</v>
+        <v>9.29490947723389</v>
       </c>
       <c r="H20" t="n">
         <v>21107831</v>
@@ -1152,7 +1152,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G27" t="n">
-        <v>7.99152803421021</v>
+        <v>7.99152851104736</v>
       </c>
       <c r="H27" t="n">
         <v>18362675</v>
@@ -1181,7 +1181,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G28" t="n">
-        <v>8.27694034576416</v>
+        <v>8.27693939208984</v>
       </c>
       <c r="H28" t="n">
         <v>22554264</v>
@@ -1239,7 +1239,7 @@
         <v>8.25500011444092</v>
       </c>
       <c r="G30" t="n">
-        <v>7.85357904434204</v>
+        <v>7.8535795211792</v>
       </c>
       <c r="H30" t="n">
         <v>17371217</v>
@@ -1268,7 +1268,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G31" t="n">
-        <v>8.17228889465332</v>
+        <v>8.17228984832764</v>
       </c>
       <c r="H31" t="n">
         <v>10187944</v>
@@ -1297,7 +1297,7 @@
         <v>8.76500034332275</v>
       </c>
       <c r="G32" t="n">
-        <v>8.33877944946289</v>
+        <v>8.33878040313721</v>
       </c>
       <c r="H32" t="n">
         <v>9462652</v>
@@ -1326,7 +1326,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G33" t="n">
-        <v>7.80125379562378</v>
+        <v>7.80125331878662</v>
       </c>
       <c r="H33" t="n">
         <v>28696243</v>
@@ -1587,7 +1587,7 @@
         <v>8.98999977111816</v>
       </c>
       <c r="G42" t="n">
-        <v>8.55283832550049</v>
+        <v>8.55283737182617</v>
       </c>
       <c r="H42" t="n">
         <v>10915001</v>
@@ -1645,7 +1645,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G44" t="n">
-        <v>8.98095512390137</v>
+        <v>8.98095607757568</v>
       </c>
       <c r="H44" t="n">
         <v>13756209</v>
@@ -1703,7 +1703,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G46" t="n">
-        <v>9.70399856567383</v>
+        <v>9.70399951934814</v>
       </c>
       <c r="H46" t="n">
         <v>20342560</v>
@@ -1732,7 +1732,7 @@
         <v>9.82499980926514</v>
       </c>
       <c r="G47" t="n">
-        <v>9.34723472595215</v>
+        <v>9.34723377227783</v>
       </c>
       <c r="H47" t="n">
         <v>11169591</v>
@@ -1790,7 +1790,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G49" t="n">
-        <v>9.64691734313965</v>
+        <v>9.64691638946533</v>
       </c>
       <c r="H49" t="n">
         <v>18523100</v>
@@ -1848,7 +1848,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G51" t="n">
-        <v>9.91330051422119</v>
+        <v>9.91330146789551</v>
       </c>
       <c r="H51" t="n">
         <v>10987806</v>
@@ -1877,7 +1877,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G52" t="n">
-        <v>9.81816387176514</v>
+        <v>9.81816291809082</v>
       </c>
       <c r="H52" t="n">
         <v>6496305</v>
@@ -1935,7 +1935,7 @@
         <v>10.3299999237061</v>
       </c>
       <c r="G54" t="n">
-        <v>9.82767772674561</v>
+        <v>9.82767677307129</v>
       </c>
       <c r="H54" t="n">
         <v>5795315</v>
@@ -2022,7 +2022,7 @@
         <v>10.4099998474121</v>
       </c>
       <c r="G57" t="n">
-        <v>9.90378665924072</v>
+        <v>9.90378761291504</v>
       </c>
       <c r="H57" t="n">
         <v>9694375</v>
@@ -2225,7 +2225,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G64" t="n">
-        <v>8.70505809783936</v>
+        <v>8.70505714416504</v>
       </c>
       <c r="H64" t="n">
         <v>14609221</v>
@@ -2283,7 +2283,7 @@
         <v>8.58500003814697</v>
       </c>
       <c r="G66" t="n">
-        <v>8.16753196716309</v>
+        <v>8.1675329208374</v>
       </c>
       <c r="H66" t="n">
         <v>11386012</v>
@@ -2312,7 +2312,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G67" t="n">
-        <v>8.18180370330811</v>
+        <v>8.18180274963379</v>
       </c>
       <c r="H67" t="n">
         <v>8994634</v>
@@ -2341,7 +2341,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G68" t="n">
-        <v>7.95347309112549</v>
+        <v>7.95347356796265</v>
       </c>
       <c r="H68" t="n">
         <v>8054619</v>
@@ -2399,7 +2399,7 @@
         <v>8.98999977111816</v>
       </c>
       <c r="G70" t="n">
-        <v>8.55283832550049</v>
+        <v>8.55283737182617</v>
       </c>
       <c r="H70" t="n">
         <v>7769877</v>
@@ -2718,7 +2718,7 @@
         <v>8.65499973297119</v>
       </c>
       <c r="G81" t="n">
-        <v>8.23412799835205</v>
+        <v>8.23412895202637</v>
       </c>
       <c r="H81" t="n">
         <v>11095524</v>
@@ -2776,7 +2776,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G83" t="n">
-        <v>8.25791358947754</v>
+        <v>8.25791263580322</v>
       </c>
       <c r="H83" t="n">
         <v>15796951</v>
@@ -2834,7 +2834,7 @@
         <v>8.46500015258789</v>
       </c>
       <c r="G85" t="n">
-        <v>8.05336856842041</v>
+        <v>8.05336761474609</v>
       </c>
       <c r="H85" t="n">
         <v>6739223</v>
@@ -2863,7 +2863,7 @@
         <v>8.36499977111816</v>
       </c>
       <c r="G86" t="n">
-        <v>7.95823001861572</v>
+        <v>7.95823049545288</v>
       </c>
       <c r="H86" t="n">
         <v>7439860</v>
@@ -2892,7 +2892,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G87" t="n">
-        <v>8.04861164093018</v>
+        <v>8.04861068725586</v>
       </c>
       <c r="H87" t="n">
         <v>6088332</v>
@@ -3037,7 +3037,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G92" t="n">
-        <v>8.05812549591064</v>
+        <v>8.05812454223633</v>
       </c>
       <c r="H92" t="n">
         <v>7818052</v>
@@ -3153,7 +3153,7 @@
         <v>8.48999977111816</v>
       </c>
       <c r="G96" t="n">
-        <v>8.07715225219727</v>
+        <v>8.07715129852295</v>
       </c>
       <c r="H96" t="n">
         <v>11841822</v>
@@ -3211,7 +3211,7 @@
         <v>8.30500030517578</v>
       </c>
       <c r="G98" t="n">
-        <v>7.90114879608154</v>
+        <v>7.90114784240723</v>
       </c>
       <c r="H98" t="n">
         <v>9583225</v>
@@ -3240,7 +3240,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G99" t="n">
-        <v>7.87736368179321</v>
+        <v>7.87736320495605</v>
       </c>
       <c r="H99" t="n">
         <v>7171888</v>
@@ -3327,7 +3327,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G102" t="n">
-        <v>7.91541862487793</v>
+        <v>7.91541814804077</v>
       </c>
       <c r="H102" t="n">
         <v>15847474</v>
@@ -3385,7 +3385,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G104" t="n">
-        <v>8.27694034576416</v>
+        <v>8.27693939208984</v>
       </c>
       <c r="H104" t="n">
         <v>8314517</v>
@@ -3675,7 +3675,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G114" t="n">
-        <v>7.82028150558472</v>
+        <v>7.82028198242188</v>
       </c>
       <c r="H114" t="n">
         <v>14068153</v>
@@ -3704,7 +3704,7 @@
         <v>7.91499996185303</v>
       </c>
       <c r="G115" t="n">
-        <v>7.53011274337769</v>
+        <v>7.53011322021484</v>
       </c>
       <c r="H115" t="n">
         <v>12688239</v>
@@ -3762,7 +3762,7 @@
         <v>7.59499979019165</v>
       </c>
       <c r="G117" t="n">
-        <v>7.22567319869995</v>
+        <v>7.22567367553711</v>
       </c>
       <c r="H117" t="n">
         <v>14127681</v>
@@ -3791,7 +3791,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G118" t="n">
-        <v>7.04015636444092</v>
+        <v>7.04015588760376</v>
       </c>
       <c r="H118" t="n">
         <v>12062526</v>
@@ -3936,7 +3936,7 @@
         <v>8.27499961853027</v>
       </c>
       <c r="G123" t="n">
-        <v>7.87260675430298</v>
+        <v>7.87260627746582</v>
       </c>
       <c r="H123" t="n">
         <v>12615589</v>
@@ -3994,7 +3994,7 @@
         <v>6.67500019073486</v>
       </c>
       <c r="G125" t="n">
-        <v>6.35041093826294</v>
+        <v>6.3504114151001</v>
       </c>
       <c r="H125" t="n">
         <v>23209498</v>
@@ -4052,7 +4052,7 @@
         <v>7.44500017166138</v>
       </c>
       <c r="G127" t="n">
-        <v>7.08296775817871</v>
+        <v>7.08296823501587</v>
       </c>
       <c r="H127" t="n">
         <v>14352211</v>
@@ -4110,7 +4110,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G129" t="n">
-        <v>7.04015636444092</v>
+        <v>7.04015588760376</v>
       </c>
       <c r="H129" t="n">
         <v>8980366</v>
@@ -4226,7 +4226,7 @@
         <v>6.33500003814697</v>
       </c>
       <c r="G133" t="n">
-        <v>6.02694416046143</v>
+        <v>6.02694463729858</v>
       </c>
       <c r="H133" t="n">
         <v>13905809</v>
@@ -4284,7 +4284,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G135" t="n">
-        <v>6.30759954452515</v>
+        <v>6.30759906768799</v>
       </c>
       <c r="H135" t="n">
         <v>6922559</v>
@@ -4313,7 +4313,7 @@
         <v>6.92500019073486</v>
       </c>
       <c r="G136" t="n">
-        <v>6.58825397491455</v>
+        <v>6.58825445175171</v>
       </c>
       <c r="H136" t="n">
         <v>10111814</v>
@@ -4429,7 +4429,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G140" t="n">
-        <v>6.60252523422241</v>
+        <v>6.60252475738525</v>
       </c>
       <c r="H140" t="n">
         <v>13382865</v>
@@ -4487,7 +4487,7 @@
         <v>6.86499977111816</v>
       </c>
       <c r="G142" t="n">
-        <v>6.53117179870605</v>
+        <v>6.5311713218689</v>
       </c>
       <c r="H142" t="n">
         <v>8811876</v>
@@ -4574,7 +4574,7 @@
         <v>7</v>
       </c>
       <c r="G145" t="n">
-        <v>6.65960693359375</v>
+        <v>6.65960741043091</v>
       </c>
       <c r="H145" t="n">
         <v>8398609</v>
@@ -4632,7 +4632,7 @@
         <v>7.46999979019165</v>
       </c>
       <c r="G147" t="n">
-        <v>7.10675191879272</v>
+        <v>7.10675239562988</v>
       </c>
       <c r="H147" t="n">
         <v>29073903</v>
@@ -4690,7 +4690,7 @@
         <v>7.63500022888184</v>
       </c>
       <c r="G149" t="n">
-        <v>7.26372909545898</v>
+        <v>7.26372861862183</v>
       </c>
       <c r="H149" t="n">
         <v>10594903</v>
@@ -4748,7 +4748,7 @@
         <v>7.44500017166138</v>
       </c>
       <c r="G151" t="n">
-        <v>7.08296775817871</v>
+        <v>7.08296823501587</v>
       </c>
       <c r="H151" t="n">
         <v>8748243</v>
@@ -4893,7 +4893,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G156" t="n">
-        <v>7.24945831298828</v>
+        <v>7.24945783615112</v>
       </c>
       <c r="H156" t="n">
         <v>4135572</v>
@@ -5125,7 +5125,7 @@
         <v>7.92999982833862</v>
       </c>
       <c r="G164" t="n">
-        <v>7.54438304901123</v>
+        <v>7.54438352584839</v>
       </c>
       <c r="H164" t="n">
         <v>4924973</v>
@@ -5212,7 +5212,7 @@
         <v>8.0649995803833</v>
       </c>
       <c r="G167" t="n">
-        <v>7.67281866073608</v>
+        <v>7.67281818389893</v>
       </c>
       <c r="H167" t="n">
         <v>5554419</v>
@@ -5299,7 +5299,7 @@
         <v>8.24499988555908</v>
       </c>
       <c r="G170" t="n">
-        <v>7.84406518936157</v>
+        <v>7.84406566619873</v>
       </c>
       <c r="H170" t="n">
         <v>6352724</v>
@@ -5328,7 +5328,7 @@
         <v>8.13500022888184</v>
       </c>
       <c r="G171" t="n">
-        <v>7.73941516876221</v>
+        <v>7.73941469192505</v>
       </c>
       <c r="H171" t="n">
         <v>7750471</v>
@@ -5357,7 +5357,7 @@
         <v>8.16499996185303</v>
       </c>
       <c r="G172" t="n">
-        <v>7.7679557800293</v>
+        <v>7.76795625686646</v>
       </c>
       <c r="H172" t="n">
         <v>8273298</v>
@@ -5386,7 +5386,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G173" t="n">
-        <v>7.80125379562378</v>
+        <v>7.80125331878662</v>
       </c>
       <c r="H173" t="n">
         <v>5239033</v>
@@ -5473,7 +5473,7 @@
         <v>8.04500007629395</v>
       </c>
       <c r="G176" t="n">
-        <v>7.6537914276123</v>
+        <v>7.65379095077515</v>
       </c>
       <c r="H176" t="n">
         <v>7646216</v>
@@ -5502,7 +5502,7 @@
         <v>8.16499996185303</v>
       </c>
       <c r="G177" t="n">
-        <v>7.7679557800293</v>
+        <v>7.76795625686646</v>
       </c>
       <c r="H177" t="n">
         <v>6137326</v>
@@ -5531,7 +5531,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G178" t="n">
-        <v>7.64903402328491</v>
+        <v>7.64903450012207</v>
       </c>
       <c r="H178" t="n">
         <v>7450630</v>
@@ -5560,7 +5560,7 @@
         <v>7.88500022888184</v>
       </c>
       <c r="G179" t="n">
-        <v>7.5015721321106</v>
+        <v>7.50157165527344</v>
       </c>
       <c r="H179" t="n">
         <v>10968844</v>
@@ -5647,7 +5647,7 @@
         <v>7.53499984741211</v>
       </c>
       <c r="G182" t="n">
-        <v>7.16859149932861</v>
+        <v>7.16859102249146</v>
       </c>
       <c r="H182" t="n">
         <v>8919248</v>
@@ -5734,7 +5734,7 @@
         <v>7.28499984741211</v>
       </c>
       <c r="G185" t="n">
-        <v>6.930748462677</v>
+        <v>6.93074798583984</v>
       </c>
       <c r="H185" t="n">
         <v>7139176</v>
@@ -5821,7 +5821,7 @@
         <v>7.63500022888184</v>
       </c>
       <c r="G188" t="n">
-        <v>7.26372909545898</v>
+        <v>7.26372861862183</v>
       </c>
       <c r="H188" t="n">
         <v>4604142</v>
@@ -5879,7 +5879,7 @@
         <v>7.34499979019165</v>
       </c>
       <c r="G190" t="n">
-        <v>6.98783016204834</v>
+        <v>6.9878306388855</v>
       </c>
       <c r="H190" t="n">
         <v>5769993</v>
@@ -5908,7 +5908,7 @@
         <v>7.49499988555908</v>
       </c>
       <c r="G191" t="n">
-        <v>7.1305365562439</v>
+        <v>7.13053607940674</v>
       </c>
       <c r="H191" t="n">
         <v>4422318</v>
@@ -5966,7 +5966,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G193" t="n">
-        <v>7.03064250946045</v>
+        <v>7.03064203262329</v>
       </c>
       <c r="H193" t="n">
         <v>9011031</v>
@@ -6053,7 +6053,7 @@
         <v>7.29500007629395</v>
       </c>
       <c r="G196" t="n">
-        <v>6.94026231765747</v>
+        <v>6.94026184082031</v>
       </c>
       <c r="H196" t="n">
         <v>10575030</v>
@@ -6140,7 +6140,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G199" t="n">
-        <v>7.04015636444092</v>
+        <v>7.04015588760376</v>
       </c>
       <c r="H199" t="n">
         <v>8616275</v>
@@ -6169,7 +6169,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G200" t="n">
-        <v>6.86890888214111</v>
+        <v>6.86890840530396</v>
       </c>
       <c r="H200" t="n">
         <v>8236131</v>
@@ -6227,7 +6227,7 @@
         <v>6.94500017166138</v>
       </c>
       <c r="G202" t="n">
-        <v>6.60728216171265</v>
+        <v>6.60728168487549</v>
       </c>
       <c r="H202" t="n">
         <v>17317483</v>
@@ -6314,7 +6314,7 @@
         <v>7.57499980926514</v>
       </c>
       <c r="G205" t="n">
-        <v>7.20664596557617</v>
+        <v>7.20664644241333</v>
       </c>
       <c r="H205" t="n">
         <v>13042674</v>
@@ -6372,7 +6372,7 @@
         <v>7.59499979019165</v>
       </c>
       <c r="G207" t="n">
-        <v>7.22567319869995</v>
+        <v>7.22567367553711</v>
       </c>
       <c r="H207" t="n">
         <v>5770682</v>
@@ -6401,7 +6401,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G208" t="n">
-        <v>7.35410928726196</v>
+        <v>7.3541088104248</v>
       </c>
       <c r="H208" t="n">
         <v>11041706</v>
@@ -6430,7 +6430,7 @@
         <v>7.92999982833862</v>
       </c>
       <c r="G209" t="n">
-        <v>7.54438304901123</v>
+        <v>7.54438352584839</v>
       </c>
       <c r="H209" t="n">
         <v>12562957</v>
@@ -6633,7 +6633,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G216" t="n">
-        <v>7.35410928726196</v>
+        <v>7.3541088104248</v>
       </c>
       <c r="H216" t="n">
         <v>11074256</v>
@@ -6662,7 +6662,7 @@
         <v>7.70499992370605</v>
       </c>
       <c r="G217" t="n">
-        <v>7.33032464981079</v>
+        <v>7.33032417297363</v>
       </c>
       <c r="H217" t="n">
         <v>6751462</v>
@@ -6778,7 +6778,7 @@
         <v>7.45499992370605</v>
       </c>
       <c r="G221" t="n">
-        <v>7.09248161315918</v>
+        <v>7.09248113632202</v>
       </c>
       <c r="H221" t="n">
         <v>19305315</v>
@@ -6952,7 +6952,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G227" t="n">
-        <v>6.67863416671753</v>
+        <v>6.67863464355469</v>
       </c>
       <c r="H227" t="n">
         <v>15148923</v>
@@ -6981,7 +6981,7 @@
         <v>6.86499977111816</v>
       </c>
       <c r="G228" t="n">
-        <v>6.53117179870605</v>
+        <v>6.5311713218689</v>
       </c>
       <c r="H228" t="n">
         <v>15141472</v>
@@ -7097,7 +7097,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G232" t="n">
-        <v>6.70717620849609</v>
+        <v>6.70717573165894</v>
       </c>
       <c r="H232" t="n">
         <v>6631825</v>
@@ -7126,7 +7126,7 @@
         <v>7.14499998092651</v>
       </c>
       <c r="G233" t="n">
-        <v>6.79755592346191</v>
+        <v>6.79755640029907</v>
       </c>
       <c r="H233" t="n">
         <v>7685848</v>
@@ -7300,7 +7300,7 @@
         <v>7</v>
       </c>
       <c r="G239" t="n">
-        <v>6.65960693359375</v>
+        <v>6.65960741043091</v>
       </c>
       <c r="H239" t="n">
         <v>16092872</v>
@@ -7358,7 +7358,7 @@
         <v>7.54500007629395</v>
       </c>
       <c r="G241" t="n">
-        <v>7.17810535430908</v>
+        <v>7.17810487747192</v>
       </c>
       <c r="H241" t="n">
         <v>14162922</v>
@@ -7416,7 +7416,7 @@
         <v>7.625</v>
       </c>
       <c r="G243" t="n">
-        <v>7.25421524047852</v>
+        <v>7.25421476364136</v>
       </c>
       <c r="H243" t="n">
         <v>7313055</v>
@@ -7561,7 +7561,7 @@
         <v>8.06999969482422</v>
       </c>
       <c r="G248" t="n">
-        <v>7.67757558822632</v>
+        <v>7.67757511138916</v>
       </c>
       <c r="H248" t="n">
         <v>19683266</v>
@@ -7648,7 +7648,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G251" t="n">
-        <v>7.99152803421021</v>
+        <v>7.99152851104736</v>
       </c>
       <c r="H251" t="n">
         <v>10995964</v>
@@ -7735,7 +7735,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G254" t="n">
-        <v>8.27694034576416</v>
+        <v>8.27693939208984</v>
       </c>
       <c r="H254" t="n">
         <v>7105744</v>
@@ -7764,7 +7764,7 @@
         <v>8.42500019073486</v>
       </c>
       <c r="G255" t="n">
-        <v>8.01531219482422</v>
+        <v>8.01531314849854</v>
       </c>
       <c r="H255" t="n">
         <v>7953684</v>
@@ -7822,7 +7822,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G257" t="n">
-        <v>7.96298694610596</v>
+        <v>7.96298742294312</v>
       </c>
       <c r="H257" t="n">
         <v>4473749</v>
@@ -7851,7 +7851,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G258" t="n">
-        <v>8.16277503967285</v>
+        <v>8.16277599334717</v>
       </c>
       <c r="H258" t="n">
         <v>6919849</v>
@@ -7938,7 +7938,7 @@
         <v>8.42500019073486</v>
       </c>
       <c r="G261" t="n">
-        <v>8.01531219482422</v>
+        <v>8.01531314849854</v>
       </c>
       <c r="H261" t="n">
         <v>8691609</v>
@@ -7996,7 +7996,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G263" t="n">
-        <v>7.82028150558472</v>
+        <v>7.82028198242188</v>
       </c>
       <c r="H263" t="n">
         <v>9698154</v>
@@ -8025,7 +8025,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G264" t="n">
-        <v>7.87736368179321</v>
+        <v>7.87736320495605</v>
       </c>
       <c r="H264" t="n">
         <v>8049414</v>
@@ -8054,7 +8054,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G265" t="n">
-        <v>8.04861164093018</v>
+        <v>8.04861068725586</v>
       </c>
       <c r="H265" t="n">
         <v>10193124</v>
@@ -8083,7 +8083,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G266" t="n">
-        <v>7.93444633483887</v>
+        <v>7.93444681167603</v>
       </c>
       <c r="H266" t="n">
         <v>5591385</v>
@@ -8141,7 +8141,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G268" t="n">
-        <v>8.10569381713867</v>
+        <v>8.10569286346436</v>
       </c>
       <c r="H268" t="n">
         <v>4819501</v>
@@ -8170,7 +8170,7 @@
         <v>8.375</v>
       </c>
       <c r="G269" t="n">
-        <v>7.96774387359619</v>
+        <v>7.96774482727051</v>
       </c>
       <c r="H269" t="n">
         <v>6854564</v>
@@ -8199,7 +8199,7 @@
         <v>8.3100004196167</v>
       </c>
       <c r="G270" t="n">
-        <v>7.90590572357178</v>
+        <v>7.90590524673462</v>
       </c>
       <c r="H270" t="n">
         <v>7624065</v>
@@ -8228,7 +8228,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G271" t="n">
-        <v>7.99152803421021</v>
+        <v>7.99152851104736</v>
       </c>
       <c r="H271" t="n">
         <v>15001217</v>
@@ -8257,7 +8257,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G272" t="n">
-        <v>8.04861164093018</v>
+        <v>8.04861068725586</v>
       </c>
       <c r="H272" t="n">
         <v>7357311</v>
@@ -8286,7 +8286,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G273" t="n">
-        <v>7.99152803421021</v>
+        <v>7.99152851104736</v>
       </c>
       <c r="H273" t="n">
         <v>6892052</v>
@@ -8315,7 +8315,7 @@
         <v>8.3100004196167</v>
       </c>
       <c r="G274" t="n">
-        <v>7.90590572357178</v>
+        <v>7.90590524673462</v>
       </c>
       <c r="H274" t="n">
         <v>10051498</v>
@@ -8344,7 +8344,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G275" t="n">
-        <v>7.82979440689087</v>
+        <v>7.82979536056519</v>
       </c>
       <c r="H275" t="n">
         <v>9477679</v>
@@ -8518,7 +8518,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G281" t="n">
-        <v>7.59195232391357</v>
+        <v>7.59195184707642</v>
       </c>
       <c r="H281" t="n">
         <v>6833809</v>
@@ -8634,7 +8634,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G285" t="n">
-        <v>7.79173994064331</v>
+        <v>7.79174041748047</v>
       </c>
       <c r="H285" t="n">
         <v>8180031</v>
@@ -8663,7 +8663,7 @@
         <v>8.25</v>
       </c>
       <c r="G286" t="n">
-        <v>7.84882211685181</v>
+        <v>7.84882259368896</v>
       </c>
       <c r="H286" t="n">
         <v>8035948</v>
@@ -8692,7 +8692,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G287" t="n">
-        <v>7.64903402328491</v>
+        <v>7.64903450012207</v>
       </c>
       <c r="H287" t="n">
         <v>9027559</v>
@@ -8750,7 +8750,7 @@
         <v>7.97499990463257</v>
       </c>
       <c r="G289" t="n">
-        <v>7.58719539642334</v>
+        <v>7.58719491958618</v>
       </c>
       <c r="H289" t="n">
         <v>7815676</v>
@@ -8808,7 +8808,7 @@
         <v>7.91499996185303</v>
       </c>
       <c r="G291" t="n">
-        <v>7.53011274337769</v>
+        <v>7.53011322021484</v>
       </c>
       <c r="H291" t="n">
         <v>6709166</v>
@@ -8895,7 +8895,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G294" t="n">
-        <v>7.3255672454834</v>
+        <v>7.32556772232056</v>
       </c>
       <c r="H294" t="n">
         <v>10570127</v>
@@ -8924,7 +8924,7 @@
         <v>7.59499979019165</v>
       </c>
       <c r="G295" t="n">
-        <v>7.22567319869995</v>
+        <v>7.22567367553711</v>
       </c>
       <c r="H295" t="n">
         <v>15446807</v>
@@ -9185,7 +9185,7 @@
         <v>7.79500007629395</v>
       </c>
       <c r="G304" t="n">
-        <v>7.41594839096069</v>
+        <v>7.41594791412354</v>
       </c>
       <c r="H304" t="n">
         <v>5768451</v>
@@ -9214,7 +9214,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G305" t="n">
-        <v>7.35410928726196</v>
+        <v>7.3541088104248</v>
       </c>
       <c r="H305" t="n">
         <v>8662340</v>
@@ -9243,7 +9243,7 @@
         <v>7.83500003814697</v>
       </c>
       <c r="G306" t="n">
-        <v>7.45400333404541</v>
+        <v>7.45400285720825</v>
       </c>
       <c r="H306" t="n">
         <v>8558245</v>
@@ -9359,7 +9359,7 @@
         <v>7.88500022888184</v>
       </c>
       <c r="G310" t="n">
-        <v>7.5015721321106</v>
+        <v>7.50157165527344</v>
       </c>
       <c r="H310" t="n">
         <v>9967793</v>
@@ -9475,7 +9475,7 @@
         <v>8.125</v>
       </c>
       <c r="G314" t="n">
-        <v>7.72990083694458</v>
+        <v>7.72990131378174</v>
       </c>
       <c r="H314" t="n">
         <v>8729316</v>
@@ -9562,7 +9562,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G317" t="n">
-        <v>7.93444633483887</v>
+        <v>7.93444681167603</v>
       </c>
       <c r="H317" t="n">
         <v>9638120</v>
@@ -9620,7 +9620,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G319" t="n">
-        <v>8.10569381713867</v>
+        <v>8.10569286346436</v>
       </c>
       <c r="H319" t="n">
         <v>9247079</v>
@@ -9649,7 +9649,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G320" t="n">
-        <v>8.01055526733398</v>
+        <v>8.0105562210083</v>
       </c>
       <c r="H320" t="n">
         <v>7285311</v>
@@ -9678,7 +9678,7 @@
         <v>8.45499992370605</v>
       </c>
       <c r="G321" t="n">
-        <v>8.04385471343994</v>
+        <v>8.04385375976562</v>
       </c>
       <c r="H321" t="n">
         <v>8408909</v>
@@ -9794,7 +9794,7 @@
         <v>8.13500022888184</v>
       </c>
       <c r="G325" t="n">
-        <v>7.73941516876221</v>
+        <v>7.73941469192505</v>
       </c>
       <c r="H325" t="n">
         <v>6312505</v>
@@ -9910,7 +9910,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G329" t="n">
-        <v>7.64903402328491</v>
+        <v>7.64903450012207</v>
       </c>
       <c r="H329" t="n">
         <v>5813093</v>
@@ -9939,7 +9939,7 @@
         <v>8.04500007629395</v>
       </c>
       <c r="G330" t="n">
-        <v>7.6537914276123</v>
+        <v>7.65379095077515</v>
       </c>
       <c r="H330" t="n">
         <v>5005452</v>
@@ -10084,7 +10084,7 @@
         <v>7.875</v>
       </c>
       <c r="G335" t="n">
-        <v>7.49205827713013</v>
+        <v>7.49205780029297</v>
       </c>
       <c r="H335" t="n">
         <v>7752172</v>
@@ -10142,7 +10142,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G337" t="n">
-        <v>7.87736368179321</v>
+        <v>7.87736320495605</v>
       </c>
       <c r="H337" t="n">
         <v>9607132</v>
@@ -10403,7 +10403,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G346" t="n">
-        <v>8.50527000427246</v>
+        <v>8.50526905059814</v>
       </c>
       <c r="H346" t="n">
         <v>9675664</v>
@@ -10548,7 +10548,7 @@
         <v>9.14500045776367</v>
       </c>
       <c r="G351" t="n">
-        <v>8.70030212402344</v>
+        <v>8.70030117034912</v>
       </c>
       <c r="H351" t="n">
         <v>9357770</v>
@@ -10751,7 +10751,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G358" t="n">
-        <v>8.23888492584229</v>
+        <v>8.2388858795166</v>
       </c>
       <c r="H358" t="n">
         <v>7073837</v>
@@ -10809,7 +10809,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G360" t="n">
-        <v>8.05812549591064</v>
+        <v>8.05812454223633</v>
       </c>
       <c r="H360" t="n">
         <v>6620743</v>
@@ -10838,7 +10838,7 @@
         <v>8.3100004196167</v>
       </c>
       <c r="G361" t="n">
-        <v>7.90590572357178</v>
+        <v>7.90590524673462</v>
       </c>
       <c r="H361" t="n">
         <v>14291998</v>
@@ -10896,7 +10896,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G363" t="n">
-        <v>7.93444633483887</v>
+        <v>7.93444681167603</v>
       </c>
       <c r="H363" t="n">
         <v>6865591</v>
@@ -11012,7 +11012,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G367" t="n">
-        <v>7.88687801361084</v>
+        <v>7.88687753677368</v>
       </c>
       <c r="H367" t="n">
         <v>7688881</v>
@@ -11041,7 +11041,7 @@
         <v>8.3100004196167</v>
       </c>
       <c r="G368" t="n">
-        <v>7.90590572357178</v>
+        <v>7.90590524673462</v>
       </c>
       <c r="H368" t="n">
         <v>8382176</v>
@@ -11070,7 +11070,7 @@
         <v>8.25</v>
       </c>
       <c r="G369" t="n">
-        <v>7.84882211685181</v>
+        <v>7.84882259368896</v>
       </c>
       <c r="H369" t="n">
         <v>8979733</v>
@@ -11099,7 +11099,7 @@
         <v>8.27499961853027</v>
       </c>
       <c r="G370" t="n">
-        <v>7.87260675430298</v>
+        <v>7.87260627746582</v>
       </c>
       <c r="H370" t="n">
         <v>7573261</v>
@@ -11128,7 +11128,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G371" t="n">
-        <v>7.91541862487793</v>
+        <v>7.91541814804077</v>
       </c>
       <c r="H371" t="n">
         <v>7773160</v>
@@ -11157,7 +11157,7 @@
         <v>8.33500003814697</v>
       </c>
       <c r="G372" t="n">
-        <v>7.92968940734863</v>
+        <v>7.92968988418579</v>
       </c>
       <c r="H372" t="n">
         <v>10290370</v>
@@ -11186,7 +11186,7 @@
         <v>8.25</v>
       </c>
       <c r="G373" t="n">
-        <v>7.84882211685181</v>
+        <v>7.84882259368896</v>
       </c>
       <c r="H373" t="n">
         <v>7754055</v>
@@ -11273,7 +11273,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G376" t="n">
-        <v>7.88687801361084</v>
+        <v>7.88687753677368</v>
       </c>
       <c r="H376" t="n">
         <v>5684368</v>
@@ -11302,7 +11302,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G377" t="n">
-        <v>7.91541862487793</v>
+        <v>7.91541814804077</v>
       </c>
       <c r="H377" t="n">
         <v>7730283</v>
@@ -11331,7 +11331,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G378" t="n">
-        <v>7.82979440689087</v>
+        <v>7.82979536056519</v>
       </c>
       <c r="H378" t="n">
         <v>6359602</v>
@@ -11418,7 +11418,7 @@
         <v>8.0649995803833</v>
       </c>
       <c r="G381" t="n">
-        <v>7.67281866073608</v>
+        <v>7.67281818389893</v>
       </c>
       <c r="H381" t="n">
         <v>6950390</v>
@@ -11534,7 +11534,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G385" t="n">
-        <v>7.82979440689087</v>
+        <v>7.82979536056519</v>
       </c>
       <c r="H385" t="n">
         <v>6247925</v>
@@ -11592,7 +11592,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G387" t="n">
-        <v>7.63000726699829</v>
+        <v>7.63000774383545</v>
       </c>
       <c r="H387" t="n">
         <v>5489232</v>
@@ -11621,7 +11621,7 @@
         <v>8.04500007629395</v>
       </c>
       <c r="G388" t="n">
-        <v>7.6537914276123</v>
+        <v>7.65379095077515</v>
       </c>
       <c r="H388" t="n">
         <v>6520553</v>
@@ -11708,7 +11708,7 @@
         <v>7.88500022888184</v>
       </c>
       <c r="G391" t="n">
-        <v>7.5015721321106</v>
+        <v>7.50157165527344</v>
       </c>
       <c r="H391" t="n">
         <v>13737506</v>
@@ -11766,7 +11766,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G393" t="n">
-        <v>7.86785078048706</v>
+        <v>7.8678503036499</v>
       </c>
       <c r="H393" t="n">
         <v>13345067</v>
@@ -11795,7 +11795,7 @@
         <v>8.04500007629395</v>
       </c>
       <c r="G394" t="n">
-        <v>7.6537914276123</v>
+        <v>7.65379095077515</v>
       </c>
       <c r="H394" t="n">
         <v>12204969</v>
@@ -11940,7 +11940,7 @@
         <v>8.125</v>
       </c>
       <c r="G399" t="n">
-        <v>7.72990083694458</v>
+        <v>7.72990131378174</v>
       </c>
       <c r="H399" t="n">
         <v>8832091</v>
@@ -12056,7 +12056,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G403" t="n">
-        <v>8.23888492584229</v>
+        <v>8.2388858795166</v>
       </c>
       <c r="H403" t="n">
         <v>8102311</v>
@@ -12114,7 +12114,7 @@
         <v>8.70499992370605</v>
       </c>
       <c r="G405" t="n">
-        <v>8.28169727325439</v>
+        <v>8.28169631958008</v>
       </c>
       <c r="H405" t="n">
         <v>9759736</v>
@@ -12201,7 +12201,7 @@
         <v>8.70499992370605</v>
       </c>
       <c r="G408" t="n">
-        <v>8.28169727325439</v>
+        <v>8.28169631958008</v>
       </c>
       <c r="H408" t="n">
         <v>5695609</v>
@@ -12404,7 +12404,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G415" t="n">
-        <v>8.05812549591064</v>
+        <v>8.05812454223633</v>
       </c>
       <c r="H415" t="n">
         <v>4472224</v>
@@ -12491,7 +12491,7 @@
         <v>8.33500003814697</v>
       </c>
       <c r="G418" t="n">
-        <v>7.92968940734863</v>
+        <v>7.92968988418579</v>
       </c>
       <c r="H418" t="n">
         <v>4935773</v>
@@ -12520,7 +12520,7 @@
         <v>8.27499961853027</v>
       </c>
       <c r="G419" t="n">
-        <v>7.87260675430298</v>
+        <v>7.87260627746582</v>
       </c>
       <c r="H419" t="n">
         <v>4715292</v>
@@ -12752,7 +12752,7 @@
         <v>8.04500007629395</v>
       </c>
       <c r="G427" t="n">
-        <v>7.6537914276123</v>
+        <v>7.65379095077515</v>
       </c>
       <c r="H427" t="n">
         <v>6232506</v>
@@ -12810,7 +12810,7 @@
         <v>7.83500003814697</v>
       </c>
       <c r="G429" t="n">
-        <v>7.45400333404541</v>
+        <v>7.45400285720825</v>
       </c>
       <c r="H429" t="n">
         <v>6232104</v>
@@ -12984,7 +12984,7 @@
         <v>7.88500022888184</v>
       </c>
       <c r="G435" t="n">
-        <v>7.5015721321106</v>
+        <v>7.50157165527344</v>
       </c>
       <c r="H435" t="n">
         <v>6028869</v>
@@ -13129,7 +13129,7 @@
         <v>8.02499961853027</v>
       </c>
       <c r="G440" t="n">
-        <v>7.63476324081421</v>
+        <v>7.63476371765137</v>
       </c>
       <c r="H440" t="n">
         <v>11093394</v>
@@ -13187,7 +13187,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G442" t="n">
-        <v>7.57292509078979</v>
+        <v>7.57292461395264</v>
       </c>
       <c r="H442" t="n">
         <v>6659325</v>
@@ -13274,7 +13274,7 @@
         <v>7.93499994277954</v>
       </c>
       <c r="G445" t="n">
-        <v>7.54913997650146</v>
+        <v>7.54914045333862</v>
       </c>
       <c r="H445" t="n">
         <v>4915478</v>
@@ -13332,7 +13332,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G447" t="n">
-        <v>7.59195232391357</v>
+        <v>7.59195184707642</v>
       </c>
       <c r="H447" t="n">
         <v>9449306</v>
@@ -13535,7 +13535,7 @@
         <v>7.63500022888184</v>
       </c>
       <c r="G454" t="n">
-        <v>7.26372909545898</v>
+        <v>7.26372861862183</v>
       </c>
       <c r="H454" t="n">
         <v>6637000</v>
@@ -13564,7 +13564,7 @@
         <v>7.54500007629395</v>
       </c>
       <c r="G455" t="n">
-        <v>7.17810535430908</v>
+        <v>7.17810487747192</v>
       </c>
       <c r="H455" t="n">
         <v>8006633</v>
@@ -13680,7 +13680,7 @@
         <v>7.625</v>
       </c>
       <c r="G459" t="n">
-        <v>7.25421524047852</v>
+        <v>7.25421476364136</v>
       </c>
       <c r="H459" t="n">
         <v>9352175</v>
@@ -13796,7 +13796,7 @@
         <v>7.68499994277954</v>
       </c>
       <c r="G463" t="n">
-        <v>7.31129693984985</v>
+        <v>7.31129741668701</v>
       </c>
       <c r="H463" t="n">
         <v>11433018</v>
@@ -14057,7 +14057,7 @@
         <v>7.63500022888184</v>
       </c>
       <c r="G472" t="n">
-        <v>7.26372909545898</v>
+        <v>7.26372861862183</v>
       </c>
       <c r="H472" t="n">
         <v>12393241</v>
@@ -14173,7 +14173,7 @@
         <v>7.35500001907349</v>
       </c>
       <c r="G476" t="n">
-        <v>6.99734401702881</v>
+        <v>6.99734449386597</v>
       </c>
       <c r="H476" t="n">
         <v>10343796</v>
@@ -14260,7 +14260,7 @@
         <v>6.89499998092651</v>
       </c>
       <c r="G479" t="n">
-        <v>6.5597128868103</v>
+        <v>6.55971336364746</v>
       </c>
       <c r="H479" t="n">
         <v>18049941</v>
@@ -14318,7 +14318,7 @@
         <v>6.81500005722046</v>
       </c>
       <c r="G481" t="n">
-        <v>6.48360300064087</v>
+        <v>6.48360347747803</v>
       </c>
       <c r="H481" t="n">
         <v>19321011</v>
@@ -14347,7 +14347,7 @@
         <v>6.89499998092651</v>
       </c>
       <c r="G482" t="n">
-        <v>6.5597128868103</v>
+        <v>6.55971336364746</v>
       </c>
       <c r="H482" t="n">
         <v>13873115</v>
@@ -14579,7 +14579,7 @@
         <v>7.04500007629395</v>
       </c>
       <c r="G490" t="n">
-        <v>6.70241928100586</v>
+        <v>6.7024188041687</v>
       </c>
       <c r="H490" t="n">
         <v>8224257</v>
@@ -14695,7 +14695,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G494" t="n">
-        <v>6.7166895866394</v>
+        <v>6.71668910980225</v>
       </c>
       <c r="H494" t="n">
         <v>7676027</v>
@@ -14782,7 +14782,7 @@
         <v>7.46999979019165</v>
       </c>
       <c r="G497" t="n">
-        <v>7.10675191879272</v>
+        <v>7.10675239562988</v>
       </c>
       <c r="H497" t="n">
         <v>16327353</v>
@@ -14811,7 +14811,7 @@
         <v>7.54500007629395</v>
       </c>
       <c r="G498" t="n">
-        <v>7.17810535430908</v>
+        <v>7.17810487747192</v>
       </c>
       <c r="H498" t="n">
         <v>9765474</v>
@@ -14927,7 +14927,7 @@
         <v>7.2649998664856</v>
       </c>
       <c r="G502" t="n">
-        <v>6.91172027587891</v>
+        <v>6.91172075271606</v>
       </c>
       <c r="H502" t="n">
         <v>12983601</v>
@@ -14985,7 +14985,7 @@
         <v>7.34499979019165</v>
       </c>
       <c r="G504" t="n">
-        <v>6.98783016204834</v>
+        <v>6.9878306388855</v>
       </c>
       <c r="H504" t="n">
         <v>8029365</v>
@@ -15014,7 +15014,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G505" t="n">
-        <v>7.04015636444092</v>
+        <v>7.04015588760376</v>
       </c>
       <c r="H505" t="n">
         <v>7758336</v>
@@ -15072,7 +15072,7 @@
         <v>7.34499979019165</v>
       </c>
       <c r="G507" t="n">
-        <v>6.98783016204834</v>
+        <v>6.9878306388855</v>
       </c>
       <c r="H507" t="n">
         <v>8653660</v>
@@ -15101,7 +15101,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G508" t="n">
-        <v>7.02112865447998</v>
+        <v>7.02112913131714</v>
       </c>
       <c r="H508" t="n">
         <v>5233596</v>
@@ -15159,7 +15159,7 @@
         <v>7.29500007629395</v>
       </c>
       <c r="G510" t="n">
-        <v>6.94026231765747</v>
+        <v>6.94026184082031</v>
       </c>
       <c r="H510" t="n">
         <v>4579894</v>
@@ -15188,7 +15188,7 @@
         <v>7.20499992370605</v>
       </c>
       <c r="G511" t="n">
-        <v>6.85463857650757</v>
+        <v>6.85463809967041</v>
       </c>
       <c r="H511" t="n">
         <v>4245157</v>
@@ -15217,7 +15217,7 @@
         <v>7.25500011444092</v>
       </c>
       <c r="G512" t="n">
-        <v>6.9022068977356</v>
+        <v>6.90220737457275</v>
       </c>
       <c r="H512" t="n">
         <v>6607233</v>
@@ -15246,7 +15246,7 @@
         <v>7.25</v>
       </c>
       <c r="G513" t="n">
-        <v>6.89744997024536</v>
+        <v>6.89745044708252</v>
       </c>
       <c r="H513" t="n">
         <v>5483915</v>
@@ -15275,7 +15275,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G514" t="n">
-        <v>6.98307371139526</v>
+        <v>6.98307418823242</v>
       </c>
       <c r="H514" t="n">
         <v>5974047</v>
@@ -15304,7 +15304,7 @@
         <v>7.38500022888184</v>
       </c>
       <c r="G515" t="n">
-        <v>7.02588605880737</v>
+        <v>7.02588558197021</v>
       </c>
       <c r="H515" t="n">
         <v>5887106</v>
@@ -15449,7 +15449,7 @@
         <v>7.43499994277954</v>
       </c>
       <c r="G520" t="n">
-        <v>7.07345390319824</v>
+        <v>7.0734543800354</v>
       </c>
       <c r="H520" t="n">
         <v>6198087</v>
@@ -15478,7 +15478,7 @@
         <v>7.38500022888184</v>
       </c>
       <c r="G521" t="n">
-        <v>7.02588605880737</v>
+        <v>7.02588558197021</v>
       </c>
       <c r="H521" t="n">
         <v>5952155</v>
@@ -15739,7 +15739,7 @@
         <v>7.20499992370605</v>
       </c>
       <c r="G530" t="n">
-        <v>6.85463857650757</v>
+        <v>6.85463809967041</v>
       </c>
       <c r="H530" t="n">
         <v>8180429</v>
@@ -15971,7 +15971,7 @@
         <v>7.21199989318848</v>
       </c>
       <c r="G538" t="n">
-        <v>6.86129760742188</v>
+        <v>6.86129808425903</v>
       </c>
       <c r="H538" t="n">
         <v>18503191</v>
@@ -16029,7 +16029,7 @@
         <v>6.98799991607666</v>
       </c>
       <c r="G540" t="n">
-        <v>6.64819097518921</v>
+        <v>6.64819049835205</v>
       </c>
       <c r="H540" t="n">
         <v>10998838</v>
@@ -16116,7 +16116,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G543" t="n">
-        <v>6.54544258117676</v>
+        <v>6.5454421043396</v>
       </c>
       <c r="H543" t="n">
         <v>9422768</v>
@@ -16261,7 +16261,7 @@
         <v>7.19600009918213</v>
       </c>
       <c r="G548" t="n">
-        <v>6.84607601165771</v>
+        <v>6.84607648849487</v>
       </c>
       <c r="H548" t="n">
         <v>13117904</v>
@@ -16348,7 +16348,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G551" t="n">
-        <v>7.02112865447998</v>
+        <v>7.02112913131714</v>
       </c>
       <c r="H551" t="n">
         <v>9959256</v>
@@ -16406,7 +16406,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G553" t="n">
-        <v>7.04015636444092</v>
+        <v>7.04015588760376</v>
       </c>
       <c r="H553" t="n">
         <v>10517150</v>
@@ -16435,7 +16435,7 @@
         <v>7.39799976348877</v>
       </c>
       <c r="G554" t="n">
-        <v>7.03825283050537</v>
+        <v>7.03825330734253</v>
       </c>
       <c r="H554" t="n">
         <v>10319173</v>
@@ -16464,7 +16464,7 @@
         <v>7.24599981307983</v>
       </c>
       <c r="G555" t="n">
-        <v>6.8936448097229</v>
+        <v>6.89364433288574</v>
       </c>
       <c r="H555" t="n">
         <v>12031756</v>
@@ -16493,7 +16493,7 @@
         <v>7.28800010681152</v>
       </c>
       <c r="G556" t="n">
-        <v>6.93360233306885</v>
+        <v>6.93360280990601</v>
       </c>
       <c r="H556" t="n">
         <v>9797279</v>
@@ -16580,7 +16580,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G559" t="n">
-        <v>7.82979440689087</v>
+        <v>7.82979536056519</v>
       </c>
       <c r="H559" t="n">
         <v>38979913</v>
@@ -16609,7 +16609,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G560" t="n">
-        <v>7.91541862487793</v>
+        <v>7.91541814804077</v>
       </c>
       <c r="H560" t="n">
         <v>29766429</v>
@@ -16638,7 +16638,7 @@
         <v>8.20199966430664</v>
       </c>
       <c r="G561" t="n">
-        <v>7.80315637588501</v>
+        <v>7.80315589904785</v>
       </c>
       <c r="H561" t="n">
         <v>15070704</v>
@@ -16667,7 +16667,7 @@
         <v>8.00800037384033</v>
       </c>
       <c r="G562" t="n">
-        <v>7.61859083175659</v>
+        <v>7.61859130859375</v>
       </c>
       <c r="H562" t="n">
         <v>17830195</v>
@@ -16696,7 +16696,7 @@
         <v>7.83199977874756</v>
       </c>
       <c r="G563" t="n">
-        <v>7.45114898681641</v>
+        <v>7.45114850997925</v>
       </c>
       <c r="H563" t="n">
         <v>15531686</v>
@@ -16754,7 +16754,7 @@
         <v>8.08800029754639</v>
       </c>
       <c r="G565" t="n">
-        <v>7.69470024108887</v>
+        <v>7.69470071792603</v>
       </c>
       <c r="H565" t="n">
         <v>13814697</v>
@@ -16783,7 +16783,7 @@
         <v>8.11600017547607</v>
       </c>
       <c r="G566" t="n">
-        <v>7.72133874893188</v>
+        <v>7.72133922576904</v>
       </c>
       <c r="H566" t="n">
         <v>11221597</v>
@@ -16899,7 +16899,7 @@
         <v>7.72599983215332</v>
       </c>
       <c r="G570" t="n">
-        <v>7.35030364990234</v>
+        <v>7.35030317306519</v>
       </c>
       <c r="H570" t="n">
         <v>11293097</v>
@@ -16957,7 +16957,7 @@
         <v>7.61399984359741</v>
       </c>
       <c r="G572" t="n">
-        <v>7.24374961853027</v>
+        <v>7.24375009536743</v>
       </c>
       <c r="H572" t="n">
         <v>8793021</v>
@@ -17073,7 +17073,7 @@
         <v>7.58199977874756</v>
       </c>
       <c r="G576" t="n">
-        <v>7.21330595016479</v>
+        <v>7.21330547332764</v>
       </c>
       <c r="H576" t="n">
         <v>7516325</v>
@@ -17247,7 +17247,7 @@
         <v>8.61200046539307</v>
       </c>
       <c r="G582" t="n">
-        <v>8.19321918487549</v>
+        <v>8.1932201385498</v>
       </c>
       <c r="H582" t="n">
         <v>21024100</v>
@@ -17334,7 +17334,7 @@
         <v>8.38199996948242</v>
       </c>
       <c r="G585" t="n">
-        <v>7.97440385818481</v>
+        <v>7.97440338134766</v>
       </c>
       <c r="H585" t="n">
         <v>16885220</v>
@@ -17421,7 +17421,7 @@
         <v>8.76200008392334</v>
       </c>
       <c r="G588" t="n">
-        <v>8.33592510223389</v>
+        <v>8.3359260559082</v>
       </c>
       <c r="H588" t="n">
         <v>19699701</v>
@@ -17450,7 +17450,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G589" t="n">
-        <v>8.27694034576416</v>
+        <v>8.27693939208984</v>
       </c>
       <c r="H589" t="n">
         <v>14602170</v>
@@ -17508,7 +17508,7 @@
         <v>8.26200008392334</v>
       </c>
       <c r="G591" t="n">
-        <v>7.86023902893066</v>
+        <v>7.86023950576782</v>
       </c>
       <c r="H591" t="n">
         <v>15384354</v>
@@ -17653,7 +17653,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G596" t="n">
-        <v>7.96298694610596</v>
+        <v>7.96298742294312</v>
       </c>
       <c r="H596" t="n">
         <v>11477450</v>
@@ -17740,7 +17740,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G599" t="n">
-        <v>8.01055526733398</v>
+        <v>8.0105562210083</v>
       </c>
       <c r="H599" t="n">
         <v>20166769</v>
@@ -17769,7 +17769,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G600" t="n">
-        <v>7.88687801361084</v>
+        <v>7.88687753677368</v>
       </c>
       <c r="H600" t="n">
         <v>10308492</v>
@@ -17914,7 +17914,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G605" t="n">
-        <v>7.35410928726196</v>
+        <v>7.3541088104248</v>
       </c>
       <c r="H605" t="n">
         <v>19807914</v>
@@ -17943,7 +17943,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G606" t="n">
-        <v>7.30654001235962</v>
+        <v>7.30654048919678</v>
       </c>
       <c r="H606" t="n">
         <v>13820402</v>
@@ -18030,7 +18030,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G609" t="n">
-        <v>7.02112865447998</v>
+        <v>7.02112913131714</v>
       </c>
       <c r="H609" t="n">
         <v>12987765</v>
@@ -18059,7 +18059,7 @@
         <v>7.31199979782104</v>
       </c>
       <c r="G610" t="n">
-        <v>6.95643520355225</v>
+        <v>6.95643472671509</v>
       </c>
       <c r="H610" t="n">
         <v>9821711</v>
@@ -18088,7 +18088,7 @@
         <v>7.30999994277954</v>
       </c>
       <c r="G611" t="n">
-        <v>6.95453262329102</v>
+        <v>6.95453214645386</v>
       </c>
       <c r="H611" t="n">
         <v>10969407</v>
@@ -18146,7 +18146,7 @@
         <v>7.14400005340576</v>
       </c>
       <c r="G613" t="n">
-        <v>6.7966046333313</v>
+        <v>6.79660511016846</v>
       </c>
       <c r="H613" t="n">
         <v>15383630</v>
@@ -18204,7 +18204,7 @@
         <v>7.01599979400635</v>
       </c>
       <c r="G615" t="n">
-        <v>6.67482852935791</v>
+        <v>6.67482900619507</v>
       </c>
       <c r="H615" t="n">
         <v>10762161</v>
@@ -18233,7 +18233,7 @@
         <v>6.87200021743774</v>
       </c>
       <c r="G616" t="n">
-        <v>6.53783130645752</v>
+        <v>6.53783178329468</v>
       </c>
       <c r="H616" t="n">
         <v>13644902</v>
@@ -18291,7 +18291,7 @@
         <v>6.98600006103516</v>
       </c>
       <c r="G618" t="n">
-        <v>6.64628791809082</v>
+        <v>6.64628839492798</v>
       </c>
       <c r="H618" t="n">
         <v>6146232</v>
@@ -18349,7 +18349,7 @@
         <v>6.91599988937378</v>
       </c>
       <c r="G620" t="n">
-        <v>6.57969188690186</v>
+        <v>6.5796914100647</v>
       </c>
       <c r="H620" t="n">
         <v>11484221</v>
@@ -18407,7 +18407,7 @@
         <v>6.72200012207031</v>
       </c>
       <c r="G622" t="n">
-        <v>6.39512586593628</v>
+        <v>6.39512538909912</v>
       </c>
       <c r="H622" t="n">
         <v>8616778</v>
@@ -18436,7 +18436,7 @@
         <v>6.87200021743774</v>
       </c>
       <c r="G623" t="n">
-        <v>6.53783130645752</v>
+        <v>6.53783178329468</v>
       </c>
       <c r="H623" t="n">
         <v>11592172</v>
@@ -18465,7 +18465,7 @@
         <v>6.85799980163574</v>
       </c>
       <c r="G624" t="n">
-        <v>6.52451181411743</v>
+        <v>6.52451229095459</v>
       </c>
       <c r="H624" t="n">
         <v>6763306</v>
@@ -18552,7 +18552,7 @@
         <v>6.7519998550415</v>
       </c>
       <c r="G627" t="n">
-        <v>6.42366647720337</v>
+        <v>6.42366695404053</v>
       </c>
       <c r="H627" t="n">
         <v>11827362</v>
@@ -18581,7 +18581,7 @@
         <v>6.76599979400635</v>
       </c>
       <c r="G628" t="n">
-        <v>6.4369854927063</v>
+        <v>6.43698596954346</v>
       </c>
       <c r="H628" t="n">
         <v>9517293</v>
@@ -18668,7 +18668,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G631" t="n">
-        <v>6.33614015579224</v>
+        <v>6.33614063262939</v>
       </c>
       <c r="H631" t="n">
         <v>8779408</v>
@@ -18784,7 +18784,7 @@
         <v>6.45599985122681</v>
       </c>
       <c r="G635" t="n">
-        <v>6.14206075668335</v>
+        <v>6.14206027984619</v>
       </c>
       <c r="H635" t="n">
         <v>13273047</v>
@@ -18842,7 +18842,7 @@
         <v>6.37400007247925</v>
       </c>
       <c r="G637" t="n">
-        <v>6.06404781341553</v>
+        <v>6.06404829025269</v>
       </c>
       <c r="H637" t="n">
         <v>8023540</v>
@@ -18871,7 +18871,7 @@
         <v>6.28200006484985</v>
       </c>
       <c r="G638" t="n">
-        <v>5.97652149200439</v>
+        <v>5.97652196884155</v>
       </c>
       <c r="H638" t="n">
         <v>5846091</v>
@@ -18929,7 +18929,7 @@
         <v>6.52400016784668</v>
       </c>
       <c r="G640" t="n">
-        <v>6.20675420761108</v>
+        <v>6.20675373077393</v>
       </c>
       <c r="H640" t="n">
         <v>5707740</v>
@@ -18987,7 +18987,7 @@
         <v>6.55200004577637</v>
       </c>
       <c r="G642" t="n">
-        <v>6.2333927154541</v>
+        <v>6.23339223861694</v>
       </c>
       <c r="H642" t="n">
         <v>6589583</v>
@@ -19045,7 +19045,7 @@
         <v>6.36600017547607</v>
       </c>
       <c r="G644" t="n">
-        <v>6.05643749237061</v>
+        <v>6.05643701553345</v>
       </c>
       <c r="H644" t="n">
         <v>10253469</v>
@@ -19074,7 +19074,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G645" t="n">
-        <v>6.01267385482788</v>
+        <v>6.01267433166504</v>
       </c>
       <c r="H645" t="n">
         <v>7151777</v>
@@ -19103,7 +19103,7 @@
         <v>6.14599990844727</v>
       </c>
       <c r="G646" t="n">
-        <v>5.84713506698608</v>
+        <v>5.84713459014893</v>
       </c>
       <c r="H646" t="n">
         <v>10297948</v>
@@ -19161,7 +19161,7 @@
         <v>6.07399988174438</v>
       </c>
       <c r="G648" t="n">
-        <v>5.77863645553589</v>
+        <v>5.77863597869873</v>
       </c>
       <c r="H648" t="n">
         <v>9314960</v>
@@ -19451,7 +19451,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G658" t="n">
-        <v>6.2790584564209</v>
+        <v>6.27905797958374</v>
       </c>
       <c r="H658" t="n">
         <v>10357178</v>
@@ -19509,7 +19509,7 @@
         <v>6.50400018692017</v>
       </c>
       <c r="G660" t="n">
-        <v>6.1877269744873</v>
+        <v>6.18772649765015</v>
       </c>
       <c r="H660" t="n">
         <v>7068352</v>
@@ -19538,7 +19538,7 @@
         <v>6.38199996948242</v>
       </c>
       <c r="G661" t="n">
-        <v>6.07165908813477</v>
+        <v>6.07165861129761</v>
       </c>
       <c r="H661" t="n">
         <v>7651712</v>
@@ -19944,7 +19944,7 @@
         <v>6</v>
       </c>
       <c r="G675" t="n">
-        <v>5.70823431015015</v>
+        <v>5.7082347869873</v>
       </c>
       <c r="H675" t="n">
         <v>8439947</v>
@@ -19973,7 +19973,7 @@
         <v>5.98799991607666</v>
       </c>
       <c r="G676" t="n">
-        <v>5.69681835174561</v>
+        <v>5.69681787490845</v>
       </c>
       <c r="H676" t="n">
         <v>6952501</v>
@@ -20002,7 +20002,7 @@
         <v>6.0019998550415</v>
       </c>
       <c r="G677" t="n">
-        <v>5.71013736724854</v>
+        <v>5.71013689041138</v>
       </c>
       <c r="H677" t="n">
         <v>3495139</v>
@@ -20031,7 +20031,7 @@
         <v>5.93800020217896</v>
       </c>
       <c r="G678" t="n">
-        <v>5.64924955368042</v>
+        <v>5.64925003051758</v>
       </c>
       <c r="H678" t="n">
         <v>6479576</v>
@@ -20118,7 +20118,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G681" t="n">
-        <v>5.22303485870361</v>
+        <v>5.22303438186646</v>
       </c>
       <c r="H681" t="n">
         <v>21485023</v>
@@ -20147,7 +20147,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G682" t="n">
-        <v>5.28011703491211</v>
+        <v>5.28011751174927</v>
       </c>
       <c r="H682" t="n">
         <v>7364755</v>
@@ -20176,7 +20176,7 @@
         <v>5.25</v>
       </c>
       <c r="G683" t="n">
-        <v>4.99470567703247</v>
+        <v>4.99470520019531</v>
       </c>
       <c r="H683" t="n">
         <v>33784406</v>
@@ -20350,7 +20350,7 @@
         <v>5.4060001373291</v>
       </c>
       <c r="G689" t="n">
-        <v>5.14311933517456</v>
+        <v>5.14311981201172</v>
       </c>
       <c r="H689" t="n">
         <v>9097960</v>
@@ -20466,7 +20466,7 @@
         <v>5.71400022506714</v>
       </c>
       <c r="G693" t="n">
-        <v>5.4361424446106</v>
+        <v>5.43614196777344</v>
       </c>
       <c r="H693" t="n">
         <v>14951668</v>
@@ -20524,7 +20524,7 @@
         <v>5.68599987030029</v>
       </c>
       <c r="G695" t="n">
-        <v>5.40950393676758</v>
+        <v>5.40950345993042</v>
       </c>
       <c r="H695" t="n">
         <v>8514680</v>
@@ -20553,7 +20553,7 @@
         <v>5.68599987030029</v>
       </c>
       <c r="G696" t="n">
-        <v>5.40950393676758</v>
+        <v>5.40950345993042</v>
       </c>
       <c r="H696" t="n">
         <v>11073700</v>
@@ -20582,7 +20582,7 @@
         <v>5.60599994659424</v>
       </c>
       <c r="G697" t="n">
-        <v>5.33339405059814</v>
+        <v>5.33339357376099</v>
       </c>
       <c r="H697" t="n">
         <v>9256009</v>
@@ -20611,7 +20611,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G698" t="n">
-        <v>5.30865859985352</v>
+        <v>5.30865812301636</v>
       </c>
       <c r="H698" t="n">
         <v>8345160</v>
@@ -20727,7 +20727,7 @@
         <v>4.95300006866455</v>
       </c>
       <c r="G702" t="n">
-        <v>4.71214818954468</v>
+        <v>4.71214771270752</v>
       </c>
       <c r="H702" t="n">
         <v>21571910</v>
@@ -20814,7 +20814,7 @@
         <v>4.95699977874756</v>
       </c>
       <c r="G705" t="n">
-        <v>4.71595287322998</v>
+        <v>4.71595335006714</v>
       </c>
       <c r="H705" t="n">
         <v>12269784</v>
@@ -20930,7 +20930,7 @@
         <v>5.03200006484985</v>
       </c>
       <c r="G709" t="n">
-        <v>4.78730630874634</v>
+        <v>4.78730583190918</v>
       </c>
       <c r="H709" t="n">
         <v>16574528</v>
@@ -20959,7 +20959,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G710" t="n">
-        <v>4.77588987350464</v>
+        <v>4.77588939666748</v>
       </c>
       <c r="H710" t="n">
         <v>13466859</v>
@@ -21133,7 +21133,7 @@
         <v>4.98600006103516</v>
       </c>
       <c r="G716" t="n">
-        <v>4.74354267120361</v>
+        <v>4.74354314804077</v>
       </c>
       <c r="H716" t="n">
         <v>11883638</v>
@@ -21365,7 +21365,7 @@
         <v>5.19199991226196</v>
       </c>
       <c r="G724" t="n">
-        <v>4.93952560424805</v>
+        <v>4.93952608108521</v>
       </c>
       <c r="H724" t="n">
         <v>11611382</v>
@@ -21452,7 +21452,7 @@
         <v>5.35400009155273</v>
       </c>
       <c r="G727" t="n">
-        <v>5.09364795684814</v>
+        <v>5.0936484336853</v>
       </c>
       <c r="H727" t="n">
         <v>5004868</v>
@@ -21510,7 +21510,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G729" t="n">
-        <v>5.08984231948853</v>
+        <v>5.08984279632568</v>
       </c>
       <c r="H729" t="n">
         <v>4502292</v>
@@ -21568,7 +21568,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G731" t="n">
-        <v>4.90908193588257</v>
+        <v>4.90908145904541</v>
       </c>
       <c r="H731" t="n">
         <v>20215708</v>
@@ -21597,7 +21597,7 @@
         <v>5.30399990081787</v>
       </c>
       <c r="G732" t="n">
-        <v>5.04607963562012</v>
+        <v>5.04607915878296</v>
       </c>
       <c r="H732" t="n">
         <v>21192969</v>
@@ -21655,7 +21655,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G734" t="n">
-        <v>4.9566502571106</v>
+        <v>4.95665073394775</v>
       </c>
       <c r="H734" t="n">
         <v>13016824</v>
@@ -21684,7 +21684,7 @@
         <v>5.16400003433228</v>
       </c>
       <c r="G735" t="n">
-        <v>4.91288757324219</v>
+        <v>4.91288709640503</v>
       </c>
       <c r="H735" t="n">
         <v>7858565</v>
@@ -21713,7 +21713,7 @@
         <v>5.26200008392334</v>
       </c>
       <c r="G736" t="n">
-        <v>5.00612163543701</v>
+        <v>5.00612211227417</v>
       </c>
       <c r="H736" t="n">
         <v>9329889</v>
@@ -22032,7 +22032,7 @@
         <v>5.74599981307983</v>
       </c>
       <c r="G747" t="n">
-        <v>5.46658563613892</v>
+        <v>5.46658611297607</v>
       </c>
       <c r="H747" t="n">
         <v>8767299</v>
@@ -22061,7 +22061,7 @@
         <v>5.69199991226196</v>
       </c>
       <c r="G748" t="n">
-        <v>5.41521167755127</v>
+        <v>5.41521215438843</v>
       </c>
       <c r="H748" t="n">
         <v>5268321</v>
@@ -22235,7 +22235,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G754" t="n">
-        <v>5.42282295227051</v>
+        <v>5.42282247543335</v>
       </c>
       <c r="H754" t="n">
         <v>8739136</v>
@@ -22380,7 +22380,7 @@
         <v>5.4520001411438</v>
       </c>
       <c r="G759" t="n">
-        <v>5.18688297271729</v>
+        <v>5.18688249588013</v>
       </c>
       <c r="H759" t="n">
         <v>9181301</v>
@@ -22409,7 +22409,7 @@
         <v>5.2020001411438</v>
       </c>
       <c r="G760" t="n">
-        <v>4.94903993606567</v>
+        <v>4.94903945922852</v>
       </c>
       <c r="H760" t="n">
         <v>11959404</v>
@@ -22467,7 +22467,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G762" t="n">
-        <v>4.58561563491821</v>
+        <v>4.58561515808105</v>
       </c>
       <c r="H762" t="n">
         <v>10213287</v>
@@ -22496,7 +22496,7 @@
         <v>4.83300018310547</v>
       </c>
       <c r="G763" t="n">
-        <v>4.59798288345337</v>
+        <v>4.59798336029053</v>
       </c>
       <c r="H763" t="n">
         <v>6812527</v>
@@ -22641,7 +22641,7 @@
         <v>5.06199979782104</v>
       </c>
       <c r="G768" t="n">
-        <v>4.81584692001343</v>
+        <v>4.81584739685059</v>
       </c>
       <c r="H768" t="n">
         <v>6948538</v>
@@ -22670,7 +22670,7 @@
         <v>4.95900011062622</v>
       </c>
       <c r="G769" t="n">
-        <v>4.71785593032837</v>
+        <v>4.71785640716553</v>
       </c>
       <c r="H769" t="n">
         <v>10542869</v>
@@ -22728,7 +22728,7 @@
         <v>5.00600004196167</v>
       </c>
       <c r="G771" t="n">
-        <v>4.76257085800171</v>
+        <v>4.76257038116455</v>
       </c>
       <c r="H771" t="n">
         <v>7037218</v>
@@ -22757,7 +22757,7 @@
         <v>5.01599979400635</v>
       </c>
       <c r="G772" t="n">
-        <v>4.77208423614502</v>
+        <v>4.77208375930786</v>
       </c>
       <c r="H772" t="n">
         <v>5703804</v>
@@ -22786,7 +22786,7 @@
         <v>5.02400016784668</v>
       </c>
       <c r="G773" t="n">
-        <v>4.7796950340271</v>
+        <v>4.77969551086426</v>
       </c>
       <c r="H773" t="n">
         <v>5160678</v>
@@ -22873,7 +22873,7 @@
         <v>4.88500022888184</v>
       </c>
       <c r="G776" t="n">
-        <v>4.64745426177979</v>
+        <v>4.64745473861694</v>
       </c>
       <c r="H776" t="n">
         <v>41676407</v>
@@ -22960,7 +22960,7 @@
         <v>4.48400020599365</v>
       </c>
       <c r="G779" t="n">
-        <v>4.26595449447632</v>
+        <v>4.26595401763916</v>
       </c>
       <c r="H779" t="n">
         <v>18215988</v>
@@ -22989,7 +22989,7 @@
         <v>4.52899980545044</v>
       </c>
       <c r="G780" t="n">
-        <v>4.30876541137695</v>
+        <v>4.30876588821411</v>
       </c>
       <c r="H780" t="n">
         <v>16117024</v>
@@ -23076,7 +23076,7 @@
         <v>4.58199977874756</v>
       </c>
       <c r="G783" t="n">
-        <v>4.35918807983398</v>
+        <v>4.35918855667114</v>
       </c>
       <c r="H783" t="n">
         <v>7847751</v>
@@ -23105,7 +23105,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G784" t="n">
-        <v>4.40485429763794</v>
+        <v>4.4048547744751</v>
       </c>
       <c r="H784" t="n">
         <v>11137135</v>
@@ -23221,7 +23221,7 @@
         <v>5.02400016784668</v>
       </c>
       <c r="G788" t="n">
-        <v>4.7796950340271</v>
+        <v>4.77969551086426</v>
       </c>
       <c r="H788" t="n">
         <v>9181552</v>
@@ -23308,7 +23308,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G791" t="n">
-        <v>4.49047756195068</v>
+        <v>4.49047803878784</v>
       </c>
       <c r="H791" t="n">
         <v>10923993</v>
@@ -23366,7 +23366,7 @@
         <v>4.81599998474121</v>
       </c>
       <c r="G793" t="n">
-        <v>4.58180952072144</v>
+        <v>4.58180999755859</v>
       </c>
       <c r="H793" t="n">
         <v>6859684</v>
@@ -23424,7 +23424,7 @@
         <v>4.8270001411438</v>
       </c>
       <c r="G795" t="n">
-        <v>4.59227466583252</v>
+        <v>4.59227514266968</v>
       </c>
       <c r="H795" t="n">
         <v>10108349</v>
@@ -23482,7 +23482,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G797" t="n">
-        <v>5.0422739982605</v>
+        <v>5.04227447509766</v>
       </c>
       <c r="H797" t="n">
         <v>14228495</v>
@@ -23627,7 +23627,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G802" t="n">
-        <v>5.09935665130615</v>
+        <v>5.09935617446899</v>
       </c>
       <c r="H802" t="n">
         <v>13548252</v>
@@ -23743,7 +23743,7 @@
         <v>5.32200002670288</v>
       </c>
       <c r="G806" t="n">
-        <v>5.06320428848267</v>
+        <v>5.06320381164551</v>
       </c>
       <c r="H806" t="n">
         <v>10595102</v>
@@ -23801,7 +23801,7 @@
         <v>5.5</v>
       </c>
       <c r="G808" t="n">
-        <v>5.23254871368408</v>
+        <v>5.23254823684692</v>
       </c>
       <c r="H808" t="n">
         <v>15904611</v>
@@ -23830,7 +23830,7 @@
         <v>5.64799976348877</v>
       </c>
       <c r="G809" t="n">
-        <v>5.37335157394409</v>
+        <v>5.37335109710693</v>
       </c>
       <c r="H809" t="n">
         <v>20711461</v>
@@ -23859,7 +23859,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G810" t="n">
-        <v>5.33719968795776</v>
+        <v>5.33719921112061</v>
       </c>
       <c r="H810" t="n">
         <v>21767982</v>
@@ -24091,7 +24091,7 @@
         <v>5.35599994659424</v>
       </c>
       <c r="G818" t="n">
-        <v>5.09555101394653</v>
+        <v>5.09555053710938</v>
       </c>
       <c r="H818" t="n">
         <v>10767173</v>
@@ -24149,7 +24149,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G820" t="n">
-        <v>5.0422739982605</v>
+        <v>5.04227447509766</v>
       </c>
       <c r="H820" t="n">
         <v>6355484</v>
@@ -24178,7 +24178,7 @@
         <v>5.25799989700317</v>
       </c>
       <c r="G821" t="n">
-        <v>5.00231599807739</v>
+        <v>5.00231647491455</v>
       </c>
       <c r="H821" t="n">
         <v>8320301</v>
@@ -24236,7 +24236,7 @@
         <v>5.31599998474121</v>
       </c>
       <c r="G823" t="n">
-        <v>5.05749559402466</v>
+        <v>5.05749607086182</v>
       </c>
       <c r="H823" t="n">
         <v>5741634</v>
@@ -24265,7 +24265,7 @@
         <v>5.35599994659424</v>
       </c>
       <c r="G824" t="n">
-        <v>5.09555101394653</v>
+        <v>5.09555053710938</v>
       </c>
       <c r="H824" t="n">
         <v>7192964</v>
@@ -24294,7 +24294,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G825" t="n">
-        <v>5.14692497253418</v>
+        <v>5.14692449569702</v>
       </c>
       <c r="H825" t="n">
         <v>6837351</v>
@@ -24381,7 +24381,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G828" t="n">
-        <v>5.08984231948853</v>
+        <v>5.08984279632568</v>
       </c>
       <c r="H828" t="n">
         <v>11314863</v>
@@ -24410,7 +24410,7 @@
         <v>5.40199995040894</v>
       </c>
       <c r="G829" t="n">
-        <v>5.13931369781494</v>
+        <v>5.1393141746521</v>
       </c>
       <c r="H829" t="n">
         <v>9915940</v>
@@ -24468,7 +24468,7 @@
         <v>5.36800003051758</v>
       </c>
       <c r="G831" t="n">
-        <v>5.10696697235107</v>
+        <v>5.10696744918823</v>
       </c>
       <c r="H831" t="n">
         <v>8336278</v>
@@ -24497,7 +24497,7 @@
         <v>5.33599996566772</v>
       </c>
       <c r="G832" t="n">
-        <v>5.0765233039856</v>
+        <v>5.07652378082275</v>
       </c>
       <c r="H832" t="n">
         <v>10088831</v>
@@ -24526,7 +24526,7 @@
         <v>5.34899997711182</v>
       </c>
       <c r="G833" t="n">
-        <v>5.08889102935791</v>
+        <v>5.08889150619507</v>
       </c>
       <c r="H833" t="n">
         <v>6378866</v>
@@ -24671,7 +24671,7 @@
         <v>5.25500011444092</v>
       </c>
       <c r="G838" t="n">
-        <v>4.99946260452271</v>
+        <v>4.99946212768555</v>
       </c>
       <c r="H838" t="n">
         <v>4873965</v>
@@ -24903,7 +24903,7 @@
         <v>4.98600006103516</v>
       </c>
       <c r="G846" t="n">
-        <v>4.74354267120361</v>
+        <v>4.74354314804077</v>
       </c>
       <c r="H846" t="n">
         <v>4443838</v>
@@ -24932,7 +24932,7 @@
         <v>4.95900011062622</v>
       </c>
       <c r="G847" t="n">
-        <v>4.71785593032837</v>
+        <v>4.71785640716553</v>
       </c>
       <c r="H847" t="n">
         <v>6501356</v>
@@ -25106,7 +25106,7 @@
         <v>4.67199993133545</v>
       </c>
       <c r="G853" t="n">
-        <v>4.44481182098389</v>
+        <v>4.44481229782104</v>
       </c>
       <c r="H853" t="n">
         <v>6493676</v>
@@ -25193,7 +25193,7 @@
         <v>4.45800018310547</v>
       </c>
       <c r="G856" t="n">
-        <v>4.24121856689453</v>
+        <v>4.24121809005737</v>
       </c>
       <c r="H856" t="n">
         <v>16786730</v>
@@ -25280,7 +25280,7 @@
         <v>4.57800006866455</v>
       </c>
       <c r="G859" t="n">
-        <v>4.35538291931152</v>
+        <v>4.35538339614868</v>
       </c>
       <c r="H859" t="n">
         <v>8359793</v>
@@ -25396,7 +25396,7 @@
         <v>4.38100004196167</v>
       </c>
       <c r="G863" t="n">
-        <v>4.16796255111694</v>
+        <v>4.1679630279541</v>
       </c>
       <c r="H863" t="n">
         <v>10295663</v>
@@ -25599,7 +25599,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G870" t="n">
-        <v>4.32398748397827</v>
+        <v>4.32398796081543</v>
       </c>
       <c r="H870" t="n">
         <v>10022461</v>
@@ -25802,7 +25802,7 @@
         <v>4.63100004196167</v>
       </c>
       <c r="G877" t="n">
-        <v>4.40580558776855</v>
+        <v>4.40580606460571</v>
       </c>
       <c r="H877" t="n">
         <v>6029498</v>
@@ -25947,7 +25947,7 @@
         <v>4.84200000762939</v>
       </c>
       <c r="G882" t="n">
-        <v>4.60654497146606</v>
+        <v>4.60654544830322</v>
       </c>
       <c r="H882" t="n">
         <v>15402357</v>
@@ -25976,7 +25976,7 @@
         <v>5.00899982452393</v>
       </c>
       <c r="G883" t="n">
-        <v>4.7654242515564</v>
+        <v>4.76542472839355</v>
       </c>
       <c r="H883" t="n">
         <v>21769809</v>
@@ -26150,7 +26150,7 @@
         <v>4.82800006866455</v>
       </c>
       <c r="G889" t="n">
-        <v>4.59322595596313</v>
+        <v>4.59322643280029</v>
       </c>
       <c r="H889" t="n">
         <v>7098552</v>
@@ -26179,7 +26179,7 @@
         <v>4.78299999237061</v>
       </c>
       <c r="G890" t="n">
-        <v>4.55041456222534</v>
+        <v>4.55041408538818</v>
       </c>
       <c r="H890" t="n">
         <v>4787528</v>
@@ -26208,7 +26208,7 @@
         <v>4.92199993133545</v>
       </c>
       <c r="G891" t="n">
-        <v>4.6826548576355</v>
+        <v>4.68265533447266</v>
       </c>
       <c r="H891" t="n">
         <v>9003798</v>
@@ -26266,7 +26266,7 @@
         <v>4.96299982070923</v>
       </c>
       <c r="G893" t="n">
-        <v>4.72166156768799</v>
+        <v>4.72166109085083</v>
       </c>
       <c r="H893" t="n">
         <v>6516566</v>
@@ -26411,7 +26411,7 @@
         <v>5.01300001144409</v>
       </c>
       <c r="G898" t="n">
-        <v>4.76922988891602</v>
+        <v>4.76923036575317</v>
       </c>
       <c r="H898" t="n">
         <v>5422412</v>
@@ -26527,7 +26527,7 @@
         <v>5.06099987030029</v>
       </c>
       <c r="G902" t="n">
-        <v>4.81489562988281</v>
+        <v>4.81489610671997</v>
       </c>
       <c r="H902" t="n">
         <v>4829287</v>
@@ -26556,7 +26556,7 @@
         <v>4.91099977493286</v>
       </c>
       <c r="G903" t="n">
-        <v>4.67219018936157</v>
+        <v>4.67218971252441</v>
       </c>
       <c r="H903" t="n">
         <v>8017443</v>
@@ -26614,7 +26614,7 @@
         <v>4.95699977874756</v>
       </c>
       <c r="G905" t="n">
-        <v>4.71595287322998</v>
+        <v>4.71595335006714</v>
       </c>
       <c r="H905" t="n">
         <v>5337026</v>
@@ -26730,7 +26730,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G909" t="n">
-        <v>4.985191822052</v>
+        <v>4.98519134521484</v>
       </c>
       <c r="H909" t="n">
         <v>10810457</v>
@@ -26788,7 +26788,7 @@
         <v>5.10599994659424</v>
       </c>
       <c r="G911" t="n">
-        <v>4.85770797729492</v>
+        <v>4.85770750045776</v>
       </c>
       <c r="H911" t="n">
         <v>5112107</v>
@@ -26846,7 +26846,7 @@
         <v>4.99599981307983</v>
       </c>
       <c r="G913" t="n">
-        <v>4.75305700302124</v>
+        <v>4.75305652618408</v>
       </c>
       <c r="H913" t="n">
         <v>6486219</v>
@@ -26904,7 +26904,7 @@
         <v>4.83400011062622</v>
       </c>
       <c r="G915" t="n">
-        <v>4.59893465042114</v>
+        <v>4.59893417358398</v>
       </c>
       <c r="H915" t="n">
         <v>6262907</v>
@@ -26933,7 +26933,7 @@
         <v>4.81599998474121</v>
       </c>
       <c r="G916" t="n">
-        <v>4.58180952072144</v>
+        <v>4.58180999755859</v>
       </c>
       <c r="H916" t="n">
         <v>4733278</v>
@@ -26962,7 +26962,7 @@
         <v>4.88800001144409</v>
       </c>
       <c r="G917" t="n">
-        <v>4.65030860900879</v>
+        <v>4.65030813217163</v>
       </c>
       <c r="H917" t="n">
         <v>5260695</v>
@@ -26991,7 +26991,7 @@
         <v>4.60200023651123</v>
       </c>
       <c r="G918" t="n">
-        <v>4.37821626663208</v>
+        <v>4.37821578979492</v>
       </c>
       <c r="H918" t="n">
         <v>11153136</v>
@@ -27136,7 +27136,7 @@
         <v>4.56500005722046</v>
       </c>
       <c r="G923" t="n">
-        <v>4.34301567077637</v>
+        <v>4.34301519393921</v>
       </c>
       <c r="H923" t="n">
         <v>5051334</v>
@@ -27165,7 +27165,7 @@
         <v>4.47200012207031</v>
       </c>
       <c r="G924" t="n">
-        <v>4.25453758239746</v>
+        <v>4.25453805923462</v>
       </c>
       <c r="H924" t="n">
         <v>5236518</v>
@@ -27223,7 +27223,7 @@
         <v>4.59800004959106</v>
       </c>
       <c r="G926" t="n">
-        <v>4.3744101524353</v>
+        <v>4.37441062927246</v>
       </c>
       <c r="H926" t="n">
         <v>5193190</v>
@@ -27252,7 +27252,7 @@
         <v>4.52600002288818</v>
       </c>
       <c r="G927" t="n">
-        <v>4.30591154098511</v>
+        <v>4.30591201782227</v>
       </c>
       <c r="H927" t="n">
         <v>4843476</v>
@@ -27484,7 +27484,7 @@
         <v>4.92600011825562</v>
       </c>
       <c r="G935" t="n">
-        <v>4.68646097183228</v>
+        <v>4.68646049499512</v>
       </c>
       <c r="H935" t="n">
         <v>7598993</v>
@@ -27513,7 +27513,7 @@
         <v>4.91800022125244</v>
       </c>
       <c r="G936" t="n">
-        <v>4.67884969711304</v>
+        <v>4.6788501739502</v>
       </c>
       <c r="H936" t="n">
         <v>8686085</v>
@@ -27687,7 +27687,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G942" t="n">
-        <v>4.9566502571106</v>
+        <v>4.95665073394775</v>
       </c>
       <c r="H942" t="n">
         <v>9765274</v>
@@ -27716,7 +27716,7 @@
         <v>5.16699981689453</v>
       </c>
       <c r="G943" t="n">
-        <v>4.91574096679688</v>
+        <v>4.91574144363403</v>
       </c>
       <c r="H943" t="n">
         <v>5370870</v>
@@ -27803,7 +27803,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G946" t="n">
-        <v>4.985191822052</v>
+        <v>4.98519134521484</v>
       </c>
       <c r="H946" t="n">
         <v>8525656</v>
@@ -27977,7 +27977,7 @@
         <v>5.19700002670288</v>
       </c>
       <c r="G952" t="n">
-        <v>4.94428300857544</v>
+        <v>4.94428253173828</v>
       </c>
       <c r="H952" t="n">
         <v>6264433</v>
@@ -28064,7 +28064,7 @@
         <v>4.94199991226196</v>
       </c>
       <c r="G955" t="n">
-        <v>4.70168256759644</v>
+        <v>4.70168209075928</v>
       </c>
       <c r="H955" t="n">
         <v>14155269</v>
@@ -28093,7 +28093,7 @@
         <v>4.96799993515015</v>
       </c>
       <c r="G956" t="n">
-        <v>4.72641849517822</v>
+        <v>4.72641801834106</v>
       </c>
       <c r="H956" t="n">
         <v>7492745</v>
@@ -28122,7 +28122,7 @@
         <v>4.97599983215332</v>
       </c>
       <c r="G957" t="n">
-        <v>4.73402881622314</v>
+        <v>4.7340292930603</v>
       </c>
       <c r="H957" t="n">
         <v>8539212</v>
@@ -28180,7 +28180,7 @@
         <v>5.06599998474121</v>
       </c>
       <c r="G959" t="n">
-        <v>4.81965255737305</v>
+        <v>4.81965303421021</v>
       </c>
       <c r="H959" t="n">
         <v>7079628</v>
@@ -28267,7 +28267,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G962" t="n">
-        <v>5.09935665130615</v>
+        <v>5.09935617446899</v>
       </c>
       <c r="H962" t="n">
         <v>9513376</v>
@@ -28354,7 +28354,7 @@
         <v>5.39400005340576</v>
       </c>
       <c r="G965" t="n">
-        <v>5.13170337677002</v>
+        <v>5.13170289993286</v>
       </c>
       <c r="H965" t="n">
         <v>7271483</v>
@@ -28412,7 +28412,7 @@
         <v>5.35400009155273</v>
       </c>
       <c r="G967" t="n">
-        <v>5.09364795684814</v>
+        <v>5.0936484336853</v>
       </c>
       <c r="H967" t="n">
         <v>7366786</v>
@@ -28528,7 +28528,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G971" t="n">
-        <v>5.06130170822144</v>
+        <v>5.06130123138428</v>
       </c>
       <c r="H971" t="n">
         <v>8251907</v>
@@ -28615,7 +28615,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G974" t="n">
-        <v>5.05178737640381</v>
+        <v>5.05178785324097</v>
       </c>
       <c r="H974" t="n">
         <v>5670673</v>
@@ -28905,7 +28905,7 @@
         <v>5.36299991607666</v>
       </c>
       <c r="G984" t="n">
-        <v>5.10221004486084</v>
+        <v>5.102210521698</v>
       </c>
       <c r="H984" t="n">
         <v>8375880</v>
@@ -28934,7 +28934,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G985" t="n">
-        <v>5.09935665130615</v>
+        <v>5.09935617446899</v>
       </c>
       <c r="H985" t="n">
         <v>6100265</v>
@@ -28963,7 +28963,7 @@
         <v>5.41300010681152</v>
       </c>
       <c r="G986" t="n">
-        <v>5.14977931976318</v>
+        <v>5.14977884292603</v>
       </c>
       <c r="H986" t="n">
         <v>11408179</v>
@@ -28992,7 +28992,7 @@
         <v>5.44099998474121</v>
       </c>
       <c r="G987" t="n">
-        <v>5.17641735076904</v>
+        <v>5.1764178276062</v>
       </c>
       <c r="H987" t="n">
         <v>5867671</v>
@@ -29050,7 +29050,7 @@
         <v>5.51800012588501</v>
       </c>
       <c r="G989" t="n">
-        <v>5.24967336654663</v>
+        <v>5.24967288970947</v>
       </c>
       <c r="H989" t="n">
         <v>8024179</v>
@@ -29079,7 +29079,7 @@
         <v>5.65100002288818</v>
       </c>
       <c r="G990" t="n">
-        <v>5.37620544433594</v>
+        <v>5.3762059211731</v>
       </c>
       <c r="H990" t="n">
         <v>12871995</v>
@@ -29166,7 +29166,7 @@
         <v>5.83900022506714</v>
       </c>
       <c r="G993" t="n">
-        <v>5.55506420135498</v>
+        <v>5.55506372451782</v>
       </c>
       <c r="H993" t="n">
         <v>5594077</v>
@@ -29224,7 +29224,7 @@
         <v>5.73899984359741</v>
       </c>
       <c r="G995" t="n">
-        <v>5.45992660522461</v>
+        <v>5.45992612838745</v>
       </c>
       <c r="H995" t="n">
         <v>8653313</v>
@@ -29253,7 +29253,7 @@
         <v>5.68599987030029</v>
       </c>
       <c r="G996" t="n">
-        <v>5.40950393676758</v>
+        <v>5.40950345993042</v>
       </c>
       <c r="H996" t="n">
         <v>4200712</v>
@@ -29340,7 +29340,7 @@
         <v>5.51200008392334</v>
       </c>
       <c r="G999" t="n">
-        <v>5.24396467208862</v>
+        <v>5.24396514892578</v>
       </c>
       <c r="H999" t="n">
         <v>5722620</v>
@@ -29601,7 +29601,7 @@
         <v>5.54199981689453</v>
       </c>
       <c r="G1008" t="n">
-        <v>5.27250623703003</v>
+        <v>5.27250576019287</v>
       </c>
       <c r="H1008" t="n">
         <v>4337873</v>
@@ -29630,7 +29630,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1009" t="n">
-        <v>5.28963041305542</v>
+        <v>5.28963088989258</v>
       </c>
       <c r="H1009" t="n">
         <v>5422481</v>
@@ -29659,7 +29659,7 @@
         <v>5.59499979019165</v>
       </c>
       <c r="G1010" t="n">
-        <v>5.32292890548706</v>
+        <v>5.3229284286499</v>
       </c>
       <c r="H1010" t="n">
         <v>7120475</v>
@@ -29688,7 +29688,7 @@
         <v>5.59499979019165</v>
       </c>
       <c r="G1011" t="n">
-        <v>5.32292890548706</v>
+        <v>5.3229284286499</v>
       </c>
       <c r="H1011" t="n">
         <v>8358777</v>
@@ -29833,7 +29833,7 @@
         <v>5.59499979019165</v>
       </c>
       <c r="G1016" t="n">
-        <v>5.32292890548706</v>
+        <v>5.3229284286499</v>
       </c>
       <c r="H1016" t="n">
         <v>3767783</v>
@@ -29978,7 +29978,7 @@
         <v>5.26300001144409</v>
       </c>
       <c r="G1021" t="n">
-        <v>5.00707292556763</v>
+        <v>5.00707340240479</v>
       </c>
       <c r="H1021" t="n">
         <v>11895409</v>
@@ -30065,7 +30065,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1024" t="n">
-        <v>4.89956855773926</v>
+        <v>4.8995680809021</v>
       </c>
       <c r="H1024" t="n">
         <v>9609886</v>
@@ -30094,7 +30094,7 @@
         <v>5.05900001525879</v>
       </c>
       <c r="G1025" t="n">
-        <v>4.81299352645874</v>
+        <v>4.81299304962158</v>
       </c>
       <c r="H1025" t="n">
         <v>6906988</v>
@@ -30152,7 +30152,7 @@
         <v>5.1230001449585</v>
       </c>
       <c r="G1027" t="n">
-        <v>4.87388134002686</v>
+        <v>4.8738808631897</v>
       </c>
       <c r="H1027" t="n">
         <v>5426424</v>
@@ -30181,7 +30181,7 @@
         <v>5.11399984359741</v>
       </c>
       <c r="G1028" t="n">
-        <v>4.86531829833984</v>
+        <v>4.865318775177</v>
       </c>
       <c r="H1028" t="n">
         <v>3560102</v>
@@ -30210,7 +30210,7 @@
         <v>5.06599998474121</v>
       </c>
       <c r="G1029" t="n">
-        <v>4.81965255737305</v>
+        <v>4.81965303421021</v>
       </c>
       <c r="H1029" t="n">
         <v>7067344</v>
@@ -30268,7 +30268,7 @@
         <v>4.94199991226196</v>
       </c>
       <c r="G1031" t="n">
-        <v>4.70168256759644</v>
+        <v>4.70168209075928</v>
       </c>
       <c r="H1031" t="n">
         <v>8681679</v>
@@ -30413,7 +30413,7 @@
         <v>5.05399990081787</v>
       </c>
       <c r="G1036" t="n">
-        <v>4.80823659896851</v>
+        <v>4.80823612213135</v>
       </c>
       <c r="H1036" t="n">
         <v>8898900</v>
@@ -30471,7 +30471,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1038" t="n">
-        <v>4.58561563491821</v>
+        <v>4.58561515808105</v>
       </c>
       <c r="H1038" t="n">
         <v>8979335</v>
@@ -30500,7 +30500,7 @@
         <v>4.91800022125244</v>
       </c>
       <c r="G1039" t="n">
-        <v>4.67884969711304</v>
+        <v>4.6788501739502</v>
       </c>
       <c r="H1039" t="n">
         <v>8140590</v>
@@ -30558,7 +30558,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1041" t="n">
-        <v>4.77588987350464</v>
+        <v>4.77588939666748</v>
       </c>
       <c r="H1041" t="n">
         <v>6949040</v>
@@ -30587,7 +30587,7 @@
         <v>4.94799995422363</v>
       </c>
       <c r="G1042" t="n">
-        <v>4.70739126205444</v>
+        <v>4.70739078521729</v>
       </c>
       <c r="H1042" t="n">
         <v>6830332</v>
@@ -30703,7 +30703,7 @@
         <v>5.25</v>
       </c>
       <c r="G1046" t="n">
-        <v>4.99470567703247</v>
+        <v>4.99470520019531</v>
       </c>
       <c r="H1046" t="n">
         <v>18341830</v>
@@ -31022,7 +31022,7 @@
         <v>5.00099992752075</v>
       </c>
       <c r="G1057" t="n">
-        <v>4.75781393051147</v>
+        <v>4.75781345367432</v>
       </c>
       <c r="H1057" t="n">
         <v>18342696</v>
@@ -31080,7 +31080,7 @@
         <v>4.77899980545044</v>
       </c>
       <c r="G1059" t="n">
-        <v>4.54660844802856</v>
+        <v>4.54660892486572</v>
       </c>
       <c r="H1059" t="n">
         <v>14134380</v>
@@ -31167,7 +31167,7 @@
         <v>4.32100009918213</v>
       </c>
       <c r="G1062" t="n">
-        <v>4.11088085174561</v>
+        <v>4.11088037490845</v>
       </c>
       <c r="H1062" t="n">
         <v>15034059</v>
@@ -31225,7 +31225,7 @@
         <v>3.67199993133545</v>
       </c>
       <c r="G1064" t="n">
-        <v>3.49343943595886</v>
+        <v>3.49343967437744</v>
       </c>
       <c r="H1064" t="n">
         <v>15459498</v>
@@ -31254,7 +31254,7 @@
         <v>3.81699991226196</v>
       </c>
       <c r="G1065" t="n">
-        <v>3.63138866424561</v>
+        <v>3.63138842582703</v>
       </c>
       <c r="H1065" t="n">
         <v>20006610</v>
@@ -31428,7 +31428,7 @@
         <v>3.7739999294281</v>
       </c>
       <c r="G1071" t="n">
-        <v>3.59047961235046</v>
+        <v>3.59047937393188</v>
       </c>
       <c r="H1071" t="n">
         <v>20539960</v>
@@ -31718,7 +31718,7 @@
         <v>3.79299998283386</v>
       </c>
       <c r="G1081" t="n">
-        <v>3.60855579376221</v>
+        <v>3.60855555534363</v>
       </c>
       <c r="H1081" t="n">
         <v>9112585</v>
@@ -31776,7 +31776,7 @@
         <v>3.92400002479553</v>
       </c>
       <c r="G1083" t="n">
-        <v>3.73318552970886</v>
+        <v>3.73318529129028</v>
       </c>
       <c r="H1083" t="n">
         <v>8125581</v>
@@ -31834,7 +31834,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G1085" t="n">
-        <v>3.61045837402344</v>
+        <v>3.61045861244202</v>
       </c>
       <c r="H1085" t="n">
         <v>9133043</v>
@@ -31921,7 +31921,7 @@
         <v>3.53399991989136</v>
       </c>
       <c r="G1088" t="n">
-        <v>3.36214995384216</v>
+        <v>3.36215019226074</v>
       </c>
       <c r="H1088" t="n">
         <v>10081010</v>
@@ -32182,7 +32182,7 @@
         <v>3.44600009918213</v>
       </c>
       <c r="G1097" t="n">
-        <v>3.27842974662781</v>
+        <v>3.27842950820923</v>
       </c>
       <c r="H1097" t="n">
         <v>7252885</v>
@@ -32211,7 +32211,7 @@
         <v>3.64400005340576</v>
       </c>
       <c r="G1098" t="n">
-        <v>3.46680116653442</v>
+        <v>3.466801404953</v>
       </c>
       <c r="H1098" t="n">
         <v>11382035</v>
@@ -32240,7 +32240,7 @@
         <v>3.6159999370575</v>
       </c>
       <c r="G1099" t="n">
-        <v>3.44016289710999</v>
+        <v>3.44016265869141</v>
       </c>
       <c r="H1099" t="n">
         <v>12293070</v>
@@ -32298,7 +32298,7 @@
         <v>3.53399991989136</v>
       </c>
       <c r="G1101" t="n">
-        <v>3.36214995384216</v>
+        <v>3.36215019226074</v>
       </c>
       <c r="H1101" t="n">
         <v>6018678</v>
@@ -32327,7 +32327,7 @@
         <v>3.50399994850159</v>
       </c>
       <c r="G1102" t="n">
-        <v>3.33360910415649</v>
+        <v>3.33360886573792</v>
       </c>
       <c r="H1102" t="n">
         <v>4601154</v>
@@ -32356,7 +32356,7 @@
         <v>3.42799997329712</v>
       </c>
       <c r="G1103" t="n">
-        <v>3.2613046169281</v>
+        <v>3.26130485534668</v>
       </c>
       <c r="H1103" t="n">
         <v>7123473</v>
@@ -32385,7 +32385,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1104" t="n">
-        <v>3.29174852371216</v>
+        <v>3.29174876213074</v>
       </c>
       <c r="H1104" t="n">
         <v>3356216</v>
@@ -32675,7 +32675,7 @@
         <v>3.20700001716614</v>
       </c>
       <c r="G1114" t="n">
-        <v>3.0510516166687</v>
+        <v>3.05105137825012</v>
       </c>
       <c r="H1114" t="n">
         <v>12499911</v>
@@ -32733,7 +32733,7 @@
         <v>3.30399990081787</v>
       </c>
       <c r="G1116" t="n">
-        <v>3.14333438873291</v>
+        <v>3.14333462715149</v>
       </c>
       <c r="H1116" t="n">
         <v>12389541</v>
@@ -32762,7 +32762,7 @@
         <v>3.3050000667572</v>
       </c>
       <c r="G1117" t="n">
-        <v>3.14428615570068</v>
+        <v>3.1442859172821</v>
       </c>
       <c r="H1117" t="n">
         <v>16377885</v>
@@ -32849,7 +32849,7 @@
         <v>3.41400003433228</v>
       </c>
       <c r="G1120" t="n">
-        <v>3.24798560142517</v>
+        <v>3.24798536300659</v>
       </c>
       <c r="H1120" t="n">
         <v>10515189</v>
@@ -32878,7 +32878,7 @@
         <v>3.52300000190735</v>
       </c>
       <c r="G1121" t="n">
-        <v>3.35168528556824</v>
+        <v>3.35168504714966</v>
       </c>
       <c r="H1121" t="n">
         <v>14830770</v>
@@ -33052,7 +33052,7 @@
         <v>3.71600008010864</v>
       </c>
       <c r="G1127" t="n">
-        <v>3.5353000164032</v>
+        <v>3.53530025482178</v>
       </c>
       <c r="H1127" t="n">
         <v>26938169</v>
@@ -33110,7 +33110,7 @@
         <v>3.53399991989136</v>
       </c>
       <c r="G1129" t="n">
-        <v>3.36214995384216</v>
+        <v>3.36215019226074</v>
       </c>
       <c r="H1129" t="n">
         <v>19235451</v>
@@ -33226,7 +33226,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1133" t="n">
-        <v>3.49153685569763</v>
+        <v>3.49153709411621</v>
       </c>
       <c r="H1133" t="n">
         <v>10659918</v>
@@ -80125,6 +80125,35 @@
         <v>5802552</v>
       </c>
       <c r="I2750" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2751">
+      <c r="A2751" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2751" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C2751" t="n">
+        <v>5.56899976730347</v>
+      </c>
+      <c r="D2751" t="n">
+        <v>5.76300001144409</v>
+      </c>
+      <c r="E2751" t="n">
+        <v>5.53000020980835</v>
+      </c>
+      <c r="F2751" t="n">
+        <v>5.76300001144409</v>
+      </c>
+      <c r="G2751" t="n">
+        <v>5.76300001144409</v>
+      </c>
+      <c r="H2751" t="n">
+        <v>2666797</v>
+      </c>
+      <c r="I2751" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TIT.MI.xlsx
+++ b/data/TIT.MI.xlsx
@@ -775,7 +775,7 @@
         <v>9.76500034332275</v>
       </c>
       <c r="G14" t="n">
-        <v>9.29015254974365</v>
+        <v>9.29015159606934</v>
       </c>
       <c r="H14" t="n">
         <v>12465433</v>
@@ -949,7 +949,7 @@
         <v>9.77000045776367</v>
       </c>
       <c r="G20" t="n">
-        <v>9.29490947723389</v>
+        <v>9.29490852355957</v>
       </c>
       <c r="H20" t="n">
         <v>21107831</v>
@@ -1152,7 +1152,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G27" t="n">
-        <v>7.99152851104736</v>
+        <v>7.99152803421021</v>
       </c>
       <c r="H27" t="n">
         <v>18362675</v>
@@ -1181,7 +1181,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G28" t="n">
-        <v>8.27693939208984</v>
+        <v>8.27694034576416</v>
       </c>
       <c r="H28" t="n">
         <v>22554264</v>
@@ -1239,7 +1239,7 @@
         <v>8.25500011444092</v>
       </c>
       <c r="G30" t="n">
-        <v>7.8535795211792</v>
+        <v>7.85357904434204</v>
       </c>
       <c r="H30" t="n">
         <v>17371217</v>
@@ -1268,7 +1268,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G31" t="n">
-        <v>8.17228984832764</v>
+        <v>8.17228889465332</v>
       </c>
       <c r="H31" t="n">
         <v>10187944</v>
@@ -1297,7 +1297,7 @@
         <v>8.76500034332275</v>
       </c>
       <c r="G32" t="n">
-        <v>8.33878040313721</v>
+        <v>8.33877944946289</v>
       </c>
       <c r="H32" t="n">
         <v>9462652</v>
@@ -1326,7 +1326,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G33" t="n">
-        <v>7.80125331878662</v>
+        <v>7.80125379562378</v>
       </c>
       <c r="H33" t="n">
         <v>28696243</v>
@@ -1587,7 +1587,7 @@
         <v>8.98999977111816</v>
       </c>
       <c r="G42" t="n">
-        <v>8.55283737182617</v>
+        <v>8.55283832550049</v>
       </c>
       <c r="H42" t="n">
         <v>10915001</v>
@@ -1645,7 +1645,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G44" t="n">
-        <v>8.98095607757568</v>
+        <v>8.98095512390137</v>
       </c>
       <c r="H44" t="n">
         <v>13756209</v>
@@ -1703,7 +1703,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G46" t="n">
-        <v>9.70399951934814</v>
+        <v>9.70399856567383</v>
       </c>
       <c r="H46" t="n">
         <v>20342560</v>
@@ -1732,7 +1732,7 @@
         <v>9.82499980926514</v>
       </c>
       <c r="G47" t="n">
-        <v>9.34723377227783</v>
+        <v>9.34723472595215</v>
       </c>
       <c r="H47" t="n">
         <v>11169591</v>
@@ -1790,7 +1790,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G49" t="n">
-        <v>9.64691638946533</v>
+        <v>9.64691734313965</v>
       </c>
       <c r="H49" t="n">
         <v>18523100</v>
@@ -1848,7 +1848,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G51" t="n">
-        <v>9.91330146789551</v>
+        <v>9.91330051422119</v>
       </c>
       <c r="H51" t="n">
         <v>10987806</v>
@@ -1877,7 +1877,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G52" t="n">
-        <v>9.81816291809082</v>
+        <v>9.81816387176514</v>
       </c>
       <c r="H52" t="n">
         <v>6496305</v>
@@ -1935,7 +1935,7 @@
         <v>10.3299999237061</v>
       </c>
       <c r="G54" t="n">
-        <v>9.82767677307129</v>
+        <v>9.82767772674561</v>
       </c>
       <c r="H54" t="n">
         <v>5795315</v>
@@ -2022,7 +2022,7 @@
         <v>10.4099998474121</v>
       </c>
       <c r="G57" t="n">
-        <v>9.90378761291504</v>
+        <v>9.90378665924072</v>
       </c>
       <c r="H57" t="n">
         <v>9694375</v>
@@ -2225,7 +2225,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G64" t="n">
-        <v>8.70505714416504</v>
+        <v>8.70505809783936</v>
       </c>
       <c r="H64" t="n">
         <v>14609221</v>
@@ -2283,7 +2283,7 @@
         <v>8.58500003814697</v>
       </c>
       <c r="G66" t="n">
-        <v>8.1675329208374</v>
+        <v>8.16753196716309</v>
       </c>
       <c r="H66" t="n">
         <v>11386012</v>
@@ -2312,7 +2312,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G67" t="n">
-        <v>8.18180274963379</v>
+        <v>8.18180370330811</v>
       </c>
       <c r="H67" t="n">
         <v>8994634</v>
@@ -2341,7 +2341,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G68" t="n">
-        <v>7.95347356796265</v>
+        <v>7.95347309112549</v>
       </c>
       <c r="H68" t="n">
         <v>8054619</v>
@@ -2399,7 +2399,7 @@
         <v>8.98999977111816</v>
       </c>
       <c r="G70" t="n">
-        <v>8.55283737182617</v>
+        <v>8.55283832550049</v>
       </c>
       <c r="H70" t="n">
         <v>7769877</v>
@@ -2718,7 +2718,7 @@
         <v>8.65499973297119</v>
       </c>
       <c r="G81" t="n">
-        <v>8.23412895202637</v>
+        <v>8.23412799835205</v>
       </c>
       <c r="H81" t="n">
         <v>11095524</v>
@@ -2776,7 +2776,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G83" t="n">
-        <v>8.25791263580322</v>
+        <v>8.25791358947754</v>
       </c>
       <c r="H83" t="n">
         <v>15796951</v>
@@ -2834,7 +2834,7 @@
         <v>8.46500015258789</v>
       </c>
       <c r="G85" t="n">
-        <v>8.05336761474609</v>
+        <v>8.05336856842041</v>
       </c>
       <c r="H85" t="n">
         <v>6739223</v>
@@ -2863,7 +2863,7 @@
         <v>8.36499977111816</v>
       </c>
       <c r="G86" t="n">
-        <v>7.95823049545288</v>
+        <v>7.95823001861572</v>
       </c>
       <c r="H86" t="n">
         <v>7439860</v>
@@ -2892,7 +2892,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G87" t="n">
-        <v>8.04861068725586</v>
+        <v>8.04861164093018</v>
       </c>
       <c r="H87" t="n">
         <v>6088332</v>
@@ -3037,7 +3037,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G92" t="n">
-        <v>8.05812454223633</v>
+        <v>8.05812549591064</v>
       </c>
       <c r="H92" t="n">
         <v>7818052</v>
@@ -3153,7 +3153,7 @@
         <v>8.48999977111816</v>
       </c>
       <c r="G96" t="n">
-        <v>8.07715129852295</v>
+        <v>8.07715225219727</v>
       </c>
       <c r="H96" t="n">
         <v>11841822</v>
@@ -3211,7 +3211,7 @@
         <v>8.30500030517578</v>
       </c>
       <c r="G98" t="n">
-        <v>7.90114784240723</v>
+        <v>7.90114879608154</v>
       </c>
       <c r="H98" t="n">
         <v>9583225</v>
@@ -3240,7 +3240,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G99" t="n">
-        <v>7.87736320495605</v>
+        <v>7.87736368179321</v>
       </c>
       <c r="H99" t="n">
         <v>7171888</v>
@@ -3327,7 +3327,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G102" t="n">
-        <v>7.91541814804077</v>
+        <v>7.91541862487793</v>
       </c>
       <c r="H102" t="n">
         <v>15847474</v>
@@ -3385,7 +3385,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G104" t="n">
-        <v>8.27693939208984</v>
+        <v>8.27694034576416</v>
       </c>
       <c r="H104" t="n">
         <v>8314517</v>
@@ -3675,7 +3675,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G114" t="n">
-        <v>7.82028198242188</v>
+        <v>7.82028150558472</v>
       </c>
       <c r="H114" t="n">
         <v>14068153</v>
@@ -3704,7 +3704,7 @@
         <v>7.91499996185303</v>
       </c>
       <c r="G115" t="n">
-        <v>7.53011322021484</v>
+        <v>7.53011274337769</v>
       </c>
       <c r="H115" t="n">
         <v>12688239</v>
@@ -3762,7 +3762,7 @@
         <v>7.59499979019165</v>
       </c>
       <c r="G117" t="n">
-        <v>7.22567367553711</v>
+        <v>7.22567319869995</v>
       </c>
       <c r="H117" t="n">
         <v>14127681</v>
@@ -3791,7 +3791,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G118" t="n">
-        <v>7.04015588760376</v>
+        <v>7.04015636444092</v>
       </c>
       <c r="H118" t="n">
         <v>12062526</v>
@@ -3936,7 +3936,7 @@
         <v>8.27499961853027</v>
       </c>
       <c r="G123" t="n">
-        <v>7.87260627746582</v>
+        <v>7.87260675430298</v>
       </c>
       <c r="H123" t="n">
         <v>12615589</v>
@@ -3994,7 +3994,7 @@
         <v>6.67500019073486</v>
       </c>
       <c r="G125" t="n">
-        <v>6.3504114151001</v>
+        <v>6.35041093826294</v>
       </c>
       <c r="H125" t="n">
         <v>23209498</v>
@@ -4052,7 +4052,7 @@
         <v>7.44500017166138</v>
       </c>
       <c r="G127" t="n">
-        <v>7.08296823501587</v>
+        <v>7.08296775817871</v>
       </c>
       <c r="H127" t="n">
         <v>14352211</v>
@@ -4110,7 +4110,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G129" t="n">
-        <v>7.04015588760376</v>
+        <v>7.04015636444092</v>
       </c>
       <c r="H129" t="n">
         <v>8980366</v>
@@ -4226,7 +4226,7 @@
         <v>6.33500003814697</v>
       </c>
       <c r="G133" t="n">
-        <v>6.02694463729858</v>
+        <v>6.02694416046143</v>
       </c>
       <c r="H133" t="n">
         <v>13905809</v>
@@ -4284,7 +4284,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G135" t="n">
-        <v>6.30759906768799</v>
+        <v>6.30759954452515</v>
       </c>
       <c r="H135" t="n">
         <v>6922559</v>
@@ -4313,7 +4313,7 @@
         <v>6.92500019073486</v>
       </c>
       <c r="G136" t="n">
-        <v>6.58825445175171</v>
+        <v>6.58825397491455</v>
       </c>
       <c r="H136" t="n">
         <v>10111814</v>
@@ -4429,7 +4429,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G140" t="n">
-        <v>6.60252475738525</v>
+        <v>6.60252523422241</v>
       </c>
       <c r="H140" t="n">
         <v>13382865</v>
@@ -4487,7 +4487,7 @@
         <v>6.86499977111816</v>
       </c>
       <c r="G142" t="n">
-        <v>6.5311713218689</v>
+        <v>6.53117179870605</v>
       </c>
       <c r="H142" t="n">
         <v>8811876</v>
@@ -4574,7 +4574,7 @@
         <v>7</v>
       </c>
       <c r="G145" t="n">
-        <v>6.65960741043091</v>
+        <v>6.65960693359375</v>
       </c>
       <c r="H145" t="n">
         <v>8398609</v>
@@ -4632,7 +4632,7 @@
         <v>7.46999979019165</v>
       </c>
       <c r="G147" t="n">
-        <v>7.10675239562988</v>
+        <v>7.10675191879272</v>
       </c>
       <c r="H147" t="n">
         <v>29073903</v>
@@ -4690,7 +4690,7 @@
         <v>7.63500022888184</v>
       </c>
       <c r="G149" t="n">
-        <v>7.26372861862183</v>
+        <v>7.26372909545898</v>
       </c>
       <c r="H149" t="n">
         <v>10594903</v>
@@ -4748,7 +4748,7 @@
         <v>7.44500017166138</v>
       </c>
       <c r="G151" t="n">
-        <v>7.08296823501587</v>
+        <v>7.08296775817871</v>
       </c>
       <c r="H151" t="n">
         <v>8748243</v>
@@ -4893,7 +4893,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G156" t="n">
-        <v>7.24945783615112</v>
+        <v>7.24945831298828</v>
       </c>
       <c r="H156" t="n">
         <v>4135572</v>
@@ -5125,7 +5125,7 @@
         <v>7.92999982833862</v>
       </c>
       <c r="G164" t="n">
-        <v>7.54438352584839</v>
+        <v>7.54438304901123</v>
       </c>
       <c r="H164" t="n">
         <v>4924973</v>
@@ -5212,7 +5212,7 @@
         <v>8.0649995803833</v>
       </c>
       <c r="G167" t="n">
-        <v>7.67281818389893</v>
+        <v>7.67281866073608</v>
       </c>
       <c r="H167" t="n">
         <v>5554419</v>
@@ -5299,7 +5299,7 @@
         <v>8.24499988555908</v>
       </c>
       <c r="G170" t="n">
-        <v>7.84406566619873</v>
+        <v>7.84406518936157</v>
       </c>
       <c r="H170" t="n">
         <v>6352724</v>
@@ -5328,7 +5328,7 @@
         <v>8.13500022888184</v>
       </c>
       <c r="G171" t="n">
-        <v>7.73941469192505</v>
+        <v>7.73941516876221</v>
       </c>
       <c r="H171" t="n">
         <v>7750471</v>
@@ -5357,7 +5357,7 @@
         <v>8.16499996185303</v>
       </c>
       <c r="G172" t="n">
-        <v>7.76795625686646</v>
+        <v>7.7679557800293</v>
       </c>
       <c r="H172" t="n">
         <v>8273298</v>
@@ -5386,7 +5386,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G173" t="n">
-        <v>7.80125331878662</v>
+        <v>7.80125379562378</v>
       </c>
       <c r="H173" t="n">
         <v>5239033</v>
@@ -5473,7 +5473,7 @@
         <v>8.04500007629395</v>
       </c>
       <c r="G176" t="n">
-        <v>7.65379095077515</v>
+        <v>7.6537914276123</v>
       </c>
       <c r="H176" t="n">
         <v>7646216</v>
@@ -5502,7 +5502,7 @@
         <v>8.16499996185303</v>
       </c>
       <c r="G177" t="n">
-        <v>7.76795625686646</v>
+        <v>7.7679557800293</v>
       </c>
       <c r="H177" t="n">
         <v>6137326</v>
@@ -5531,7 +5531,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G178" t="n">
-        <v>7.64903450012207</v>
+        <v>7.64903402328491</v>
       </c>
       <c r="H178" t="n">
         <v>7450630</v>
@@ -5560,7 +5560,7 @@
         <v>7.88500022888184</v>
       </c>
       <c r="G179" t="n">
-        <v>7.50157165527344</v>
+        <v>7.5015721321106</v>
       </c>
       <c r="H179" t="n">
         <v>10968844</v>
@@ -5647,7 +5647,7 @@
         <v>7.53499984741211</v>
       </c>
       <c r="G182" t="n">
-        <v>7.16859102249146</v>
+        <v>7.16859149932861</v>
       </c>
       <c r="H182" t="n">
         <v>8919248</v>
@@ -5734,7 +5734,7 @@
         <v>7.28499984741211</v>
       </c>
       <c r="G185" t="n">
-        <v>6.93074798583984</v>
+        <v>6.930748462677</v>
       </c>
       <c r="H185" t="n">
         <v>7139176</v>
@@ -5821,7 +5821,7 @@
         <v>7.63500022888184</v>
       </c>
       <c r="G188" t="n">
-        <v>7.26372861862183</v>
+        <v>7.26372909545898</v>
       </c>
       <c r="H188" t="n">
         <v>4604142</v>
@@ -5879,7 +5879,7 @@
         <v>7.34499979019165</v>
       </c>
       <c r="G190" t="n">
-        <v>6.9878306388855</v>
+        <v>6.98783016204834</v>
       </c>
       <c r="H190" t="n">
         <v>5769993</v>
@@ -5908,7 +5908,7 @@
         <v>7.49499988555908</v>
       </c>
       <c r="G191" t="n">
-        <v>7.13053607940674</v>
+        <v>7.1305365562439</v>
       </c>
       <c r="H191" t="n">
         <v>4422318</v>
@@ -5966,7 +5966,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G193" t="n">
-        <v>7.03064203262329</v>
+        <v>7.03064250946045</v>
       </c>
       <c r="H193" t="n">
         <v>9011031</v>
@@ -6053,7 +6053,7 @@
         <v>7.29500007629395</v>
       </c>
       <c r="G196" t="n">
-        <v>6.94026184082031</v>
+        <v>6.94026231765747</v>
       </c>
       <c r="H196" t="n">
         <v>10575030</v>
@@ -6140,7 +6140,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G199" t="n">
-        <v>7.04015588760376</v>
+        <v>7.04015636444092</v>
       </c>
       <c r="H199" t="n">
         <v>8616275</v>
@@ -6169,7 +6169,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G200" t="n">
-        <v>6.86890840530396</v>
+        <v>6.86890888214111</v>
       </c>
       <c r="H200" t="n">
         <v>8236131</v>
@@ -6227,7 +6227,7 @@
         <v>6.94500017166138</v>
       </c>
       <c r="G202" t="n">
-        <v>6.60728168487549</v>
+        <v>6.60728216171265</v>
       </c>
       <c r="H202" t="n">
         <v>17317483</v>
@@ -6314,7 +6314,7 @@
         <v>7.57499980926514</v>
       </c>
       <c r="G205" t="n">
-        <v>7.20664644241333</v>
+        <v>7.20664596557617</v>
       </c>
       <c r="H205" t="n">
         <v>13042674</v>
@@ -6372,7 +6372,7 @@
         <v>7.59499979019165</v>
       </c>
       <c r="G207" t="n">
-        <v>7.22567367553711</v>
+        <v>7.22567319869995</v>
       </c>
       <c r="H207" t="n">
         <v>5770682</v>
@@ -6401,7 +6401,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G208" t="n">
-        <v>7.3541088104248</v>
+        <v>7.35410928726196</v>
       </c>
       <c r="H208" t="n">
         <v>11041706</v>
@@ -6430,7 +6430,7 @@
         <v>7.92999982833862</v>
       </c>
       <c r="G209" t="n">
-        <v>7.54438352584839</v>
+        <v>7.54438304901123</v>
       </c>
       <c r="H209" t="n">
         <v>12562957</v>
@@ -6633,7 +6633,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G216" t="n">
-        <v>7.3541088104248</v>
+        <v>7.35410928726196</v>
       </c>
       <c r="H216" t="n">
         <v>11074256</v>
@@ -6662,7 +6662,7 @@
         <v>7.70499992370605</v>
       </c>
       <c r="G217" t="n">
-        <v>7.33032417297363</v>
+        <v>7.33032464981079</v>
       </c>
       <c r="H217" t="n">
         <v>6751462</v>
@@ -6778,7 +6778,7 @@
         <v>7.45499992370605</v>
       </c>
       <c r="G221" t="n">
-        <v>7.09248113632202</v>
+        <v>7.09248161315918</v>
       </c>
       <c r="H221" t="n">
         <v>19305315</v>
@@ -6952,7 +6952,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G227" t="n">
-        <v>6.67863464355469</v>
+        <v>6.67863416671753</v>
       </c>
       <c r="H227" t="n">
         <v>15148923</v>
@@ -6981,7 +6981,7 @@
         <v>6.86499977111816</v>
       </c>
       <c r="G228" t="n">
-        <v>6.5311713218689</v>
+        <v>6.53117179870605</v>
       </c>
       <c r="H228" t="n">
         <v>15141472</v>
@@ -7097,7 +7097,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G232" t="n">
-        <v>6.70717573165894</v>
+        <v>6.70717620849609</v>
       </c>
       <c r="H232" t="n">
         <v>6631825</v>
@@ -7126,7 +7126,7 @@
         <v>7.14499998092651</v>
       </c>
       <c r="G233" t="n">
-        <v>6.79755640029907</v>
+        <v>6.79755592346191</v>
       </c>
       <c r="H233" t="n">
         <v>7685848</v>
@@ -7300,7 +7300,7 @@
         <v>7</v>
       </c>
       <c r="G239" t="n">
-        <v>6.65960741043091</v>
+        <v>6.65960693359375</v>
       </c>
       <c r="H239" t="n">
         <v>16092872</v>
@@ -7358,7 +7358,7 @@
         <v>7.54500007629395</v>
       </c>
       <c r="G241" t="n">
-        <v>7.17810487747192</v>
+        <v>7.17810535430908</v>
       </c>
       <c r="H241" t="n">
         <v>14162922</v>
@@ -7416,7 +7416,7 @@
         <v>7.625</v>
       </c>
       <c r="G243" t="n">
-        <v>7.25421476364136</v>
+        <v>7.25421524047852</v>
       </c>
       <c r="H243" t="n">
         <v>7313055</v>
@@ -7561,7 +7561,7 @@
         <v>8.06999969482422</v>
       </c>
       <c r="G248" t="n">
-        <v>7.67757511138916</v>
+        <v>7.67757558822632</v>
       </c>
       <c r="H248" t="n">
         <v>19683266</v>
@@ -7648,7 +7648,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G251" t="n">
-        <v>7.99152851104736</v>
+        <v>7.99152803421021</v>
       </c>
       <c r="H251" t="n">
         <v>10995964</v>
@@ -7735,7 +7735,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G254" t="n">
-        <v>8.27693939208984</v>
+        <v>8.27694034576416</v>
       </c>
       <c r="H254" t="n">
         <v>7105744</v>
@@ -7764,7 +7764,7 @@
         <v>8.42500019073486</v>
       </c>
       <c r="G255" t="n">
-        <v>8.01531314849854</v>
+        <v>8.01531219482422</v>
       </c>
       <c r="H255" t="n">
         <v>7953684</v>
@@ -7822,7 +7822,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G257" t="n">
-        <v>7.96298742294312</v>
+        <v>7.96298694610596</v>
       </c>
       <c r="H257" t="n">
         <v>4473749</v>
@@ -7851,7 +7851,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G258" t="n">
-        <v>8.16277599334717</v>
+        <v>8.16277503967285</v>
       </c>
       <c r="H258" t="n">
         <v>6919849</v>
@@ -7938,7 +7938,7 @@
         <v>8.42500019073486</v>
       </c>
       <c r="G261" t="n">
-        <v>8.01531314849854</v>
+        <v>8.01531219482422</v>
       </c>
       <c r="H261" t="n">
         <v>8691609</v>
@@ -7996,7 +7996,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G263" t="n">
-        <v>7.82028198242188</v>
+        <v>7.82028150558472</v>
       </c>
       <c r="H263" t="n">
         <v>9698154</v>
@@ -8025,7 +8025,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G264" t="n">
-        <v>7.87736320495605</v>
+        <v>7.87736368179321</v>
       </c>
       <c r="H264" t="n">
         <v>8049414</v>
@@ -8054,7 +8054,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G265" t="n">
-        <v>8.04861068725586</v>
+        <v>8.04861164093018</v>
       </c>
       <c r="H265" t="n">
         <v>10193124</v>
@@ -8083,7 +8083,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G266" t="n">
-        <v>7.93444681167603</v>
+        <v>7.93444633483887</v>
       </c>
       <c r="H266" t="n">
         <v>5591385</v>
@@ -8141,7 +8141,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G268" t="n">
-        <v>8.10569286346436</v>
+        <v>8.10569381713867</v>
       </c>
       <c r="H268" t="n">
         <v>4819501</v>
@@ -8170,7 +8170,7 @@
         <v>8.375</v>
       </c>
       <c r="G269" t="n">
-        <v>7.96774482727051</v>
+        <v>7.96774387359619</v>
       </c>
       <c r="H269" t="n">
         <v>6854564</v>
@@ -8199,7 +8199,7 @@
         <v>8.3100004196167</v>
       </c>
       <c r="G270" t="n">
-        <v>7.90590524673462</v>
+        <v>7.90590572357178</v>
       </c>
       <c r="H270" t="n">
         <v>7624065</v>
@@ -8228,7 +8228,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G271" t="n">
-        <v>7.99152851104736</v>
+        <v>7.99152803421021</v>
       </c>
       <c r="H271" t="n">
         <v>15001217</v>
@@ -8257,7 +8257,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G272" t="n">
-        <v>8.04861068725586</v>
+        <v>8.04861164093018</v>
       </c>
       <c r="H272" t="n">
         <v>7357311</v>
@@ -8286,7 +8286,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G273" t="n">
-        <v>7.99152851104736</v>
+        <v>7.99152803421021</v>
       </c>
       <c r="H273" t="n">
         <v>6892052</v>
@@ -8315,7 +8315,7 @@
         <v>8.3100004196167</v>
       </c>
       <c r="G274" t="n">
-        <v>7.90590524673462</v>
+        <v>7.90590572357178</v>
       </c>
       <c r="H274" t="n">
         <v>10051498</v>
@@ -8344,7 +8344,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G275" t="n">
-        <v>7.82979536056519</v>
+        <v>7.82979440689087</v>
       </c>
       <c r="H275" t="n">
         <v>9477679</v>
@@ -8518,7 +8518,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G281" t="n">
-        <v>7.59195184707642</v>
+        <v>7.59195232391357</v>
       </c>
       <c r="H281" t="n">
         <v>6833809</v>
@@ -8634,7 +8634,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G285" t="n">
-        <v>7.79174041748047</v>
+        <v>7.79173994064331</v>
       </c>
       <c r="H285" t="n">
         <v>8180031</v>
@@ -8663,7 +8663,7 @@
         <v>8.25</v>
       </c>
       <c r="G286" t="n">
-        <v>7.84882259368896</v>
+        <v>7.84882211685181</v>
       </c>
       <c r="H286" t="n">
         <v>8035948</v>
@@ -8692,7 +8692,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G287" t="n">
-        <v>7.64903450012207</v>
+        <v>7.64903402328491</v>
       </c>
       <c r="H287" t="n">
         <v>9027559</v>
@@ -8750,7 +8750,7 @@
         <v>7.97499990463257</v>
       </c>
       <c r="G289" t="n">
-        <v>7.58719491958618</v>
+        <v>7.58719539642334</v>
       </c>
       <c r="H289" t="n">
         <v>7815676</v>
@@ -8808,7 +8808,7 @@
         <v>7.91499996185303</v>
       </c>
       <c r="G291" t="n">
-        <v>7.53011322021484</v>
+        <v>7.53011274337769</v>
       </c>
       <c r="H291" t="n">
         <v>6709166</v>
@@ -8895,7 +8895,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G294" t="n">
-        <v>7.32556772232056</v>
+        <v>7.3255672454834</v>
       </c>
       <c r="H294" t="n">
         <v>10570127</v>
@@ -8924,7 +8924,7 @@
         <v>7.59499979019165</v>
       </c>
       <c r="G295" t="n">
-        <v>7.22567367553711</v>
+        <v>7.22567319869995</v>
       </c>
       <c r="H295" t="n">
         <v>15446807</v>
@@ -9185,7 +9185,7 @@
         <v>7.79500007629395</v>
       </c>
       <c r="G304" t="n">
-        <v>7.41594791412354</v>
+        <v>7.41594839096069</v>
       </c>
       <c r="H304" t="n">
         <v>5768451</v>
@@ -9214,7 +9214,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G305" t="n">
-        <v>7.3541088104248</v>
+        <v>7.35410928726196</v>
       </c>
       <c r="H305" t="n">
         <v>8662340</v>
@@ -9243,7 +9243,7 @@
         <v>7.83500003814697</v>
       </c>
       <c r="G306" t="n">
-        <v>7.45400285720825</v>
+        <v>7.45400333404541</v>
       </c>
       <c r="H306" t="n">
         <v>8558245</v>
@@ -9359,7 +9359,7 @@
         <v>7.88500022888184</v>
       </c>
       <c r="G310" t="n">
-        <v>7.50157165527344</v>
+        <v>7.5015721321106</v>
       </c>
       <c r="H310" t="n">
         <v>9967793</v>
@@ -9475,7 +9475,7 @@
         <v>8.125</v>
       </c>
       <c r="G314" t="n">
-        <v>7.72990131378174</v>
+        <v>7.72990083694458</v>
       </c>
       <c r="H314" t="n">
         <v>8729316</v>
@@ -9562,7 +9562,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G317" t="n">
-        <v>7.93444681167603</v>
+        <v>7.93444633483887</v>
       </c>
       <c r="H317" t="n">
         <v>9638120</v>
@@ -9620,7 +9620,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G319" t="n">
-        <v>8.10569286346436</v>
+        <v>8.10569381713867</v>
       </c>
       <c r="H319" t="n">
         <v>9247079</v>
@@ -9649,7 +9649,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G320" t="n">
-        <v>8.0105562210083</v>
+        <v>8.01055526733398</v>
       </c>
       <c r="H320" t="n">
         <v>7285311</v>
@@ -9678,7 +9678,7 @@
         <v>8.45499992370605</v>
       </c>
       <c r="G321" t="n">
-        <v>8.04385375976562</v>
+        <v>8.04385471343994</v>
       </c>
       <c r="H321" t="n">
         <v>8408909</v>
@@ -9794,7 +9794,7 @@
         <v>8.13500022888184</v>
       </c>
       <c r="G325" t="n">
-        <v>7.73941469192505</v>
+        <v>7.73941516876221</v>
       </c>
       <c r="H325" t="n">
         <v>6312505</v>
@@ -9910,7 +9910,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G329" t="n">
-        <v>7.64903450012207</v>
+        <v>7.64903402328491</v>
       </c>
       <c r="H329" t="n">
         <v>5813093</v>
@@ -9939,7 +9939,7 @@
         <v>8.04500007629395</v>
       </c>
       <c r="G330" t="n">
-        <v>7.65379095077515</v>
+        <v>7.6537914276123</v>
       </c>
       <c r="H330" t="n">
         <v>5005452</v>
@@ -10084,7 +10084,7 @@
         <v>7.875</v>
       </c>
       <c r="G335" t="n">
-        <v>7.49205780029297</v>
+        <v>7.49205827713013</v>
       </c>
       <c r="H335" t="n">
         <v>7752172</v>
@@ -10142,7 +10142,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G337" t="n">
-        <v>7.87736320495605</v>
+        <v>7.87736368179321</v>
       </c>
       <c r="H337" t="n">
         <v>9607132</v>
@@ -10403,7 +10403,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G346" t="n">
-        <v>8.50526905059814</v>
+        <v>8.50527000427246</v>
       </c>
       <c r="H346" t="n">
         <v>9675664</v>
@@ -10548,7 +10548,7 @@
         <v>9.14500045776367</v>
       </c>
       <c r="G351" t="n">
-        <v>8.70030117034912</v>
+        <v>8.70030212402344</v>
       </c>
       <c r="H351" t="n">
         <v>9357770</v>
@@ -10751,7 +10751,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G358" t="n">
-        <v>8.2388858795166</v>
+        <v>8.23888492584229</v>
       </c>
       <c r="H358" t="n">
         <v>7073837</v>
@@ -10809,7 +10809,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G360" t="n">
-        <v>8.05812454223633</v>
+        <v>8.05812549591064</v>
       </c>
       <c r="H360" t="n">
         <v>6620743</v>
@@ -10838,7 +10838,7 @@
         <v>8.3100004196167</v>
       </c>
       <c r="G361" t="n">
-        <v>7.90590524673462</v>
+        <v>7.90590572357178</v>
       </c>
       <c r="H361" t="n">
         <v>14291998</v>
@@ -10896,7 +10896,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G363" t="n">
-        <v>7.93444681167603</v>
+        <v>7.93444633483887</v>
       </c>
       <c r="H363" t="n">
         <v>6865591</v>
@@ -11012,7 +11012,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G367" t="n">
-        <v>7.88687753677368</v>
+        <v>7.88687801361084</v>
       </c>
       <c r="H367" t="n">
         <v>7688881</v>
@@ -11041,7 +11041,7 @@
         <v>8.3100004196167</v>
       </c>
       <c r="G368" t="n">
-        <v>7.90590524673462</v>
+        <v>7.90590572357178</v>
       </c>
       <c r="H368" t="n">
         <v>8382176</v>
@@ -11070,7 +11070,7 @@
         <v>8.25</v>
       </c>
       <c r="G369" t="n">
-        <v>7.84882259368896</v>
+        <v>7.84882211685181</v>
       </c>
       <c r="H369" t="n">
         <v>8979733</v>
@@ -11099,7 +11099,7 @@
         <v>8.27499961853027</v>
       </c>
       <c r="G370" t="n">
-        <v>7.87260627746582</v>
+        <v>7.87260675430298</v>
       </c>
       <c r="H370" t="n">
         <v>7573261</v>
@@ -11128,7 +11128,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G371" t="n">
-        <v>7.91541814804077</v>
+        <v>7.91541862487793</v>
       </c>
       <c r="H371" t="n">
         <v>7773160</v>
@@ -11157,7 +11157,7 @@
         <v>8.33500003814697</v>
       </c>
       <c r="G372" t="n">
-        <v>7.92968988418579</v>
+        <v>7.92968940734863</v>
       </c>
       <c r="H372" t="n">
         <v>10290370</v>
@@ -11186,7 +11186,7 @@
         <v>8.25</v>
       </c>
       <c r="G373" t="n">
-        <v>7.84882259368896</v>
+        <v>7.84882211685181</v>
       </c>
       <c r="H373" t="n">
         <v>7754055</v>
@@ -11273,7 +11273,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G376" t="n">
-        <v>7.88687753677368</v>
+        <v>7.88687801361084</v>
       </c>
       <c r="H376" t="n">
         <v>5684368</v>
@@ -11302,7 +11302,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G377" t="n">
-        <v>7.91541814804077</v>
+        <v>7.91541862487793</v>
       </c>
       <c r="H377" t="n">
         <v>7730283</v>
@@ -11331,7 +11331,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G378" t="n">
-        <v>7.82979536056519</v>
+        <v>7.82979440689087</v>
       </c>
       <c r="H378" t="n">
         <v>6359602</v>
@@ -11418,7 +11418,7 @@
         <v>8.0649995803833</v>
       </c>
       <c r="G381" t="n">
-        <v>7.67281818389893</v>
+        <v>7.67281866073608</v>
       </c>
       <c r="H381" t="n">
         <v>6950390</v>
@@ -11534,7 +11534,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G385" t="n">
-        <v>7.82979536056519</v>
+        <v>7.82979440689087</v>
       </c>
       <c r="H385" t="n">
         <v>6247925</v>
@@ -11592,7 +11592,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G387" t="n">
-        <v>7.63000774383545</v>
+        <v>7.63000726699829</v>
       </c>
       <c r="H387" t="n">
         <v>5489232</v>
@@ -11621,7 +11621,7 @@
         <v>8.04500007629395</v>
       </c>
       <c r="G388" t="n">
-        <v>7.65379095077515</v>
+        <v>7.6537914276123</v>
       </c>
       <c r="H388" t="n">
         <v>6520553</v>
@@ -11708,7 +11708,7 @@
         <v>7.88500022888184</v>
       </c>
       <c r="G391" t="n">
-        <v>7.50157165527344</v>
+        <v>7.5015721321106</v>
       </c>
       <c r="H391" t="n">
         <v>13737506</v>
@@ -11766,7 +11766,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G393" t="n">
-        <v>7.8678503036499</v>
+        <v>7.86785078048706</v>
       </c>
       <c r="H393" t="n">
         <v>13345067</v>
@@ -11795,7 +11795,7 @@
         <v>8.04500007629395</v>
       </c>
       <c r="G394" t="n">
-        <v>7.65379095077515</v>
+        <v>7.6537914276123</v>
       </c>
       <c r="H394" t="n">
         <v>12204969</v>
@@ -11940,7 +11940,7 @@
         <v>8.125</v>
       </c>
       <c r="G399" t="n">
-        <v>7.72990131378174</v>
+        <v>7.72990083694458</v>
       </c>
       <c r="H399" t="n">
         <v>8832091</v>
@@ -12056,7 +12056,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G403" t="n">
-        <v>8.2388858795166</v>
+        <v>8.23888492584229</v>
       </c>
       <c r="H403" t="n">
         <v>8102311</v>
@@ -12114,7 +12114,7 @@
         <v>8.70499992370605</v>
       </c>
       <c r="G405" t="n">
-        <v>8.28169631958008</v>
+        <v>8.28169727325439</v>
       </c>
       <c r="H405" t="n">
         <v>9759736</v>
@@ -12201,7 +12201,7 @@
         <v>8.70499992370605</v>
       </c>
       <c r="G408" t="n">
-        <v>8.28169631958008</v>
+        <v>8.28169727325439</v>
       </c>
       <c r="H408" t="n">
         <v>5695609</v>
@@ -12404,7 +12404,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G415" t="n">
-        <v>8.05812454223633</v>
+        <v>8.05812549591064</v>
       </c>
       <c r="H415" t="n">
         <v>4472224</v>
@@ -12491,7 +12491,7 @@
         <v>8.33500003814697</v>
       </c>
       <c r="G418" t="n">
-        <v>7.92968988418579</v>
+        <v>7.92968940734863</v>
       </c>
       <c r="H418" t="n">
         <v>4935773</v>
@@ -12520,7 +12520,7 @@
         <v>8.27499961853027</v>
       </c>
       <c r="G419" t="n">
-        <v>7.87260627746582</v>
+        <v>7.87260675430298</v>
       </c>
       <c r="H419" t="n">
         <v>4715292</v>
@@ -12752,7 +12752,7 @@
         <v>8.04500007629395</v>
       </c>
       <c r="G427" t="n">
-        <v>7.65379095077515</v>
+        <v>7.6537914276123</v>
       </c>
       <c r="H427" t="n">
         <v>6232506</v>
@@ -12810,7 +12810,7 @@
         <v>7.83500003814697</v>
       </c>
       <c r="G429" t="n">
-        <v>7.45400285720825</v>
+        <v>7.45400333404541</v>
       </c>
       <c r="H429" t="n">
         <v>6232104</v>
@@ -12984,7 +12984,7 @@
         <v>7.88500022888184</v>
       </c>
       <c r="G435" t="n">
-        <v>7.50157165527344</v>
+        <v>7.5015721321106</v>
       </c>
       <c r="H435" t="n">
         <v>6028869</v>
@@ -13129,7 +13129,7 @@
         <v>8.02499961853027</v>
       </c>
       <c r="G440" t="n">
-        <v>7.63476371765137</v>
+        <v>7.63476324081421</v>
       </c>
       <c r="H440" t="n">
         <v>11093394</v>
@@ -13187,7 +13187,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G442" t="n">
-        <v>7.57292461395264</v>
+        <v>7.57292509078979</v>
       </c>
       <c r="H442" t="n">
         <v>6659325</v>
@@ -13274,7 +13274,7 @@
         <v>7.93499994277954</v>
       </c>
       <c r="G445" t="n">
-        <v>7.54914045333862</v>
+        <v>7.54913997650146</v>
       </c>
       <c r="H445" t="n">
         <v>4915478</v>
@@ -13332,7 +13332,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G447" t="n">
-        <v>7.59195184707642</v>
+        <v>7.59195232391357</v>
       </c>
       <c r="H447" t="n">
         <v>9449306</v>
@@ -13535,7 +13535,7 @@
         <v>7.63500022888184</v>
       </c>
       <c r="G454" t="n">
-        <v>7.26372861862183</v>
+        <v>7.26372909545898</v>
       </c>
       <c r="H454" t="n">
         <v>6637000</v>
@@ -13564,7 +13564,7 @@
         <v>7.54500007629395</v>
       </c>
       <c r="G455" t="n">
-        <v>7.17810487747192</v>
+        <v>7.17810535430908</v>
       </c>
       <c r="H455" t="n">
         <v>8006633</v>
@@ -13680,7 +13680,7 @@
         <v>7.625</v>
       </c>
       <c r="G459" t="n">
-        <v>7.25421476364136</v>
+        <v>7.25421524047852</v>
       </c>
       <c r="H459" t="n">
         <v>9352175</v>
@@ -13796,7 +13796,7 @@
         <v>7.68499994277954</v>
       </c>
       <c r="G463" t="n">
-        <v>7.31129741668701</v>
+        <v>7.31129693984985</v>
       </c>
       <c r="H463" t="n">
         <v>11433018</v>
@@ -14057,7 +14057,7 @@
         <v>7.63500022888184</v>
       </c>
       <c r="G472" t="n">
-        <v>7.26372861862183</v>
+        <v>7.26372909545898</v>
       </c>
       <c r="H472" t="n">
         <v>12393241</v>
@@ -14173,7 +14173,7 @@
         <v>7.35500001907349</v>
       </c>
       <c r="G476" t="n">
-        <v>6.99734449386597</v>
+        <v>6.99734401702881</v>
       </c>
       <c r="H476" t="n">
         <v>10343796</v>
@@ -14260,7 +14260,7 @@
         <v>6.89499998092651</v>
       </c>
       <c r="G479" t="n">
-        <v>6.55971336364746</v>
+        <v>6.5597128868103</v>
       </c>
       <c r="H479" t="n">
         <v>18049941</v>
@@ -14318,7 +14318,7 @@
         <v>6.81500005722046</v>
       </c>
       <c r="G481" t="n">
-        <v>6.48360347747803</v>
+        <v>6.48360300064087</v>
       </c>
       <c r="H481" t="n">
         <v>19321011</v>
@@ -14347,7 +14347,7 @@
         <v>6.89499998092651</v>
       </c>
       <c r="G482" t="n">
-        <v>6.55971336364746</v>
+        <v>6.5597128868103</v>
       </c>
       <c r="H482" t="n">
         <v>13873115</v>
@@ -14579,7 +14579,7 @@
         <v>7.04500007629395</v>
       </c>
       <c r="G490" t="n">
-        <v>6.7024188041687</v>
+        <v>6.70241928100586</v>
       </c>
       <c r="H490" t="n">
         <v>8224257</v>
@@ -14695,7 +14695,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G494" t="n">
-        <v>6.71668910980225</v>
+        <v>6.7166895866394</v>
       </c>
       <c r="H494" t="n">
         <v>7676027</v>
@@ -14782,7 +14782,7 @@
         <v>7.46999979019165</v>
       </c>
       <c r="G497" t="n">
-        <v>7.10675239562988</v>
+        <v>7.10675191879272</v>
       </c>
       <c r="H497" t="n">
         <v>16327353</v>
@@ -14811,7 +14811,7 @@
         <v>7.54500007629395</v>
       </c>
       <c r="G498" t="n">
-        <v>7.17810487747192</v>
+        <v>7.17810535430908</v>
       </c>
       <c r="H498" t="n">
         <v>9765474</v>
@@ -14927,7 +14927,7 @@
         <v>7.2649998664856</v>
       </c>
       <c r="G502" t="n">
-        <v>6.91172075271606</v>
+        <v>6.91172027587891</v>
       </c>
       <c r="H502" t="n">
         <v>12983601</v>
@@ -14985,7 +14985,7 @@
         <v>7.34499979019165</v>
       </c>
       <c r="G504" t="n">
-        <v>6.9878306388855</v>
+        <v>6.98783016204834</v>
       </c>
       <c r="H504" t="n">
         <v>8029365</v>
@@ -15014,7 +15014,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G505" t="n">
-        <v>7.04015588760376</v>
+        <v>7.04015636444092</v>
       </c>
       <c r="H505" t="n">
         <v>7758336</v>
@@ -15072,7 +15072,7 @@
         <v>7.34499979019165</v>
       </c>
       <c r="G507" t="n">
-        <v>6.9878306388855</v>
+        <v>6.98783016204834</v>
       </c>
       <c r="H507" t="n">
         <v>8653660</v>
@@ -15101,7 +15101,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G508" t="n">
-        <v>7.02112913131714</v>
+        <v>7.02112865447998</v>
       </c>
       <c r="H508" t="n">
         <v>5233596</v>
@@ -15159,7 +15159,7 @@
         <v>7.29500007629395</v>
       </c>
       <c r="G510" t="n">
-        <v>6.94026184082031</v>
+        <v>6.94026231765747</v>
       </c>
       <c r="H510" t="n">
         <v>4579894</v>
@@ -15188,7 +15188,7 @@
         <v>7.20499992370605</v>
       </c>
       <c r="G511" t="n">
-        <v>6.85463809967041</v>
+        <v>6.85463857650757</v>
       </c>
       <c r="H511" t="n">
         <v>4245157</v>
@@ -15217,7 +15217,7 @@
         <v>7.25500011444092</v>
       </c>
       <c r="G512" t="n">
-        <v>6.90220737457275</v>
+        <v>6.9022068977356</v>
       </c>
       <c r="H512" t="n">
         <v>6607233</v>
@@ -15246,7 +15246,7 @@
         <v>7.25</v>
       </c>
       <c r="G513" t="n">
-        <v>6.89745044708252</v>
+        <v>6.89744997024536</v>
       </c>
       <c r="H513" t="n">
         <v>5483915</v>
@@ -15275,7 +15275,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G514" t="n">
-        <v>6.98307418823242</v>
+        <v>6.98307371139526</v>
       </c>
       <c r="H514" t="n">
         <v>5974047</v>
@@ -15304,7 +15304,7 @@
         <v>7.38500022888184</v>
       </c>
       <c r="G515" t="n">
-        <v>7.02588558197021</v>
+        <v>7.02588605880737</v>
       </c>
       <c r="H515" t="n">
         <v>5887106</v>
@@ -15449,7 +15449,7 @@
         <v>7.43499994277954</v>
       </c>
       <c r="G520" t="n">
-        <v>7.0734543800354</v>
+        <v>7.07345390319824</v>
       </c>
       <c r="H520" t="n">
         <v>6198087</v>
@@ -15478,7 +15478,7 @@
         <v>7.38500022888184</v>
       </c>
       <c r="G521" t="n">
-        <v>7.02588558197021</v>
+        <v>7.02588605880737</v>
       </c>
       <c r="H521" t="n">
         <v>5952155</v>
@@ -15739,7 +15739,7 @@
         <v>7.20499992370605</v>
       </c>
       <c r="G530" t="n">
-        <v>6.85463809967041</v>
+        <v>6.85463857650757</v>
       </c>
       <c r="H530" t="n">
         <v>8180429</v>
@@ -15971,7 +15971,7 @@
         <v>7.21199989318848</v>
       </c>
       <c r="G538" t="n">
-        <v>6.86129808425903</v>
+        <v>6.86129760742188</v>
       </c>
       <c r="H538" t="n">
         <v>18503191</v>
@@ -16029,7 +16029,7 @@
         <v>6.98799991607666</v>
       </c>
       <c r="G540" t="n">
-        <v>6.64819049835205</v>
+        <v>6.64819097518921</v>
       </c>
       <c r="H540" t="n">
         <v>10998838</v>
@@ -16116,7 +16116,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G543" t="n">
-        <v>6.5454421043396</v>
+        <v>6.54544258117676</v>
       </c>
       <c r="H543" t="n">
         <v>9422768</v>
@@ -16261,7 +16261,7 @@
         <v>7.19600009918213</v>
       </c>
       <c r="G548" t="n">
-        <v>6.84607648849487</v>
+        <v>6.84607601165771</v>
       </c>
       <c r="H548" t="n">
         <v>13117904</v>
@@ -16348,7 +16348,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G551" t="n">
-        <v>7.02112913131714</v>
+        <v>7.02112865447998</v>
       </c>
       <c r="H551" t="n">
         <v>9959256</v>
@@ -16406,7 +16406,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G553" t="n">
-        <v>7.04015588760376</v>
+        <v>7.04015636444092</v>
       </c>
       <c r="H553" t="n">
         <v>10517150</v>
@@ -16435,7 +16435,7 @@
         <v>7.39799976348877</v>
       </c>
       <c r="G554" t="n">
-        <v>7.03825330734253</v>
+        <v>7.03825283050537</v>
       </c>
       <c r="H554" t="n">
         <v>10319173</v>
@@ -16464,7 +16464,7 @@
         <v>7.24599981307983</v>
       </c>
       <c r="G555" t="n">
-        <v>6.89364433288574</v>
+        <v>6.8936448097229</v>
       </c>
       <c r="H555" t="n">
         <v>12031756</v>
@@ -16493,7 +16493,7 @@
         <v>7.28800010681152</v>
       </c>
       <c r="G556" t="n">
-        <v>6.93360280990601</v>
+        <v>6.93360233306885</v>
       </c>
       <c r="H556" t="n">
         <v>9797279</v>
@@ -16580,7 +16580,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G559" t="n">
-        <v>7.82979536056519</v>
+        <v>7.82979440689087</v>
       </c>
       <c r="H559" t="n">
         <v>38979913</v>
@@ -16609,7 +16609,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G560" t="n">
-        <v>7.91541814804077</v>
+        <v>7.91541862487793</v>
       </c>
       <c r="H560" t="n">
         <v>29766429</v>
@@ -16638,7 +16638,7 @@
         <v>8.20199966430664</v>
       </c>
       <c r="G561" t="n">
-        <v>7.80315589904785</v>
+        <v>7.80315637588501</v>
       </c>
       <c r="H561" t="n">
         <v>15070704</v>
@@ -16667,7 +16667,7 @@
         <v>8.00800037384033</v>
       </c>
       <c r="G562" t="n">
-        <v>7.61859130859375</v>
+        <v>7.61859083175659</v>
       </c>
       <c r="H562" t="n">
         <v>17830195</v>
@@ -16696,7 +16696,7 @@
         <v>7.83199977874756</v>
       </c>
       <c r="G563" t="n">
-        <v>7.45114850997925</v>
+        <v>7.45114898681641</v>
       </c>
       <c r="H563" t="n">
         <v>15531686</v>
@@ -16754,7 +16754,7 @@
         <v>8.08800029754639</v>
       </c>
       <c r="G565" t="n">
-        <v>7.69470071792603</v>
+        <v>7.69470024108887</v>
       </c>
       <c r="H565" t="n">
         <v>13814697</v>
@@ -16783,7 +16783,7 @@
         <v>8.11600017547607</v>
       </c>
       <c r="G566" t="n">
-        <v>7.72133922576904</v>
+        <v>7.72133874893188</v>
       </c>
       <c r="H566" t="n">
         <v>11221597</v>
@@ -16899,7 +16899,7 @@
         <v>7.72599983215332</v>
       </c>
       <c r="G570" t="n">
-        <v>7.35030317306519</v>
+        <v>7.35030364990234</v>
       </c>
       <c r="H570" t="n">
         <v>11293097</v>
@@ -16957,7 +16957,7 @@
         <v>7.61399984359741</v>
       </c>
       <c r="G572" t="n">
-        <v>7.24375009536743</v>
+        <v>7.24374961853027</v>
       </c>
       <c r="H572" t="n">
         <v>8793021</v>
@@ -17073,7 +17073,7 @@
         <v>7.58199977874756</v>
       </c>
       <c r="G576" t="n">
-        <v>7.21330547332764</v>
+        <v>7.21330595016479</v>
       </c>
       <c r="H576" t="n">
         <v>7516325</v>
@@ -17247,7 +17247,7 @@
         <v>8.61200046539307</v>
       </c>
       <c r="G582" t="n">
-        <v>8.1932201385498</v>
+        <v>8.19321918487549</v>
       </c>
       <c r="H582" t="n">
         <v>21024100</v>
@@ -17334,7 +17334,7 @@
         <v>8.38199996948242</v>
       </c>
       <c r="G585" t="n">
-        <v>7.97440338134766</v>
+        <v>7.97440385818481</v>
       </c>
       <c r="H585" t="n">
         <v>16885220</v>
@@ -17421,7 +17421,7 @@
         <v>8.76200008392334</v>
       </c>
       <c r="G588" t="n">
-        <v>8.3359260559082</v>
+        <v>8.33592510223389</v>
       </c>
       <c r="H588" t="n">
         <v>19699701</v>
@@ -17450,7 +17450,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G589" t="n">
-        <v>8.27693939208984</v>
+        <v>8.27694034576416</v>
       </c>
       <c r="H589" t="n">
         <v>14602170</v>
@@ -17508,7 +17508,7 @@
         <v>8.26200008392334</v>
       </c>
       <c r="G591" t="n">
-        <v>7.86023950576782</v>
+        <v>7.86023902893066</v>
       </c>
       <c r="H591" t="n">
         <v>15384354</v>
@@ -17653,7 +17653,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G596" t="n">
-        <v>7.96298742294312</v>
+        <v>7.96298694610596</v>
       </c>
       <c r="H596" t="n">
         <v>11477450</v>
@@ -17740,7 +17740,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G599" t="n">
-        <v>8.0105562210083</v>
+        <v>8.01055526733398</v>
       </c>
       <c r="H599" t="n">
         <v>20166769</v>
@@ -17769,7 +17769,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G600" t="n">
-        <v>7.88687753677368</v>
+        <v>7.88687801361084</v>
       </c>
       <c r="H600" t="n">
         <v>10308492</v>
@@ -17914,7 +17914,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G605" t="n">
-        <v>7.3541088104248</v>
+        <v>7.35410928726196</v>
       </c>
       <c r="H605" t="n">
         <v>19807914</v>
@@ -17943,7 +17943,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G606" t="n">
-        <v>7.30654048919678</v>
+        <v>7.30654001235962</v>
       </c>
       <c r="H606" t="n">
         <v>13820402</v>
@@ -18030,7 +18030,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G609" t="n">
-        <v>7.02112913131714</v>
+        <v>7.02112865447998</v>
       </c>
       <c r="H609" t="n">
         <v>12987765</v>
@@ -18059,7 +18059,7 @@
         <v>7.31199979782104</v>
       </c>
       <c r="G610" t="n">
-        <v>6.95643472671509</v>
+        <v>6.95643520355225</v>
       </c>
       <c r="H610" t="n">
         <v>9821711</v>
@@ -18088,7 +18088,7 @@
         <v>7.30999994277954</v>
       </c>
       <c r="G611" t="n">
-        <v>6.95453214645386</v>
+        <v>6.95453262329102</v>
       </c>
       <c r="H611" t="n">
         <v>10969407</v>
@@ -18146,7 +18146,7 @@
         <v>7.14400005340576</v>
       </c>
       <c r="G613" t="n">
-        <v>6.79660511016846</v>
+        <v>6.7966046333313</v>
       </c>
       <c r="H613" t="n">
         <v>15383630</v>
@@ -18204,7 +18204,7 @@
         <v>7.01599979400635</v>
       </c>
       <c r="G615" t="n">
-        <v>6.67482900619507</v>
+        <v>6.67482852935791</v>
       </c>
       <c r="H615" t="n">
         <v>10762161</v>
@@ -18233,7 +18233,7 @@
         <v>6.87200021743774</v>
       </c>
       <c r="G616" t="n">
-        <v>6.53783178329468</v>
+        <v>6.53783130645752</v>
       </c>
       <c r="H616" t="n">
         <v>13644902</v>
@@ -18291,7 +18291,7 @@
         <v>6.98600006103516</v>
       </c>
       <c r="G618" t="n">
-        <v>6.64628839492798</v>
+        <v>6.64628791809082</v>
       </c>
       <c r="H618" t="n">
         <v>6146232</v>
@@ -18349,7 +18349,7 @@
         <v>6.91599988937378</v>
       </c>
       <c r="G620" t="n">
-        <v>6.5796914100647</v>
+        <v>6.57969188690186</v>
       </c>
       <c r="H620" t="n">
         <v>11484221</v>
@@ -18407,7 +18407,7 @@
         <v>6.72200012207031</v>
       </c>
       <c r="G622" t="n">
-        <v>6.39512538909912</v>
+        <v>6.39512586593628</v>
       </c>
       <c r="H622" t="n">
         <v>8616778</v>
@@ -18436,7 +18436,7 @@
         <v>6.87200021743774</v>
       </c>
       <c r="G623" t="n">
-        <v>6.53783178329468</v>
+        <v>6.53783130645752</v>
       </c>
       <c r="H623" t="n">
         <v>11592172</v>
@@ -18465,7 +18465,7 @@
         <v>6.85799980163574</v>
       </c>
       <c r="G624" t="n">
-        <v>6.52451229095459</v>
+        <v>6.52451181411743</v>
       </c>
       <c r="H624" t="n">
         <v>6763306</v>
@@ -18552,7 +18552,7 @@
         <v>6.7519998550415</v>
       </c>
       <c r="G627" t="n">
-        <v>6.42366695404053</v>
+        <v>6.42366647720337</v>
       </c>
       <c r="H627" t="n">
         <v>11827362</v>
@@ -18581,7 +18581,7 @@
         <v>6.76599979400635</v>
       </c>
       <c r="G628" t="n">
-        <v>6.43698596954346</v>
+        <v>6.4369854927063</v>
       </c>
       <c r="H628" t="n">
         <v>9517293</v>
@@ -18668,7 +18668,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G631" t="n">
-        <v>6.33614063262939</v>
+        <v>6.33614015579224</v>
       </c>
       <c r="H631" t="n">
         <v>8779408</v>
@@ -18784,7 +18784,7 @@
         <v>6.45599985122681</v>
       </c>
       <c r="G635" t="n">
-        <v>6.14206027984619</v>
+        <v>6.14206075668335</v>
       </c>
       <c r="H635" t="n">
         <v>13273047</v>
@@ -18842,7 +18842,7 @@
         <v>6.37400007247925</v>
       </c>
       <c r="G637" t="n">
-        <v>6.06404829025269</v>
+        <v>6.06404781341553</v>
       </c>
       <c r="H637" t="n">
         <v>8023540</v>
@@ -18871,7 +18871,7 @@
         <v>6.28200006484985</v>
       </c>
       <c r="G638" t="n">
-        <v>5.97652196884155</v>
+        <v>5.97652149200439</v>
       </c>
       <c r="H638" t="n">
         <v>5846091</v>
@@ -18929,7 +18929,7 @@
         <v>6.52400016784668</v>
       </c>
       <c r="G640" t="n">
-        <v>6.20675373077393</v>
+        <v>6.20675420761108</v>
       </c>
       <c r="H640" t="n">
         <v>5707740</v>
@@ -18987,7 +18987,7 @@
         <v>6.55200004577637</v>
       </c>
       <c r="G642" t="n">
-        <v>6.23339223861694</v>
+        <v>6.2333927154541</v>
       </c>
       <c r="H642" t="n">
         <v>6589583</v>
@@ -19045,7 +19045,7 @@
         <v>6.36600017547607</v>
       </c>
       <c r="G644" t="n">
-        <v>6.05643701553345</v>
+        <v>6.05643749237061</v>
       </c>
       <c r="H644" t="n">
         <v>10253469</v>
@@ -19074,7 +19074,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G645" t="n">
-        <v>6.01267433166504</v>
+        <v>6.01267385482788</v>
       </c>
       <c r="H645" t="n">
         <v>7151777</v>
@@ -19103,7 +19103,7 @@
         <v>6.14599990844727</v>
       </c>
       <c r="G646" t="n">
-        <v>5.84713459014893</v>
+        <v>5.84713506698608</v>
       </c>
       <c r="H646" t="n">
         <v>10297948</v>
@@ -19161,7 +19161,7 @@
         <v>6.07399988174438</v>
       </c>
       <c r="G648" t="n">
-        <v>5.77863597869873</v>
+        <v>5.77863645553589</v>
       </c>
       <c r="H648" t="n">
         <v>9314960</v>
@@ -19451,7 +19451,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G658" t="n">
-        <v>6.27905797958374</v>
+        <v>6.2790584564209</v>
       </c>
       <c r="H658" t="n">
         <v>10357178</v>
@@ -19509,7 +19509,7 @@
         <v>6.50400018692017</v>
       </c>
       <c r="G660" t="n">
-        <v>6.18772649765015</v>
+        <v>6.1877269744873</v>
       </c>
       <c r="H660" t="n">
         <v>7068352</v>
@@ -19538,7 +19538,7 @@
         <v>6.38199996948242</v>
       </c>
       <c r="G661" t="n">
-        <v>6.07165861129761</v>
+        <v>6.07165908813477</v>
       </c>
       <c r="H661" t="n">
         <v>7651712</v>
@@ -19944,7 +19944,7 @@
         <v>6</v>
       </c>
       <c r="G675" t="n">
-        <v>5.7082347869873</v>
+        <v>5.70823431015015</v>
       </c>
       <c r="H675" t="n">
         <v>8439947</v>
@@ -19973,7 +19973,7 @@
         <v>5.98799991607666</v>
       </c>
       <c r="G676" t="n">
-        <v>5.69681787490845</v>
+        <v>5.69681835174561</v>
       </c>
       <c r="H676" t="n">
         <v>6952501</v>
@@ -20002,7 +20002,7 @@
         <v>6.0019998550415</v>
       </c>
       <c r="G677" t="n">
-        <v>5.71013689041138</v>
+        <v>5.71013736724854</v>
       </c>
       <c r="H677" t="n">
         <v>3495139</v>
@@ -20031,7 +20031,7 @@
         <v>5.93800020217896</v>
       </c>
       <c r="G678" t="n">
-        <v>5.64925003051758</v>
+        <v>5.64924955368042</v>
       </c>
       <c r="H678" t="n">
         <v>6479576</v>
@@ -20118,7 +20118,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G681" t="n">
-        <v>5.22303438186646</v>
+        <v>5.22303485870361</v>
       </c>
       <c r="H681" t="n">
         <v>21485023</v>
@@ -20147,7 +20147,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G682" t="n">
-        <v>5.28011751174927</v>
+        <v>5.28011703491211</v>
       </c>
       <c r="H682" t="n">
         <v>7364755</v>
@@ -20176,7 +20176,7 @@
         <v>5.25</v>
       </c>
       <c r="G683" t="n">
-        <v>4.99470520019531</v>
+        <v>4.99470567703247</v>
       </c>
       <c r="H683" t="n">
         <v>33784406</v>
@@ -20350,7 +20350,7 @@
         <v>5.4060001373291</v>
       </c>
       <c r="G689" t="n">
-        <v>5.14311981201172</v>
+        <v>5.14311933517456</v>
       </c>
       <c r="H689" t="n">
         <v>9097960</v>
@@ -20466,7 +20466,7 @@
         <v>5.71400022506714</v>
       </c>
       <c r="G693" t="n">
-        <v>5.43614196777344</v>
+        <v>5.4361424446106</v>
       </c>
       <c r="H693" t="n">
         <v>14951668</v>
@@ -20524,7 +20524,7 @@
         <v>5.68599987030029</v>
       </c>
       <c r="G695" t="n">
-        <v>5.40950345993042</v>
+        <v>5.40950393676758</v>
       </c>
       <c r="H695" t="n">
         <v>8514680</v>
@@ -20553,7 +20553,7 @@
         <v>5.68599987030029</v>
       </c>
       <c r="G696" t="n">
-        <v>5.40950345993042</v>
+        <v>5.40950393676758</v>
       </c>
       <c r="H696" t="n">
         <v>11073700</v>
@@ -20582,7 +20582,7 @@
         <v>5.60599994659424</v>
       </c>
       <c r="G697" t="n">
-        <v>5.33339357376099</v>
+        <v>5.33339405059814</v>
       </c>
       <c r="H697" t="n">
         <v>9256009</v>
@@ -20611,7 +20611,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G698" t="n">
-        <v>5.30865812301636</v>
+        <v>5.30865859985352</v>
       </c>
       <c r="H698" t="n">
         <v>8345160</v>
@@ -20727,7 +20727,7 @@
         <v>4.95300006866455</v>
       </c>
       <c r="G702" t="n">
-        <v>4.71214771270752</v>
+        <v>4.71214818954468</v>
       </c>
       <c r="H702" t="n">
         <v>21571910</v>
@@ -20814,7 +20814,7 @@
         <v>4.95699977874756</v>
       </c>
       <c r="G705" t="n">
-        <v>4.71595335006714</v>
+        <v>4.71595287322998</v>
       </c>
       <c r="H705" t="n">
         <v>12269784</v>
@@ -20930,7 +20930,7 @@
         <v>5.03200006484985</v>
       </c>
       <c r="G709" t="n">
-        <v>4.78730583190918</v>
+        <v>4.78730630874634</v>
       </c>
       <c r="H709" t="n">
         <v>16574528</v>
@@ -20959,7 +20959,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G710" t="n">
-        <v>4.77588939666748</v>
+        <v>4.77588987350464</v>
       </c>
       <c r="H710" t="n">
         <v>13466859</v>
@@ -21133,7 +21133,7 @@
         <v>4.98600006103516</v>
       </c>
       <c r="G716" t="n">
-        <v>4.74354314804077</v>
+        <v>4.74354267120361</v>
       </c>
       <c r="H716" t="n">
         <v>11883638</v>
@@ -21365,7 +21365,7 @@
         <v>5.19199991226196</v>
       </c>
       <c r="G724" t="n">
-        <v>4.93952608108521</v>
+        <v>4.93952560424805</v>
       </c>
       <c r="H724" t="n">
         <v>11611382</v>
@@ -21452,7 +21452,7 @@
         <v>5.35400009155273</v>
       </c>
       <c r="G727" t="n">
-        <v>5.0936484336853</v>
+        <v>5.09364795684814</v>
       </c>
       <c r="H727" t="n">
         <v>5004868</v>
@@ -21510,7 +21510,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G729" t="n">
-        <v>5.08984279632568</v>
+        <v>5.08984231948853</v>
       </c>
       <c r="H729" t="n">
         <v>4502292</v>
@@ -21568,7 +21568,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G731" t="n">
-        <v>4.90908145904541</v>
+        <v>4.90908193588257</v>
       </c>
       <c r="H731" t="n">
         <v>20215708</v>
@@ -21597,7 +21597,7 @@
         <v>5.30399990081787</v>
       </c>
       <c r="G732" t="n">
-        <v>5.04607915878296</v>
+        <v>5.04607963562012</v>
       </c>
       <c r="H732" t="n">
         <v>21192969</v>
@@ -21655,7 +21655,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G734" t="n">
-        <v>4.95665073394775</v>
+        <v>4.9566502571106</v>
       </c>
       <c r="H734" t="n">
         <v>13016824</v>
@@ -21684,7 +21684,7 @@
         <v>5.16400003433228</v>
       </c>
       <c r="G735" t="n">
-        <v>4.91288709640503</v>
+        <v>4.91288757324219</v>
       </c>
       <c r="H735" t="n">
         <v>7858565</v>
@@ -21713,7 +21713,7 @@
         <v>5.26200008392334</v>
       </c>
       <c r="G736" t="n">
-        <v>5.00612211227417</v>
+        <v>5.00612163543701</v>
       </c>
       <c r="H736" t="n">
         <v>9329889</v>
@@ -22032,7 +22032,7 @@
         <v>5.74599981307983</v>
       </c>
       <c r="G747" t="n">
-        <v>5.46658611297607</v>
+        <v>5.46658563613892</v>
       </c>
       <c r="H747" t="n">
         <v>8767299</v>
@@ -22061,7 +22061,7 @@
         <v>5.69199991226196</v>
       </c>
       <c r="G748" t="n">
-        <v>5.41521215438843</v>
+        <v>5.41521167755127</v>
       </c>
       <c r="H748" t="n">
         <v>5268321</v>
@@ -22235,7 +22235,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G754" t="n">
-        <v>5.42282247543335</v>
+        <v>5.42282295227051</v>
       </c>
       <c r="H754" t="n">
         <v>8739136</v>
@@ -22380,7 +22380,7 @@
         <v>5.4520001411438</v>
       </c>
       <c r="G759" t="n">
-        <v>5.18688249588013</v>
+        <v>5.18688297271729</v>
       </c>
       <c r="H759" t="n">
         <v>9181301</v>
@@ -22409,7 +22409,7 @@
         <v>5.2020001411438</v>
       </c>
       <c r="G760" t="n">
-        <v>4.94903945922852</v>
+        <v>4.94903993606567</v>
       </c>
       <c r="H760" t="n">
         <v>11959404</v>
@@ -22467,7 +22467,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G762" t="n">
-        <v>4.58561515808105</v>
+        <v>4.58561563491821</v>
       </c>
       <c r="H762" t="n">
         <v>10213287</v>
@@ -22496,7 +22496,7 @@
         <v>4.83300018310547</v>
       </c>
       <c r="G763" t="n">
-        <v>4.59798336029053</v>
+        <v>4.59798288345337</v>
       </c>
       <c r="H763" t="n">
         <v>6812527</v>
@@ -22641,7 +22641,7 @@
         <v>5.06199979782104</v>
       </c>
       <c r="G768" t="n">
-        <v>4.81584739685059</v>
+        <v>4.81584692001343</v>
       </c>
       <c r="H768" t="n">
         <v>6948538</v>
@@ -22670,7 +22670,7 @@
         <v>4.95900011062622</v>
       </c>
       <c r="G769" t="n">
-        <v>4.71785640716553</v>
+        <v>4.71785593032837</v>
       </c>
       <c r="H769" t="n">
         <v>10542869</v>
@@ -22728,7 +22728,7 @@
         <v>5.00600004196167</v>
       </c>
       <c r="G771" t="n">
-        <v>4.76257038116455</v>
+        <v>4.76257085800171</v>
       </c>
       <c r="H771" t="n">
         <v>7037218</v>
@@ -22757,7 +22757,7 @@
         <v>5.01599979400635</v>
       </c>
       <c r="G772" t="n">
-        <v>4.77208375930786</v>
+        <v>4.77208423614502</v>
       </c>
       <c r="H772" t="n">
         <v>5703804</v>
@@ -22786,7 +22786,7 @@
         <v>5.02400016784668</v>
       </c>
       <c r="G773" t="n">
-        <v>4.77969551086426</v>
+        <v>4.7796950340271</v>
       </c>
       <c r="H773" t="n">
         <v>5160678</v>
@@ -22873,7 +22873,7 @@
         <v>4.88500022888184</v>
       </c>
       <c r="G776" t="n">
-        <v>4.64745473861694</v>
+        <v>4.64745426177979</v>
       </c>
       <c r="H776" t="n">
         <v>41676407</v>
@@ -22960,7 +22960,7 @@
         <v>4.48400020599365</v>
       </c>
       <c r="G779" t="n">
-        <v>4.26595401763916</v>
+        <v>4.26595449447632</v>
       </c>
       <c r="H779" t="n">
         <v>18215988</v>
@@ -22989,7 +22989,7 @@
         <v>4.52899980545044</v>
       </c>
       <c r="G780" t="n">
-        <v>4.30876588821411</v>
+        <v>4.30876541137695</v>
       </c>
       <c r="H780" t="n">
         <v>16117024</v>
@@ -23076,7 +23076,7 @@
         <v>4.58199977874756</v>
       </c>
       <c r="G783" t="n">
-        <v>4.35918855667114</v>
+        <v>4.35918807983398</v>
       </c>
       <c r="H783" t="n">
         <v>7847751</v>
@@ -23105,7 +23105,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G784" t="n">
-        <v>4.4048547744751</v>
+        <v>4.40485429763794</v>
       </c>
       <c r="H784" t="n">
         <v>11137135</v>
@@ -23221,7 +23221,7 @@
         <v>5.02400016784668</v>
       </c>
       <c r="G788" t="n">
-        <v>4.77969551086426</v>
+        <v>4.7796950340271</v>
       </c>
       <c r="H788" t="n">
         <v>9181552</v>
@@ -23308,7 +23308,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G791" t="n">
-        <v>4.49047803878784</v>
+        <v>4.49047756195068</v>
       </c>
       <c r="H791" t="n">
         <v>10923993</v>
@@ -23366,7 +23366,7 @@
         <v>4.81599998474121</v>
       </c>
       <c r="G793" t="n">
-        <v>4.58180999755859</v>
+        <v>4.58180952072144</v>
       </c>
       <c r="H793" t="n">
         <v>6859684</v>
@@ -23424,7 +23424,7 @@
         <v>4.8270001411438</v>
       </c>
       <c r="G795" t="n">
-        <v>4.59227514266968</v>
+        <v>4.59227466583252</v>
       </c>
       <c r="H795" t="n">
         <v>10108349</v>
@@ -23482,7 +23482,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G797" t="n">
-        <v>5.04227447509766</v>
+        <v>5.0422739982605</v>
       </c>
       <c r="H797" t="n">
         <v>14228495</v>
@@ -23627,7 +23627,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G802" t="n">
-        <v>5.09935617446899</v>
+        <v>5.09935665130615</v>
       </c>
       <c r="H802" t="n">
         <v>13548252</v>
@@ -23743,7 +23743,7 @@
         <v>5.32200002670288</v>
       </c>
       <c r="G806" t="n">
-        <v>5.06320381164551</v>
+        <v>5.06320428848267</v>
       </c>
       <c r="H806" t="n">
         <v>10595102</v>
@@ -23801,7 +23801,7 @@
         <v>5.5</v>
       </c>
       <c r="G808" t="n">
-        <v>5.23254823684692</v>
+        <v>5.23254871368408</v>
       </c>
       <c r="H808" t="n">
         <v>15904611</v>
@@ -23830,7 +23830,7 @@
         <v>5.64799976348877</v>
       </c>
       <c r="G809" t="n">
-        <v>5.37335109710693</v>
+        <v>5.37335157394409</v>
       </c>
       <c r="H809" t="n">
         <v>20711461</v>
@@ -23859,7 +23859,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G810" t="n">
-        <v>5.33719921112061</v>
+        <v>5.33719968795776</v>
       </c>
       <c r="H810" t="n">
         <v>21767982</v>
@@ -24091,7 +24091,7 @@
         <v>5.35599994659424</v>
       </c>
       <c r="G818" t="n">
-        <v>5.09555053710938</v>
+        <v>5.09555101394653</v>
       </c>
       <c r="H818" t="n">
         <v>10767173</v>
@@ -24149,7 +24149,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G820" t="n">
-        <v>5.04227447509766</v>
+        <v>5.0422739982605</v>
       </c>
       <c r="H820" t="n">
         <v>6355484</v>
@@ -24178,7 +24178,7 @@
         <v>5.25799989700317</v>
       </c>
       <c r="G821" t="n">
-        <v>5.00231647491455</v>
+        <v>5.00231599807739</v>
       </c>
       <c r="H821" t="n">
         <v>8320301</v>
@@ -24236,7 +24236,7 @@
         <v>5.31599998474121</v>
       </c>
       <c r="G823" t="n">
-        <v>5.05749607086182</v>
+        <v>5.05749559402466</v>
       </c>
       <c r="H823" t="n">
         <v>5741634</v>
@@ -24265,7 +24265,7 @@
         <v>5.35599994659424</v>
       </c>
       <c r="G824" t="n">
-        <v>5.09555053710938</v>
+        <v>5.09555101394653</v>
       </c>
       <c r="H824" t="n">
         <v>7192964</v>
@@ -24294,7 +24294,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G825" t="n">
-        <v>5.14692449569702</v>
+        <v>5.14692497253418</v>
       </c>
       <c r="H825" t="n">
         <v>6837351</v>
@@ -24381,7 +24381,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G828" t="n">
-        <v>5.08984279632568</v>
+        <v>5.08984231948853</v>
       </c>
       <c r="H828" t="n">
         <v>11314863</v>
@@ -24410,7 +24410,7 @@
         <v>5.40199995040894</v>
       </c>
       <c r="G829" t="n">
-        <v>5.1393141746521</v>
+        <v>5.13931369781494</v>
       </c>
       <c r="H829" t="n">
         <v>9915940</v>
@@ -24468,7 +24468,7 @@
         <v>5.36800003051758</v>
       </c>
       <c r="G831" t="n">
-        <v>5.10696744918823</v>
+        <v>5.10696697235107</v>
       </c>
       <c r="H831" t="n">
         <v>8336278</v>
@@ -24497,7 +24497,7 @@
         <v>5.33599996566772</v>
       </c>
       <c r="G832" t="n">
-        <v>5.07652378082275</v>
+        <v>5.0765233039856</v>
       </c>
       <c r="H832" t="n">
         <v>10088831</v>
@@ -24526,7 +24526,7 @@
         <v>5.34899997711182</v>
       </c>
       <c r="G833" t="n">
-        <v>5.08889150619507</v>
+        <v>5.08889102935791</v>
       </c>
       <c r="H833" t="n">
         <v>6378866</v>
@@ -24671,7 +24671,7 @@
         <v>5.25500011444092</v>
       </c>
       <c r="G838" t="n">
-        <v>4.99946212768555</v>
+        <v>4.99946260452271</v>
       </c>
       <c r="H838" t="n">
         <v>4873965</v>
@@ -24903,7 +24903,7 @@
         <v>4.98600006103516</v>
       </c>
       <c r="G846" t="n">
-        <v>4.74354314804077</v>
+        <v>4.74354267120361</v>
       </c>
       <c r="H846" t="n">
         <v>4443838</v>
@@ -24932,7 +24932,7 @@
         <v>4.95900011062622</v>
       </c>
       <c r="G847" t="n">
-        <v>4.71785640716553</v>
+        <v>4.71785593032837</v>
       </c>
       <c r="H847" t="n">
         <v>6501356</v>
@@ -25106,7 +25106,7 @@
         <v>4.67199993133545</v>
       </c>
       <c r="G853" t="n">
-        <v>4.44481229782104</v>
+        <v>4.44481182098389</v>
       </c>
       <c r="H853" t="n">
         <v>6493676</v>
@@ -25193,7 +25193,7 @@
         <v>4.45800018310547</v>
       </c>
       <c r="G856" t="n">
-        <v>4.24121809005737</v>
+        <v>4.24121856689453</v>
       </c>
       <c r="H856" t="n">
         <v>16786730</v>
@@ -25280,7 +25280,7 @@
         <v>4.57800006866455</v>
       </c>
       <c r="G859" t="n">
-        <v>4.35538339614868</v>
+        <v>4.35538291931152</v>
       </c>
       <c r="H859" t="n">
         <v>8359793</v>
@@ -25396,7 +25396,7 @@
         <v>4.38100004196167</v>
       </c>
       <c r="G863" t="n">
-        <v>4.1679630279541</v>
+        <v>4.16796255111694</v>
       </c>
       <c r="H863" t="n">
         <v>10295663</v>
@@ -25599,7 +25599,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G870" t="n">
-        <v>4.32398796081543</v>
+        <v>4.32398748397827</v>
       </c>
       <c r="H870" t="n">
         <v>10022461</v>
@@ -25802,7 +25802,7 @@
         <v>4.63100004196167</v>
       </c>
       <c r="G877" t="n">
-        <v>4.40580606460571</v>
+        <v>4.40580558776855</v>
       </c>
       <c r="H877" t="n">
         <v>6029498</v>
@@ -25947,7 +25947,7 @@
         <v>4.84200000762939</v>
       </c>
       <c r="G882" t="n">
-        <v>4.60654544830322</v>
+        <v>4.60654497146606</v>
       </c>
       <c r="H882" t="n">
         <v>15402357</v>
@@ -25976,7 +25976,7 @@
         <v>5.00899982452393</v>
       </c>
       <c r="G883" t="n">
-        <v>4.76542472839355</v>
+        <v>4.7654242515564</v>
       </c>
       <c r="H883" t="n">
         <v>21769809</v>
@@ -26150,7 +26150,7 @@
         <v>4.82800006866455</v>
       </c>
       <c r="G889" t="n">
-        <v>4.59322643280029</v>
+        <v>4.59322595596313</v>
       </c>
       <c r="H889" t="n">
         <v>7098552</v>
@@ -26179,7 +26179,7 @@
         <v>4.78299999237061</v>
       </c>
       <c r="G890" t="n">
-        <v>4.55041408538818</v>
+        <v>4.55041456222534</v>
       </c>
       <c r="H890" t="n">
         <v>4787528</v>
@@ -26208,7 +26208,7 @@
         <v>4.92199993133545</v>
       </c>
       <c r="G891" t="n">
-        <v>4.68265533447266</v>
+        <v>4.6826548576355</v>
       </c>
       <c r="H891" t="n">
         <v>9003798</v>
@@ -26266,7 +26266,7 @@
         <v>4.96299982070923</v>
       </c>
       <c r="G893" t="n">
-        <v>4.72166109085083</v>
+        <v>4.72166156768799</v>
       </c>
       <c r="H893" t="n">
         <v>6516566</v>
@@ -26411,7 +26411,7 @@
         <v>5.01300001144409</v>
       </c>
       <c r="G898" t="n">
-        <v>4.76923036575317</v>
+        <v>4.76922988891602</v>
       </c>
       <c r="H898" t="n">
         <v>5422412</v>
@@ -26527,7 +26527,7 @@
         <v>5.06099987030029</v>
       </c>
       <c r="G902" t="n">
-        <v>4.81489610671997</v>
+        <v>4.81489562988281</v>
       </c>
       <c r="H902" t="n">
         <v>4829287</v>
@@ -26556,7 +26556,7 @@
         <v>4.91099977493286</v>
       </c>
       <c r="G903" t="n">
-        <v>4.67218971252441</v>
+        <v>4.67219018936157</v>
       </c>
       <c r="H903" t="n">
         <v>8017443</v>
@@ -26614,7 +26614,7 @@
         <v>4.95699977874756</v>
       </c>
       <c r="G905" t="n">
-        <v>4.71595335006714</v>
+        <v>4.71595287322998</v>
       </c>
       <c r="H905" t="n">
         <v>5337026</v>
@@ -26730,7 +26730,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G909" t="n">
-        <v>4.98519134521484</v>
+        <v>4.985191822052</v>
       </c>
       <c r="H909" t="n">
         <v>10810457</v>
@@ -26788,7 +26788,7 @@
         <v>5.10599994659424</v>
       </c>
       <c r="G911" t="n">
-        <v>4.85770750045776</v>
+        <v>4.85770797729492</v>
       </c>
       <c r="H911" t="n">
         <v>5112107</v>
@@ -26846,7 +26846,7 @@
         <v>4.99599981307983</v>
       </c>
       <c r="G913" t="n">
-        <v>4.75305652618408</v>
+        <v>4.75305700302124</v>
       </c>
       <c r="H913" t="n">
         <v>6486219</v>
@@ -26904,7 +26904,7 @@
         <v>4.83400011062622</v>
       </c>
       <c r="G915" t="n">
-        <v>4.59893417358398</v>
+        <v>4.59893465042114</v>
       </c>
       <c r="H915" t="n">
         <v>6262907</v>
@@ -26933,7 +26933,7 @@
         <v>4.81599998474121</v>
       </c>
       <c r="G916" t="n">
-        <v>4.58180999755859</v>
+        <v>4.58180952072144</v>
       </c>
       <c r="H916" t="n">
         <v>4733278</v>
@@ -26962,7 +26962,7 @@
         <v>4.88800001144409</v>
       </c>
       <c r="G917" t="n">
-        <v>4.65030813217163</v>
+        <v>4.65030860900879</v>
       </c>
       <c r="H917" t="n">
         <v>5260695</v>
@@ -26991,7 +26991,7 @@
         <v>4.60200023651123</v>
       </c>
       <c r="G918" t="n">
-        <v>4.37821578979492</v>
+        <v>4.37821626663208</v>
       </c>
       <c r="H918" t="n">
         <v>11153136</v>
@@ -27136,7 +27136,7 @@
         <v>4.56500005722046</v>
       </c>
       <c r="G923" t="n">
-        <v>4.34301519393921</v>
+        <v>4.34301567077637</v>
       </c>
       <c r="H923" t="n">
         <v>5051334</v>
@@ -27165,7 +27165,7 @@
         <v>4.47200012207031</v>
       </c>
       <c r="G924" t="n">
-        <v>4.25453805923462</v>
+        <v>4.25453758239746</v>
       </c>
       <c r="H924" t="n">
         <v>5236518</v>
@@ -27223,7 +27223,7 @@
         <v>4.59800004959106</v>
       </c>
       <c r="G926" t="n">
-        <v>4.37441062927246</v>
+        <v>4.3744101524353</v>
       </c>
       <c r="H926" t="n">
         <v>5193190</v>
@@ -27252,7 +27252,7 @@
         <v>4.52600002288818</v>
       </c>
       <c r="G927" t="n">
-        <v>4.30591201782227</v>
+        <v>4.30591154098511</v>
       </c>
       <c r="H927" t="n">
         <v>4843476</v>
@@ -27484,7 +27484,7 @@
         <v>4.92600011825562</v>
       </c>
       <c r="G935" t="n">
-        <v>4.68646049499512</v>
+        <v>4.68646097183228</v>
       </c>
       <c r="H935" t="n">
         <v>7598993</v>
@@ -27513,7 +27513,7 @@
         <v>4.91800022125244</v>
       </c>
       <c r="G936" t="n">
-        <v>4.6788501739502</v>
+        <v>4.67884969711304</v>
       </c>
       <c r="H936" t="n">
         <v>8686085</v>
@@ -27687,7 +27687,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G942" t="n">
-        <v>4.95665073394775</v>
+        <v>4.9566502571106</v>
       </c>
       <c r="H942" t="n">
         <v>9765274</v>
@@ -27716,7 +27716,7 @@
         <v>5.16699981689453</v>
       </c>
       <c r="G943" t="n">
-        <v>4.91574144363403</v>
+        <v>4.91574096679688</v>
       </c>
       <c r="H943" t="n">
         <v>5370870</v>
@@ -27803,7 +27803,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G946" t="n">
-        <v>4.98519134521484</v>
+        <v>4.985191822052</v>
       </c>
       <c r="H946" t="n">
         <v>8525656</v>
@@ -27977,7 +27977,7 @@
         <v>5.19700002670288</v>
       </c>
       <c r="G952" t="n">
-        <v>4.94428253173828</v>
+        <v>4.94428300857544</v>
       </c>
       <c r="H952" t="n">
         <v>6264433</v>
@@ -28064,7 +28064,7 @@
         <v>4.94199991226196</v>
       </c>
       <c r="G955" t="n">
-        <v>4.70168209075928</v>
+        <v>4.70168256759644</v>
       </c>
       <c r="H955" t="n">
         <v>14155269</v>
@@ -28093,7 +28093,7 @@
         <v>4.96799993515015</v>
       </c>
       <c r="G956" t="n">
-        <v>4.72641801834106</v>
+        <v>4.72641849517822</v>
       </c>
       <c r="H956" t="n">
         <v>7492745</v>
@@ -28122,7 +28122,7 @@
         <v>4.97599983215332</v>
       </c>
       <c r="G957" t="n">
-        <v>4.7340292930603</v>
+        <v>4.73402881622314</v>
       </c>
       <c r="H957" t="n">
         <v>8539212</v>
@@ -28180,7 +28180,7 @@
         <v>5.06599998474121</v>
       </c>
       <c r="G959" t="n">
-        <v>4.81965303421021</v>
+        <v>4.81965255737305</v>
       </c>
       <c r="H959" t="n">
         <v>7079628</v>
@@ -28267,7 +28267,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G962" t="n">
-        <v>5.09935617446899</v>
+        <v>5.09935665130615</v>
       </c>
       <c r="H962" t="n">
         <v>9513376</v>
@@ -28354,7 +28354,7 @@
         <v>5.39400005340576</v>
       </c>
       <c r="G965" t="n">
-        <v>5.13170289993286</v>
+        <v>5.13170337677002</v>
       </c>
       <c r="H965" t="n">
         <v>7271483</v>
@@ -28412,7 +28412,7 @@
         <v>5.35400009155273</v>
       </c>
       <c r="G967" t="n">
-        <v>5.0936484336853</v>
+        <v>5.09364795684814</v>
       </c>
       <c r="H967" t="n">
         <v>7366786</v>
@@ -28528,7 +28528,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G971" t="n">
-        <v>5.06130123138428</v>
+        <v>5.06130170822144</v>
       </c>
       <c r="H971" t="n">
         <v>8251907</v>
@@ -28615,7 +28615,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G974" t="n">
-        <v>5.05178785324097</v>
+        <v>5.05178737640381</v>
       </c>
       <c r="H974" t="n">
         <v>5670673</v>
@@ -28905,7 +28905,7 @@
         <v>5.36299991607666</v>
       </c>
       <c r="G984" t="n">
-        <v>5.102210521698</v>
+        <v>5.10221004486084</v>
       </c>
       <c r="H984" t="n">
         <v>8375880</v>
@@ -28934,7 +28934,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G985" t="n">
-        <v>5.09935617446899</v>
+        <v>5.09935665130615</v>
       </c>
       <c r="H985" t="n">
         <v>6100265</v>
@@ -28963,7 +28963,7 @@
         <v>5.41300010681152</v>
       </c>
       <c r="G986" t="n">
-        <v>5.14977884292603</v>
+        <v>5.14977931976318</v>
       </c>
       <c r="H986" t="n">
         <v>11408179</v>
@@ -28992,7 +28992,7 @@
         <v>5.44099998474121</v>
       </c>
       <c r="G987" t="n">
-        <v>5.1764178276062</v>
+        <v>5.17641735076904</v>
       </c>
       <c r="H987" t="n">
         <v>5867671</v>
@@ -29050,7 +29050,7 @@
         <v>5.51800012588501</v>
       </c>
       <c r="G989" t="n">
-        <v>5.24967288970947</v>
+        <v>5.24967336654663</v>
       </c>
       <c r="H989" t="n">
         <v>8024179</v>
@@ -29079,7 +29079,7 @@
         <v>5.65100002288818</v>
       </c>
       <c r="G990" t="n">
-        <v>5.3762059211731</v>
+        <v>5.37620544433594</v>
       </c>
       <c r="H990" t="n">
         <v>12871995</v>
@@ -29166,7 +29166,7 @@
         <v>5.83900022506714</v>
       </c>
       <c r="G993" t="n">
-        <v>5.55506372451782</v>
+        <v>5.55506420135498</v>
       </c>
       <c r="H993" t="n">
         <v>5594077</v>
@@ -29224,7 +29224,7 @@
         <v>5.73899984359741</v>
       </c>
       <c r="G995" t="n">
-        <v>5.45992612838745</v>
+        <v>5.45992660522461</v>
       </c>
       <c r="H995" t="n">
         <v>8653313</v>
@@ -29253,7 +29253,7 @@
         <v>5.68599987030029</v>
       </c>
       <c r="G996" t="n">
-        <v>5.40950345993042</v>
+        <v>5.40950393676758</v>
       </c>
       <c r="H996" t="n">
         <v>4200712</v>
@@ -29340,7 +29340,7 @@
         <v>5.51200008392334</v>
       </c>
       <c r="G999" t="n">
-        <v>5.24396514892578</v>
+        <v>5.24396467208862</v>
       </c>
       <c r="H999" t="n">
         <v>5722620</v>
@@ -29601,7 +29601,7 @@
         <v>5.54199981689453</v>
       </c>
       <c r="G1008" t="n">
-        <v>5.27250576019287</v>
+        <v>5.27250623703003</v>
       </c>
       <c r="H1008" t="n">
         <v>4337873</v>
@@ -29630,7 +29630,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1009" t="n">
-        <v>5.28963088989258</v>
+        <v>5.28963041305542</v>
       </c>
       <c r="H1009" t="n">
         <v>5422481</v>
@@ -29659,7 +29659,7 @@
         <v>5.59499979019165</v>
       </c>
       <c r="G1010" t="n">
-        <v>5.3229284286499</v>
+        <v>5.32292890548706</v>
       </c>
       <c r="H1010" t="n">
         <v>7120475</v>
@@ -29688,7 +29688,7 @@
         <v>5.59499979019165</v>
       </c>
       <c r="G1011" t="n">
-        <v>5.3229284286499</v>
+        <v>5.32292890548706</v>
       </c>
       <c r="H1011" t="n">
         <v>8358777</v>
@@ -29833,7 +29833,7 @@
         <v>5.59499979019165</v>
       </c>
       <c r="G1016" t="n">
-        <v>5.3229284286499</v>
+        <v>5.32292890548706</v>
       </c>
       <c r="H1016" t="n">
         <v>3767783</v>
@@ -29978,7 +29978,7 @@
         <v>5.26300001144409</v>
       </c>
       <c r="G1021" t="n">
-        <v>5.00707340240479</v>
+        <v>5.00707292556763</v>
       </c>
       <c r="H1021" t="n">
         <v>11895409</v>
@@ -30065,7 +30065,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1024" t="n">
-        <v>4.8995680809021</v>
+        <v>4.89956855773926</v>
       </c>
       <c r="H1024" t="n">
         <v>9609886</v>
@@ -30094,7 +30094,7 @@
         <v>5.05900001525879</v>
       </c>
       <c r="G1025" t="n">
-        <v>4.81299304962158</v>
+        <v>4.81299352645874</v>
       </c>
       <c r="H1025" t="n">
         <v>6906988</v>
@@ -30152,7 +30152,7 @@
         <v>5.1230001449585</v>
       </c>
       <c r="G1027" t="n">
-        <v>4.8738808631897</v>
+        <v>4.87388134002686</v>
       </c>
       <c r="H1027" t="n">
         <v>5426424</v>
@@ -30181,7 +30181,7 @@
         <v>5.11399984359741</v>
       </c>
       <c r="G1028" t="n">
-        <v>4.865318775177</v>
+        <v>4.86531829833984</v>
       </c>
       <c r="H1028" t="n">
         <v>3560102</v>
@@ -30210,7 +30210,7 @@
         <v>5.06599998474121</v>
       </c>
       <c r="G1029" t="n">
-        <v>4.81965303421021</v>
+        <v>4.81965255737305</v>
       </c>
       <c r="H1029" t="n">
         <v>7067344</v>
@@ -30268,7 +30268,7 @@
         <v>4.94199991226196</v>
       </c>
       <c r="G1031" t="n">
-        <v>4.70168209075928</v>
+        <v>4.70168256759644</v>
       </c>
       <c r="H1031" t="n">
         <v>8681679</v>
@@ -30413,7 +30413,7 @@
         <v>5.05399990081787</v>
       </c>
       <c r="G1036" t="n">
-        <v>4.80823612213135</v>
+        <v>4.80823659896851</v>
       </c>
       <c r="H1036" t="n">
         <v>8898900</v>
@@ -30471,7 +30471,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1038" t="n">
-        <v>4.58561515808105</v>
+        <v>4.58561563491821</v>
       </c>
       <c r="H1038" t="n">
         <v>8979335</v>
@@ -30500,7 +30500,7 @@
         <v>4.91800022125244</v>
       </c>
       <c r="G1039" t="n">
-        <v>4.6788501739502</v>
+        <v>4.67884969711304</v>
       </c>
       <c r="H1039" t="n">
         <v>8140590</v>
@@ -30558,7 +30558,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1041" t="n">
-        <v>4.77588939666748</v>
+        <v>4.77588987350464</v>
       </c>
       <c r="H1041" t="n">
         <v>6949040</v>
@@ -30587,7 +30587,7 @@
         <v>4.94799995422363</v>
       </c>
       <c r="G1042" t="n">
-        <v>4.70739078521729</v>
+        <v>4.70739126205444</v>
       </c>
       <c r="H1042" t="n">
         <v>6830332</v>
@@ -30703,7 +30703,7 @@
         <v>5.25</v>
       </c>
       <c r="G1046" t="n">
-        <v>4.99470520019531</v>
+        <v>4.99470567703247</v>
       </c>
       <c r="H1046" t="n">
         <v>18341830</v>
@@ -31022,7 +31022,7 @@
         <v>5.00099992752075</v>
       </c>
       <c r="G1057" t="n">
-        <v>4.75781345367432</v>
+        <v>4.75781393051147</v>
       </c>
       <c r="H1057" t="n">
         <v>18342696</v>
@@ -31080,7 +31080,7 @@
         <v>4.77899980545044</v>
       </c>
       <c r="G1059" t="n">
-        <v>4.54660892486572</v>
+        <v>4.54660844802856</v>
       </c>
       <c r="H1059" t="n">
         <v>14134380</v>
@@ -31167,7 +31167,7 @@
         <v>4.32100009918213</v>
       </c>
       <c r="G1062" t="n">
-        <v>4.11088037490845</v>
+        <v>4.11088085174561</v>
       </c>
       <c r="H1062" t="n">
         <v>15034059</v>
@@ -31225,7 +31225,7 @@
         <v>3.67199993133545</v>
       </c>
       <c r="G1064" t="n">
-        <v>3.49343967437744</v>
+        <v>3.49343943595886</v>
       </c>
       <c r="H1064" t="n">
         <v>15459498</v>
@@ -31254,7 +31254,7 @@
         <v>3.81699991226196</v>
       </c>
       <c r="G1065" t="n">
-        <v>3.63138842582703</v>
+        <v>3.63138866424561</v>
       </c>
       <c r="H1065" t="n">
         <v>20006610</v>
@@ -31428,7 +31428,7 @@
         <v>3.7739999294281</v>
       </c>
       <c r="G1071" t="n">
-        <v>3.59047937393188</v>
+        <v>3.59047961235046</v>
       </c>
       <c r="H1071" t="n">
         <v>20539960</v>
@@ -31718,7 +31718,7 @@
         <v>3.79299998283386</v>
       </c>
       <c r="G1081" t="n">
-        <v>3.60855555534363</v>
+        <v>3.60855579376221</v>
       </c>
       <c r="H1081" t="n">
         <v>9112585</v>
@@ -31776,7 +31776,7 @@
         <v>3.92400002479553</v>
       </c>
       <c r="G1083" t="n">
-        <v>3.73318529129028</v>
+        <v>3.73318552970886</v>
       </c>
       <c r="H1083" t="n">
         <v>8125581</v>
@@ -31834,7 +31834,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G1085" t="n">
-        <v>3.61045861244202</v>
+        <v>3.61045837402344</v>
       </c>
       <c r="H1085" t="n">
         <v>9133043</v>
@@ -31921,7 +31921,7 @@
         <v>3.53399991989136</v>
       </c>
       <c r="G1088" t="n">
-        <v>3.36215019226074</v>
+        <v>3.36214995384216</v>
       </c>
       <c r="H1088" t="n">
         <v>10081010</v>
@@ -32182,7 +32182,7 @@
         <v>3.44600009918213</v>
       </c>
       <c r="G1097" t="n">
-        <v>3.27842950820923</v>
+        <v>3.27842974662781</v>
       </c>
       <c r="H1097" t="n">
         <v>7252885</v>
@@ -32211,7 +32211,7 @@
         <v>3.64400005340576</v>
       </c>
       <c r="G1098" t="n">
-        <v>3.466801404953</v>
+        <v>3.46680116653442</v>
       </c>
       <c r="H1098" t="n">
         <v>11382035</v>
@@ -32240,7 +32240,7 @@
         <v>3.6159999370575</v>
       </c>
       <c r="G1099" t="n">
-        <v>3.44016265869141</v>
+        <v>3.44016289710999</v>
       </c>
       <c r="H1099" t="n">
         <v>12293070</v>
@@ -32298,7 +32298,7 @@
         <v>3.53399991989136</v>
       </c>
       <c r="G1101" t="n">
-        <v>3.36215019226074</v>
+        <v>3.36214995384216</v>
       </c>
       <c r="H1101" t="n">
         <v>6018678</v>
@@ -32327,7 +32327,7 @@
         <v>3.50399994850159</v>
       </c>
       <c r="G1102" t="n">
-        <v>3.33360886573792</v>
+        <v>3.33360910415649</v>
       </c>
       <c r="H1102" t="n">
         <v>4601154</v>
@@ -32356,7 +32356,7 @@
         <v>3.42799997329712</v>
       </c>
       <c r="G1103" t="n">
-        <v>3.26130485534668</v>
+        <v>3.2613046169281</v>
       </c>
       <c r="H1103" t="n">
         <v>7123473</v>
@@ -32385,7 +32385,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1104" t="n">
-        <v>3.29174876213074</v>
+        <v>3.29174852371216</v>
       </c>
       <c r="H1104" t="n">
         <v>3356216</v>
@@ -32675,7 +32675,7 @@
         <v>3.20700001716614</v>
       </c>
       <c r="G1114" t="n">
-        <v>3.05105137825012</v>
+        <v>3.0510516166687</v>
       </c>
       <c r="H1114" t="n">
         <v>12499911</v>
@@ -32733,7 +32733,7 @@
         <v>3.30399990081787</v>
       </c>
       <c r="G1116" t="n">
-        <v>3.14333462715149</v>
+        <v>3.14333438873291</v>
       </c>
       <c r="H1116" t="n">
         <v>12389541</v>
@@ -32762,7 +32762,7 @@
         <v>3.3050000667572</v>
       </c>
       <c r="G1117" t="n">
-        <v>3.1442859172821</v>
+        <v>3.14428615570068</v>
       </c>
       <c r="H1117" t="n">
         <v>16377885</v>
@@ -32849,7 +32849,7 @@
         <v>3.41400003433228</v>
       </c>
       <c r="G1120" t="n">
-        <v>3.24798536300659</v>
+        <v>3.24798560142517</v>
       </c>
       <c r="H1120" t="n">
         <v>10515189</v>
@@ -32878,7 +32878,7 @@
         <v>3.52300000190735</v>
       </c>
       <c r="G1121" t="n">
-        <v>3.35168504714966</v>
+        <v>3.35168528556824</v>
       </c>
       <c r="H1121" t="n">
         <v>14830770</v>
@@ -33052,7 +33052,7 @@
         <v>3.71600008010864</v>
       </c>
       <c r="G1127" t="n">
-        <v>3.53530025482178</v>
+        <v>3.5353000164032</v>
       </c>
       <c r="H1127" t="n">
         <v>26938169</v>
@@ -33110,7 +33110,7 @@
         <v>3.53399991989136</v>
       </c>
       <c r="G1129" t="n">
-        <v>3.36215019226074</v>
+        <v>3.36214995384216</v>
       </c>
       <c r="H1129" t="n">
         <v>19235451</v>
@@ -33226,7 +33226,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1133" t="n">
-        <v>3.49153709411621</v>
+        <v>3.49153685569763</v>
       </c>
       <c r="H1133" t="n">
         <v>10659918</v>
@@ -80154,6 +80154,35 @@
         <v>2666797</v>
       </c>
       <c r="I2751" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2752">
+      <c r="A2752" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2752" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C2752" t="n">
+        <v>5.67399978637695</v>
+      </c>
+      <c r="D2752" t="n">
+        <v>5.75500011444092</v>
+      </c>
+      <c r="E2752" t="n">
+        <v>5.64200019836426</v>
+      </c>
+      <c r="F2752" t="n">
+        <v>5.67600011825562</v>
+      </c>
+      <c r="G2752" t="n">
+        <v>5.67600011825562</v>
+      </c>
+      <c r="H2752" t="n">
+        <v>2003141</v>
+      </c>
+      <c r="I2752" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TIT.MI.xlsx
+++ b/data/TIT.MI.xlsx
@@ -775,7 +775,7 @@
         <v>9.76500034332275</v>
       </c>
       <c r="G14" t="n">
-        <v>9.29015159606934</v>
+        <v>9.29015254974365</v>
       </c>
       <c r="H14" t="n">
         <v>12465433</v>
@@ -949,7 +949,7 @@
         <v>9.77000045776367</v>
       </c>
       <c r="G20" t="n">
-        <v>9.29490852355957</v>
+        <v>9.29490947723389</v>
       </c>
       <c r="H20" t="n">
         <v>21107831</v>
@@ -1152,7 +1152,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G27" t="n">
-        <v>7.99152803421021</v>
+        <v>7.99152851104736</v>
       </c>
       <c r="H27" t="n">
         <v>18362675</v>
@@ -1181,7 +1181,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G28" t="n">
-        <v>8.27694034576416</v>
+        <v>8.27693939208984</v>
       </c>
       <c r="H28" t="n">
         <v>22554264</v>
@@ -1239,7 +1239,7 @@
         <v>8.25500011444092</v>
       </c>
       <c r="G30" t="n">
-        <v>7.85357904434204</v>
+        <v>7.8535795211792</v>
       </c>
       <c r="H30" t="n">
         <v>17371217</v>
@@ -1268,7 +1268,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G31" t="n">
-        <v>8.17228889465332</v>
+        <v>8.17228984832764</v>
       </c>
       <c r="H31" t="n">
         <v>10187944</v>
@@ -1297,7 +1297,7 @@
         <v>8.76500034332275</v>
       </c>
       <c r="G32" t="n">
-        <v>8.33877944946289</v>
+        <v>8.33878040313721</v>
       </c>
       <c r="H32" t="n">
         <v>9462652</v>
@@ -1326,7 +1326,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G33" t="n">
-        <v>7.80125379562378</v>
+        <v>7.80125331878662</v>
       </c>
       <c r="H33" t="n">
         <v>28696243</v>
@@ -1587,7 +1587,7 @@
         <v>8.98999977111816</v>
       </c>
       <c r="G42" t="n">
-        <v>8.55283832550049</v>
+        <v>8.55283737182617</v>
       </c>
       <c r="H42" t="n">
         <v>10915001</v>
@@ -1645,7 +1645,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G44" t="n">
-        <v>8.98095512390137</v>
+        <v>8.98095607757568</v>
       </c>
       <c r="H44" t="n">
         <v>13756209</v>
@@ -1703,7 +1703,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G46" t="n">
-        <v>9.70399856567383</v>
+        <v>9.70399951934814</v>
       </c>
       <c r="H46" t="n">
         <v>20342560</v>
@@ -1732,7 +1732,7 @@
         <v>9.82499980926514</v>
       </c>
       <c r="G47" t="n">
-        <v>9.34723472595215</v>
+        <v>9.34723377227783</v>
       </c>
       <c r="H47" t="n">
         <v>11169591</v>
@@ -1790,7 +1790,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G49" t="n">
-        <v>9.64691734313965</v>
+        <v>9.64691638946533</v>
       </c>
       <c r="H49" t="n">
         <v>18523100</v>
@@ -1848,7 +1848,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G51" t="n">
-        <v>9.91330051422119</v>
+        <v>9.91330146789551</v>
       </c>
       <c r="H51" t="n">
         <v>10987806</v>
@@ -1877,7 +1877,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G52" t="n">
-        <v>9.81816387176514</v>
+        <v>9.81816291809082</v>
       </c>
       <c r="H52" t="n">
         <v>6496305</v>
@@ -1935,7 +1935,7 @@
         <v>10.3299999237061</v>
       </c>
       <c r="G54" t="n">
-        <v>9.82767772674561</v>
+        <v>9.82767677307129</v>
       </c>
       <c r="H54" t="n">
         <v>5795315</v>
@@ -2022,7 +2022,7 @@
         <v>10.4099998474121</v>
       </c>
       <c r="G57" t="n">
-        <v>9.90378665924072</v>
+        <v>9.90378761291504</v>
       </c>
       <c r="H57" t="n">
         <v>9694375</v>
@@ -2225,7 +2225,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G64" t="n">
-        <v>8.70505809783936</v>
+        <v>8.70505714416504</v>
       </c>
       <c r="H64" t="n">
         <v>14609221</v>
@@ -2283,7 +2283,7 @@
         <v>8.58500003814697</v>
       </c>
       <c r="G66" t="n">
-        <v>8.16753196716309</v>
+        <v>8.1675329208374</v>
       </c>
       <c r="H66" t="n">
         <v>11386012</v>
@@ -2312,7 +2312,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G67" t="n">
-        <v>8.18180370330811</v>
+        <v>8.18180274963379</v>
       </c>
       <c r="H67" t="n">
         <v>8994634</v>
@@ -2341,7 +2341,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G68" t="n">
-        <v>7.95347309112549</v>
+        <v>7.95347356796265</v>
       </c>
       <c r="H68" t="n">
         <v>8054619</v>
@@ -2399,7 +2399,7 @@
         <v>8.98999977111816</v>
       </c>
       <c r="G70" t="n">
-        <v>8.55283832550049</v>
+        <v>8.55283737182617</v>
       </c>
       <c r="H70" t="n">
         <v>7769877</v>
@@ -2718,7 +2718,7 @@
         <v>8.65499973297119</v>
       </c>
       <c r="G81" t="n">
-        <v>8.23412799835205</v>
+        <v>8.23412895202637</v>
       </c>
       <c r="H81" t="n">
         <v>11095524</v>
@@ -2776,7 +2776,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G83" t="n">
-        <v>8.25791358947754</v>
+        <v>8.25791263580322</v>
       </c>
       <c r="H83" t="n">
         <v>15796951</v>
@@ -2834,7 +2834,7 @@
         <v>8.46500015258789</v>
       </c>
       <c r="G85" t="n">
-        <v>8.05336856842041</v>
+        <v>8.05336761474609</v>
       </c>
       <c r="H85" t="n">
         <v>6739223</v>
@@ -2863,7 +2863,7 @@
         <v>8.36499977111816</v>
       </c>
       <c r="G86" t="n">
-        <v>7.95823001861572</v>
+        <v>7.95823049545288</v>
       </c>
       <c r="H86" t="n">
         <v>7439860</v>
@@ -2892,7 +2892,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G87" t="n">
-        <v>8.04861164093018</v>
+        <v>8.04861068725586</v>
       </c>
       <c r="H87" t="n">
         <v>6088332</v>
@@ -3037,7 +3037,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G92" t="n">
-        <v>8.05812549591064</v>
+        <v>8.05812454223633</v>
       </c>
       <c r="H92" t="n">
         <v>7818052</v>
@@ -3153,7 +3153,7 @@
         <v>8.48999977111816</v>
       </c>
       <c r="G96" t="n">
-        <v>8.07715225219727</v>
+        <v>8.07715129852295</v>
       </c>
       <c r="H96" t="n">
         <v>11841822</v>
@@ -3211,7 +3211,7 @@
         <v>8.30500030517578</v>
       </c>
       <c r="G98" t="n">
-        <v>7.90114879608154</v>
+        <v>7.90114784240723</v>
       </c>
       <c r="H98" t="n">
         <v>9583225</v>
@@ -3240,7 +3240,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G99" t="n">
-        <v>7.87736368179321</v>
+        <v>7.87736320495605</v>
       </c>
       <c r="H99" t="n">
         <v>7171888</v>
@@ -3327,7 +3327,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G102" t="n">
-        <v>7.91541862487793</v>
+        <v>7.91541814804077</v>
       </c>
       <c r="H102" t="n">
         <v>15847474</v>
@@ -3385,7 +3385,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G104" t="n">
-        <v>8.27694034576416</v>
+        <v>8.27693939208984</v>
       </c>
       <c r="H104" t="n">
         <v>8314517</v>
@@ -3675,7 +3675,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G114" t="n">
-        <v>7.82028150558472</v>
+        <v>7.82028198242188</v>
       </c>
       <c r="H114" t="n">
         <v>14068153</v>
@@ -3704,7 +3704,7 @@
         <v>7.91499996185303</v>
       </c>
       <c r="G115" t="n">
-        <v>7.53011274337769</v>
+        <v>7.53011322021484</v>
       </c>
       <c r="H115" t="n">
         <v>12688239</v>
@@ -3762,7 +3762,7 @@
         <v>7.59499979019165</v>
       </c>
       <c r="G117" t="n">
-        <v>7.22567319869995</v>
+        <v>7.22567367553711</v>
       </c>
       <c r="H117" t="n">
         <v>14127681</v>
@@ -3791,7 +3791,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G118" t="n">
-        <v>7.04015636444092</v>
+        <v>7.04015588760376</v>
       </c>
       <c r="H118" t="n">
         <v>12062526</v>
@@ -3936,7 +3936,7 @@
         <v>8.27499961853027</v>
       </c>
       <c r="G123" t="n">
-        <v>7.87260675430298</v>
+        <v>7.87260627746582</v>
       </c>
       <c r="H123" t="n">
         <v>12615589</v>
@@ -3994,7 +3994,7 @@
         <v>6.67500019073486</v>
       </c>
       <c r="G125" t="n">
-        <v>6.35041093826294</v>
+        <v>6.3504114151001</v>
       </c>
       <c r="H125" t="n">
         <v>23209498</v>
@@ -4052,7 +4052,7 @@
         <v>7.44500017166138</v>
       </c>
       <c r="G127" t="n">
-        <v>7.08296775817871</v>
+        <v>7.08296823501587</v>
       </c>
       <c r="H127" t="n">
         <v>14352211</v>
@@ -4110,7 +4110,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G129" t="n">
-        <v>7.04015636444092</v>
+        <v>7.04015588760376</v>
       </c>
       <c r="H129" t="n">
         <v>8980366</v>
@@ -4226,7 +4226,7 @@
         <v>6.33500003814697</v>
       </c>
       <c r="G133" t="n">
-        <v>6.02694416046143</v>
+        <v>6.02694463729858</v>
       </c>
       <c r="H133" t="n">
         <v>13905809</v>
@@ -4284,7 +4284,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G135" t="n">
-        <v>6.30759954452515</v>
+        <v>6.30759906768799</v>
       </c>
       <c r="H135" t="n">
         <v>6922559</v>
@@ -4313,7 +4313,7 @@
         <v>6.92500019073486</v>
       </c>
       <c r="G136" t="n">
-        <v>6.58825397491455</v>
+        <v>6.58825445175171</v>
       </c>
       <c r="H136" t="n">
         <v>10111814</v>
@@ -4429,7 +4429,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G140" t="n">
-        <v>6.60252523422241</v>
+        <v>6.60252475738525</v>
       </c>
       <c r="H140" t="n">
         <v>13382865</v>
@@ -4487,7 +4487,7 @@
         <v>6.86499977111816</v>
       </c>
       <c r="G142" t="n">
-        <v>6.53117179870605</v>
+        <v>6.5311713218689</v>
       </c>
       <c r="H142" t="n">
         <v>8811876</v>
@@ -4574,7 +4574,7 @@
         <v>7</v>
       </c>
       <c r="G145" t="n">
-        <v>6.65960693359375</v>
+        <v>6.65960741043091</v>
       </c>
       <c r="H145" t="n">
         <v>8398609</v>
@@ -4632,7 +4632,7 @@
         <v>7.46999979019165</v>
       </c>
       <c r="G147" t="n">
-        <v>7.10675191879272</v>
+        <v>7.10675239562988</v>
       </c>
       <c r="H147" t="n">
         <v>29073903</v>
@@ -4690,7 +4690,7 @@
         <v>7.63500022888184</v>
       </c>
       <c r="G149" t="n">
-        <v>7.26372909545898</v>
+        <v>7.26372861862183</v>
       </c>
       <c r="H149" t="n">
         <v>10594903</v>
@@ -4748,7 +4748,7 @@
         <v>7.44500017166138</v>
       </c>
       <c r="G151" t="n">
-        <v>7.08296775817871</v>
+        <v>7.08296823501587</v>
       </c>
       <c r="H151" t="n">
         <v>8748243</v>
@@ -4893,7 +4893,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G156" t="n">
-        <v>7.24945831298828</v>
+        <v>7.24945783615112</v>
       </c>
       <c r="H156" t="n">
         <v>4135572</v>
@@ -5125,7 +5125,7 @@
         <v>7.92999982833862</v>
       </c>
       <c r="G164" t="n">
-        <v>7.54438304901123</v>
+        <v>7.54438352584839</v>
       </c>
       <c r="H164" t="n">
         <v>4924973</v>
@@ -5212,7 +5212,7 @@
         <v>8.0649995803833</v>
       </c>
       <c r="G167" t="n">
-        <v>7.67281866073608</v>
+        <v>7.67281818389893</v>
       </c>
       <c r="H167" t="n">
         <v>5554419</v>
@@ -5299,7 +5299,7 @@
         <v>8.24499988555908</v>
       </c>
       <c r="G170" t="n">
-        <v>7.84406518936157</v>
+        <v>7.84406566619873</v>
       </c>
       <c r="H170" t="n">
         <v>6352724</v>
@@ -5328,7 +5328,7 @@
         <v>8.13500022888184</v>
       </c>
       <c r="G171" t="n">
-        <v>7.73941516876221</v>
+        <v>7.73941469192505</v>
       </c>
       <c r="H171" t="n">
         <v>7750471</v>
@@ -5357,7 +5357,7 @@
         <v>8.16499996185303</v>
       </c>
       <c r="G172" t="n">
-        <v>7.7679557800293</v>
+        <v>7.76795625686646</v>
       </c>
       <c r="H172" t="n">
         <v>8273298</v>
@@ -5386,7 +5386,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G173" t="n">
-        <v>7.80125379562378</v>
+        <v>7.80125331878662</v>
       </c>
       <c r="H173" t="n">
         <v>5239033</v>
@@ -5473,7 +5473,7 @@
         <v>8.04500007629395</v>
       </c>
       <c r="G176" t="n">
-        <v>7.6537914276123</v>
+        <v>7.65379095077515</v>
       </c>
       <c r="H176" t="n">
         <v>7646216</v>
@@ -5502,7 +5502,7 @@
         <v>8.16499996185303</v>
       </c>
       <c r="G177" t="n">
-        <v>7.7679557800293</v>
+        <v>7.76795625686646</v>
       </c>
       <c r="H177" t="n">
         <v>6137326</v>
@@ -5531,7 +5531,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G178" t="n">
-        <v>7.64903402328491</v>
+        <v>7.64903450012207</v>
       </c>
       <c r="H178" t="n">
         <v>7450630</v>
@@ -5560,7 +5560,7 @@
         <v>7.88500022888184</v>
       </c>
       <c r="G179" t="n">
-        <v>7.5015721321106</v>
+        <v>7.50157165527344</v>
       </c>
       <c r="H179" t="n">
         <v>10968844</v>
@@ -5647,7 +5647,7 @@
         <v>7.53499984741211</v>
       </c>
       <c r="G182" t="n">
-        <v>7.16859149932861</v>
+        <v>7.16859102249146</v>
       </c>
       <c r="H182" t="n">
         <v>8919248</v>
@@ -5734,7 +5734,7 @@
         <v>7.28499984741211</v>
       </c>
       <c r="G185" t="n">
-        <v>6.930748462677</v>
+        <v>6.93074798583984</v>
       </c>
       <c r="H185" t="n">
         <v>7139176</v>
@@ -5821,7 +5821,7 @@
         <v>7.63500022888184</v>
       </c>
       <c r="G188" t="n">
-        <v>7.26372909545898</v>
+        <v>7.26372861862183</v>
       </c>
       <c r="H188" t="n">
         <v>4604142</v>
@@ -5879,7 +5879,7 @@
         <v>7.34499979019165</v>
       </c>
       <c r="G190" t="n">
-        <v>6.98783016204834</v>
+        <v>6.9878306388855</v>
       </c>
       <c r="H190" t="n">
         <v>5769993</v>
@@ -5908,7 +5908,7 @@
         <v>7.49499988555908</v>
       </c>
       <c r="G191" t="n">
-        <v>7.1305365562439</v>
+        <v>7.13053607940674</v>
       </c>
       <c r="H191" t="n">
         <v>4422318</v>
@@ -5966,7 +5966,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G193" t="n">
-        <v>7.03064250946045</v>
+        <v>7.03064203262329</v>
       </c>
       <c r="H193" t="n">
         <v>9011031</v>
@@ -6053,7 +6053,7 @@
         <v>7.29500007629395</v>
       </c>
       <c r="G196" t="n">
-        <v>6.94026231765747</v>
+        <v>6.94026184082031</v>
       </c>
       <c r="H196" t="n">
         <v>10575030</v>
@@ -6140,7 +6140,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G199" t="n">
-        <v>7.04015636444092</v>
+        <v>7.04015588760376</v>
       </c>
       <c r="H199" t="n">
         <v>8616275</v>
@@ -6169,7 +6169,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G200" t="n">
-        <v>6.86890888214111</v>
+        <v>6.86890840530396</v>
       </c>
       <c r="H200" t="n">
         <v>8236131</v>
@@ -6227,7 +6227,7 @@
         <v>6.94500017166138</v>
       </c>
       <c r="G202" t="n">
-        <v>6.60728216171265</v>
+        <v>6.60728168487549</v>
       </c>
       <c r="H202" t="n">
         <v>17317483</v>
@@ -6314,7 +6314,7 @@
         <v>7.57499980926514</v>
       </c>
       <c r="G205" t="n">
-        <v>7.20664596557617</v>
+        <v>7.20664644241333</v>
       </c>
       <c r="H205" t="n">
         <v>13042674</v>
@@ -6372,7 +6372,7 @@
         <v>7.59499979019165</v>
       </c>
       <c r="G207" t="n">
-        <v>7.22567319869995</v>
+        <v>7.22567367553711</v>
       </c>
       <c r="H207" t="n">
         <v>5770682</v>
@@ -6401,7 +6401,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G208" t="n">
-        <v>7.35410928726196</v>
+        <v>7.3541088104248</v>
       </c>
       <c r="H208" t="n">
         <v>11041706</v>
@@ -6430,7 +6430,7 @@
         <v>7.92999982833862</v>
       </c>
       <c r="G209" t="n">
-        <v>7.54438304901123</v>
+        <v>7.54438352584839</v>
       </c>
       <c r="H209" t="n">
         <v>12562957</v>
@@ -6633,7 +6633,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G216" t="n">
-        <v>7.35410928726196</v>
+        <v>7.3541088104248</v>
       </c>
       <c r="H216" t="n">
         <v>11074256</v>
@@ -6662,7 +6662,7 @@
         <v>7.70499992370605</v>
       </c>
       <c r="G217" t="n">
-        <v>7.33032464981079</v>
+        <v>7.33032417297363</v>
       </c>
       <c r="H217" t="n">
         <v>6751462</v>
@@ -6778,7 +6778,7 @@
         <v>7.45499992370605</v>
       </c>
       <c r="G221" t="n">
-        <v>7.09248161315918</v>
+        <v>7.09248113632202</v>
       </c>
       <c r="H221" t="n">
         <v>19305315</v>
@@ -6952,7 +6952,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G227" t="n">
-        <v>6.67863416671753</v>
+        <v>6.67863464355469</v>
       </c>
       <c r="H227" t="n">
         <v>15148923</v>
@@ -6981,7 +6981,7 @@
         <v>6.86499977111816</v>
       </c>
       <c r="G228" t="n">
-        <v>6.53117179870605</v>
+        <v>6.5311713218689</v>
       </c>
       <c r="H228" t="n">
         <v>15141472</v>
@@ -7097,7 +7097,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G232" t="n">
-        <v>6.70717620849609</v>
+        <v>6.70717573165894</v>
       </c>
       <c r="H232" t="n">
         <v>6631825</v>
@@ -7126,7 +7126,7 @@
         <v>7.14499998092651</v>
       </c>
       <c r="G233" t="n">
-        <v>6.79755592346191</v>
+        <v>6.79755640029907</v>
       </c>
       <c r="H233" t="n">
         <v>7685848</v>
@@ -7300,7 +7300,7 @@
         <v>7</v>
       </c>
       <c r="G239" t="n">
-        <v>6.65960693359375</v>
+        <v>6.65960741043091</v>
       </c>
       <c r="H239" t="n">
         <v>16092872</v>
@@ -7358,7 +7358,7 @@
         <v>7.54500007629395</v>
       </c>
       <c r="G241" t="n">
-        <v>7.17810535430908</v>
+        <v>7.17810487747192</v>
       </c>
       <c r="H241" t="n">
         <v>14162922</v>
@@ -7416,7 +7416,7 @@
         <v>7.625</v>
       </c>
       <c r="G243" t="n">
-        <v>7.25421524047852</v>
+        <v>7.25421476364136</v>
       </c>
       <c r="H243" t="n">
         <v>7313055</v>
@@ -7561,7 +7561,7 @@
         <v>8.06999969482422</v>
       </c>
       <c r="G248" t="n">
-        <v>7.67757558822632</v>
+        <v>7.67757511138916</v>
       </c>
       <c r="H248" t="n">
         <v>19683266</v>
@@ -7648,7 +7648,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G251" t="n">
-        <v>7.99152803421021</v>
+        <v>7.99152851104736</v>
       </c>
       <c r="H251" t="n">
         <v>10995964</v>
@@ -7735,7 +7735,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G254" t="n">
-        <v>8.27694034576416</v>
+        <v>8.27693939208984</v>
       </c>
       <c r="H254" t="n">
         <v>7105744</v>
@@ -7764,7 +7764,7 @@
         <v>8.42500019073486</v>
       </c>
       <c r="G255" t="n">
-        <v>8.01531219482422</v>
+        <v>8.01531314849854</v>
       </c>
       <c r="H255" t="n">
         <v>7953684</v>
@@ -7822,7 +7822,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G257" t="n">
-        <v>7.96298694610596</v>
+        <v>7.96298742294312</v>
       </c>
       <c r="H257" t="n">
         <v>4473749</v>
@@ -7851,7 +7851,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G258" t="n">
-        <v>8.16277503967285</v>
+        <v>8.16277599334717</v>
       </c>
       <c r="H258" t="n">
         <v>6919849</v>
@@ -7938,7 +7938,7 @@
         <v>8.42500019073486</v>
       </c>
       <c r="G261" t="n">
-        <v>8.01531219482422</v>
+        <v>8.01531314849854</v>
       </c>
       <c r="H261" t="n">
         <v>8691609</v>
@@ -7996,7 +7996,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G263" t="n">
-        <v>7.82028150558472</v>
+        <v>7.82028198242188</v>
       </c>
       <c r="H263" t="n">
         <v>9698154</v>
@@ -8025,7 +8025,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G264" t="n">
-        <v>7.87736368179321</v>
+        <v>7.87736320495605</v>
       </c>
       <c r="H264" t="n">
         <v>8049414</v>
@@ -8054,7 +8054,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G265" t="n">
-        <v>8.04861164093018</v>
+        <v>8.04861068725586</v>
       </c>
       <c r="H265" t="n">
         <v>10193124</v>
@@ -8083,7 +8083,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G266" t="n">
-        <v>7.93444633483887</v>
+        <v>7.93444681167603</v>
       </c>
       <c r="H266" t="n">
         <v>5591385</v>
@@ -8141,7 +8141,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G268" t="n">
-        <v>8.10569381713867</v>
+        <v>8.10569286346436</v>
       </c>
       <c r="H268" t="n">
         <v>4819501</v>
@@ -8170,7 +8170,7 @@
         <v>8.375</v>
       </c>
       <c r="G269" t="n">
-        <v>7.96774387359619</v>
+        <v>7.96774482727051</v>
       </c>
       <c r="H269" t="n">
         <v>6854564</v>
@@ -8199,7 +8199,7 @@
         <v>8.3100004196167</v>
       </c>
       <c r="G270" t="n">
-        <v>7.90590572357178</v>
+        <v>7.90590524673462</v>
       </c>
       <c r="H270" t="n">
         <v>7624065</v>
@@ -8228,7 +8228,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G271" t="n">
-        <v>7.99152803421021</v>
+        <v>7.99152851104736</v>
       </c>
       <c r="H271" t="n">
         <v>15001217</v>
@@ -8257,7 +8257,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G272" t="n">
-        <v>8.04861164093018</v>
+        <v>8.04861068725586</v>
       </c>
       <c r="H272" t="n">
         <v>7357311</v>
@@ -8286,7 +8286,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G273" t="n">
-        <v>7.99152803421021</v>
+        <v>7.99152851104736</v>
       </c>
       <c r="H273" t="n">
         <v>6892052</v>
@@ -8315,7 +8315,7 @@
         <v>8.3100004196167</v>
       </c>
       <c r="G274" t="n">
-        <v>7.90590572357178</v>
+        <v>7.90590524673462</v>
       </c>
       <c r="H274" t="n">
         <v>10051498</v>
@@ -8344,7 +8344,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G275" t="n">
-        <v>7.82979440689087</v>
+        <v>7.82979536056519</v>
       </c>
       <c r="H275" t="n">
         <v>9477679</v>
@@ -8518,7 +8518,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G281" t="n">
-        <v>7.59195232391357</v>
+        <v>7.59195184707642</v>
       </c>
       <c r="H281" t="n">
         <v>6833809</v>
@@ -8634,7 +8634,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G285" t="n">
-        <v>7.79173994064331</v>
+        <v>7.79174041748047</v>
       </c>
       <c r="H285" t="n">
         <v>8180031</v>
@@ -8663,7 +8663,7 @@
         <v>8.25</v>
       </c>
       <c r="G286" t="n">
-        <v>7.84882211685181</v>
+        <v>7.84882259368896</v>
       </c>
       <c r="H286" t="n">
         <v>8035948</v>
@@ -8692,7 +8692,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G287" t="n">
-        <v>7.64903402328491</v>
+        <v>7.64903450012207</v>
       </c>
       <c r="H287" t="n">
         <v>9027559</v>
@@ -8750,7 +8750,7 @@
         <v>7.97499990463257</v>
       </c>
       <c r="G289" t="n">
-        <v>7.58719539642334</v>
+        <v>7.58719491958618</v>
       </c>
       <c r="H289" t="n">
         <v>7815676</v>
@@ -8808,7 +8808,7 @@
         <v>7.91499996185303</v>
       </c>
       <c r="G291" t="n">
-        <v>7.53011274337769</v>
+        <v>7.53011322021484</v>
       </c>
       <c r="H291" t="n">
         <v>6709166</v>
@@ -8895,7 +8895,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G294" t="n">
-        <v>7.3255672454834</v>
+        <v>7.32556772232056</v>
       </c>
       <c r="H294" t="n">
         <v>10570127</v>
@@ -8924,7 +8924,7 @@
         <v>7.59499979019165</v>
       </c>
       <c r="G295" t="n">
-        <v>7.22567319869995</v>
+        <v>7.22567367553711</v>
       </c>
       <c r="H295" t="n">
         <v>15446807</v>
@@ -9185,7 +9185,7 @@
         <v>7.79500007629395</v>
       </c>
       <c r="G304" t="n">
-        <v>7.41594839096069</v>
+        <v>7.41594791412354</v>
       </c>
       <c r="H304" t="n">
         <v>5768451</v>
@@ -9214,7 +9214,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G305" t="n">
-        <v>7.35410928726196</v>
+        <v>7.3541088104248</v>
       </c>
       <c r="H305" t="n">
         <v>8662340</v>
@@ -9243,7 +9243,7 @@
         <v>7.83500003814697</v>
       </c>
       <c r="G306" t="n">
-        <v>7.45400333404541</v>
+        <v>7.45400285720825</v>
       </c>
       <c r="H306" t="n">
         <v>8558245</v>
@@ -9359,7 +9359,7 @@
         <v>7.88500022888184</v>
       </c>
       <c r="G310" t="n">
-        <v>7.5015721321106</v>
+        <v>7.50157165527344</v>
       </c>
       <c r="H310" t="n">
         <v>9967793</v>
@@ -9475,7 +9475,7 @@
         <v>8.125</v>
       </c>
       <c r="G314" t="n">
-        <v>7.72990083694458</v>
+        <v>7.72990131378174</v>
       </c>
       <c r="H314" t="n">
         <v>8729316</v>
@@ -9562,7 +9562,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G317" t="n">
-        <v>7.93444633483887</v>
+        <v>7.93444681167603</v>
       </c>
       <c r="H317" t="n">
         <v>9638120</v>
@@ -9620,7 +9620,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G319" t="n">
-        <v>8.10569381713867</v>
+        <v>8.10569286346436</v>
       </c>
       <c r="H319" t="n">
         <v>9247079</v>
@@ -9649,7 +9649,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G320" t="n">
-        <v>8.01055526733398</v>
+        <v>8.0105562210083</v>
       </c>
       <c r="H320" t="n">
         <v>7285311</v>
@@ -9678,7 +9678,7 @@
         <v>8.45499992370605</v>
       </c>
       <c r="G321" t="n">
-        <v>8.04385471343994</v>
+        <v>8.04385375976562</v>
       </c>
       <c r="H321" t="n">
         <v>8408909</v>
@@ -9794,7 +9794,7 @@
         <v>8.13500022888184</v>
       </c>
       <c r="G325" t="n">
-        <v>7.73941516876221</v>
+        <v>7.73941469192505</v>
       </c>
       <c r="H325" t="n">
         <v>6312505</v>
@@ -9910,7 +9910,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G329" t="n">
-        <v>7.64903402328491</v>
+        <v>7.64903450012207</v>
       </c>
       <c r="H329" t="n">
         <v>5813093</v>
@@ -9939,7 +9939,7 @@
         <v>8.04500007629395</v>
       </c>
       <c r="G330" t="n">
-        <v>7.6537914276123</v>
+        <v>7.65379095077515</v>
       </c>
       <c r="H330" t="n">
         <v>5005452</v>
@@ -10084,7 +10084,7 @@
         <v>7.875</v>
       </c>
       <c r="G335" t="n">
-        <v>7.49205827713013</v>
+        <v>7.49205780029297</v>
       </c>
       <c r="H335" t="n">
         <v>7752172</v>
@@ -10142,7 +10142,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G337" t="n">
-        <v>7.87736368179321</v>
+        <v>7.87736320495605</v>
       </c>
       <c r="H337" t="n">
         <v>9607132</v>
@@ -10403,7 +10403,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G346" t="n">
-        <v>8.50527000427246</v>
+        <v>8.50526905059814</v>
       </c>
       <c r="H346" t="n">
         <v>9675664</v>
@@ -10548,7 +10548,7 @@
         <v>9.14500045776367</v>
       </c>
       <c r="G351" t="n">
-        <v>8.70030212402344</v>
+        <v>8.70030117034912</v>
       </c>
       <c r="H351" t="n">
         <v>9357770</v>
@@ -10751,7 +10751,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G358" t="n">
-        <v>8.23888492584229</v>
+        <v>8.2388858795166</v>
       </c>
       <c r="H358" t="n">
         <v>7073837</v>
@@ -10809,7 +10809,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G360" t="n">
-        <v>8.05812549591064</v>
+        <v>8.05812454223633</v>
       </c>
       <c r="H360" t="n">
         <v>6620743</v>
@@ -10838,7 +10838,7 @@
         <v>8.3100004196167</v>
       </c>
       <c r="G361" t="n">
-        <v>7.90590572357178</v>
+        <v>7.90590524673462</v>
       </c>
       <c r="H361" t="n">
         <v>14291998</v>
@@ -10896,7 +10896,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G363" t="n">
-        <v>7.93444633483887</v>
+        <v>7.93444681167603</v>
       </c>
       <c r="H363" t="n">
         <v>6865591</v>
@@ -11012,7 +11012,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G367" t="n">
-        <v>7.88687801361084</v>
+        <v>7.88687753677368</v>
       </c>
       <c r="H367" t="n">
         <v>7688881</v>
@@ -11041,7 +11041,7 @@
         <v>8.3100004196167</v>
       </c>
       <c r="G368" t="n">
-        <v>7.90590572357178</v>
+        <v>7.90590524673462</v>
       </c>
       <c r="H368" t="n">
         <v>8382176</v>
@@ -11070,7 +11070,7 @@
         <v>8.25</v>
       </c>
       <c r="G369" t="n">
-        <v>7.84882211685181</v>
+        <v>7.84882259368896</v>
       </c>
       <c r="H369" t="n">
         <v>8979733</v>
@@ -11099,7 +11099,7 @@
         <v>8.27499961853027</v>
       </c>
       <c r="G370" t="n">
-        <v>7.87260675430298</v>
+        <v>7.87260627746582</v>
       </c>
       <c r="H370" t="n">
         <v>7573261</v>
@@ -11128,7 +11128,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G371" t="n">
-        <v>7.91541862487793</v>
+        <v>7.91541814804077</v>
       </c>
       <c r="H371" t="n">
         <v>7773160</v>
@@ -11157,7 +11157,7 @@
         <v>8.33500003814697</v>
       </c>
       <c r="G372" t="n">
-        <v>7.92968940734863</v>
+        <v>7.92968988418579</v>
       </c>
       <c r="H372" t="n">
         <v>10290370</v>
@@ -11186,7 +11186,7 @@
         <v>8.25</v>
       </c>
       <c r="G373" t="n">
-        <v>7.84882211685181</v>
+        <v>7.84882259368896</v>
       </c>
       <c r="H373" t="n">
         <v>7754055</v>
@@ -11273,7 +11273,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G376" t="n">
-        <v>7.88687801361084</v>
+        <v>7.88687753677368</v>
       </c>
       <c r="H376" t="n">
         <v>5684368</v>
@@ -11302,7 +11302,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G377" t="n">
-        <v>7.91541862487793</v>
+        <v>7.91541814804077</v>
       </c>
       <c r="H377" t="n">
         <v>7730283</v>
@@ -11331,7 +11331,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G378" t="n">
-        <v>7.82979440689087</v>
+        <v>7.82979536056519</v>
       </c>
       <c r="H378" t="n">
         <v>6359602</v>
@@ -11418,7 +11418,7 @@
         <v>8.0649995803833</v>
       </c>
       <c r="G381" t="n">
-        <v>7.67281866073608</v>
+        <v>7.67281818389893</v>
       </c>
       <c r="H381" t="n">
         <v>6950390</v>
@@ -11534,7 +11534,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G385" t="n">
-        <v>7.82979440689087</v>
+        <v>7.82979536056519</v>
       </c>
       <c r="H385" t="n">
         <v>6247925</v>
@@ -11592,7 +11592,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G387" t="n">
-        <v>7.63000726699829</v>
+        <v>7.63000774383545</v>
       </c>
       <c r="H387" t="n">
         <v>5489232</v>
@@ -11621,7 +11621,7 @@
         <v>8.04500007629395</v>
       </c>
       <c r="G388" t="n">
-        <v>7.6537914276123</v>
+        <v>7.65379095077515</v>
       </c>
       <c r="H388" t="n">
         <v>6520553</v>
@@ -11708,7 +11708,7 @@
         <v>7.88500022888184</v>
       </c>
       <c r="G391" t="n">
-        <v>7.5015721321106</v>
+        <v>7.50157165527344</v>
       </c>
       <c r="H391" t="n">
         <v>13737506</v>
@@ -11766,7 +11766,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G393" t="n">
-        <v>7.86785078048706</v>
+        <v>7.8678503036499</v>
       </c>
       <c r="H393" t="n">
         <v>13345067</v>
@@ -11795,7 +11795,7 @@
         <v>8.04500007629395</v>
       </c>
       <c r="G394" t="n">
-        <v>7.6537914276123</v>
+        <v>7.65379095077515</v>
       </c>
       <c r="H394" t="n">
         <v>12204969</v>
@@ -11940,7 +11940,7 @@
         <v>8.125</v>
       </c>
       <c r="G399" t="n">
-        <v>7.72990083694458</v>
+        <v>7.72990131378174</v>
       </c>
       <c r="H399" t="n">
         <v>8832091</v>
@@ -12056,7 +12056,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G403" t="n">
-        <v>8.23888492584229</v>
+        <v>8.2388858795166</v>
       </c>
       <c r="H403" t="n">
         <v>8102311</v>
@@ -12114,7 +12114,7 @@
         <v>8.70499992370605</v>
       </c>
       <c r="G405" t="n">
-        <v>8.28169727325439</v>
+        <v>8.28169631958008</v>
       </c>
       <c r="H405" t="n">
         <v>9759736</v>
@@ -12201,7 +12201,7 @@
         <v>8.70499992370605</v>
       </c>
       <c r="G408" t="n">
-        <v>8.28169727325439</v>
+        <v>8.28169631958008</v>
       </c>
       <c r="H408" t="n">
         <v>5695609</v>
@@ -12404,7 +12404,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G415" t="n">
-        <v>8.05812549591064</v>
+        <v>8.05812454223633</v>
       </c>
       <c r="H415" t="n">
         <v>4472224</v>
@@ -12491,7 +12491,7 @@
         <v>8.33500003814697</v>
       </c>
       <c r="G418" t="n">
-        <v>7.92968940734863</v>
+        <v>7.92968988418579</v>
       </c>
       <c r="H418" t="n">
         <v>4935773</v>
@@ -12520,7 +12520,7 @@
         <v>8.27499961853027</v>
       </c>
       <c r="G419" t="n">
-        <v>7.87260675430298</v>
+        <v>7.87260627746582</v>
       </c>
       <c r="H419" t="n">
         <v>4715292</v>
@@ -12752,7 +12752,7 @@
         <v>8.04500007629395</v>
       </c>
       <c r="G427" t="n">
-        <v>7.6537914276123</v>
+        <v>7.65379095077515</v>
       </c>
       <c r="H427" t="n">
         <v>6232506</v>
@@ -12810,7 +12810,7 @@
         <v>7.83500003814697</v>
       </c>
       <c r="G429" t="n">
-        <v>7.45400333404541</v>
+        <v>7.45400285720825</v>
       </c>
       <c r="H429" t="n">
         <v>6232104</v>
@@ -12984,7 +12984,7 @@
         <v>7.88500022888184</v>
       </c>
       <c r="G435" t="n">
-        <v>7.5015721321106</v>
+        <v>7.50157165527344</v>
       </c>
       <c r="H435" t="n">
         <v>6028869</v>
@@ -13129,7 +13129,7 @@
         <v>8.02499961853027</v>
       </c>
       <c r="G440" t="n">
-        <v>7.63476324081421</v>
+        <v>7.63476371765137</v>
       </c>
       <c r="H440" t="n">
         <v>11093394</v>
@@ -13187,7 +13187,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G442" t="n">
-        <v>7.57292509078979</v>
+        <v>7.57292461395264</v>
       </c>
       <c r="H442" t="n">
         <v>6659325</v>
@@ -13274,7 +13274,7 @@
         <v>7.93499994277954</v>
       </c>
       <c r="G445" t="n">
-        <v>7.54913997650146</v>
+        <v>7.54914045333862</v>
       </c>
       <c r="H445" t="n">
         <v>4915478</v>
@@ -13332,7 +13332,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G447" t="n">
-        <v>7.59195232391357</v>
+        <v>7.59195184707642</v>
       </c>
       <c r="H447" t="n">
         <v>9449306</v>
@@ -13535,7 +13535,7 @@
         <v>7.63500022888184</v>
       </c>
       <c r="G454" t="n">
-        <v>7.26372909545898</v>
+        <v>7.26372861862183</v>
       </c>
       <c r="H454" t="n">
         <v>6637000</v>
@@ -13564,7 +13564,7 @@
         <v>7.54500007629395</v>
       </c>
       <c r="G455" t="n">
-        <v>7.17810535430908</v>
+        <v>7.17810487747192</v>
       </c>
       <c r="H455" t="n">
         <v>8006633</v>
@@ -13680,7 +13680,7 @@
         <v>7.625</v>
       </c>
       <c r="G459" t="n">
-        <v>7.25421524047852</v>
+        <v>7.25421476364136</v>
       </c>
       <c r="H459" t="n">
         <v>9352175</v>
@@ -13796,7 +13796,7 @@
         <v>7.68499994277954</v>
       </c>
       <c r="G463" t="n">
-        <v>7.31129693984985</v>
+        <v>7.31129741668701</v>
       </c>
       <c r="H463" t="n">
         <v>11433018</v>
@@ -14057,7 +14057,7 @@
         <v>7.63500022888184</v>
       </c>
       <c r="G472" t="n">
-        <v>7.26372909545898</v>
+        <v>7.26372861862183</v>
       </c>
       <c r="H472" t="n">
         <v>12393241</v>
@@ -14173,7 +14173,7 @@
         <v>7.35500001907349</v>
       </c>
       <c r="G476" t="n">
-        <v>6.99734401702881</v>
+        <v>6.99734449386597</v>
       </c>
       <c r="H476" t="n">
         <v>10343796</v>
@@ -14260,7 +14260,7 @@
         <v>6.89499998092651</v>
       </c>
       <c r="G479" t="n">
-        <v>6.5597128868103</v>
+        <v>6.55971336364746</v>
       </c>
       <c r="H479" t="n">
         <v>18049941</v>
@@ -14318,7 +14318,7 @@
         <v>6.81500005722046</v>
       </c>
       <c r="G481" t="n">
-        <v>6.48360300064087</v>
+        <v>6.48360347747803</v>
       </c>
       <c r="H481" t="n">
         <v>19321011</v>
@@ -14347,7 +14347,7 @@
         <v>6.89499998092651</v>
       </c>
       <c r="G482" t="n">
-        <v>6.5597128868103</v>
+        <v>6.55971336364746</v>
       </c>
       <c r="H482" t="n">
         <v>13873115</v>
@@ -14579,7 +14579,7 @@
         <v>7.04500007629395</v>
       </c>
       <c r="G490" t="n">
-        <v>6.70241928100586</v>
+        <v>6.7024188041687</v>
       </c>
       <c r="H490" t="n">
         <v>8224257</v>
@@ -14695,7 +14695,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G494" t="n">
-        <v>6.7166895866394</v>
+        <v>6.71668910980225</v>
       </c>
       <c r="H494" t="n">
         <v>7676027</v>
@@ -14782,7 +14782,7 @@
         <v>7.46999979019165</v>
       </c>
       <c r="G497" t="n">
-        <v>7.10675191879272</v>
+        <v>7.10675239562988</v>
       </c>
       <c r="H497" t="n">
         <v>16327353</v>
@@ -14811,7 +14811,7 @@
         <v>7.54500007629395</v>
       </c>
       <c r="G498" t="n">
-        <v>7.17810535430908</v>
+        <v>7.17810487747192</v>
       </c>
       <c r="H498" t="n">
         <v>9765474</v>
@@ -14927,7 +14927,7 @@
         <v>7.2649998664856</v>
       </c>
       <c r="G502" t="n">
-        <v>6.91172027587891</v>
+        <v>6.91172075271606</v>
       </c>
       <c r="H502" t="n">
         <v>12983601</v>
@@ -14985,7 +14985,7 @@
         <v>7.34499979019165</v>
       </c>
       <c r="G504" t="n">
-        <v>6.98783016204834</v>
+        <v>6.9878306388855</v>
       </c>
       <c r="H504" t="n">
         <v>8029365</v>
@@ -15014,7 +15014,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G505" t="n">
-        <v>7.04015636444092</v>
+        <v>7.04015588760376</v>
       </c>
       <c r="H505" t="n">
         <v>7758336</v>
@@ -15072,7 +15072,7 @@
         <v>7.34499979019165</v>
       </c>
       <c r="G507" t="n">
-        <v>6.98783016204834</v>
+        <v>6.9878306388855</v>
       </c>
       <c r="H507" t="n">
         <v>8653660</v>
@@ -15101,7 +15101,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G508" t="n">
-        <v>7.02112865447998</v>
+        <v>7.02112913131714</v>
       </c>
       <c r="H508" t="n">
         <v>5233596</v>
@@ -15159,7 +15159,7 @@
         <v>7.29500007629395</v>
       </c>
       <c r="G510" t="n">
-        <v>6.94026231765747</v>
+        <v>6.94026184082031</v>
       </c>
       <c r="H510" t="n">
         <v>4579894</v>
@@ -15188,7 +15188,7 @@
         <v>7.20499992370605</v>
       </c>
       <c r="G511" t="n">
-        <v>6.85463857650757</v>
+        <v>6.85463809967041</v>
       </c>
       <c r="H511" t="n">
         <v>4245157</v>
@@ -15217,7 +15217,7 @@
         <v>7.25500011444092</v>
       </c>
       <c r="G512" t="n">
-        <v>6.9022068977356</v>
+        <v>6.90220737457275</v>
       </c>
       <c r="H512" t="n">
         <v>6607233</v>
@@ -15246,7 +15246,7 @@
         <v>7.25</v>
       </c>
       <c r="G513" t="n">
-        <v>6.89744997024536</v>
+        <v>6.89745044708252</v>
       </c>
       <c r="H513" t="n">
         <v>5483915</v>
@@ -15275,7 +15275,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G514" t="n">
-        <v>6.98307371139526</v>
+        <v>6.98307418823242</v>
       </c>
       <c r="H514" t="n">
         <v>5974047</v>
@@ -15304,7 +15304,7 @@
         <v>7.38500022888184</v>
       </c>
       <c r="G515" t="n">
-        <v>7.02588605880737</v>
+        <v>7.02588558197021</v>
       </c>
       <c r="H515" t="n">
         <v>5887106</v>
@@ -15449,7 +15449,7 @@
         <v>7.43499994277954</v>
       </c>
       <c r="G520" t="n">
-        <v>7.07345390319824</v>
+        <v>7.0734543800354</v>
       </c>
       <c r="H520" t="n">
         <v>6198087</v>
@@ -15478,7 +15478,7 @@
         <v>7.38500022888184</v>
       </c>
       <c r="G521" t="n">
-        <v>7.02588605880737</v>
+        <v>7.02588558197021</v>
       </c>
       <c r="H521" t="n">
         <v>5952155</v>
@@ -15739,7 +15739,7 @@
         <v>7.20499992370605</v>
       </c>
       <c r="G530" t="n">
-        <v>6.85463857650757</v>
+        <v>6.85463809967041</v>
       </c>
       <c r="H530" t="n">
         <v>8180429</v>
@@ -15971,7 +15971,7 @@
         <v>7.21199989318848</v>
       </c>
       <c r="G538" t="n">
-        <v>6.86129760742188</v>
+        <v>6.86129808425903</v>
       </c>
       <c r="H538" t="n">
         <v>18503191</v>
@@ -16029,7 +16029,7 @@
         <v>6.98799991607666</v>
       </c>
       <c r="G540" t="n">
-        <v>6.64819097518921</v>
+        <v>6.64819049835205</v>
       </c>
       <c r="H540" t="n">
         <v>10998838</v>
@@ -16116,7 +16116,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G543" t="n">
-        <v>6.54544258117676</v>
+        <v>6.5454421043396</v>
       </c>
       <c r="H543" t="n">
         <v>9422768</v>
@@ -16261,7 +16261,7 @@
         <v>7.19600009918213</v>
       </c>
       <c r="G548" t="n">
-        <v>6.84607601165771</v>
+        <v>6.84607648849487</v>
       </c>
       <c r="H548" t="n">
         <v>13117904</v>
@@ -16348,7 +16348,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G551" t="n">
-        <v>7.02112865447998</v>
+        <v>7.02112913131714</v>
       </c>
       <c r="H551" t="n">
         <v>9959256</v>
@@ -16406,7 +16406,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G553" t="n">
-        <v>7.04015636444092</v>
+        <v>7.04015588760376</v>
       </c>
       <c r="H553" t="n">
         <v>10517150</v>
@@ -16435,7 +16435,7 @@
         <v>7.39799976348877</v>
       </c>
       <c r="G554" t="n">
-        <v>7.03825283050537</v>
+        <v>7.03825330734253</v>
       </c>
       <c r="H554" t="n">
         <v>10319173</v>
@@ -16464,7 +16464,7 @@
         <v>7.24599981307983</v>
       </c>
       <c r="G555" t="n">
-        <v>6.8936448097229</v>
+        <v>6.89364433288574</v>
       </c>
       <c r="H555" t="n">
         <v>12031756</v>
@@ -16493,7 +16493,7 @@
         <v>7.28800010681152</v>
       </c>
       <c r="G556" t="n">
-        <v>6.93360233306885</v>
+        <v>6.93360280990601</v>
       </c>
       <c r="H556" t="n">
         <v>9797279</v>
@@ -16580,7 +16580,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G559" t="n">
-        <v>7.82979440689087</v>
+        <v>7.82979536056519</v>
       </c>
       <c r="H559" t="n">
         <v>38979913</v>
@@ -16609,7 +16609,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G560" t="n">
-        <v>7.91541862487793</v>
+        <v>7.91541814804077</v>
       </c>
       <c r="H560" t="n">
         <v>29766429</v>
@@ -16638,7 +16638,7 @@
         <v>8.20199966430664</v>
       </c>
       <c r="G561" t="n">
-        <v>7.80315637588501</v>
+        <v>7.80315589904785</v>
       </c>
       <c r="H561" t="n">
         <v>15070704</v>
@@ -16667,7 +16667,7 @@
         <v>8.00800037384033</v>
       </c>
       <c r="G562" t="n">
-        <v>7.61859083175659</v>
+        <v>7.61859130859375</v>
       </c>
       <c r="H562" t="n">
         <v>17830195</v>
@@ -16696,7 +16696,7 @@
         <v>7.83199977874756</v>
       </c>
       <c r="G563" t="n">
-        <v>7.45114898681641</v>
+        <v>7.45114850997925</v>
       </c>
       <c r="H563" t="n">
         <v>15531686</v>
@@ -16754,7 +16754,7 @@
         <v>8.08800029754639</v>
       </c>
       <c r="G565" t="n">
-        <v>7.69470024108887</v>
+        <v>7.69470071792603</v>
       </c>
       <c r="H565" t="n">
         <v>13814697</v>
@@ -16783,7 +16783,7 @@
         <v>8.11600017547607</v>
       </c>
       <c r="G566" t="n">
-        <v>7.72133874893188</v>
+        <v>7.72133922576904</v>
       </c>
       <c r="H566" t="n">
         <v>11221597</v>
@@ -16899,7 +16899,7 @@
         <v>7.72599983215332</v>
       </c>
       <c r="G570" t="n">
-        <v>7.35030364990234</v>
+        <v>7.35030317306519</v>
       </c>
       <c r="H570" t="n">
         <v>11293097</v>
@@ -16957,7 +16957,7 @@
         <v>7.61399984359741</v>
       </c>
       <c r="G572" t="n">
-        <v>7.24374961853027</v>
+        <v>7.24375009536743</v>
       </c>
       <c r="H572" t="n">
         <v>8793021</v>
@@ -17073,7 +17073,7 @@
         <v>7.58199977874756</v>
       </c>
       <c r="G576" t="n">
-        <v>7.21330595016479</v>
+        <v>7.21330547332764</v>
       </c>
       <c r="H576" t="n">
         <v>7516325</v>
@@ -17247,7 +17247,7 @@
         <v>8.61200046539307</v>
       </c>
       <c r="G582" t="n">
-        <v>8.19321918487549</v>
+        <v>8.1932201385498</v>
       </c>
       <c r="H582" t="n">
         <v>21024100</v>
@@ -17334,7 +17334,7 @@
         <v>8.38199996948242</v>
       </c>
       <c r="G585" t="n">
-        <v>7.97440385818481</v>
+        <v>7.97440338134766</v>
       </c>
       <c r="H585" t="n">
         <v>16885220</v>
@@ -17421,7 +17421,7 @@
         <v>8.76200008392334</v>
       </c>
       <c r="G588" t="n">
-        <v>8.33592510223389</v>
+        <v>8.3359260559082</v>
       </c>
       <c r="H588" t="n">
         <v>19699701</v>
@@ -17450,7 +17450,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G589" t="n">
-        <v>8.27694034576416</v>
+        <v>8.27693939208984</v>
       </c>
       <c r="H589" t="n">
         <v>14602170</v>
@@ -17508,7 +17508,7 @@
         <v>8.26200008392334</v>
       </c>
       <c r="G591" t="n">
-        <v>7.86023902893066</v>
+        <v>7.86023950576782</v>
       </c>
       <c r="H591" t="n">
         <v>15384354</v>
@@ -17653,7 +17653,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G596" t="n">
-        <v>7.96298694610596</v>
+        <v>7.96298742294312</v>
       </c>
       <c r="H596" t="n">
         <v>11477450</v>
@@ -17740,7 +17740,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G599" t="n">
-        <v>8.01055526733398</v>
+        <v>8.0105562210083</v>
       </c>
       <c r="H599" t="n">
         <v>20166769</v>
@@ -17769,7 +17769,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G600" t="n">
-        <v>7.88687801361084</v>
+        <v>7.88687753677368</v>
       </c>
       <c r="H600" t="n">
         <v>10308492</v>
@@ -17914,7 +17914,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G605" t="n">
-        <v>7.35410928726196</v>
+        <v>7.3541088104248</v>
       </c>
       <c r="H605" t="n">
         <v>19807914</v>
@@ -17943,7 +17943,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G606" t="n">
-        <v>7.30654001235962</v>
+        <v>7.30654048919678</v>
       </c>
       <c r="H606" t="n">
         <v>13820402</v>
@@ -18030,7 +18030,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G609" t="n">
-        <v>7.02112865447998</v>
+        <v>7.02112913131714</v>
       </c>
       <c r="H609" t="n">
         <v>12987765</v>
@@ -18059,7 +18059,7 @@
         <v>7.31199979782104</v>
       </c>
       <c r="G610" t="n">
-        <v>6.95643520355225</v>
+        <v>6.95643472671509</v>
       </c>
       <c r="H610" t="n">
         <v>9821711</v>
@@ -18088,7 +18088,7 @@
         <v>7.30999994277954</v>
       </c>
       <c r="G611" t="n">
-        <v>6.95453262329102</v>
+        <v>6.95453214645386</v>
       </c>
       <c r="H611" t="n">
         <v>10969407</v>
@@ -18146,7 +18146,7 @@
         <v>7.14400005340576</v>
       </c>
       <c r="G613" t="n">
-        <v>6.7966046333313</v>
+        <v>6.79660511016846</v>
       </c>
       <c r="H613" t="n">
         <v>15383630</v>
@@ -18204,7 +18204,7 @@
         <v>7.01599979400635</v>
       </c>
       <c r="G615" t="n">
-        <v>6.67482852935791</v>
+        <v>6.67482900619507</v>
       </c>
       <c r="H615" t="n">
         <v>10762161</v>
@@ -18233,7 +18233,7 @@
         <v>6.87200021743774</v>
       </c>
       <c r="G616" t="n">
-        <v>6.53783130645752</v>
+        <v>6.53783178329468</v>
       </c>
       <c r="H616" t="n">
         <v>13644902</v>
@@ -18291,7 +18291,7 @@
         <v>6.98600006103516</v>
       </c>
       <c r="G618" t="n">
-        <v>6.64628791809082</v>
+        <v>6.64628839492798</v>
       </c>
       <c r="H618" t="n">
         <v>6146232</v>
@@ -18349,7 +18349,7 @@
         <v>6.91599988937378</v>
       </c>
       <c r="G620" t="n">
-        <v>6.57969188690186</v>
+        <v>6.5796914100647</v>
       </c>
       <c r="H620" t="n">
         <v>11484221</v>
@@ -18407,7 +18407,7 @@
         <v>6.72200012207031</v>
       </c>
       <c r="G622" t="n">
-        <v>6.39512586593628</v>
+        <v>6.39512538909912</v>
       </c>
       <c r="H622" t="n">
         <v>8616778</v>
@@ -18436,7 +18436,7 @@
         <v>6.87200021743774</v>
       </c>
       <c r="G623" t="n">
-        <v>6.53783130645752</v>
+        <v>6.53783178329468</v>
       </c>
       <c r="H623" t="n">
         <v>11592172</v>
@@ -18465,7 +18465,7 @@
         <v>6.85799980163574</v>
       </c>
       <c r="G624" t="n">
-        <v>6.52451181411743</v>
+        <v>6.52451229095459</v>
       </c>
       <c r="H624" t="n">
         <v>6763306</v>
@@ -18552,7 +18552,7 @@
         <v>6.7519998550415</v>
       </c>
       <c r="G627" t="n">
-        <v>6.42366647720337</v>
+        <v>6.42366695404053</v>
       </c>
       <c r="H627" t="n">
         <v>11827362</v>
@@ -18581,7 +18581,7 @@
         <v>6.76599979400635</v>
       </c>
       <c r="G628" t="n">
-        <v>6.4369854927063</v>
+        <v>6.43698596954346</v>
       </c>
       <c r="H628" t="n">
         <v>9517293</v>
@@ -18668,7 +18668,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G631" t="n">
-        <v>6.33614015579224</v>
+        <v>6.33614063262939</v>
       </c>
       <c r="H631" t="n">
         <v>8779408</v>
@@ -18784,7 +18784,7 @@
         <v>6.45599985122681</v>
       </c>
       <c r="G635" t="n">
-        <v>6.14206075668335</v>
+        <v>6.14206027984619</v>
       </c>
       <c r="H635" t="n">
         <v>13273047</v>
@@ -18842,7 +18842,7 @@
         <v>6.37400007247925</v>
       </c>
       <c r="G637" t="n">
-        <v>6.06404781341553</v>
+        <v>6.06404829025269</v>
       </c>
       <c r="H637" t="n">
         <v>8023540</v>
@@ -18871,7 +18871,7 @@
         <v>6.28200006484985</v>
       </c>
       <c r="G638" t="n">
-        <v>5.97652149200439</v>
+        <v>5.97652196884155</v>
       </c>
       <c r="H638" t="n">
         <v>5846091</v>
@@ -18929,7 +18929,7 @@
         <v>6.52400016784668</v>
       </c>
       <c r="G640" t="n">
-        <v>6.20675420761108</v>
+        <v>6.20675373077393</v>
       </c>
       <c r="H640" t="n">
         <v>5707740</v>
@@ -18987,7 +18987,7 @@
         <v>6.55200004577637</v>
       </c>
       <c r="G642" t="n">
-        <v>6.2333927154541</v>
+        <v>6.23339223861694</v>
       </c>
       <c r="H642" t="n">
         <v>6589583</v>
@@ -19045,7 +19045,7 @@
         <v>6.36600017547607</v>
       </c>
       <c r="G644" t="n">
-        <v>6.05643749237061</v>
+        <v>6.05643701553345</v>
       </c>
       <c r="H644" t="n">
         <v>10253469</v>
@@ -19074,7 +19074,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G645" t="n">
-        <v>6.01267385482788</v>
+        <v>6.01267433166504</v>
       </c>
       <c r="H645" t="n">
         <v>7151777</v>
@@ -19103,7 +19103,7 @@
         <v>6.14599990844727</v>
       </c>
       <c r="G646" t="n">
-        <v>5.84713506698608</v>
+        <v>5.84713459014893</v>
       </c>
       <c r="H646" t="n">
         <v>10297948</v>
@@ -19161,7 +19161,7 @@
         <v>6.07399988174438</v>
       </c>
       <c r="G648" t="n">
-        <v>5.77863645553589</v>
+        <v>5.77863597869873</v>
       </c>
       <c r="H648" t="n">
         <v>9314960</v>
@@ -19451,7 +19451,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G658" t="n">
-        <v>6.2790584564209</v>
+        <v>6.27905797958374</v>
       </c>
       <c r="H658" t="n">
         <v>10357178</v>
@@ -19509,7 +19509,7 @@
         <v>6.50400018692017</v>
       </c>
       <c r="G660" t="n">
-        <v>6.1877269744873</v>
+        <v>6.18772649765015</v>
       </c>
       <c r="H660" t="n">
         <v>7068352</v>
@@ -19538,7 +19538,7 @@
         <v>6.38199996948242</v>
       </c>
       <c r="G661" t="n">
-        <v>6.07165908813477</v>
+        <v>6.07165861129761</v>
       </c>
       <c r="H661" t="n">
         <v>7651712</v>
@@ -19944,7 +19944,7 @@
         <v>6</v>
       </c>
       <c r="G675" t="n">
-        <v>5.70823431015015</v>
+        <v>5.7082347869873</v>
       </c>
       <c r="H675" t="n">
         <v>8439947</v>
@@ -19973,7 +19973,7 @@
         <v>5.98799991607666</v>
       </c>
       <c r="G676" t="n">
-        <v>5.69681835174561</v>
+        <v>5.69681787490845</v>
       </c>
       <c r="H676" t="n">
         <v>6952501</v>
@@ -20002,7 +20002,7 @@
         <v>6.0019998550415</v>
       </c>
       <c r="G677" t="n">
-        <v>5.71013736724854</v>
+        <v>5.71013689041138</v>
       </c>
       <c r="H677" t="n">
         <v>3495139</v>
@@ -20031,7 +20031,7 @@
         <v>5.93800020217896</v>
       </c>
       <c r="G678" t="n">
-        <v>5.64924955368042</v>
+        <v>5.64925003051758</v>
       </c>
       <c r="H678" t="n">
         <v>6479576</v>
@@ -20118,7 +20118,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G681" t="n">
-        <v>5.22303485870361</v>
+        <v>5.22303438186646</v>
       </c>
       <c r="H681" t="n">
         <v>21485023</v>
@@ -20147,7 +20147,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G682" t="n">
-        <v>5.28011703491211</v>
+        <v>5.28011751174927</v>
       </c>
       <c r="H682" t="n">
         <v>7364755</v>
@@ -20176,7 +20176,7 @@
         <v>5.25</v>
       </c>
       <c r="G683" t="n">
-        <v>4.99470567703247</v>
+        <v>4.99470520019531</v>
       </c>
       <c r="H683" t="n">
         <v>33784406</v>
@@ -20350,7 +20350,7 @@
         <v>5.4060001373291</v>
       </c>
       <c r="G689" t="n">
-        <v>5.14311933517456</v>
+        <v>5.14311981201172</v>
       </c>
       <c r="H689" t="n">
         <v>9097960</v>
@@ -20466,7 +20466,7 @@
         <v>5.71400022506714</v>
       </c>
       <c r="G693" t="n">
-        <v>5.4361424446106</v>
+        <v>5.43614196777344</v>
       </c>
       <c r="H693" t="n">
         <v>14951668</v>
@@ -20524,7 +20524,7 @@
         <v>5.68599987030029</v>
       </c>
       <c r="G695" t="n">
-        <v>5.40950393676758</v>
+        <v>5.40950345993042</v>
       </c>
       <c r="H695" t="n">
         <v>8514680</v>
@@ -20553,7 +20553,7 @@
         <v>5.68599987030029</v>
       </c>
       <c r="G696" t="n">
-        <v>5.40950393676758</v>
+        <v>5.40950345993042</v>
       </c>
       <c r="H696" t="n">
         <v>11073700</v>
@@ -20582,7 +20582,7 @@
         <v>5.60599994659424</v>
       </c>
       <c r="G697" t="n">
-        <v>5.33339405059814</v>
+        <v>5.33339357376099</v>
       </c>
       <c r="H697" t="n">
         <v>9256009</v>
@@ -20611,7 +20611,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G698" t="n">
-        <v>5.30865859985352</v>
+        <v>5.30865812301636</v>
       </c>
       <c r="H698" t="n">
         <v>8345160</v>
@@ -20727,7 +20727,7 @@
         <v>4.95300006866455</v>
       </c>
       <c r="G702" t="n">
-        <v>4.71214818954468</v>
+        <v>4.71214771270752</v>
       </c>
       <c r="H702" t="n">
         <v>21571910</v>
@@ -20814,7 +20814,7 @@
         <v>4.95699977874756</v>
       </c>
       <c r="G705" t="n">
-        <v>4.71595287322998</v>
+        <v>4.71595335006714</v>
       </c>
       <c r="H705" t="n">
         <v>12269784</v>
@@ -20930,7 +20930,7 @@
         <v>5.03200006484985</v>
       </c>
       <c r="G709" t="n">
-        <v>4.78730630874634</v>
+        <v>4.78730583190918</v>
       </c>
       <c r="H709" t="n">
         <v>16574528</v>
@@ -20959,7 +20959,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G710" t="n">
-        <v>4.77588987350464</v>
+        <v>4.77588939666748</v>
       </c>
       <c r="H710" t="n">
         <v>13466859</v>
@@ -21133,7 +21133,7 @@
         <v>4.98600006103516</v>
       </c>
       <c r="G716" t="n">
-        <v>4.74354267120361</v>
+        <v>4.74354314804077</v>
       </c>
       <c r="H716" t="n">
         <v>11883638</v>
@@ -21365,7 +21365,7 @@
         <v>5.19199991226196</v>
       </c>
       <c r="G724" t="n">
-        <v>4.93952560424805</v>
+        <v>4.93952608108521</v>
       </c>
       <c r="H724" t="n">
         <v>11611382</v>
@@ -21452,7 +21452,7 @@
         <v>5.35400009155273</v>
       </c>
       <c r="G727" t="n">
-        <v>5.09364795684814</v>
+        <v>5.0936484336853</v>
       </c>
       <c r="H727" t="n">
         <v>5004868</v>
@@ -21510,7 +21510,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G729" t="n">
-        <v>5.08984231948853</v>
+        <v>5.08984279632568</v>
       </c>
       <c r="H729" t="n">
         <v>4502292</v>
@@ -21568,7 +21568,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G731" t="n">
-        <v>4.90908193588257</v>
+        <v>4.90908145904541</v>
       </c>
       <c r="H731" t="n">
         <v>20215708</v>
@@ -21597,7 +21597,7 @@
         <v>5.30399990081787</v>
       </c>
       <c r="G732" t="n">
-        <v>5.04607963562012</v>
+        <v>5.04607915878296</v>
       </c>
       <c r="H732" t="n">
         <v>21192969</v>
@@ -21655,7 +21655,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G734" t="n">
-        <v>4.9566502571106</v>
+        <v>4.95665073394775</v>
       </c>
       <c r="H734" t="n">
         <v>13016824</v>
@@ -21684,7 +21684,7 @@
         <v>5.16400003433228</v>
       </c>
       <c r="G735" t="n">
-        <v>4.91288757324219</v>
+        <v>4.91288709640503</v>
       </c>
       <c r="H735" t="n">
         <v>7858565</v>
@@ -21713,7 +21713,7 @@
         <v>5.26200008392334</v>
       </c>
       <c r="G736" t="n">
-        <v>5.00612163543701</v>
+        <v>5.00612211227417</v>
       </c>
       <c r="H736" t="n">
         <v>9329889</v>
@@ -22032,7 +22032,7 @@
         <v>5.74599981307983</v>
       </c>
       <c r="G747" t="n">
-        <v>5.46658563613892</v>
+        <v>5.46658611297607</v>
       </c>
       <c r="H747" t="n">
         <v>8767299</v>
@@ -22061,7 +22061,7 @@
         <v>5.69199991226196</v>
       </c>
       <c r="G748" t="n">
-        <v>5.41521167755127</v>
+        <v>5.41521215438843</v>
       </c>
       <c r="H748" t="n">
         <v>5268321</v>
@@ -22235,7 +22235,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G754" t="n">
-        <v>5.42282295227051</v>
+        <v>5.42282247543335</v>
       </c>
       <c r="H754" t="n">
         <v>8739136</v>
@@ -22380,7 +22380,7 @@
         <v>5.4520001411438</v>
       </c>
       <c r="G759" t="n">
-        <v>5.18688297271729</v>
+        <v>5.18688249588013</v>
       </c>
       <c r="H759" t="n">
         <v>9181301</v>
@@ -22409,7 +22409,7 @@
         <v>5.2020001411438</v>
       </c>
       <c r="G760" t="n">
-        <v>4.94903993606567</v>
+        <v>4.94903945922852</v>
       </c>
       <c r="H760" t="n">
         <v>11959404</v>
@@ -22467,7 +22467,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G762" t="n">
-        <v>4.58561563491821</v>
+        <v>4.58561515808105</v>
       </c>
       <c r="H762" t="n">
         <v>10213287</v>
@@ -22496,7 +22496,7 @@
         <v>4.83300018310547</v>
       </c>
       <c r="G763" t="n">
-        <v>4.59798288345337</v>
+        <v>4.59798336029053</v>
       </c>
       <c r="H763" t="n">
         <v>6812527</v>
@@ -22641,7 +22641,7 @@
         <v>5.06199979782104</v>
       </c>
       <c r="G768" t="n">
-        <v>4.81584692001343</v>
+        <v>4.81584739685059</v>
       </c>
       <c r="H768" t="n">
         <v>6948538</v>
@@ -22670,7 +22670,7 @@
         <v>4.95900011062622</v>
       </c>
       <c r="G769" t="n">
-        <v>4.71785593032837</v>
+        <v>4.71785640716553</v>
       </c>
       <c r="H769" t="n">
         <v>10542869</v>
@@ -22728,7 +22728,7 @@
         <v>5.00600004196167</v>
       </c>
       <c r="G771" t="n">
-        <v>4.76257085800171</v>
+        <v>4.76257038116455</v>
       </c>
       <c r="H771" t="n">
         <v>7037218</v>
@@ -22757,7 +22757,7 @@
         <v>5.01599979400635</v>
       </c>
       <c r="G772" t="n">
-        <v>4.77208423614502</v>
+        <v>4.77208375930786</v>
       </c>
       <c r="H772" t="n">
         <v>5703804</v>
@@ -22786,7 +22786,7 @@
         <v>5.02400016784668</v>
       </c>
       <c r="G773" t="n">
-        <v>4.7796950340271</v>
+        <v>4.77969551086426</v>
       </c>
       <c r="H773" t="n">
         <v>5160678</v>
@@ -22873,7 +22873,7 @@
         <v>4.88500022888184</v>
       </c>
       <c r="G776" t="n">
-        <v>4.64745426177979</v>
+        <v>4.64745473861694</v>
       </c>
       <c r="H776" t="n">
         <v>41676407</v>
@@ -22960,7 +22960,7 @@
         <v>4.48400020599365</v>
       </c>
       <c r="G779" t="n">
-        <v>4.26595449447632</v>
+        <v>4.26595401763916</v>
       </c>
       <c r="H779" t="n">
         <v>18215988</v>
@@ -22989,7 +22989,7 @@
         <v>4.52899980545044</v>
       </c>
       <c r="G780" t="n">
-        <v>4.30876541137695</v>
+        <v>4.30876588821411</v>
       </c>
       <c r="H780" t="n">
         <v>16117024</v>
@@ -23076,7 +23076,7 @@
         <v>4.58199977874756</v>
       </c>
       <c r="G783" t="n">
-        <v>4.35918807983398</v>
+        <v>4.35918855667114</v>
       </c>
       <c r="H783" t="n">
         <v>7847751</v>
@@ -23105,7 +23105,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G784" t="n">
-        <v>4.40485429763794</v>
+        <v>4.4048547744751</v>
       </c>
       <c r="H784" t="n">
         <v>11137135</v>
@@ -23221,7 +23221,7 @@
         <v>5.02400016784668</v>
       </c>
       <c r="G788" t="n">
-        <v>4.7796950340271</v>
+        <v>4.77969551086426</v>
       </c>
       <c r="H788" t="n">
         <v>9181552</v>
@@ -23308,7 +23308,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G791" t="n">
-        <v>4.49047756195068</v>
+        <v>4.49047803878784</v>
       </c>
       <c r="H791" t="n">
         <v>10923993</v>
@@ -23366,7 +23366,7 @@
         <v>4.81599998474121</v>
       </c>
       <c r="G793" t="n">
-        <v>4.58180952072144</v>
+        <v>4.58180999755859</v>
       </c>
       <c r="H793" t="n">
         <v>6859684</v>
@@ -23424,7 +23424,7 @@
         <v>4.8270001411438</v>
       </c>
       <c r="G795" t="n">
-        <v>4.59227466583252</v>
+        <v>4.59227514266968</v>
       </c>
       <c r="H795" t="n">
         <v>10108349</v>
@@ -23482,7 +23482,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G797" t="n">
-        <v>5.0422739982605</v>
+        <v>5.04227447509766</v>
       </c>
       <c r="H797" t="n">
         <v>14228495</v>
@@ -23627,7 +23627,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G802" t="n">
-        <v>5.09935665130615</v>
+        <v>5.09935617446899</v>
       </c>
       <c r="H802" t="n">
         <v>13548252</v>
@@ -23743,7 +23743,7 @@
         <v>5.32200002670288</v>
       </c>
       <c r="G806" t="n">
-        <v>5.06320428848267</v>
+        <v>5.06320381164551</v>
       </c>
       <c r="H806" t="n">
         <v>10595102</v>
@@ -23801,7 +23801,7 @@
         <v>5.5</v>
       </c>
       <c r="G808" t="n">
-        <v>5.23254871368408</v>
+        <v>5.23254823684692</v>
       </c>
       <c r="H808" t="n">
         <v>15904611</v>
@@ -23830,7 +23830,7 @@
         <v>5.64799976348877</v>
       </c>
       <c r="G809" t="n">
-        <v>5.37335157394409</v>
+        <v>5.37335109710693</v>
       </c>
       <c r="H809" t="n">
         <v>20711461</v>
@@ -23859,7 +23859,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G810" t="n">
-        <v>5.33719968795776</v>
+        <v>5.33719921112061</v>
       </c>
       <c r="H810" t="n">
         <v>21767982</v>
@@ -24091,7 +24091,7 @@
         <v>5.35599994659424</v>
       </c>
       <c r="G818" t="n">
-        <v>5.09555101394653</v>
+        <v>5.09555053710938</v>
       </c>
       <c r="H818" t="n">
         <v>10767173</v>
@@ -24149,7 +24149,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G820" t="n">
-        <v>5.0422739982605</v>
+        <v>5.04227447509766</v>
       </c>
       <c r="H820" t="n">
         <v>6355484</v>
@@ -24178,7 +24178,7 @@
         <v>5.25799989700317</v>
       </c>
       <c r="G821" t="n">
-        <v>5.00231599807739</v>
+        <v>5.00231647491455</v>
       </c>
       <c r="H821" t="n">
         <v>8320301</v>
@@ -24236,7 +24236,7 @@
         <v>5.31599998474121</v>
       </c>
       <c r="G823" t="n">
-        <v>5.05749559402466</v>
+        <v>5.05749607086182</v>
       </c>
       <c r="H823" t="n">
         <v>5741634</v>
@@ -24265,7 +24265,7 @@
         <v>5.35599994659424</v>
       </c>
       <c r="G824" t="n">
-        <v>5.09555101394653</v>
+        <v>5.09555053710938</v>
       </c>
       <c r="H824" t="n">
         <v>7192964</v>
@@ -24294,7 +24294,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G825" t="n">
-        <v>5.14692497253418</v>
+        <v>5.14692449569702</v>
       </c>
       <c r="H825" t="n">
         <v>6837351</v>
@@ -24381,7 +24381,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G828" t="n">
-        <v>5.08984231948853</v>
+        <v>5.08984279632568</v>
       </c>
       <c r="H828" t="n">
         <v>11314863</v>
@@ -24410,7 +24410,7 @@
         <v>5.40199995040894</v>
       </c>
       <c r="G829" t="n">
-        <v>5.13931369781494</v>
+        <v>5.1393141746521</v>
       </c>
       <c r="H829" t="n">
         <v>9915940</v>
@@ -24468,7 +24468,7 @@
         <v>5.36800003051758</v>
       </c>
       <c r="G831" t="n">
-        <v>5.10696697235107</v>
+        <v>5.10696744918823</v>
       </c>
       <c r="H831" t="n">
         <v>8336278</v>
@@ -24497,7 +24497,7 @@
         <v>5.33599996566772</v>
       </c>
       <c r="G832" t="n">
-        <v>5.0765233039856</v>
+        <v>5.07652378082275</v>
       </c>
       <c r="H832" t="n">
         <v>10088831</v>
@@ -24526,7 +24526,7 @@
         <v>5.34899997711182</v>
       </c>
       <c r="G833" t="n">
-        <v>5.08889102935791</v>
+        <v>5.08889150619507</v>
       </c>
       <c r="H833" t="n">
         <v>6378866</v>
@@ -24671,7 +24671,7 @@
         <v>5.25500011444092</v>
       </c>
       <c r="G838" t="n">
-        <v>4.99946260452271</v>
+        <v>4.99946212768555</v>
       </c>
       <c r="H838" t="n">
         <v>4873965</v>
@@ -24903,7 +24903,7 @@
         <v>4.98600006103516</v>
       </c>
       <c r="G846" t="n">
-        <v>4.74354267120361</v>
+        <v>4.74354314804077</v>
       </c>
       <c r="H846" t="n">
         <v>4443838</v>
@@ -24932,7 +24932,7 @@
         <v>4.95900011062622</v>
       </c>
       <c r="G847" t="n">
-        <v>4.71785593032837</v>
+        <v>4.71785640716553</v>
       </c>
       <c r="H847" t="n">
         <v>6501356</v>
@@ -25106,7 +25106,7 @@
         <v>4.67199993133545</v>
       </c>
       <c r="G853" t="n">
-        <v>4.44481182098389</v>
+        <v>4.44481229782104</v>
       </c>
       <c r="H853" t="n">
         <v>6493676</v>
@@ -25193,7 +25193,7 @@
         <v>4.45800018310547</v>
       </c>
       <c r="G856" t="n">
-        <v>4.24121856689453</v>
+        <v>4.24121809005737</v>
       </c>
       <c r="H856" t="n">
         <v>16786730</v>
@@ -25280,7 +25280,7 @@
         <v>4.57800006866455</v>
       </c>
       <c r="G859" t="n">
-        <v>4.35538291931152</v>
+        <v>4.35538339614868</v>
       </c>
       <c r="H859" t="n">
         <v>8359793</v>
@@ -25396,7 +25396,7 @@
         <v>4.38100004196167</v>
       </c>
       <c r="G863" t="n">
-        <v>4.16796255111694</v>
+        <v>4.1679630279541</v>
       </c>
       <c r="H863" t="n">
         <v>10295663</v>
@@ -25599,7 +25599,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G870" t="n">
-        <v>4.32398748397827</v>
+        <v>4.32398796081543</v>
       </c>
       <c r="H870" t="n">
         <v>10022461</v>
@@ -25802,7 +25802,7 @@
         <v>4.63100004196167</v>
       </c>
       <c r="G877" t="n">
-        <v>4.40580558776855</v>
+        <v>4.40580606460571</v>
       </c>
       <c r="H877" t="n">
         <v>6029498</v>
@@ -25947,7 +25947,7 @@
         <v>4.84200000762939</v>
       </c>
       <c r="G882" t="n">
-        <v>4.60654497146606</v>
+        <v>4.60654544830322</v>
       </c>
       <c r="H882" t="n">
         <v>15402357</v>
@@ -25976,7 +25976,7 @@
         <v>5.00899982452393</v>
       </c>
       <c r="G883" t="n">
-        <v>4.7654242515564</v>
+        <v>4.76542472839355</v>
       </c>
       <c r="H883" t="n">
         <v>21769809</v>
@@ -26150,7 +26150,7 @@
         <v>4.82800006866455</v>
       </c>
       <c r="G889" t="n">
-        <v>4.59322595596313</v>
+        <v>4.59322643280029</v>
       </c>
       <c r="H889" t="n">
         <v>7098552</v>
@@ -26179,7 +26179,7 @@
         <v>4.78299999237061</v>
       </c>
       <c r="G890" t="n">
-        <v>4.55041456222534</v>
+        <v>4.55041408538818</v>
       </c>
       <c r="H890" t="n">
         <v>4787528</v>
@@ -26208,7 +26208,7 @@
         <v>4.92199993133545</v>
       </c>
       <c r="G891" t="n">
-        <v>4.6826548576355</v>
+        <v>4.68265533447266</v>
       </c>
       <c r="H891" t="n">
         <v>9003798</v>
@@ -26266,7 +26266,7 @@
         <v>4.96299982070923</v>
       </c>
       <c r="G893" t="n">
-        <v>4.72166156768799</v>
+        <v>4.72166109085083</v>
       </c>
       <c r="H893" t="n">
         <v>6516566</v>
@@ -26411,7 +26411,7 @@
         <v>5.01300001144409</v>
       </c>
       <c r="G898" t="n">
-        <v>4.76922988891602</v>
+        <v>4.76923036575317</v>
       </c>
       <c r="H898" t="n">
         <v>5422412</v>
@@ -26527,7 +26527,7 @@
         <v>5.06099987030029</v>
       </c>
       <c r="G902" t="n">
-        <v>4.81489562988281</v>
+        <v>4.81489610671997</v>
       </c>
       <c r="H902" t="n">
         <v>4829287</v>
@@ -26556,7 +26556,7 @@
         <v>4.91099977493286</v>
       </c>
       <c r="G903" t="n">
-        <v>4.67219018936157</v>
+        <v>4.67218971252441</v>
       </c>
       <c r="H903" t="n">
         <v>8017443</v>
@@ -26614,7 +26614,7 @@
         <v>4.95699977874756</v>
       </c>
       <c r="G905" t="n">
-        <v>4.71595287322998</v>
+        <v>4.71595335006714</v>
       </c>
       <c r="H905" t="n">
         <v>5337026</v>
@@ -26730,7 +26730,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G909" t="n">
-        <v>4.985191822052</v>
+        <v>4.98519134521484</v>
       </c>
       <c r="H909" t="n">
         <v>10810457</v>
@@ -26788,7 +26788,7 @@
         <v>5.10599994659424</v>
       </c>
       <c r="G911" t="n">
-        <v>4.85770797729492</v>
+        <v>4.85770750045776</v>
       </c>
       <c r="H911" t="n">
         <v>5112107</v>
@@ -26846,7 +26846,7 @@
         <v>4.99599981307983</v>
       </c>
       <c r="G913" t="n">
-        <v>4.75305700302124</v>
+        <v>4.75305652618408</v>
       </c>
       <c r="H913" t="n">
         <v>6486219</v>
@@ -26904,7 +26904,7 @@
         <v>4.83400011062622</v>
       </c>
       <c r="G915" t="n">
-        <v>4.59893465042114</v>
+        <v>4.59893417358398</v>
       </c>
       <c r="H915" t="n">
         <v>6262907</v>
@@ -26933,7 +26933,7 @@
         <v>4.81599998474121</v>
       </c>
       <c r="G916" t="n">
-        <v>4.58180952072144</v>
+        <v>4.58180999755859</v>
       </c>
       <c r="H916" t="n">
         <v>4733278</v>
@@ -26962,7 +26962,7 @@
         <v>4.88800001144409</v>
       </c>
       <c r="G917" t="n">
-        <v>4.65030860900879</v>
+        <v>4.65030813217163</v>
       </c>
       <c r="H917" t="n">
         <v>5260695</v>
@@ -26991,7 +26991,7 @@
         <v>4.60200023651123</v>
       </c>
       <c r="G918" t="n">
-        <v>4.37821626663208</v>
+        <v>4.37821578979492</v>
       </c>
       <c r="H918" t="n">
         <v>11153136</v>
@@ -27136,7 +27136,7 @@
         <v>4.56500005722046</v>
       </c>
       <c r="G923" t="n">
-        <v>4.34301567077637</v>
+        <v>4.34301519393921</v>
       </c>
       <c r="H923" t="n">
         <v>5051334</v>
@@ -27165,7 +27165,7 @@
         <v>4.47200012207031</v>
       </c>
       <c r="G924" t="n">
-        <v>4.25453758239746</v>
+        <v>4.25453805923462</v>
       </c>
       <c r="H924" t="n">
         <v>5236518</v>
@@ -27223,7 +27223,7 @@
         <v>4.59800004959106</v>
       </c>
       <c r="G926" t="n">
-        <v>4.3744101524353</v>
+        <v>4.37441062927246</v>
       </c>
       <c r="H926" t="n">
         <v>5193190</v>
@@ -27252,7 +27252,7 @@
         <v>4.52600002288818</v>
       </c>
       <c r="G927" t="n">
-        <v>4.30591154098511</v>
+        <v>4.30591201782227</v>
       </c>
       <c r="H927" t="n">
         <v>4843476</v>
@@ -27484,7 +27484,7 @@
         <v>4.92600011825562</v>
       </c>
       <c r="G935" t="n">
-        <v>4.68646097183228</v>
+        <v>4.68646049499512</v>
       </c>
       <c r="H935" t="n">
         <v>7598993</v>
@@ -27513,7 +27513,7 @@
         <v>4.91800022125244</v>
       </c>
       <c r="G936" t="n">
-        <v>4.67884969711304</v>
+        <v>4.6788501739502</v>
       </c>
       <c r="H936" t="n">
         <v>8686085</v>
@@ -27687,7 +27687,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G942" t="n">
-        <v>4.9566502571106</v>
+        <v>4.95665073394775</v>
       </c>
       <c r="H942" t="n">
         <v>9765274</v>
@@ -27716,7 +27716,7 @@
         <v>5.16699981689453</v>
       </c>
       <c r="G943" t="n">
-        <v>4.91574096679688</v>
+        <v>4.91574144363403</v>
       </c>
       <c r="H943" t="n">
         <v>5370870</v>
@@ -27803,7 +27803,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G946" t="n">
-        <v>4.985191822052</v>
+        <v>4.98519134521484</v>
       </c>
       <c r="H946" t="n">
         <v>8525656</v>
@@ -27977,7 +27977,7 @@
         <v>5.19700002670288</v>
       </c>
       <c r="G952" t="n">
-        <v>4.94428300857544</v>
+        <v>4.94428253173828</v>
       </c>
       <c r="H952" t="n">
         <v>6264433</v>
@@ -28064,7 +28064,7 @@
         <v>4.94199991226196</v>
       </c>
       <c r="G955" t="n">
-        <v>4.70168256759644</v>
+        <v>4.70168209075928</v>
       </c>
       <c r="H955" t="n">
         <v>14155269</v>
@@ -28093,7 +28093,7 @@
         <v>4.96799993515015</v>
       </c>
       <c r="G956" t="n">
-        <v>4.72641849517822</v>
+        <v>4.72641801834106</v>
       </c>
       <c r="H956" t="n">
         <v>7492745</v>
@@ -28122,7 +28122,7 @@
         <v>4.97599983215332</v>
       </c>
       <c r="G957" t="n">
-        <v>4.73402881622314</v>
+        <v>4.7340292930603</v>
       </c>
       <c r="H957" t="n">
         <v>8539212</v>
@@ -28180,7 +28180,7 @@
         <v>5.06599998474121</v>
       </c>
       <c r="G959" t="n">
-        <v>4.81965255737305</v>
+        <v>4.81965303421021</v>
       </c>
       <c r="H959" t="n">
         <v>7079628</v>
@@ -28267,7 +28267,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G962" t="n">
-        <v>5.09935665130615</v>
+        <v>5.09935617446899</v>
       </c>
       <c r="H962" t="n">
         <v>9513376</v>
@@ -28354,7 +28354,7 @@
         <v>5.39400005340576</v>
       </c>
       <c r="G965" t="n">
-        <v>5.13170337677002</v>
+        <v>5.13170289993286</v>
       </c>
       <c r="H965" t="n">
         <v>7271483</v>
@@ -28412,7 +28412,7 @@
         <v>5.35400009155273</v>
       </c>
       <c r="G967" t="n">
-        <v>5.09364795684814</v>
+        <v>5.0936484336853</v>
       </c>
       <c r="H967" t="n">
         <v>7366786</v>
@@ -28528,7 +28528,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G971" t="n">
-        <v>5.06130170822144</v>
+        <v>5.06130123138428</v>
       </c>
       <c r="H971" t="n">
         <v>8251907</v>
@@ -28615,7 +28615,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G974" t="n">
-        <v>5.05178737640381</v>
+        <v>5.05178785324097</v>
       </c>
       <c r="H974" t="n">
         <v>5670673</v>
@@ -28905,7 +28905,7 @@
         <v>5.36299991607666</v>
       </c>
       <c r="G984" t="n">
-        <v>5.10221004486084</v>
+        <v>5.102210521698</v>
       </c>
       <c r="H984" t="n">
         <v>8375880</v>
@@ -28934,7 +28934,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G985" t="n">
-        <v>5.09935665130615</v>
+        <v>5.09935617446899</v>
       </c>
       <c r="H985" t="n">
         <v>6100265</v>
@@ -28963,7 +28963,7 @@
         <v>5.41300010681152</v>
       </c>
       <c r="G986" t="n">
-        <v>5.14977931976318</v>
+        <v>5.14977884292603</v>
       </c>
       <c r="H986" t="n">
         <v>11408179</v>
@@ -28992,7 +28992,7 @@
         <v>5.44099998474121</v>
       </c>
       <c r="G987" t="n">
-        <v>5.17641735076904</v>
+        <v>5.1764178276062</v>
       </c>
       <c r="H987" t="n">
         <v>5867671</v>
@@ -29050,7 +29050,7 @@
         <v>5.51800012588501</v>
       </c>
       <c r="G989" t="n">
-        <v>5.24967336654663</v>
+        <v>5.24967288970947</v>
       </c>
       <c r="H989" t="n">
         <v>8024179</v>
@@ -29079,7 +29079,7 @@
         <v>5.65100002288818</v>
       </c>
       <c r="G990" t="n">
-        <v>5.37620544433594</v>
+        <v>5.3762059211731</v>
       </c>
       <c r="H990" t="n">
         <v>12871995</v>
@@ -29166,7 +29166,7 @@
         <v>5.83900022506714</v>
       </c>
       <c r="G993" t="n">
-        <v>5.55506420135498</v>
+        <v>5.55506372451782</v>
       </c>
       <c r="H993" t="n">
         <v>5594077</v>
@@ -29224,7 +29224,7 @@
         <v>5.73899984359741</v>
       </c>
       <c r="G995" t="n">
-        <v>5.45992660522461</v>
+        <v>5.45992612838745</v>
       </c>
       <c r="H995" t="n">
         <v>8653313</v>
@@ -29253,7 +29253,7 @@
         <v>5.68599987030029</v>
       </c>
       <c r="G996" t="n">
-        <v>5.40950393676758</v>
+        <v>5.40950345993042</v>
       </c>
       <c r="H996" t="n">
         <v>4200712</v>
@@ -29340,7 +29340,7 @@
         <v>5.51200008392334</v>
       </c>
       <c r="G999" t="n">
-        <v>5.24396467208862</v>
+        <v>5.24396514892578</v>
       </c>
       <c r="H999" t="n">
         <v>5722620</v>
@@ -29601,7 +29601,7 @@
         <v>5.54199981689453</v>
       </c>
       <c r="G1008" t="n">
-        <v>5.27250623703003</v>
+        <v>5.27250576019287</v>
       </c>
       <c r="H1008" t="n">
         <v>4337873</v>
@@ -29630,7 +29630,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1009" t="n">
-        <v>5.28963041305542</v>
+        <v>5.28963088989258</v>
       </c>
       <c r="H1009" t="n">
         <v>5422481</v>
@@ -29659,7 +29659,7 @@
         <v>5.59499979019165</v>
       </c>
       <c r="G1010" t="n">
-        <v>5.32292890548706</v>
+        <v>5.3229284286499</v>
       </c>
       <c r="H1010" t="n">
         <v>7120475</v>
@@ -29688,7 +29688,7 @@
         <v>5.59499979019165</v>
       </c>
       <c r="G1011" t="n">
-        <v>5.32292890548706</v>
+        <v>5.3229284286499</v>
       </c>
       <c r="H1011" t="n">
         <v>8358777</v>
@@ -29833,7 +29833,7 @@
         <v>5.59499979019165</v>
       </c>
       <c r="G1016" t="n">
-        <v>5.32292890548706</v>
+        <v>5.3229284286499</v>
       </c>
       <c r="H1016" t="n">
         <v>3767783</v>
@@ -29978,7 +29978,7 @@
         <v>5.26300001144409</v>
       </c>
       <c r="G1021" t="n">
-        <v>5.00707292556763</v>
+        <v>5.00707340240479</v>
       </c>
       <c r="H1021" t="n">
         <v>11895409</v>
@@ -30065,7 +30065,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1024" t="n">
-        <v>4.89956855773926</v>
+        <v>4.8995680809021</v>
       </c>
       <c r="H1024" t="n">
         <v>9609886</v>
@@ -30094,7 +30094,7 @@
         <v>5.05900001525879</v>
       </c>
       <c r="G1025" t="n">
-        <v>4.81299352645874</v>
+        <v>4.81299304962158</v>
       </c>
       <c r="H1025" t="n">
         <v>6906988</v>
@@ -30152,7 +30152,7 @@
         <v>5.1230001449585</v>
       </c>
       <c r="G1027" t="n">
-        <v>4.87388134002686</v>
+        <v>4.8738808631897</v>
       </c>
       <c r="H1027" t="n">
         <v>5426424</v>
@@ -30181,7 +30181,7 @@
         <v>5.11399984359741</v>
       </c>
       <c r="G1028" t="n">
-        <v>4.86531829833984</v>
+        <v>4.865318775177</v>
       </c>
       <c r="H1028" t="n">
         <v>3560102</v>
@@ -30210,7 +30210,7 @@
         <v>5.06599998474121</v>
       </c>
       <c r="G1029" t="n">
-        <v>4.81965255737305</v>
+        <v>4.81965303421021</v>
       </c>
       <c r="H1029" t="n">
         <v>7067344</v>
@@ -30268,7 +30268,7 @@
         <v>4.94199991226196</v>
       </c>
       <c r="G1031" t="n">
-        <v>4.70168256759644</v>
+        <v>4.70168209075928</v>
       </c>
       <c r="H1031" t="n">
         <v>8681679</v>
@@ -30413,7 +30413,7 @@
         <v>5.05399990081787</v>
       </c>
       <c r="G1036" t="n">
-        <v>4.80823659896851</v>
+        <v>4.80823612213135</v>
       </c>
       <c r="H1036" t="n">
         <v>8898900</v>
@@ -30471,7 +30471,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1038" t="n">
-        <v>4.58561563491821</v>
+        <v>4.58561515808105</v>
       </c>
       <c r="H1038" t="n">
         <v>8979335</v>
@@ -30500,7 +30500,7 @@
         <v>4.91800022125244</v>
       </c>
       <c r="G1039" t="n">
-        <v>4.67884969711304</v>
+        <v>4.6788501739502</v>
       </c>
       <c r="H1039" t="n">
         <v>8140590</v>
@@ -30558,7 +30558,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1041" t="n">
-        <v>4.77588987350464</v>
+        <v>4.77588939666748</v>
       </c>
       <c r="H1041" t="n">
         <v>6949040</v>
@@ -30587,7 +30587,7 @@
         <v>4.94799995422363</v>
       </c>
       <c r="G1042" t="n">
-        <v>4.70739126205444</v>
+        <v>4.70739078521729</v>
       </c>
       <c r="H1042" t="n">
         <v>6830332</v>
@@ -30703,7 +30703,7 @@
         <v>5.25</v>
       </c>
       <c r="G1046" t="n">
-        <v>4.99470567703247</v>
+        <v>4.99470520019531</v>
       </c>
       <c r="H1046" t="n">
         <v>18341830</v>
@@ -31022,7 +31022,7 @@
         <v>5.00099992752075</v>
       </c>
       <c r="G1057" t="n">
-        <v>4.75781393051147</v>
+        <v>4.75781345367432</v>
       </c>
       <c r="H1057" t="n">
         <v>18342696</v>
@@ -31080,7 +31080,7 @@
         <v>4.77899980545044</v>
       </c>
       <c r="G1059" t="n">
-        <v>4.54660844802856</v>
+        <v>4.54660892486572</v>
       </c>
       <c r="H1059" t="n">
         <v>14134380</v>
@@ -31167,7 +31167,7 @@
         <v>4.32100009918213</v>
       </c>
       <c r="G1062" t="n">
-        <v>4.11088085174561</v>
+        <v>4.11088037490845</v>
       </c>
       <c r="H1062" t="n">
         <v>15034059</v>
@@ -31225,7 +31225,7 @@
         <v>3.67199993133545</v>
       </c>
       <c r="G1064" t="n">
-        <v>3.49343943595886</v>
+        <v>3.49343967437744</v>
       </c>
       <c r="H1064" t="n">
         <v>15459498</v>
@@ -31254,7 +31254,7 @@
         <v>3.81699991226196</v>
       </c>
       <c r="G1065" t="n">
-        <v>3.63138866424561</v>
+        <v>3.63138842582703</v>
       </c>
       <c r="H1065" t="n">
         <v>20006610</v>
@@ -31428,7 +31428,7 @@
         <v>3.7739999294281</v>
       </c>
       <c r="G1071" t="n">
-        <v>3.59047961235046</v>
+        <v>3.59047937393188</v>
       </c>
       <c r="H1071" t="n">
         <v>20539960</v>
@@ -31718,7 +31718,7 @@
         <v>3.79299998283386</v>
       </c>
       <c r="G1081" t="n">
-        <v>3.60855579376221</v>
+        <v>3.60855555534363</v>
       </c>
       <c r="H1081" t="n">
         <v>9112585</v>
@@ -31776,7 +31776,7 @@
         <v>3.92400002479553</v>
       </c>
       <c r="G1083" t="n">
-        <v>3.73318552970886</v>
+        <v>3.73318529129028</v>
       </c>
       <c r="H1083" t="n">
         <v>8125581</v>
@@ -31834,7 +31834,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G1085" t="n">
-        <v>3.61045837402344</v>
+        <v>3.61045861244202</v>
       </c>
       <c r="H1085" t="n">
         <v>9133043</v>
@@ -31921,7 +31921,7 @@
         <v>3.53399991989136</v>
       </c>
       <c r="G1088" t="n">
-        <v>3.36214995384216</v>
+        <v>3.36215019226074</v>
       </c>
       <c r="H1088" t="n">
         <v>10081010</v>
@@ -32182,7 +32182,7 @@
         <v>3.44600009918213</v>
       </c>
       <c r="G1097" t="n">
-        <v>3.27842974662781</v>
+        <v>3.27842950820923</v>
       </c>
       <c r="H1097" t="n">
         <v>7252885</v>
@@ -32211,7 +32211,7 @@
         <v>3.64400005340576</v>
       </c>
       <c r="G1098" t="n">
-        <v>3.46680116653442</v>
+        <v>3.466801404953</v>
       </c>
       <c r="H1098" t="n">
         <v>11382035</v>
@@ -32240,7 +32240,7 @@
         <v>3.6159999370575</v>
       </c>
       <c r="G1099" t="n">
-        <v>3.44016289710999</v>
+        <v>3.44016265869141</v>
       </c>
       <c r="H1099" t="n">
         <v>12293070</v>
@@ -32298,7 +32298,7 @@
         <v>3.53399991989136</v>
       </c>
       <c r="G1101" t="n">
-        <v>3.36214995384216</v>
+        <v>3.36215019226074</v>
       </c>
       <c r="H1101" t="n">
         <v>6018678</v>
@@ -32327,7 +32327,7 @@
         <v>3.50399994850159</v>
       </c>
       <c r="G1102" t="n">
-        <v>3.33360910415649</v>
+        <v>3.33360886573792</v>
       </c>
       <c r="H1102" t="n">
         <v>4601154</v>
@@ -32356,7 +32356,7 @@
         <v>3.42799997329712</v>
       </c>
       <c r="G1103" t="n">
-        <v>3.2613046169281</v>
+        <v>3.26130485534668</v>
       </c>
       <c r="H1103" t="n">
         <v>7123473</v>
@@ -32385,7 +32385,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1104" t="n">
-        <v>3.29174852371216</v>
+        <v>3.29174876213074</v>
       </c>
       <c r="H1104" t="n">
         <v>3356216</v>
@@ -32675,7 +32675,7 @@
         <v>3.20700001716614</v>
       </c>
       <c r="G1114" t="n">
-        <v>3.0510516166687</v>
+        <v>3.05105137825012</v>
       </c>
       <c r="H1114" t="n">
         <v>12499911</v>
@@ -32733,7 +32733,7 @@
         <v>3.30399990081787</v>
       </c>
       <c r="G1116" t="n">
-        <v>3.14333438873291</v>
+        <v>3.14333462715149</v>
       </c>
       <c r="H1116" t="n">
         <v>12389541</v>
@@ -32762,7 +32762,7 @@
         <v>3.3050000667572</v>
       </c>
       <c r="G1117" t="n">
-        <v>3.14428615570068</v>
+        <v>3.1442859172821</v>
       </c>
       <c r="H1117" t="n">
         <v>16377885</v>
@@ -32849,7 +32849,7 @@
         <v>3.41400003433228</v>
       </c>
       <c r="G1120" t="n">
-        <v>3.24798560142517</v>
+        <v>3.24798536300659</v>
       </c>
       <c r="H1120" t="n">
         <v>10515189</v>
@@ -32878,7 +32878,7 @@
         <v>3.52300000190735</v>
       </c>
       <c r="G1121" t="n">
-        <v>3.35168528556824</v>
+        <v>3.35168504714966</v>
       </c>
       <c r="H1121" t="n">
         <v>14830770</v>
@@ -33052,7 +33052,7 @@
         <v>3.71600008010864</v>
       </c>
       <c r="G1127" t="n">
-        <v>3.5353000164032</v>
+        <v>3.53530025482178</v>
       </c>
       <c r="H1127" t="n">
         <v>26938169</v>
@@ -33110,7 +33110,7 @@
         <v>3.53399991989136</v>
       </c>
       <c r="G1129" t="n">
-        <v>3.36214995384216</v>
+        <v>3.36215019226074</v>
       </c>
       <c r="H1129" t="n">
         <v>19235451</v>
@@ -33226,7 +33226,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1133" t="n">
-        <v>3.49153685569763</v>
+        <v>3.49153709411621</v>
       </c>
       <c r="H1133" t="n">
         <v>10659918</v>
@@ -80180,9 +80180,38 @@
         <v>5.67600011825562</v>
       </c>
       <c r="H2752" t="n">
-        <v>2003141</v>
+        <v>2020683</v>
       </c>
       <c r="I2752" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2753">
+      <c r="A2753" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2753" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C2753" t="n">
+        <v>5.71999979019165</v>
+      </c>
+      <c r="D2753" t="n">
+        <v>5.76000022888184</v>
+      </c>
+      <c r="E2753" t="n">
+        <v>5.66800022125244</v>
+      </c>
+      <c r="F2753" t="n">
+        <v>5.75600004196167</v>
+      </c>
+      <c r="G2753" t="n">
+        <v>5.75600004196167</v>
+      </c>
+      <c r="H2753" t="n">
+        <v>2817209</v>
+      </c>
+      <c r="I2753" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TIT.MI.xlsx
+++ b/data/TIT.MI.xlsx
@@ -80215,6 +80215,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2754">
+      <c r="A2754" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2754" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C2754" t="n">
+        <v>5.75899982452393</v>
+      </c>
+      <c r="D2754" t="n">
+        <v>5.75899982452393</v>
+      </c>
+      <c r="E2754" t="n">
+        <v>5.68499994277954</v>
+      </c>
+      <c r="F2754" t="n">
+        <v>5.74200010299683</v>
+      </c>
+      <c r="G2754" t="n">
+        <v>5.74200010299683</v>
+      </c>
+      <c r="H2754" t="n">
+        <v>1577673</v>
+      </c>
+      <c r="I2754" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
